--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -21,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,35 +37,85 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="007A7A7A"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E6B52"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <color rgb="007A7A7A"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00A23B3B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0020507D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="007A7A7A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E78"/>
+      <color rgb="0010243E"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -73,27 +124,57 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="0010243E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00C8A24B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="001F3B5C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCEFC9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E6B52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A23B3B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F0EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0020507D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EAF2"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,69 +188,216 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00D0D3D8"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00D0D3D8"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00D0D3D8"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00D0D3D8"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -259,7 +487,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Total por grupo: 2025 vs 2026</a:t>
+              <a:t>Activos / Pasivos / Patrimonio: 2025 vs 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -274,7 +502,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!B4</f>
+              <f>'Dashboard'!D35</f>
             </strRef>
           </tx>
           <spPr>
@@ -284,12 +512,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$5:$A$8</f>
+              <f>'Dashboard'!$B$36:$B$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$5:$B$8</f>
+              <f>'Dashboard'!$D$36:$D$38</f>
             </numRef>
           </val>
         </ser>
@@ -298,7 +526,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!C4</f>
+              <f>'Dashboard'!E35</f>
             </strRef>
           </tx>
           <spPr>
@@ -308,12 +536,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$5:$A$8</f>
+              <f>'Dashboard'!$B$36:$B$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$C$5:$C$8</f>
+              <f>'Dashboard'!$E$36:$E$38</f>
             </numRef>
           </val>
         </ser>
@@ -384,15 +612,18 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$5:$A$7</f>
+              <f>'Dashboard'!$B$13:$B$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$5:$B$7</f>
+              <f>'Dashboard'!$D$13:$D$15</f>
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showPercent val="1"/>
+        </dLbls>
         <firstSliceAng val="0"/>
       </pieChart>
     </plotArea>
@@ -418,7 +649,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Variacion proyectada por grupo (2025-&gt;2026)</a:t>
+              <a:t>Variacion proyectada (2025 -&gt; 2026)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -433,7 +664,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!D4</f>
+              <f>'Dashboard'!F35</f>
             </strRef>
           </tx>
           <spPr>
@@ -443,12 +674,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$5:$A$8</f>
+              <f>'Dashboard'!$B$36:$B$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$5:$D$8</f>
+              <f>'Dashboard'!$F$36:$F$38</f>
             </numRef>
           </val>
         </ser>
@@ -492,12 +723,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="3240000"/>
+    <ext cx="5400000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -514,12 +745,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3240000"/>
+    <ext cx="5040000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -536,12 +767,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>38</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="3240000"/>
+    <ext cx="5400000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -848,276 +1079,636 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD - DECLARACION PATRIMONIAL 2025 vs 2026</t>
+          <t>DECLARACION PATRIMONIAL  -  TABLERO EJECUTIVO</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Declarante: GONZALEZ NAVAS MARCO VINICIO  |  R - RUC: 1709164899001  |  SOC - Sociedad conyugal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Edite la columna amarilla en cada hoja de grupo; los totales, variaciones y graficos se actualizan solos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+          <t>GONZALEZ NAVAS MARCO VINICIO   |   R - RUC: 1709164899001   |   SOC - Sociedad conyugal   |   Comparativo 2025 vs 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="5" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="5" ht="6" customHeight="1">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL ACTIVOS</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL PASIVOS</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>PATRIMONIO NETO</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="14">
+        <f>D17</f>
+        <v/>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="15">
+        <f>D22</f>
+        <v/>
+      </c>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="16">
+        <f>D28</f>
+        <v/>
+      </c>
+      <c r="G7" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Var. proyectada</t>
+        </is>
+      </c>
+      <c r="C8" s="18">
+        <f>G17</f>
+        <v/>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Var. proyectada</t>
+        </is>
+      </c>
+      <c r="E8" s="20">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>Var. proyectada</t>
+        </is>
+      </c>
+      <c r="G8" s="22">
+        <f>G28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>ACTIVOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="G12" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Dinero</t>
-        </is>
-      </c>
-      <c r="B5" s="6">
-        <f>'Dinero'!E8</f>
-        <v/>
-      </c>
-      <c r="C5" s="6">
-        <f>'Dinero'!F8</f>
-        <v/>
-      </c>
-      <c r="D5" s="6">
-        <f>C5-B5</f>
-        <v/>
-      </c>
-      <c r="E5" s="7">
-        <f>IF(B5=0,"",(C5-B5)/B5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Dinero e inversiones</t>
+        </is>
+      </c>
+      <c r="D13" s="28">
+        <f>'Dinero'!E10</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>'Dinero'!F10</f>
+        <v/>
+      </c>
+      <c r="F13" s="28">
+        <f>E13-D13</f>
+        <v/>
+      </c>
+      <c r="G13" s="29">
+        <f>IF(D13=0,"",(E13-D13)/D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>Vehiculos</t>
         </is>
       </c>
-      <c r="B6" s="6">
-        <f>'Vehiculos'!D7</f>
-        <v/>
-      </c>
-      <c r="C6" s="6">
-        <f>'Vehiculos'!E7</f>
-        <v/>
-      </c>
-      <c r="D6" s="6">
-        <f>C6-B6</f>
-        <v/>
-      </c>
-      <c r="E6" s="7">
-        <f>IF(B6=0,"",(C6-B6)/B6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Bienes Inmuebles</t>
-        </is>
-      </c>
-      <c r="B7" s="6">
-        <f>'Bienes Inmuebles'!E8</f>
-        <v/>
-      </c>
-      <c r="C7" s="6">
-        <f>'Bienes Inmuebles'!F8</f>
-        <v/>
-      </c>
-      <c r="D7" s="6">
-        <f>C7-B7</f>
-        <v/>
-      </c>
-      <c r="E7" s="7">
-        <f>IF(B7=0,"",(C7-B7)/B7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Pasivo</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>'Pasivo'!E6</f>
-        <v/>
-      </c>
-      <c r="C8" s="6">
-        <f>'Pasivo'!F6</f>
-        <v/>
-      </c>
-      <c r="D8" s="6">
-        <f>C8-B8</f>
-        <v/>
-      </c>
-      <c r="E8" s="7">
-        <f>IF(B8=0,"",(C8-B8)/B8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="D14" s="28">
+        <f>'Vehiculos'!D9</f>
+        <v/>
+      </c>
+      <c r="E14" s="28">
+        <f>'Vehiculos'!E9</f>
+        <v/>
+      </c>
+      <c r="F14" s="28">
+        <f>E14-D14</f>
+        <v/>
+      </c>
+      <c r="G14" s="29">
+        <f>IF(D14=0,"",(E14-D14)/D14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Bienes inmuebles</t>
+        </is>
+      </c>
+      <c r="D15" s="28">
+        <f>'Bienes Inmuebles'!E10</f>
+        <v/>
+      </c>
+      <c r="E15" s="28">
+        <f>'Bienes Inmuebles'!F10</f>
+        <v/>
+      </c>
+      <c r="F15" s="28">
+        <f>E15-D15</f>
+        <v/>
+      </c>
+      <c r="G15" s="29">
+        <f>IF(D15=0,"",(E15-D15)/D15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>Total bruto de activos</t>
+        </is>
+      </c>
+      <c r="D16" s="28">
+        <f>SUM(D13:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="28">
+        <f>SUM(E13:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="28">
+        <f>E16-D16</f>
+        <v/>
+      </c>
+      <c r="G16" s="29">
+        <f>IF(D16=0,"",(E16-D16)/D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>TOTAL ACTIVOS</t>
         </is>
       </c>
-      <c r="B9" s="9">
-        <f>SUM(B5:B7)</f>
-        <v/>
-      </c>
-      <c r="C9" s="9">
-        <f>SUM(C5:C7)</f>
-        <v/>
-      </c>
-      <c r="D9" s="9">
-        <f>SUM(D5:D7)</f>
-        <v/>
-      </c>
-      <c r="E9" s="10">
-        <f>IF(B9=0,"",(C9-B9)/B9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>PATRIMONIO NETO (Activos - Pasivo)</t>
-        </is>
-      </c>
-      <c r="B10" s="12">
-        <f>B9-B8</f>
-        <v/>
-      </c>
-      <c r="C10" s="12">
-        <f>C9-C8</f>
-        <v/>
-      </c>
-      <c r="D10" s="12">
-        <f>D9-D8</f>
-        <v/>
-      </c>
-      <c r="E10" s="13">
-        <f>IF(B10=0,"",(C10-B10)/B10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>INDICADORES CLAVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Patrimonio declarado 2025</t>
-        </is>
-      </c>
-      <c r="B13" s="16">
-        <f>B10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Patrimonio declarado (XML) 2025</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
+      <c r="D17" s="31">
+        <f>D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="31">
+        <f>E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="31">
+        <f>E17-D17</f>
+        <v/>
+      </c>
+      <c r="G17" s="32">
+        <f>IF(D17=0,"",(E17-D17)/D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>PASIVOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>Total 2025</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>Total 2026</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>Variacion</t>
+        </is>
+      </c>
+      <c r="G20" s="26" t="inlineStr">
+        <is>
+          <t>Variacion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>Deudas y obligaciones</t>
+        </is>
+      </c>
+      <c r="D21" s="35">
+        <f>'Pasivo'!E8</f>
+        <v/>
+      </c>
+      <c r="E21" s="35">
+        <f>'Pasivo'!F8</f>
+        <v/>
+      </c>
+      <c r="F21" s="35">
+        <f>E21-D21</f>
+        <v/>
+      </c>
+      <c r="G21" s="36">
+        <f>IF(D21=0,"",(E21-D21)/D21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>TOTAL PASIVOS</t>
+        </is>
+      </c>
+      <c r="D22" s="38">
+        <f>D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="38">
+        <f>E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="38">
+        <f>E22-D22</f>
+        <v/>
+      </c>
+      <c r="G22" s="39">
+        <f>IF(D22=0,"",(E22-D22)/D22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>PATRIMONIO NETO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Total 2025</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>Total 2026</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>Variacion</t>
+        </is>
+      </c>
+      <c r="G25" s="26" t="inlineStr">
+        <is>
+          <t>Variacion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>(+) Total activos</t>
+        </is>
+      </c>
+      <c r="D26" s="42">
+        <f>D17</f>
+        <v/>
+      </c>
+      <c r="E26" s="42">
+        <f>E17</f>
+        <v/>
+      </c>
+      <c r="F26" s="42">
+        <f>E26-D26</f>
+        <v/>
+      </c>
+      <c r="G26" s="43">
+        <f>IF(D26=0,"",(E26-D26)/D26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="B27" s="41" t="inlineStr">
+        <is>
+          <t>(-) Total pasivos</t>
+        </is>
+      </c>
+      <c r="D27" s="42">
+        <f>D22</f>
+        <v/>
+      </c>
+      <c r="E27" s="42">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="F27" s="42">
+        <f>E27-D27</f>
+        <v/>
+      </c>
+      <c r="G27" s="43">
+        <f>IF(D27=0,"",(E27-D27)/D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>(=) PATRIMONIO NETO</t>
+        </is>
+      </c>
+      <c r="D28" s="45">
+        <f>D26-D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="45">
+        <f>E26-E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="45">
+        <f>E28-D28</f>
+        <v/>
+      </c>
+      <c r="G28" s="46">
+        <f>IF(D28=0,"",(E28-D28)/D28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="47" t="inlineStr">
+        <is>
+          <t>Patrimonio declarado en el XML (2025)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="48" t="n">
         <v>883285.5600000001</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Patrimonio anio anterior</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="47" t="inlineStr">
+        <is>
+          <t>Patrimonio neto del anio anterior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="48" t="n">
         <v>801569.97</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Crecimiento patrimonial (XML)</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="47" t="inlineStr">
+        <is>
+          <t>Crecimiento patrimonial declarado (XML)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="48" t="n">
         <v>81715.59</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Variacion proyectada 2025-&gt;2026</t>
-        </is>
-      </c>
-      <c r="B17" s="16">
-        <f>D10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Variacion % proyectada 2025-&gt;2026</t>
-        </is>
-      </c>
-      <c r="B18" s="17">
-        <f>E10</f>
-        <v/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="49" t="inlineStr">
+        <is>
+          <t>CONSOLIDADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="n"/>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>Total 2025</t>
+        </is>
+      </c>
+      <c r="E35" s="26" t="inlineStr">
+        <is>
+          <t>Total 2026</t>
+        </is>
+      </c>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>Variacion</t>
+        </is>
+      </c>
+      <c r="G35" s="26" t="inlineStr">
+        <is>
+          <t>Variacion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="B36" s="50" t="inlineStr">
+        <is>
+          <t>Activos</t>
+        </is>
+      </c>
+      <c r="D36" s="51">
+        <f>D17</f>
+        <v/>
+      </c>
+      <c r="E36" s="51">
+        <f>E17</f>
+        <v/>
+      </c>
+      <c r="F36" s="51">
+        <f>E36-D36</f>
+        <v/>
+      </c>
+      <c r="G36" s="52">
+        <f>IF(D36=0,"",(E36-D36)/D36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="B37" s="53" t="inlineStr">
+        <is>
+          <t>Pasivos</t>
+        </is>
+      </c>
+      <c r="D37" s="54">
+        <f>D22</f>
+        <v/>
+      </c>
+      <c r="E37" s="54">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="F37" s="54">
+        <f>E37-D37</f>
+        <v/>
+      </c>
+      <c r="G37" s="55">
+        <f>IF(D37=0,"",(E37-D37)/D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="B38" s="56" t="inlineStr">
+        <is>
+          <t>Patrimonio neto</t>
+        </is>
+      </c>
+      <c r="D38" s="57">
+        <f>D28</f>
+        <v/>
+      </c>
+      <c r="E38" s="57">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="F38" s="57">
+        <f>E38-D38</f>
+        <v/>
+      </c>
+      <c r="G38" s="58">
+        <f>IF(D38=0,"",(E38-D38)/D38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="59" t="inlineStr">
+        <is>
+          <t>Edite la columna amarilla en las hojas de cada grupo; las tarjetas, secciones y graficos se recalculan solos.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="36">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B11:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1130,240 +1721,252 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>DINERO E INVERSIONES</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Declaracion 2025  -  columna 2026 editable</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="5" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Institucion / detalle</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Moneda</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Valor 2026  (editable)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>Valor 2026</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>IFI - Institucion financiera / ECU - Ecuador</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>3 - Inversion / poliza</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>1029</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E6" s="61" t="n">
         <v>130.2</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F6" s="62" t="n">
         <v>130.2</v>
       </c>
-      <c r="G4" s="6">
-        <f>F4-E4</f>
-        <v/>
-      </c>
-      <c r="H4" s="7">
-        <f>IF(E4=0,"",(F4-E4)/E4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="G6" s="61">
+        <f>F6-E6</f>
+        <v/>
+      </c>
+      <c r="H6" s="63">
+        <f>IF(E6=0,"",(F6-E6)/E6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>IFI - Institucion financiera / ECU - Ecuador</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>4 - Deposito a plazo</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>1029</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D7" s="64" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E7" s="65" t="n">
         <v>5590.32</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F7" s="62" t="n">
         <v>5590.32</v>
       </c>
-      <c r="G5" s="6">
-        <f>F5-E5</f>
-        <v/>
-      </c>
-      <c r="H5" s="7">
-        <f>IF(E5=0,"",(F5-E5)/E5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="G7" s="65">
+        <f>F7-E7</f>
+        <v/>
+      </c>
+      <c r="H7" s="66">
+        <f>IF(E7=0,"",(F7-E7)/E7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>IFI - Institucion financiera / ECU - Ecuador</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>3 - Inversion / poliza</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>1418</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E8" s="61" t="n">
         <v>53237.31</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F8" s="62" t="n">
         <v>53237.31</v>
       </c>
-      <c r="G6" s="6">
-        <f>F6-E6</f>
-        <v/>
-      </c>
-      <c r="H6" s="7">
-        <f>IF(E6=0,"",(F6-E6)/E6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="G8" s="61">
+        <f>F8-E8</f>
+        <v/>
+      </c>
+      <c r="H8" s="63">
+        <f>IF(E8=0,"",(F8-E8)/E8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>IFI - Institucion financiera / EXT - Exterior</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>2 - Cuenta corriente</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C9" s="64" t="inlineStr">
         <is>
           <t>BANCO PICHINCHA CA</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D9" s="64" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E9" s="65" t="n">
         <v>189049.31</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F9" s="62" t="n">
         <v>189049.31</v>
       </c>
-      <c r="G7" s="6">
-        <f>F7-E7</f>
-        <v/>
-      </c>
-      <c r="H7" s="7">
-        <f>IF(E7=0,"",(F7-E7)/E7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="G9" s="65">
+        <f>F9-E9</f>
+        <v/>
+      </c>
+      <c r="H9" s="66">
+        <f>IF(E9=0,"",(F9-E9)/E9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n"/>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="21">
-        <f>SUM(E4:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="21">
-        <f>SUM(F4:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="21">
-        <f>F8-E8</f>
-        <v/>
-      </c>
-      <c r="H8" s="22">
-        <f>IF(E8=0,"",(F8-E8)/E8)</f>
+      <c r="B10" s="67" t="n"/>
+      <c r="C10" s="67" t="n"/>
+      <c r="D10" s="67" t="n"/>
+      <c r="E10" s="31">
+        <f>SUM(E6:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="31">
+        <f>SUM(F6:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="31">
+        <f>F10-E10</f>
+        <v/>
+      </c>
+      <c r="H10" s="32">
+        <f>IF(E10=0,"",(F10-E10)/E10)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1376,182 +1979,194 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>VEHICULOS</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Declaracion 2025  -  columna 2026 editable</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="5" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Tipo de vehiculo</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Placa</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Valor 2026  (editable)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>Valor 2026</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>1 - Vehiculo terrestre</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>PBO7092</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>ECU - Ecuador</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D6" s="61" t="n">
         <v>12000</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E6" s="62" t="n">
         <v>12000</v>
       </c>
-      <c r="F4" s="6">
-        <f>E4-D4</f>
-        <v/>
-      </c>
-      <c r="G4" s="7">
-        <f>IF(D4=0,"",(E4-D4)/D4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="F6" s="61">
+        <f>E6-D6</f>
+        <v/>
+      </c>
+      <c r="G6" s="63">
+        <f>IF(D6=0,"",(E6-D6)/D6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>1 - Vehiculo terrestre</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>PBF9690</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>ECU - Ecuador</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D7" s="65" t="n">
         <v>20000</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E7" s="62" t="n">
         <v>20000</v>
       </c>
-      <c r="F5" s="6">
-        <f>E5-D5</f>
-        <v/>
-      </c>
-      <c r="G5" s="7">
-        <f>IF(D5=0,"",(E5-D5)/D5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="F7" s="65">
+        <f>E7-D7</f>
+        <v/>
+      </c>
+      <c r="G7" s="66">
+        <f>IF(D7=0,"",(E7-D7)/D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>1 - Vehiculo terrestre</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>PFC8683</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>ECU - Ecuador</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D8" s="61" t="n">
         <v>32000</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E8" s="62" t="n">
         <v>32000</v>
       </c>
-      <c r="F6" s="6">
-        <f>E6-D6</f>
-        <v/>
-      </c>
-      <c r="G6" s="7">
-        <f>IF(D6=0,"",(E6-D6)/D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="F8" s="61">
+        <f>E8-D8</f>
+        <v/>
+      </c>
+      <c r="G8" s="63">
+        <f>IF(D8=0,"",(E8-D8)/D8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="67" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n"/>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="21">
-        <f>SUM(D4:D6)</f>
-        <v/>
-      </c>
-      <c r="E7" s="21">
-        <f>SUM(E4:E6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="21">
-        <f>E7-D7</f>
-        <v/>
-      </c>
-      <c r="G7" s="22">
-        <f>IF(D7=0,"",(E7-D7)/D7)</f>
+      <c r="B9" s="67" t="n"/>
+      <c r="C9" s="67" t="n"/>
+      <c r="D9" s="31">
+        <f>SUM(D6:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="31">
+        <f>SUM(E6:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="31">
+        <f>E9-D9</f>
+        <v/>
+      </c>
+      <c r="G9" s="32">
+        <f>IF(D9=0,"",(E9-D9)/D9)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1564,232 +2179,244 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BIENES INMUEBLES</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Declaracion 2025  -  columna 2026 editable</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="5" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Tipo de inmueble</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Clave catastral</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Inscripcion</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Valor 2026  (editable)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>Valor 2026</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>3 - Terreno</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>ECU - Ecuador</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>1042203018</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>22/10/2008</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E6" s="61" t="n">
         <v>267340.8</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F6" s="62" t="n">
         <v>267340.8</v>
       </c>
-      <c r="G4" s="6">
-        <f>F4-E4</f>
-        <v/>
-      </c>
-      <c r="H4" s="7">
-        <f>IF(E4=0,"",(F4-E4)/E4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="G6" s="61">
+        <f>F6-E6</f>
+        <v/>
+      </c>
+      <c r="H6" s="63">
+        <f>IF(E6=0,"",(F6-E6)/E6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>1 - Edificacion / casa</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>ECU - Ecuador</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>1012005008000000000</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D7" s="64" t="inlineStr">
         <is>
           <t>13/03/1997</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E7" s="65" t="n">
         <v>198118.55</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F7" s="62" t="n">
         <v>198118.55</v>
       </c>
-      <c r="G5" s="6">
-        <f>F5-E5</f>
-        <v/>
-      </c>
-      <c r="H5" s="7">
-        <f>IF(E5=0,"",(F5-E5)/E5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="G7" s="65">
+        <f>F7-E7</f>
+        <v/>
+      </c>
+      <c r="H7" s="66">
+        <f>IF(E7=0,"",(F7-E7)/E7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>1 - Edificacion / casa</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>ECU - Ecuador</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>1042203018</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr"/>
-      <c r="E6" s="6" t="n">
+      <c r="D8" s="60" t="inlineStr"/>
+      <c r="E8" s="61" t="n">
         <v>33634.04</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F8" s="62" t="n">
         <v>33634.04</v>
       </c>
-      <c r="G6" s="6">
-        <f>F6-E6</f>
-        <v/>
-      </c>
-      <c r="H6" s="7">
-        <f>IF(E6=0,"",(F6-E6)/E6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="G8" s="61">
+        <f>F8-E8</f>
+        <v/>
+      </c>
+      <c r="H8" s="63">
+        <f>IF(E8=0,"",(F8-E8)/E8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>3 - Terreno</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>ECU - Ecuador</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C9" s="64" t="inlineStr">
         <is>
           <t>1012005008000000000</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr"/>
-      <c r="E7" s="6" t="n">
+      <c r="D9" s="64" t="inlineStr"/>
+      <c r="E9" s="65" t="n">
         <v>82624.22</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F9" s="62" t="n">
         <v>82624.22</v>
       </c>
-      <c r="G7" s="6">
-        <f>F7-E7</f>
-        <v/>
-      </c>
-      <c r="H7" s="7">
-        <f>IF(E7=0,"",(F7-E7)/E7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="G9" s="65">
+        <f>F9-E9</f>
+        <v/>
+      </c>
+      <c r="H9" s="66">
+        <f>IF(E9=0,"",(F9-E9)/E9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n"/>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="21">
-        <f>SUM(E4:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="21">
-        <f>SUM(F4:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="21">
-        <f>F8-E8</f>
-        <v/>
-      </c>
-      <c r="H8" s="22">
-        <f>IF(E8=0,"",(F8-E8)/E8)</f>
+      <c r="B10" s="67" t="n"/>
+      <c r="C10" s="67" t="n"/>
+      <c r="D10" s="67" t="n"/>
+      <c r="E10" s="31">
+        <f>SUM(E6:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="31">
+        <f>SUM(F6:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="31">
+        <f>F10-E10</f>
+        <v/>
+      </c>
+      <c r="H10" s="32">
+        <f>IF(E10=0,"",(F10-E10)/E10)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1802,168 +2429,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PASIVOS / DEUDAS</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Declaracion 2025  -  columna 2026 editable</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="5" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Tipo de acreedor</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Acreedor</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Domicilio</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Identificacion</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Valor 2026  (editable)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>Valor 2026</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>IFI - Institucion financiera</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>DINERS CLUB DEL ECUADOR</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>ECU - Ecuador</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>1792260957001</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E6" s="61" t="n">
         <v>4891.88</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F6" s="62" t="n">
         <v>4891.88</v>
       </c>
-      <c r="G4" s="6">
-        <f>F4-E4</f>
-        <v/>
-      </c>
-      <c r="H4" s="7">
-        <f>IF(E4=0,"",(F4-E4)/E4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="G6" s="61">
+        <f>F6-E6</f>
+        <v/>
+      </c>
+      <c r="H6" s="63">
+        <f>IF(E6=0,"",(F6-E6)/E6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>IFI - Institucion financiera</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>BANCO DEL PICHINCHA</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>ECU - Ecuador</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D7" s="64" t="inlineStr">
         <is>
           <t>1790010937001</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E7" s="65" t="n">
         <v>5547.31</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F7" s="62" t="n">
         <v>5547.31</v>
       </c>
-      <c r="G5" s="6">
-        <f>F5-E5</f>
-        <v/>
-      </c>
-      <c r="H5" s="7">
-        <f>IF(E5=0,"",(F5-E5)/E5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="G7" s="65">
+        <f>F7-E7</f>
+        <v/>
+      </c>
+      <c r="H7" s="66">
+        <f>IF(E7=0,"",(F7-E7)/E7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n"/>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="21">
-        <f>SUM(E4:E5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="21">
-        <f>SUM(F4:F5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="21">
-        <f>F6-E6</f>
-        <v/>
-      </c>
-      <c r="H6" s="22">
-        <f>IF(E6=0,"",(F6-E6)/E6)</f>
+      <c r="B8" s="68" t="n"/>
+      <c r="C8" s="68" t="n"/>
+      <c r="D8" s="68" t="n"/>
+      <c r="E8" s="38">
+        <f>SUM(E6:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="38">
+        <f>SUM(F6:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="38">
+        <f>F8-E8</f>
+        <v/>
+      </c>
+      <c r="H8" s="39">
+        <f>IF(E8=0,"",(F8-E8)/E8)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1976,219 +2615,223 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>DATOS GENERALES DE LA DECLARACION</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+    <row r="3" ht="5" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="69" t="inlineStr">
         <is>
           <t>Anio de la declaracion</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B5" s="70" t="n">
         <v>2025</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="69" t="inlineStr">
         <is>
           <t>Tipo de declaracion</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B6" s="70" t="inlineStr">
         <is>
           <t>SOC - Sociedad conyugal</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B7" s="70" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="69" t="inlineStr">
         <is>
           <t>Numero de identificacion</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B8" s="70" t="inlineStr">
         <is>
           <t>1709164899001</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>Nombre del declarante</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B9" s="70" t="inlineStr">
         <is>
           <t>GONZALEZ NAVAS MARCO VINICIO</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="69" t="inlineStr">
         <is>
           <t>Identificacion del conyuge</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B10" s="70" t="inlineStr">
         <is>
           <t>C - Cedula</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>Numero ident. conyuge</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B11" s="70" t="inlineStr">
         <is>
           <t>1709784225</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="69" t="inlineStr">
         <is>
           <t>Nombre del conyuge</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B12" s="70" t="inlineStr">
         <is>
           <t>HIDALGO LOZA ROSA CONSUELO</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="69" t="inlineStr">
         <is>
           <t>Total creditos</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B13" s="71" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="23" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="72" t="inlineStr"/>
+      <c r="B14" s="73" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="69" t="inlineStr">
         <is>
           <t>Patrimonio total declarado</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B15" s="71" t="n">
         <v>883285.5600000001</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="69" t="inlineStr">
         <is>
           <t>Atribuible a hijos</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B16" s="71" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="69" t="inlineStr">
         <is>
           <t>Sociedad conyugal</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B17" s="71" t="n">
         <v>883285.5600000001</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="69" t="inlineStr">
         <is>
           <t>Individual</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B18" s="71" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="69" t="inlineStr">
         <is>
           <t>Patrimonio anio anterior</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B19" s="71" t="n">
         <v>801569.97</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="69" t="inlineStr">
         <is>
           <t>Crecimiento patrimonial</t>
         </is>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B20" s="71" t="n">
         <v>81715.59</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="74" t="inlineStr">
         <is>
           <t>Justificacion de la variacion patrimonial</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="73" t="inlineStr">
         <is>
           <t>- 1 - Ingresos por trabajo en relacion de dependencia</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="73" t="inlineStr">
         <is>
           <t>- 6 - Otros ingresos / variaciones de mercado</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="59" t="inlineStr">
         <is>
           <t>Nota: las descripciones de codigos son de referencia; verificar contra el catalogo oficial del SRI.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -9509,11 +9509,7 @@
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
+      <c r="E6" s="59" t="inlineStr"/>
       <c r="F6" s="59" t="inlineStr">
         <is>
           <t>DOLARES</t>
@@ -9560,11 +9556,7 @@
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E7" s="63" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
+      <c r="E7" s="63" t="inlineStr"/>
       <c r="F7" s="63" t="inlineStr">
         <is>
           <t>DOLARES</t>
@@ -9611,11 +9603,7 @@
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
-        <is>
-          <t>1418</t>
-        </is>
-      </c>
+      <c r="E8" s="59" t="inlineStr"/>
       <c r="F8" s="59" t="inlineStr">
         <is>
           <t>DOLARES</t>

--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="D12" s="27">
-        <f>'Dinero'!H10</f>
+        <f>'Dinero'!J10</f>
         <v/>
       </c>
       <c r="E12" s="27">
-        <f>'Dinero'!I10</f>
+        <f>'Dinero'!K10</f>
         <v/>
       </c>
       <c r="F12" s="27">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="D13" s="27">
-        <f>'Derechos de Capital'!H14</f>
+        <f>'Derechos de Capital'!J14</f>
         <v/>
       </c>
       <c r="E13" s="27">
-        <f>'Derechos de Capital'!I14</f>
+        <f>'Derechos de Capital'!K14</f>
         <v/>
       </c>
       <c r="F13" s="27">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="D14" s="27">
-        <f>'Cuentas por Cobrar'!G14</f>
+        <f>'Cuentas por Cobrar'!J14</f>
         <v/>
       </c>
       <c r="E14" s="27">
-        <f>'Cuentas por Cobrar'!H14</f>
+        <f>'Cuentas por Cobrar'!K14</f>
         <v/>
       </c>
       <c r="F14" s="27">
@@ -1520,11 +1520,11 @@
         </is>
       </c>
       <c r="D15" s="27">
-        <f>'Bienes Muebles'!E14</f>
+        <f>'Bienes Muebles'!F14</f>
         <v/>
       </c>
       <c r="E15" s="27">
-        <f>'Bienes Muebles'!F14</f>
+        <f>'Bienes Muebles'!G14</f>
         <v/>
       </c>
       <c r="F15" s="27">
@@ -1543,11 +1543,11 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>'Vehiculos'!E9</f>
+        <f>'Vehiculos'!G9</f>
         <v/>
       </c>
       <c r="E16" s="27">
-        <f>'Vehiculos'!F9</f>
+        <f>'Vehiculos'!H9</f>
         <v/>
       </c>
       <c r="F16" s="27">
@@ -1566,11 +1566,11 @@
         </is>
       </c>
       <c r="D17" s="27">
-        <f>'Derechos'!E14</f>
+        <f>'Derechos'!F14</f>
         <v/>
       </c>
       <c r="E17" s="27">
-        <f>'Derechos'!F14</f>
+        <f>'Derechos'!G14</f>
         <v/>
       </c>
       <c r="F17" s="27">
@@ -1589,11 +1589,11 @@
         </is>
       </c>
       <c r="D18" s="27">
-        <f>'Bienes Inmuebles'!H10</f>
+        <f>'Bienes Inmuebles'!J10</f>
         <v/>
       </c>
       <c r="E18" s="27">
-        <f>'Bienes Inmuebles'!I10</f>
+        <f>'Bienes Inmuebles'!K10</f>
         <v/>
       </c>
       <c r="F18" s="27">
@@ -1612,11 +1612,11 @@
         </is>
       </c>
       <c r="D19" s="27">
-        <f>'Otros Activos'!D14</f>
+        <f>'Otros Activos'!F14</f>
         <v/>
       </c>
       <c r="E19" s="27">
-        <f>'Otros Activos'!E14</f>
+        <f>'Otros Activos'!G14</f>
         <v/>
       </c>
       <c r="F19" s="27">
@@ -2046,14 +2046,14 @@
   <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -2281,7 +2281,7 @@
   </mergeCells>
   <dataValidations count="5">
     <dataValidation sqref="A6:A7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Catalogos!$O$2:$O$8</formula1>
+      <formula1>Catalogos!$O$2:$O$9</formula1>
     </dataValidation>
     <dataValidation sqref="B6:B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$C$2:$C$3</formula1>
@@ -2525,7 +2525,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B12:B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Catalogos!$Q$2:$Q$7</formula1>
+      <formula1>Catalogos!$R$2:$R$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2542,7 +2542,7 @@
   <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2660,7 +2660,7 @@
     <row r="14">
       <c r="A14" s="78" t="inlineStr">
         <is>
-          <t>Total creditos</t>
+          <t>Total creditos / cuentas por cobrar</t>
         </is>
       </c>
       <c r="B14" s="60" t="n">
@@ -2809,7 +2809,7 @@
     <row r="34">
       <c r="A34" s="58" t="inlineStr">
         <is>
-          <t>Catalogos del SRI integrados (Tablas 1-19 del archivo CATALOGO.xls).</t>
+          <t>Catalogos del SRI integrados (Tablas 1-19 del archivo CATALOGO.xls). El XML se genera con generar_xml_sri.py.</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R519"/>
+  <dimension ref="A1:S519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2917,10 +2917,15 @@
       </c>
       <c r="Q1" s="82" t="inlineStr">
         <is>
+          <t>REGULARIZACION</t>
+        </is>
+      </c>
+      <c r="R1" s="82" t="inlineStr">
+        <is>
           <t>JUSTIF_INCREMENTO</t>
         </is>
       </c>
-      <c r="R1" s="82" t="inlineStr">
+      <c r="S1" s="82" t="inlineStr">
         <is>
           <t>JUSTIF_DECREMENTO</t>
         </is>
@@ -2949,7 +2954,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>002 - BANCO AMAZONAS S.A.</t>
+          <t>1002 - BANCO AMAZONAS S.A.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3009,10 +3014,15 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>1 - Si</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>1 - Ingresos locales</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>1 - Compra de bienes</t>
         </is>
@@ -3041,7 +3051,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>004 - BANCO DEL AUSTRO S.A.</t>
+          <t>1004 - BANCO DEL AUSTRO S.A.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3101,10 +3111,15 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>2 - No</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>2 - Ingresos exterior</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2 - Pago de servicios</t>
         </is>
@@ -3128,7 +3143,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>006 - BANCO DE GUAYAQUIL S.A.</t>
+          <t>1006 - BANCO DE GUAYAQUIL S.A.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3168,7 +3183,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>DIV - Dividendos</t>
+          <t>CRE - Credito a mutuo</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -3176,12 +3191,12 @@
           <t>P - Pasaporte</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>3 - Herencias, legados o donaciones</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>3 - Nuevas inversiones</t>
         </is>
@@ -3200,7 +3215,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>007 - BANCO BOLIVARIANO C.A.</t>
+          <t>1007 - BANCO BOLIVARIANO C.A.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3230,7 +3245,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>IES - IESS</t>
+          <t>DIV - Dividendos</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -3238,12 +3253,12 @@
           <t>R - RUC</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>4 - Loterias o rifas</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>4 - Otros</t>
         </is>
@@ -3262,7 +3277,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>008 - BANCO CENTRO MUNDO S.A.</t>
+          <t>1008 - BANCO CENTRO MUNDO S.A.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3292,10 +3307,10 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>IFI - Instituciones financieras</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+          <t>IES - IESS</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>5 - Ganancias de capital</t>
         </is>
@@ -3314,7 +3329,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>009 - CITIBANK N.A.</t>
+          <t>1009 - CITIBANK N.A.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3344,10 +3359,10 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>OTR - Otros pasivos</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+          <t>IFI - Instituciones financieras</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>6 - Otros</t>
         </is>
@@ -3366,7 +3381,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>010 - BANCO COFIEC C.A.</t>
+          <t>1010 - BANCO COFIEC C.A.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3391,7 +3406,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>TRA - Transferencias casa matriz</t>
+          <t>OTR - Otros pasivos</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3418,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>011 - BANCO COMERCIAL DE MANABI C.A.</t>
+          <t>1011 - BANCO COMERCIAL DE MANABI C.A.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3424,6 +3439,11 @@
       <c r="N9" t="inlineStr">
         <is>
           <t>10708 - MARCABELI</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>TRA - Transferencias casa matriz</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3455,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>014 - BANCO DEL LITORAL S.A.</t>
+          <t>1014 - BANCO DEL LITORAL S.A.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>9 - Otros</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -3457,7 +3482,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16 - RED BANCARIA</t>
+          <t>1016 - RED BANCARIA</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -3479,7 +3504,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>020 - BANCO GENERAL RUMIÑAHUI S.A.</t>
+          <t>1020 - BANCO GENERAL RUMIÑAHUI S.A.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -3501,7 +3526,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>022 - ING BANK N.V.</t>
+          <t>1022 - ING BANK N.V.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -3523,7 +3548,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>023 - BANCO INTERNACIONAL S.A.</t>
+          <t>1023 - BANCO INTERNACIONAL S.A.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -3545,7 +3570,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>024 - LLOYDS BANK BLSA LIMITED</t>
+          <t>1024 - LLOYDS BANK BLSA LIMITED</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -3567,7 +3592,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>025 - BANCO DE LOJA S.A.</t>
+          <t>1025 - BANCO DE LOJA S.A.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -3589,7 +3614,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>026 - BANCO DE MACHALA S.A.</t>
+          <t>1026 - BANCO DE MACHALA S.A.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -3611,7 +3636,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>027 - TRUST FIDUCIARIA S.A.</t>
+          <t>1027 - TRUST FIDUCIARIA S.A.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3633,7 +3658,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>028 - BANCO DEL PACIFICO S.A.</t>
+          <t>1028 - BANCO DEL PACIFICO S.A.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3655,7 +3680,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>029 - BANCO PICHINCHA C.A.</t>
+          <t>1029 - BANCO PICHINCHA C.A.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3677,7 +3702,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>033 - BANCO DE LA PRODUCCION S.A. PRODUBANCO</t>
+          <t>1033 - BANCO DE LA PRODUCCION S.A. PRODUBANCO</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3699,7 +3724,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>035 - BANCO DE DESARROLLO ECONOMICO Y SOCIAL DE VENEZUELA</t>
+          <t>1035 - BANCO DE DESARROLLO ECONOMICO Y SOCIAL DE VENEZUELA</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3721,7 +3746,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>037 - BANCO SOLIDARIO S.A.</t>
+          <t>1037 - BANCO SOLIDARIO S.A.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3743,7 +3768,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>038 - BANCO SUDAMERICANO S.A.</t>
+          <t>1038 - BANCO SUDAMERICANO S.A.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3765,7 +3790,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>039 - BANCO TERRITORIAL S.A.</t>
+          <t>1039 - BANCO TERRITORIAL S.A.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3787,7 +3812,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>043 - ALMACENERA CONTINENTAL S.A. ALMACONTI</t>
+          <t>1043 - ALMACENERA CONTINENTAL S.A. ALMACONTI</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3804,7 +3829,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>044 - ALMACENERA ALMACOPIO S.A.</t>
+          <t>1044 - ALMACENERA ALMACOPIO S.A.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3821,7 +3846,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>045 - ALMACENERA DE GRANOS Y MERCADERIAS ALGRACESA</t>
+          <t>1045 - ALMACENERA DE GRANOS Y MERCADERIAS ALGRACESA</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3838,7 +3863,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>046 - ALMACENERA DEL AGRO S.A. ALMAGRO</t>
+          <t>1046 - ALMACENERA DEL AGRO S.A. ALMAGRO</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3855,7 +3880,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>047 - ALMACENERA DEL PROGRESO ALMACEPRO</t>
+          <t>1047 - ALMACENERA DEL PROGRESO ALMACEPRO</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3872,7 +3897,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>048 - ALMACENERA DEL ECUADOR S.A. ALMESA</t>
+          <t>1048 - ALMACENERA DEL ECUADOR S.A. ALMESA</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3889,7 +3914,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>049 - ALMACENERA GUAYAQUIL S.A. ALMAQUIL</t>
+          <t>1049 - ALMACENERA GUAYAQUIL S.A. ALMAQUIL</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3906,7 +3931,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>050 - BANCO CENTRAL DEL ECUADOR</t>
+          <t>1050 - BANCO CENTRAL DEL ECUADOR</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3923,7 +3948,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>051 - BANCO DEL ESTADO</t>
+          <t>1051 - BANCO DEL ESTADO</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3940,7 +3965,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>052 - BANCO ECUATORIANO DE LA VIVIENDA</t>
+          <t>1052 - BANCO ECUATORIANO DE LA VIVIENDA</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3957,7 +3982,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>053 - BANCO NACIONAL DE FOMENTO</t>
+          <t>1053 - BANCO NACIONAL DE FOMENTO</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3974,7 +3999,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>054 - CORPORACION FINANCIERA NACIONAL</t>
+          <t>1054 - CORPORACION FINANCIERA NACIONAL</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3991,7 +4016,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>055 - FONDO DE SOLIDARIDAD</t>
+          <t>1055 - FONDO DE SOLIDARIDAD</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4008,7 +4033,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>056 - INSTITUTO ECUATORIANO DE CREDITO EDUCATIVO Y BECAS</t>
+          <t>1056 - INSTITUTO ECUATORIANO DE CREDITO EDUCATIVO Y BECAS</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4025,7 +4050,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>057 - CAMBIOS INTERNACIONALES S.A. CAMBIOSA</t>
+          <t>1057 - CAMBIOS INTERNACIONALES S.A. CAMBIOSA</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4042,7 +4067,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>058 - CAMBIARIA AUSTRAL SOCIEDAD ANONIMA</t>
+          <t>1058 - CAMBIARIA AUSTRAL SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4059,7 +4084,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>059 - CAMBIARIA AMBATO CAMBIATO C.A.</t>
+          <t>1059 - CAMBIARIA AMBATO CAMBIATO C.A.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4076,7 +4101,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>060 - CASA DE CAMBIOS CAMBIDEX S.A.</t>
+          <t>1060 - CASA DE CAMBIOS CAMBIDEX S.A.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4093,7 +4118,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>061 - CASA DE CAMBIOS DELGADO S.A.</t>
+          <t>1061 - CASA DE CAMBIOS DELGADO S.A.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4110,7 +4135,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>062 - INTERFINSA S.A. CASA DE CAMBIOS</t>
+          <t>1062 - INTERFINSA S.A. CASA DE CAMBIOS</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4127,7 +4152,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>063 - CASA DE CAMBIOS JOSE IMBACUAN BUSTOS E HIJOS S.A.</t>
+          <t>1063 - CASA DE CAMBIOS JOSE IMBACUAN BUSTOS E HIJOS S.A.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4144,7 +4169,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>064 - LA MONEDA S.A.</t>
+          <t>1064 - LA MONEDA S.A.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4161,7 +4186,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>065 - MULTICAMBIO S.A.</t>
+          <t>1065 - MULTICAMBIO S.A.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4178,7 +4203,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>066 - COOPERATIVA DE AHORRO Y CREDITO TEXTIL 14 DE MARZO</t>
+          <t>1066 - COOPERATIVA DE AHORRO Y CREDITO TEXTIL 14 DE MARZO</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4195,7 +4220,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>068 - VICCAMBIOS S.A.</t>
+          <t>1068 - VICCAMBIOS S.A.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4212,7 +4237,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>069 - WANDER CAMBIOS S.A.</t>
+          <t>1069 - WANDER CAMBIOS S.A.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4229,7 +4254,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>070 - ASOCIACION MUTUALISTA AMBATO</t>
+          <t>1070 - ASOCIACION MUTUALISTA AMBATO</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4246,7 +4271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>071 - MUTUALISTA AZUAY</t>
+          <t>1071 - MUTUALISTA AZUAY</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4263,7 +4288,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>073 - MUTUALISTA CHIMBORAZO</t>
+          <t>1073 - MUTUALISTA CHIMBORAZO</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4280,7 +4305,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>074 - MUTUALISTA IMBABURA</t>
+          <t>1074 - MUTUALISTA IMBABURA</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4297,7 +4322,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>076 - ASOCIACION MUTUALISTA PICHINCHA PARA LA VIVIENDA</t>
+          <t>1076 - ASOCIACION MUTUALISTA PICHINCHA PARA LA VIVIENDA</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4314,7 +4339,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>077 - ACE SEGUROS S.A.</t>
+          <t>1077 - ACE SEGUROS S.A.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4331,7 +4356,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>078 - AIG METROPOLITANA COMPAÑÍA DE SEGUROS Y REASEGUROS S.A.</t>
+          <t>1078 - AIG METROPOLITANA COMPAÑÍA DE SEGUROS Y REASEGUROS S.A.</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4348,7 +4373,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>079 - ALIANZA COMPAÑÍA DE SEGUROS Y REASEGUROS S.A.</t>
+          <t>1079 - ALIANZA COMPAÑÍA DE SEGUROS Y REASEGUROS S.A.</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4365,7 +4390,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>080 - ASEGURADORA DEL SUR C.A.</t>
+          <t>1080 - ASEGURADORA DEL SUR C.A.</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4382,7 +4407,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>081 - ATLAS COMPAÑÍA DE SEGUROS S.A.</t>
+          <t>1081 - ATLAS COMPAÑÍA DE SEGUROS S.A.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4399,7 +4424,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>082 - BMI DEL ECUADOR COMPAÑÍA DE SEGUROS DE VIDA S.A.</t>
+          <t>1082 - BMI DEL ECUADOR COMPAÑÍA DE SEGUROS DE VIDA S.A.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4416,7 +4441,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>083 - AGENCIA COLOCADORA DE SEGUROS BOLIVARIANA S.A BOLIVARSA</t>
+          <t>1083 - AGENCIA COLOCADORA DE SEGUROS BOLIVARIANA S.A BOLIVARSA</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4433,7 +4458,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>084 - CERVANTES S.A. COMPAÑÍA DE SEGUROS Y REASEGUROS</t>
+          <t>1084 - CERVANTES S.A. COMPAÑÍA DE SEGUROS Y REASEGUROS</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4450,7 +4475,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>085 - COMPAÑÍA DE SEGUROS Y REASEGUROS GENERALES COLON S.A.</t>
+          <t>1085 - COMPAÑÍA DE SEGUROS Y REASEGUROS GENERALES COLON S.A.</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4467,7 +4492,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>086 - COLONIAL COMPAÑÍA DE SEGUROS Y REASEGUROS S..A</t>
+          <t>1086 - COLONIAL COMPAÑÍA DE SEGUROS Y REASEGUROS S..A</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4484,7 +4509,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>087 - COMPAÑÍA DE SEGUROS DE VIDA COLVIDA S.A.</t>
+          <t>1087 - COMPAÑÍA DE SEGUROS DE VIDA COLVIDA S.A.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -4501,7 +4526,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>088 - COMPAÑIA DE SEGUROS CONDOR S.A.</t>
+          <t>1088 - COMPAÑIA DE SEGUROS CONDOR S.A.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -4518,7 +4543,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>89 - SERVICIO DE RENTAS INTERNAS</t>
+          <t>1089 - SERVICIO DE RENTAS INTERNAS</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -4535,7 +4560,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>090 - COOPSEGUROS DEL ECUADOR S.A.</t>
+          <t>1090 - COOPSEGUROS DEL ECUADOR S.A.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -4552,7 +4577,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>091 - COOPERATIVA DE AHORRO Y CREDITO ALFONSO JARAMILLO  LEON C.C.C</t>
+          <t>1091 - COOPERATIVA DE AHORRO Y CREDITO ALFONSO JARAMILLO  LEON C.C.C</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -4569,7 +4594,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>092 - SEGUROS DEL PICHINCHA S.A. COMPAÑIA DE SEGUROS Y REASEGUROS</t>
+          <t>1092 - SEGUROS DEL PICHINCHA S.A. COMPAÑIA DE SEGUROS Y REASEGUROS</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -4586,7 +4611,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>093 - COMPAÑIA DE SEGUROS ECUATORIANO-SUIZA S.A.</t>
+          <t>1093 - COMPAÑIA DE SEGUROS ECUATORIANO-SUIZA S.A.</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -4603,7 +4628,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>095 - COMPAÑIA DE SEGUROS GENERALES EQUINOCCIAL S.A.</t>
+          <t>1095 - COMPAÑIA DE SEGUROS GENERALES EQUINOCCIAL S.A.</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -4620,7 +4645,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>096 - EQUIVIDA COMPAÑIA DE SEGUROS Y REASEGUROS S.A.</t>
+          <t>1096 - EQUIVIDA COMPAÑIA DE SEGUROS Y REASEGUROS S.A.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -4637,7 +4662,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>097 - EL FENIX DEL ECUADOR C.A.</t>
+          <t>1097 - EL FENIX DEL ECUADOR C.A.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -4654,7 +4679,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>098 - INCA COMPAÑIA DE SEGUROS S.A.</t>
+          <t>1098 - INCA COMPAÑIA DE SEGUROS S.A.</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -4671,7 +4696,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>099 - INTEGRAL S.A. COMPAÑIA DE SEGUROS Y REASEGUROS</t>
+          <t>1099 - INTEGRAL S.A. COMPAÑIA DE SEGUROS Y REASEGUROS</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -4688,7 +4713,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>100 - INTEROCEANICA C.A. DE SEGUROS Y REASEGUROS</t>
+          <t>1100 - INTEROCEANICA C.A. DE SEGUROS Y REASEGUROS</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -4705,7 +4730,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>101 - SOCIEDAD FINANCIERA VAZCORP S.A.</t>
+          <t>1101 - SOCIEDAD FINANCIERA VAZCORP S.A.</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -4722,7 +4747,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>102 - LA UNION COMPAÑIA NACIONAL DE SEGUROS S.A.</t>
+          <t>1102 - LA UNION COMPAÑIA NACIONAL DE SEGUROS S.A.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -4739,7 +4764,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>103 - MEMORIAS SERVICIOS DEL ECUADOR S.A. MEMOSER COMPAÑIA DE SEGUROS</t>
+          <t>1103 - MEMORIAS SERVICIOS DEL ECUADOR S.A. MEMOSER COMPAÑIA DE SEGUROS</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -4756,7 +4781,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>104 - OLYMPUS S.A. SEGUROS Y REASEGUROS</t>
+          <t>1104 - OLYMPUS S.A. SEGUROS Y REASEGUROS</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -4773,7 +4798,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>105 - SEGUROS ORIENTE S.A.</t>
+          <t>1105 - SEGUROS ORIENTE S.A.</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -4790,7 +4815,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>107 - PANAMERICANA DEL ECUADOR S.A. CIA. DE SEGUROS Y REASEGUROS</t>
+          <t>1107 - PANAMERICANA DEL ECUADOR S.A. CIA. DE SEGUROS Y REASEGUROS</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -4807,7 +4832,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>109 - PRIMMA COMPAÑIA DE SEGUROS Y REASEGUROS S.A.</t>
+          <t>1109 - PRIMMA COMPAÑIA DE SEGUROS Y REASEGUROS S.A.</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -4824,7 +4849,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>110 - PROGRESO COMPAÑIA DE SEGUROS Y REASEGUROS S.A.</t>
+          <t>1110 - PROGRESO COMPAÑIA DE SEGUROS Y REASEGUROS S.A.</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -4841,7 +4866,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>111 - RIO GUAYAS CIA. DE SEGUROS Y REASEGUROS S.A.</t>
+          <t>1111 - RIO GUAYAS CIA. DE SEGUROS Y REASEGUROS S.A.</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -4858,7 +4883,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>112 - SEGUROS ROCAFUERTE S.A.</t>
+          <t>1112 - SEGUROS ROCAFUERTE S.A.</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -4875,7 +4900,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>113 - SEGUROS SUCRE S.A.</t>
+          <t>1113 - SEGUROS SUCRE S.A.</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -4892,7 +4917,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>114 - SUD AMERICA COMPAÑIA DE SEGUROS</t>
+          <t>1114 - SUD AMERICA COMPAÑIA DE SEGUROS</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -4909,7 +4934,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>115 - SUL AMERICA COMPAÑIA DE SEGUROS DEL ECUADOR C.A.</t>
+          <t>1115 - SUL AMERICA COMPAÑIA DE SEGUROS DEL ECUADOR C.A.</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -4926,7 +4951,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>116 - SEGUROS UNIDOS S.A.</t>
+          <t>1116 - SEGUROS UNIDOS S.A.</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -4943,7 +4968,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>119 - COOPERATIVA DE AHORRO Y CREDITO ONCE DE JUNIO LTDA.</t>
+          <t>1119 - COOPERATIVA DE AHORRO Y CREDITO ONCE DE JUNIO LTDA.</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -4960,7 +4985,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>120 - COOPERATIVA DE AHORRO Y CREDITO 15 DE ABRIL LTDA.</t>
+          <t>1120 - COOPERATIVA DE AHORRO Y CREDITO 15 DE ABRIL LTDA.</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -4977,7 +5002,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>121 - COOPERATIVA DE AHORRO Y CREDITO 23 DE JULIO LTDA.</t>
+          <t>1121 - COOPERATIVA DE AHORRO Y CREDITO 23 DE JULIO LTDA.</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -4994,7 +5019,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>122 - COOPERATIVA DE AHORRO Y CREDITO 29 DE OCTUBRE LTDA.</t>
+          <t>1122 - COOPERATIVA DE AHORRO Y CREDITO 29 DE OCTUBRE LTDA.</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -5011,7 +5036,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>123 - COOPERATIVA DE AHORRO Y CREDITO ANDALUCIA LTDA.</t>
+          <t>1123 - COOPERATIVA DE AHORRO Y CREDITO ANDALUCIA LTDA.</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -5028,7 +5053,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>124 - COOPERATIVA DE AHORRO Y CREDITO ATUNTAQUI LTDA.</t>
+          <t>1124 - COOPERATIVA DE AHORRO Y CREDITO ATUNTAQUI LTDA.</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -5045,7 +5070,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>125 - COOPERATIVA DE AHORRO Y CREDITO PEQUEÑA EMPRESA DE COTOPAXI CACPECO</t>
+          <t>1125 - COOPERATIVA DE AHORRO Y CREDITO PEQUEÑA EMPRESA DE COTOPAXI CACPECO</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -5062,7 +5087,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>127 - COOPERATIVA DE AHORRO Y CREDITO CHONE LTDA.</t>
+          <t>1127 - COOPERATIVA DE AHORRO Y CREDITO CHONE LTDA.</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -5079,7 +5104,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>128 - BANCO DESARROLLO DE LOS PUEBLOS S.A.</t>
+          <t>1128 - BANCO DESARROLLO DE LOS PUEBLOS S.A.</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -5096,7 +5121,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>129 - COOPERATIVA DE AHORRO Y CREDITO COMERCIO LTDA.</t>
+          <t>1129 - COOPERATIVA DE AHORRO Y CREDITO COMERCIO LTDA.</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -5113,7 +5138,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>130 - COOPERATIVA DE AHORRO Y CREDITO COTOCOLLAO LTDA</t>
+          <t>1130 - COOPERATIVA DE AHORRO Y CREDITO COTOCOLLAO LTDA</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -5130,7 +5155,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>131 - COOPERATIVA DE AHORRO Y CREDITO EL SAGRARIO LTDA.</t>
+          <t>1131 - COOPERATIVA DE AHORRO Y CREDITO EL SAGRARIO LTDA.</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -5147,7 +5172,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>132 - COOPERATIVA DE AHORRO Y CREDITO GUARANDA LTDA.</t>
+          <t>1132 - COOPERATIVA DE AHORRO Y CREDITO GUARANDA LTDA.</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -5164,7 +5189,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>133 - COOPERATIVA DE AHORRO Y CREDITO LA DOLOROSA LTDA.</t>
+          <t>1133 - COOPERATIVA DE AHORRO Y CREDITO LA DOLOROSA LTDA.</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -5181,7 +5206,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>134 - BANCO COOPNACIONAL S.A.</t>
+          <t>1134 - BANCO COOPNACIONAL S.A.</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -5198,7 +5223,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>135 - COOPERATIVA DE AHORRO Y CREDITO OSCUS LTDA.</t>
+          <t>1135 - COOPERATIVA DE AHORRO Y CREDITO OSCUS LTDA.</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -5215,7 +5240,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>136 - COOPERATIVA DE AHORRO Y CREDITO PABLO MUÑOZ VEGA LTDA.</t>
+          <t>1136 - COOPERATIVA DE AHORRO Y CREDITO PABLO MUÑOZ VEGA LTDA.</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -5232,7 +5257,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>137 - COOPERATIVA DE AHORRO Y CREDITO COOPROGRESO LTDA.</t>
+          <t>1137 - COOPERATIVA DE AHORRO Y CREDITO COOPROGRESO LTDA.</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -5249,7 +5274,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>138 - COOPERATIVA DE AHORRO Y CREDITO RIOBAMBA LTDA.</t>
+          <t>1138 - COOPERATIVA DE AHORRO Y CREDITO RIOBAMBA LTDA.</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -5266,7 +5291,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>139 - COOPERATIVA DE AHORRO Y CREDITO SAN FRANCISCO LTDA.</t>
+          <t>1139 - COOPERATIVA DE AHORRO Y CREDITO SAN FRANCISCO LTDA.</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -5283,7 +5308,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>140 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO SANTA ANA LTDA.</t>
+          <t>1140 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO SANTA ANA LTDA.</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -5300,7 +5325,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>141 - COOPERATIVA DE AHORRO Y CREDITO SANTA ROSA LTDA.</t>
+          <t>1141 - COOPERATIVA DE AHORRO Y CREDITO SANTA ROSA LTDA.</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -5317,7 +5342,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>143 - COOPERATIVA DE AHORRO Y CREDITO TULCAN</t>
+          <t>1143 - COOPERATIVA DE AHORRO Y CREDITO TULCAN</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -5334,7 +5359,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>145 - CORPORACION DE RETROGARANTIA CREDITICIA</t>
+          <t>1145 - CORPORACION DE RETROGARANTIA CREDITICIA</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -5351,7 +5376,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>146 - CORPORACION DE DESARROLLO DE MERCADO SECUNDARIO DE HIPOTECAS</t>
+          <t>1146 - CORPORACION DE DESARROLLO DE MERCADO SECUNDARIO DE HIPOTECAS</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -5368,7 +5393,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>148 - BANCO PROCREDIT S.A.</t>
+          <t>1148 - BANCO PROCREDIT S.A.</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -5385,7 +5410,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>150 - CONSULCREDITO SOCIEDAD FINANCIERA S.A.</t>
+          <t>1150 - CONSULCREDITO SOCIEDAD FINANCIERA S.A.</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -5402,7 +5427,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>152 - DINERS CLUB DEL ECUADOR S.A. SOCIEDAD FINANCIERA</t>
+          <t>1152 - DINERS CLUB DEL ECUADOR S.A. SOCIEDAD FINANCIERA</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -5419,7 +5444,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>153 - BCE-DINERO ELECTRONICO</t>
+          <t>1153 - BCE-DINERO ELECTRONICO</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -5436,7 +5461,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>155 - SOCIEDAD FINANCIERA DEL AUSTRO 'FIDASA'</t>
+          <t>1155 - SOCIEDAD FINANCIERA DEL AUSTRO 'FIDASA'</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -5453,7 +5478,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>156 - FINANCAPITAL SOCIEDAD FINANCIERA CAPITAL S.A.</t>
+          <t>1156 - FINANCAPITAL SOCIEDAD FINANCIERA CAPITAL S.A.</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -5470,7 +5495,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>158 - FINANCIERA DE LA REPUBLICA S.A. FIRESA</t>
+          <t>1158 - FINANCIERA DE LA REPUBLICA S.A. FIRESA</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -5487,7 +5512,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>159 - GLOBAL SOCIEDAD FINANCIERA S.A.</t>
+          <t>1159 - GLOBAL SOCIEDAD FINANCIERA S.A.</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -5504,7 +5529,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>160 - SOCIEDAD FINANCIERA HEMISFERIO S.A.</t>
+          <t>1160 - SOCIEDAD FINANCIERA HEMISFERIO S.A.</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -5521,7 +5546,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>161 - SOCIEDAD FINANCIERA INTERAMERICANA S.A.</t>
+          <t>1161 - SOCIEDAD FINANCIERA INTERAMERICANA S.A.</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -5538,7 +5563,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>162 - SOCIEDAD FINANCIERA LEASINGCORP S.A.</t>
+          <t>1162 - SOCIEDAD FINANCIERA LEASINGCORP S.A.</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -5555,7 +5580,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>166 - COMPAÑIA PROINCO SOCIEDAD FINANCIERA S.A.</t>
+          <t>1166 - COMPAÑIA PROINCO SOCIEDAD FINANCIERA S.A.</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -5572,7 +5597,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>167 - CORPORACION DE INVERSION Y DESARROLLO TECFINSA S.A.</t>
+          <t>1167 - CORPORACION DE INVERSION Y DESARROLLO TECFINSA S.A.</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -5589,7 +5614,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>168 - UNION FINANCIERA CENTRAL S.A. UNIFINSA</t>
+          <t>1168 - UNION FINANCIERA CENTRAL S.A. UNIFINSA</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -5606,7 +5631,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>170 - CODECA INTERMEDIARIA FINANCIERA S.A.</t>
+          <t>1170 - CODECA INTERMEDIARIA FINANCIERA S.A.</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -5623,7 +5648,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>172 - INVESTLEASING S.A.</t>
+          <t>1172 - INVESTLEASING S.A.</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -5640,7 +5665,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>173 - LEASING ATLANTICO S.A. LEASATLANTIC</t>
+          <t>1173 - LEASING ATLANTICO S.A. LEASATLANTIC</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -5657,7 +5682,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>174 - AMERICAN HOME ASSURANCE COMPANY</t>
+          <t>1174 - AMERICAN HOME ASSURANCE COMPANY</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -5674,7 +5699,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>175 - CIGNA WORLDWIDE INSURANCE COMPANY</t>
+          <t>1175 - CIGNA WORLDWIDE INSURANCE COMPANY</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -5691,7 +5716,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>176 - NORWICH UNION FIRE INSURANCE SOCIETY LTD</t>
+          <t>1176 - NORWICH UNION FIRE INSURANCE SOCIETY LTD</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -5708,7 +5733,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>177 - PAN AMERICAN LIFE INSURANCE COMPANY</t>
+          <t>1177 - PAN AMERICAN LIFE INSURANCE COMPANY</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -5725,7 +5750,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>178 - COMPAÑIA REASEGURADORA DEL ECUADOR S.A.</t>
+          <t>1178 - COMPAÑIA REASEGURADORA DEL ECUADOR S.A.</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -5742,7 +5767,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>179 - UNIVERSAL COMPAÑIA DE REASEGUROS S.A.</t>
+          <t>1179 - UNIVERSAL COMPAÑIA DE REASEGUROS S.A.</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -5759,7 +5784,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>180 - COOPERATIVA DE AHORRO Y CREDITO 8 DE SEPTIEMBRE LTDA.</t>
+          <t>1180 - COOPERATIVA DE AHORRO Y CREDITO 8 DE SEPTIEMBRE LTDA.</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -5776,7 +5801,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>182 - COOPERATIVA DE AHORRO Y CREDITO SAN FRANCISCO DE ASIS</t>
+          <t>1182 - COOPERATIVA DE AHORRO Y CREDITO SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -5793,7 +5818,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>183 - ALVEXCORP S.A.</t>
+          <t>1183 - ALVEXCORP S.A.</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -5810,7 +5835,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>184 - INMOBILIARIA BANDEL C.A.</t>
+          <t>1184 - INMOBILIARIA BANDEL C.A.</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -5827,7 +5852,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>185 - BENFRATELO S.A.</t>
+          <t>1185 - BENFRATELO S.A.</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -5844,7 +5869,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>186 - INMOBILIARIA MOCHA VEINTE S.A.</t>
+          <t>1186 - INMOBILIARIA MOCHA VEINTE S.A.</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -5861,7 +5886,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>187 - CONCOR S.A.</t>
+          <t>1187 - CONCOR S.A.</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -5878,7 +5903,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>188 - EL CARBAYON S.A. COMPAÑIA INMOBILIARIA</t>
+          <t>1188 - EL CARBAYON S.A. COMPAÑIA INMOBILIARIA</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -5895,7 +5920,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>189 - EPIDAURO S.A.</t>
+          <t>1189 - EPIDAURO S.A.</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -5912,7 +5937,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>190 - GETAFECORP</t>
+          <t>1190 - GETAFECORP</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -5929,7 +5954,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>191 - INMOBILIARIA EL FLORON S.A. INFLORONSA</t>
+          <t>1191 - INMOBILIARIA EL FLORON S.A. INFLORONSA</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -5946,7 +5971,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>192 - INMOBILIARIA CENTRO MUNDO S.A. MUCENIN</t>
+          <t>1192 - INMOBILIARIA CENTRO MUNDO S.A. MUCENIN</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -5963,7 +5988,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>193 - ADMINISTRADORA DE FONDOS INVERS.FIDEI.DESARRO.INVIDEPRO S.A.</t>
+          <t>1193 - ADMINISTRADORA DE FONDOS INVERS.FIDEI.DESARRO.INVIDEPRO S.A.</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -5980,7 +6005,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>195 - MILNER S.A.</t>
+          <t>1195 - MILNER S.A.</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -5997,7 +6022,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>196 - PREDIAL POCAHONTAS S.A.</t>
+          <t>1196 - PREDIAL POCAHONTAS S.A.</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -6014,7 +6039,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>197 - PRIMISACORP S.A.</t>
+          <t>1197 - PRIMISACORP S.A.</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -6031,7 +6056,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>198 - SERVICIOS DEL AUSTRO S.A.</t>
+          <t>1198 - SERVICIOS DEL AUSTRO S.A.</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -6048,7 +6073,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>199 - EUROASSETS ADMINISTRADORA DE FONDOS Y FIDUCIA S.A.</t>
+          <t>1199 - EUROASSETS ADMINISTRADORA DE FONDOS Y FIDUCIA S.A.</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -6065,7 +6090,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>200 - INTERFONDOS S.A. ADMINISTRADORA DE FONDOS</t>
+          <t>1200 - INTERFONDOS S.A. ADMINISTRADORA DE FONDOS</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -6082,7 +6107,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>201 - FIDELITY TRUST ADMINISTRADORA DE FONDOS Y FIDEICOMISOS S.A. FTAFFSA</t>
+          <t>1201 - FIDELITY TRUST ADMINISTRADORA DE FONDOS Y FIDEICOMISOS S.A. FTAFFSA</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -6099,7 +6124,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>202 - INTEGRA S.A. ADMINISTRADORA DE FIDEICOMISOS (INTEGRASA)</t>
+          <t>1202 - INTEGRA S.A. ADMINISTRADORA DE FIDEICOMISOS (INTEGRASA)</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -6116,7 +6141,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>203 - MORGAN &amp; MORGAN, FIDUCIARY TRUST CORPORATION  S.A. 'FIDUCIARIA DEL ECUADOR'</t>
+          <t>1203 - MORGAN &amp; MORGAN, FIDUCIARY TRUST CORPORATION  S.A. 'FIDUCIARIA DEL ECUADOR'</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -6133,7 +6158,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>205 - STANFORD TRUST COMPANY ADMINISTRADORA DE FONDOS Y FIDEICOMISOS S.A.</t>
+          <t>1205 - STANFORD TRUST COMPANY ADMINISTRADORA DE FONDOS Y FIDEICOMISOS S.A.</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -6150,7 +6175,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>206 - ANALYTICAFINDS MANAGEMENT C.A. ADMINISTRADORA DE FONDOS Y FIDEICOMISOS</t>
+          <t>1206 - ANALYTICAFINDS MANAGEMENT C.A. ADMINISTRADORA DE FONDOS Y FIDEICOMISOS</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -6167,7 +6192,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>210 - COOPERATIVA DE AHORRO Y CREDITO DE LA PEQUEÑA EMPRESA DE PASTAZA</t>
+          <t>1210 - COOPERATIVA DE AHORRO Y CREDITO DE LA PEQUEÑA EMPRESA DE PASTAZA</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -6184,7 +6209,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>211 - COOPERATIVA DE AHORRO Y CREDITO CAJA CENTRAL 'FINANNCOOP'</t>
+          <t>1211 - COOPERATIVA DE AHORRO Y CREDITO CAJA CENTRAL 'FINANNCOOP'</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -6201,7 +6226,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>212 - CASA DE VALORES AFINSOL S.A.</t>
+          <t>1212 - CASA DE VALORES AFINSOL S.A.</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -6218,7 +6243,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>213 - AGROVALORES S.A. CASA DE VALORES</t>
+          <t>1213 - AGROVALORES S.A. CASA DE VALORES</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -6235,7 +6260,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>214 - CASA DE VALORES ANDINO CAPITAL MARKETS ANDIVALORES S.A.</t>
+          <t>1214 - CASA DE VALORES ANDINO CAPITAL MARKETS ANDIVALORES S.A.</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -6252,7 +6277,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>215 - AUSTROVALORES S.A.</t>
+          <t>1215 - AUSTROVALORES S.A.</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -6269,7 +6294,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>216 - CASA DE VALORES COFIVALORES S.A.</t>
+          <t>1216 - CASA DE VALORES COFIVALORES S.A.</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -6286,7 +6311,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>217 - CASA DE VALORES CONTINENTAL CONTIVALORES S.A.</t>
+          <t>1217 - CASA DE VALORES CONTINENTAL CONTIVALORES S.A.</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -6303,7 +6328,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>218 - COOPERATIVA DE AHORRO Y CREDITO ALIANZA DEL VALLE</t>
+          <t>1218 - COOPERATIVA DE AHORRO Y CREDITO ALIANZA DEL VALLE</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -6320,7 +6345,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>219 - COOPERATIVA DE AHORRO Y CREDITO CALCETA</t>
+          <t>1219 - COOPERATIVA DE AHORRO Y CREDITO CALCETA</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -6337,7 +6362,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>220 - ENLACE VALORES S.A. ENLACEVAL CASA DE VALORES</t>
+          <t>1220 - ENLACE VALORES S.A. ENLACEVAL CASA DE VALORES</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -6354,7 +6379,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>221 - FILAN CASA DE VALORES S.A.</t>
+          <t>1221 - FILAN CASA DE VALORES S.A.</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -6371,7 +6396,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>222 - MINISTERIO DE FINANZAS</t>
+          <t>1222 - MINISTERIO DE FINANZAS</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -6388,7 +6413,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>223 - CASA DE VALORES FINANZAS E INVERSIONES FINVER S.A.</t>
+          <t>1223 - CASA DE VALORES FINANZAS E INVERSIONES FINVER S.A.</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -6405,7 +6430,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>224 - INVESTUNION S.A. CASA DE VALORES</t>
+          <t>1224 - INVESTUNION S.A. CASA DE VALORES</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -6422,7 +6447,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>225 - CASA DE VALORES LADUPONT S.A.</t>
+          <t>1225 - CASA DE VALORES LADUPONT S.A.</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -6439,7 +6464,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>226 - CASA DE VALORES MERVALORES S.A.</t>
+          <t>1226 - CASA DE VALORES MERVALORES S.A.</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -6456,7 +6481,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>227 - CASA DE VALORES MULTIVALORES BG S.A.</t>
+          <t>1227 - CASA DE VALORES MULTIVALORES BG S.A.</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -6473,7 +6498,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>228 - PICHINCHA CASA DE VALORES PICAVAL S.A.</t>
+          <t>1228 - PICHINCHA CASA DE VALORES PICAVAL S.A.</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -6490,7 +6515,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>230 - PRESBURSATIL S.A. CASA DE VALORES</t>
+          <t>1230 - PRESBURSATIL S.A. CASA DE VALORES</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -6507,7 +6532,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>231 - CASA DE VALORES PREVIBURSATIL S.A.</t>
+          <t>1231 - CASA DE VALORES PREVIBURSATIL S.A.</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -6524,7 +6549,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>232 - CASA DE VALORES PRIME S.A.</t>
+          <t>1232 - CASA DE VALORES PRIME S.A.</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -6541,7 +6566,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>233 - CASA DE VALORES PRODUVALORES S.A.</t>
+          <t>1233 - CASA DE VALORES PRODUVALORES S.A.</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -6558,7 +6583,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>234 - SU CASA DE VALORES SUCAVAL S.A.</t>
+          <t>1234 - SU CASA DE VALORES SUCAVAL S.A.</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -6575,7 +6600,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>235 - CASA DE VALORES TRANSBURSATIL S.A.</t>
+          <t>1235 - CASA DE VALORES TRANSBURSATIL S.A.</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -6592,7 +6617,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>236 - CASA DE VALORES DEL PACIFICO VALPACIFIC S.A.</t>
+          <t>1236 - CASA DE VALORES DEL PACIFICO VALPACIFIC S.A.</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -6609,7 +6634,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>237 - ADMINISTRADORA DE FONDOS DE INVERSION Y FIDEICOMISO BG S.A.</t>
+          <t>1237 - ADMINISTRADORA DE FONDOS DE INVERSION Y FIDEICOMISO BG S.A.</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -6626,7 +6651,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>238 - ACCIONES Y VALORES CASA DE VALORES S.A. ACCIVAL</t>
+          <t>1238 - ACCIONES Y VALORES CASA DE VALORES S.A. ACCIVAL</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -6643,7 +6668,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>239 - ADMINISTRADORA DE FONDOS Y FIDEICOMISOS PACIFICO ADPACIFIC S.A.</t>
+          <t>1239 - ADMINISTRADORA DE FONDOS Y FIDEICOMISOS PACIFICO ADPACIFIC S.A.</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -6660,7 +6685,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>240 - AFP GENESIS ADMINISTRADORA DE FONDOS Y FIDEICOMISOS S.A.</t>
+          <t>1240 - AFP GENESIS ADMINISTRADORA DE FONDOS Y FIDEICOMISOS S.A.</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -6677,7 +6702,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>241 - ADMINISTRADORA DE FONDOS CONTIFONDOS S.A.</t>
+          <t>1241 - ADMINISTRADORA DE FONDOS CONTIFONDOS S.A.</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -6694,7 +6719,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>242 - ENLACEFONDOS S.A. ADMINISTRADORA DE FONDOS Y FIDEICOMISOS</t>
+          <t>1242 - ENLACEFONDOS S.A. ADMINISTRADORA DE FONDOS Y FIDEICOMISOS</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -6711,7 +6736,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>243 - FIDEVAL S.A. ADMINISTRADORA DE FONDOS Y FIDEICOMISOS</t>
+          <t>1243 - FIDEVAL S.A. ADMINISTRADORA DE FONDOS Y FIDEICOMISOS</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -6728,7 +6753,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>244 - FIDUCIA S.A. ADMINISTRADORA DE FONDOS Y FIDEICOMISOS</t>
+          <t>1244 - FIDUCIA S.A. ADMINISTRADORA DE FONDOS Y FIDEICOMISOS</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -6745,7 +6770,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>245 - FIDUPRO S.A. ADMINISTRADORA DE FONDOS</t>
+          <t>1245 - FIDUPRO S.A. ADMINISTRADORA DE FONDOS</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -6762,7 +6787,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>246 - FILANFONDOS S.A. ADMINIS. DE FONDOS Y FIDECOMISOS</t>
+          <t>1246 - FILANFONDOS S.A. ADMINIS. DE FONDOS Y FIDECOMISOS</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -6779,7 +6804,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>248 - FINVERFONDOS ADMINISTRADORA DE FONDOS</t>
+          <t>1248 - FINVERFONDOS ADMINISTRADORA DE FONDOS</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -6796,7 +6821,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>249 - ADMINISTRADORA DE FONDOS FODEVA S.A. FODEVASA</t>
+          <t>1249 - ADMINISTRADORA DE FONDOS FODEVA S.A. FODEVASA</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -6813,7 +6838,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>250 - ADMINISTRADORA DE FONDOS DEL PICHINCHA FONDOS PICHINCHA S.A.</t>
+          <t>1250 - ADMINISTRADORA DE FONDOS DEL PICHINCHA FONDOS PICHINCHA S.A.</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -6830,7 +6855,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>251 - PRESFONDOS S.A. ADMINISTRADORA DE FONDOS</t>
+          <t>1251 - PRESFONDOS S.A. ADMINISTRADORA DE FONDOS</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -6847,7 +6872,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>252 - ADMINISTRADORA DE FONDOS PREVIFONDOS S.A.</t>
+          <t>1252 - ADMINISTRADORA DE FONDOS PREVIFONDOS S.A.</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -6864,7 +6889,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>253 - ADMINISTRADORA DE FONDOS PRODUFONDOS S.A.</t>
+          <t>1253 - ADMINISTRADORA DE FONDOS PRODUFONDOS S.A.</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -6881,7 +6906,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>254 - TRANSFIEC S.A.</t>
+          <t>1254 - TRANSFIEC S.A.</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -6898,7 +6923,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>255 - A.F.P.V. ADMINISTRADORA DE FONDOS Y FIDUCIARIA  S.A.</t>
+          <t>1255 - A.F.P.V. ADMINISTRADORA DE FONDOS Y FIDUCIARIA  S.A.</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -6915,7 +6940,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>256 - AMERAFIN S.A.</t>
+          <t>1256 - AMERAFIN S.A.</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -6932,7 +6957,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>257 - ASESORES NACIONALES S.A. ANASA</t>
+          <t>1257 - ASESORES NACIONALES S.A. ANASA</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -6949,7 +6974,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>262 - CREDI FE DE DESARROLLO MICROEMPRESARIAL S.A.</t>
+          <t>1262 - CREDI FE DE DESARROLLO MICROEMPRESARIAL S.A.</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -6966,7 +6991,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>263 - DERUGNE S.A.</t>
+          <t>1263 - DERUGNE S.A.</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -6983,7 +7008,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>264 - ECUHABITAT S.A.</t>
+          <t>1264 - ECUHABITAT S.A.</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -7000,7 +7025,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>265 - ENLACESERVICIOS S.A.</t>
+          <t>1265 - ENLACESERVICIOS S.A.</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -7017,7 +7042,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>267 - FRANISA S.A.</t>
+          <t>1267 - FRANISA S.A.</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -7034,7 +7059,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>269 - INTERDIN S.A. COMPAÑIA DE RECUPERACIONES</t>
+          <t>1269 - INTERDIN S.A. COMPAÑIA DE RECUPERACIONES</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -7051,7 +7076,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>270 - NEDERLANDIA S.A.</t>
+          <t>1270 - NEDERLANDIA S.A.</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -7068,7 +7093,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>272 - OTRAPART S.A.</t>
+          <t>1272 - OTRAPART S.A.</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -7085,7 +7110,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>273 - PROENOC S.A.</t>
+          <t>1273 - PROENOC S.A.</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -7102,7 +7127,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>274 - ASESORIA Y RECUPERACIONES S.A. RECUPSA</t>
+          <t>1274 - ASESORIA Y RECUPERACIONES S.A. RECUPSA</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -7119,7 +7144,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>275 - COMPAÑIA DE SERVICIOS AUXILIARES DEL PACIFICO S.A. SERENTRESA</t>
+          <t>1275 - COMPAÑIA DE SERVICIOS AUXILIARES DEL PACIFICO S.A. SERENTRESA</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -7136,7 +7161,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>276 - SEVIMAC S.A.</t>
+          <t>1276 - SEVIMAC S.A.</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7173,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>277 - SICOBRA S.A.</t>
+          <t>1277 - SICOBRA S.A.</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7185,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>279 - TECSOFT S.A.</t>
+          <t>1279 - TECSOFT S.A.</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7197,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>280 - COMPAÑIA DE TRANSPORTE DE VALORES Y SEGURIDAD RUMIÑAHUI S.A.</t>
+          <t>1280 - COMPAÑIA DE TRANSPORTE DE VALORES Y SEGURIDAD RUMIÑAHUI S.A.</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7209,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>281 - VIVERO MIÑO VIVEMISA S.A.</t>
+          <t>1281 - VIVERO MIÑO VIVEMISA S.A.</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7221,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>282 - BANCO DE SANTANDER SOCIEDAD ANONIMA DE CREDITO</t>
+          <t>1282 - BANCO DE SANTANDER SOCIEDAD ANONIMA DE CREDITO</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7233,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>284 - CHASE MANHATTAN BANK N.A.</t>
+          <t>1284 - CHASE MANHATTAN BANK N.A.</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7245,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>287 - BANCO DO BRASIL S.A.</t>
+          <t>1287 - BANCO DO BRASIL S.A.</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7257,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>288 - DRESDNER BANK LATEINAMERIKA AKTIENGESELLSCHAFT</t>
+          <t>1288 - DRESDNER BANK LATEINAMERIKA AKTIENGESELLSCHAFT</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7269,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>290 - BANCO DE LA NACION ARGENTINA</t>
+          <t>1290 - BANCO DE LA NACION ARGENTINA</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7281,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>300 - COOPERATIVA DE AHORRO Y CREDITO CONSTRUCCION COMERCIO Y PRODUCCION LTDA.</t>
+          <t>1300 - COOPERATIVA DE AHORRO Y CREDITO CONSTRUCCION COMERCIO Y PRODUCCION LTDA.</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7293,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>302 - COOPERATIVA JUVENTUD ECUATORIANA PROGRESISTA</t>
+          <t>1302 - COOPERATIVA JUVENTUD ECUATORIANA PROGRESISTA</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7305,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>303 - COOPERATIVA DE AHORRO Y CREDITO METROPOLITANA</t>
+          <t>1303 - COOPERATIVA DE AHORRO Y CREDITO METROPOLITANA</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7317,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>304 - COOPERATIVA DE AHORRO Y CREDITO PADRE JULIAN LORENT</t>
+          <t>1304 - COOPERATIVA DE AHORRO Y CREDITO PADRE JULIAN LORENT</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7329,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>306 - COOPERATIVA DE AHORRO Y CREDITO VICENTINA MANUEL ESTEBAN GODOY ORTEGA LTDA</t>
+          <t>1306 - COOPERATIVA DE AHORRO Y CREDITO VICENTINA MANUEL ESTEBAN GODOY ORTEGA LTDA</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7341,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>330 - CAMBIOSUR S.A.</t>
+          <t>1330 - CAMBIOSUR S.A.</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7353,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>336 - ASOCIACION MUTUALISTA DE AHORRO Y CREDITO PARA LA VIVIENDA GUAYAQUIL</t>
+          <t>1336 - ASOCIACION MUTUALISTA DE AHORRO Y CREDITO PARA LA VIVIENDA GUAYAQUIL</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7365,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>352 - COOPERATIVA DE AHORRO Y CREDITO DE LA PEQUENA EMPRESA BIBLIAN</t>
+          <t>1352 - COOPERATIVA DE AHORRO Y CREDITO DE LA PEQUENA EMPRESA BIBLIAN</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7377,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>364 - COOPERATIVA DE AHORRO Y CREDITO SAN JOSE LIMITADA</t>
+          <t>1364 - COOPERATIVA DE AHORRO Y CREDITO SAN JOSE LIMITADA</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7389,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>381 - BOLIVARIANO ADMINISTRADORA DE FONDOS Y FIDEICOMISOS AFFB S.A.</t>
+          <t>1381 - BOLIVARIANO ADMINISTRADORA DE FONDOS Y FIDEICOMISOS AFFB S.A.</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7401,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>388 - COOPERATIVA DE AHORRO Y CREDITO PAD LTDA. COOPAD</t>
+          <t>1388 - COOPERATIVA DE AHORRO Y CREDITO PAD LTDA. COOPAD</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7413,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>400 - DEPOSITO CENTRALIZADO DE COMPENSACION Y LIQUIDACION DE VALORES DECEVALE S.A.</t>
+          <t>1400 - DEPOSITO CENTRALIZADO DE COMPENSACION Y LIQUIDACION DE VALORES DECEVALE S.A.</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7425,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>409 - PACIFICARD S.A.</t>
+          <t>1409 - PACIFICARD S.A.</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7437,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>418 - BANCO PROMERICA S.A.</t>
+          <t>1418 - BANCO PROMERICA S.A.</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7449,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>422 - BANCO DELBANK S.A.</t>
+          <t>1422 - BANCO DELBANK S.A.</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7461,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>501 - BANCO CAPITAL SOCIEDAD ANONIMA</t>
+          <t>1501 - BANCO CAPITAL SOCIEDAD ANONIMA</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7473,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>590 - CASA DE CAMBIOS ARGENTUM S.A.</t>
+          <t>1590 - CASA DE CAMBIOS ARGENTUM S.A.</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7485,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>615 - COOPERATIVA DE AHORRO Y CREDITO JARDIN AZUAYO LTDA.</t>
+          <t>1615 - COOPERATIVA DE AHORRO Y CREDITO JARDIN AZUAYO LTDA.</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7497,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>616 - COOPERATIVA DE AHORRO Y CREDITO MANANTIAL DE ORO LTDA.</t>
+          <t>1616 - COOPERATIVA DE AHORRO Y CREDITO MANANTIAL DE ORO LTDA.</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7509,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>617 - COOPERATIVA DE AHORRO Y CREDITO JUAN DE SALINAS</t>
+          <t>1617 - COOPERATIVA DE AHORRO Y CREDITO JUAN DE SALINAS</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7521,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>618 - COOPERATIVA DE AHORRO Y CREDITO PUELLARO LTDA.</t>
+          <t>1618 - COOPERATIVA DE AHORRO Y CREDITO PUELLARO LTDA.</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7533,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>619 - COOPERATIVA DE AHORRO Y CREDITO LA NUEVA JERUSALEN</t>
+          <t>1619 - COOPERATIVA DE AHORRO Y CREDITO LA NUEVA JERUSALEN</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7545,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>620 - COOPERATIVA DE AHORRO Y CREDITO MALCHINGUI LTDA.</t>
+          <t>1620 - COOPERATIVA DE AHORRO Y CREDITO MALCHINGUI LTDA.</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7557,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>621 - COOPERATIVA DE AHORRO Y CREDITO AMAZONAS LTDA.</t>
+          <t>1621 - COOPERATIVA DE AHORRO Y CREDITO AMAZONAS LTDA.</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7569,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>622 - COOPERATIVA DE AHORRO Y CREDITO AGRARIA MUSHUK KAWSAY LTDA</t>
+          <t>1622 - COOPERATIVA DE AHORRO Y CREDITO AGRARIA MUSHUK KAWSAY LTDA</t>
         </is>
       </c>
     </row>
@@ -7556,1834 +7581,1834 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>623 - COOPERATIVA DE AHORRO Y CREDITO TENA LTDA.</t>
+          <t>1623 - COOPERATIVA DE AHORRO Y CREDITO TENA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="E259" t="inlineStr">
         <is>
-          <t>624 - COOPERATIVA DE AHORRO Y CREDITO DE LA PEQUEÑA EMPRESA GUALAQUIZA</t>
+          <t>1624 - COOPERATIVA DE AHORRO Y CREDITO DE LA PEQUEÑA EMPRESA GUALAQUIZA</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="E260" t="inlineStr">
         <is>
-          <t>625 - COOPERATIVA DE AHORRO Y CREDITO ALIANZA MINAS LTDA.</t>
+          <t>1625 - COOPERATIVA DE AHORRO Y CREDITO ALIANZA MINAS LTDA.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="E261" t="inlineStr">
         <is>
-          <t>626 - COOPERATIVA DE AHORRO Y CREDITO MI TIERRA</t>
+          <t>1626 - COOPERATIVA DE AHORRO Y CREDITO MI TIERRA</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="E262" t="inlineStr">
         <is>
-          <t>627 - COOPERATIVA DE AHORRO Y CREDITO DE LA PEQUEÑA EMPRESA CACPE YANZATZA LTDA.</t>
+          <t>1627 - COOPERATIVA DE AHORRO Y CREDITO DE LA PEQUEÑA EMPRESA CACPE YANZATZA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="E263" t="inlineStr">
         <is>
-          <t>628 - COOPERATIVA DE AHORRO Y CREDITO FUTURO Y DESARROLLO FUNDESARROLLO</t>
+          <t>1628 - COOPERATIVA DE AHORRO Y CREDITO FUTURO Y DESARROLLO FUNDESARROLLO</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="E264" t="inlineStr">
         <is>
-          <t>629 - COOPERATIVA DE AHORRO Y CREDITO DE LA PEQUEÑA EMPRESA ZAMORA CHINCHIPE</t>
+          <t>1629 - COOPERATIVA DE AHORRO Y CREDITO DE LA PEQUEÑA EMPRESA ZAMORA CHINCHIPE</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="E265" t="inlineStr">
         <is>
-          <t>630 - COOPERATIVA DE AHORRO Y CREDITO DESARROLLO INTEGRAL</t>
+          <t>1630 - COOPERATIVA DE AHORRO Y CREDITO DESARROLLO INTEGRAL</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="E266" t="inlineStr">
         <is>
-          <t>631 - COOPERATIVA DE AHORRO Y CREDITO EDUCADORES DE PASTAZA LTDA</t>
+          <t>1631 - COOPERATIVA DE AHORRO Y CREDITO EDUCADORES DE PASTAZA LTDA</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="E267" t="inlineStr">
         <is>
-          <t>632 - COOPERATIVA DE AHORRO Y CREDITO GRAMEEN AMAZONAS LTDA.</t>
+          <t>1632 - COOPERATIVA DE AHORRO Y CREDITO GRAMEEN AMAZONAS LTDA.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="E268" t="inlineStr">
         <is>
-          <t>633 - COOP. AHORRO Y CREDITO DE LOS SERVIDORES PUBLICOS DEL MIN DE EDUCACION Y CULTURA</t>
+          <t>1633 - COOP. AHORRO Y CREDITO DE LOS SERVIDORES PUBLICOS DEL MIN DE EDUCACION Y CULTURA</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="E269" t="inlineStr">
         <is>
-          <t>634 - COOPERATIVA DE AHORRO Y CREDITO PEDRO MONCAYO LTDA.</t>
+          <t>1634 - COOPERATIVA DE AHORRO Y CREDITO PEDRO MONCAYO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="E270" t="inlineStr">
         <is>
-          <t>635 - COOPERATIVA DE AHORRO Y CREDITO SAN MIGUEL DE LOS BANCOS LTDA.</t>
+          <t>1635 - COOPERATIVA DE AHORRO Y CREDITO SAN MIGUEL DE LOS BANCOS LTDA.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="E271" t="inlineStr">
         <is>
-          <t>636 - COOPERATIVA DE AHORRO Y CREDITO POLICIA NACIONAL LTDA.</t>
+          <t>1636 - COOPERATIVA DE AHORRO Y CREDITO POLICIA NACIONAL LTDA.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="E272" t="inlineStr">
         <is>
-          <t>637 - COOPERATIVA DE AHORRO Y CREDITO NUEVA HUANCAVILCA</t>
+          <t>1637 - COOPERATIVA DE AHORRO Y CREDITO NUEVA HUANCAVILCA</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="E273" t="inlineStr">
         <is>
-          <t>638 - COOPERATIVA DE AHORRO Y CREDITO LA MERCED LTDA.</t>
+          <t>1638 - COOPERATIVA DE AHORRO Y CREDITO LA MERCED LTDA.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="E274" t="inlineStr">
         <is>
-          <t>639 - COOPERATIVA DE AHORRO Y CREDITO PROMOCION DE VIDA ASOCIADA LTDA.</t>
+          <t>1639 - COOPERATIVA DE AHORRO Y CREDITO PROMOCION DE VIDA ASOCIADA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="E275" t="inlineStr">
         <is>
-          <t>640 - COOPERATIVA DE AHORRO Y CREDITO SAN JOSE S.J.</t>
+          <t>1640 - COOPERATIVA DE AHORRO Y CREDITO SAN JOSE S.J.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="E276" t="inlineStr">
         <is>
-          <t>642 - COOPERATIVA DE AHORRO Y CREDITO SEÑOR DE GIRON</t>
+          <t>1642 - COOPERATIVA DE AHORRO Y CREDITO SEÑOR DE GIRON</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="E277" t="inlineStr">
         <is>
-          <t>644 - COOPERATIVA DE AHORRO Y CREDITO INTEGRAL</t>
+          <t>1644 - COOPERATIVA DE AHORRO Y CREDITO INTEGRAL</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="E278" t="inlineStr">
         <is>
-          <t>645 - COOPERATIVA DE AHORRO CREDITO ERCO LTDA.</t>
+          <t>1645 - COOPERATIVA DE AHORRO CREDITO ERCO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="E279" t="inlineStr">
         <is>
-          <t>646 - COOPERATIVA DE AHORRO Y CREDITO BAÑOS LTDA</t>
+          <t>1646 - COOPERATIVA DE AHORRO Y CREDITO BAÑOS LTDA</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="E280" t="inlineStr">
         <is>
-          <t>647 - COOPERATIVA DE AHORRO Y CREDITO EDUCADORES DE TUNGURAHUA LTDA</t>
+          <t>1647 - COOPERATIVA DE AHORRO Y CREDITO EDUCADORES DE TUNGURAHUA LTDA</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="E281" t="inlineStr">
         <is>
-          <t>648 - COOPERATIVA DE AHORRO Y CREDITO AMBATO LTDA.</t>
+          <t>1648 - COOPERATIVA DE AHORRO Y CREDITO AMBATO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="E282" t="inlineStr">
         <is>
-          <t>649 - COOPERATIVA DE AHORRO Y CREDITO TUNGURAHUA LTDA.</t>
+          <t>1649 - COOPERATIVA DE AHORRO Y CREDITO TUNGURAHUA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="E283" t="inlineStr">
         <is>
-          <t>651 - COOPERATIVA DE AHORRO Y CREDITO LLANGANATES</t>
+          <t>1651 - COOPERATIVA DE AHORRO Y CREDITO LLANGANATES</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="E284" t="inlineStr">
         <is>
-          <t>652 - COOPERATIVA DE AHORRO Y CREDITO DORADO LTDA</t>
+          <t>1652 - COOPERATIVA DE AHORRO Y CREDITO DORADO LTDA</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="E285" t="inlineStr">
         <is>
-          <t>653 - COOPERATIVA DE AHORRO Y CREDITO EL CALVARIO LTDA.</t>
+          <t>1653 - COOPERATIVA DE AHORRO Y CREDITO EL CALVARIO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="E286" t="inlineStr">
         <is>
-          <t>654 - COOPERATIVA DE AHORRO Y CREDITO CREDI FACIL LTDA.</t>
+          <t>1654 - COOPERATIVA DE AHORRO Y CREDITO CREDI FACIL LTDA.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="E287" t="inlineStr">
         <is>
-          <t>655 - COOPERATIVA DE AHORRO Y CREDITO VENCEDORES DE TUNGURAHUA LTDA.</t>
+          <t>1655 - COOPERATIVA DE AHORRO Y CREDITO VENCEDORES DE TUNGURAHUA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="E288" t="inlineStr">
         <is>
-          <t>656 - COOPERATIVA DE AHORRO Y CREDITO LOS RIOS</t>
+          <t>1656 - COOPERATIVA DE AHORRO Y CREDITO LOS RIOS</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="E289" t="inlineStr">
         <is>
-          <t>657 - COOPERATIVA DE AHORRO Y CREDITO NUESTROS ABUELOS LTDA</t>
+          <t>1657 - COOPERATIVA DE AHORRO Y CREDITO NUESTROS ABUELOS LTDA</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="E290" t="inlineStr">
         <is>
-          <t>658 - COOPERATIVA DE AHORRO Y CREDITO JUAN PIO DE MORA LTDA.</t>
+          <t>1658 - COOPERATIVA DE AHORRO Y CREDITO JUAN PIO DE MORA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="E291" t="inlineStr">
         <is>
-          <t>659 - COOPERATIVA DE AHORRO Y CREDITO ARTESANOS LTDA.</t>
+          <t>1659 - COOPERATIVA DE AHORRO Y CREDITO ARTESANOS LTDA.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="E292" t="inlineStr">
         <is>
-          <t>660 - COOPERATIVA DE AHORRO Y CREDITO SANTA ANITA LTDA.</t>
+          <t>1660 - COOPERATIVA DE AHORRO Y CREDITO SANTA ANITA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="E293" t="inlineStr">
         <is>
-          <t>661 - COOPERATIVA DE AHORRO Y CREDITO MUJERES UNIDAS</t>
+          <t>1661 - COOPERATIVA DE AHORRO Y CREDITO MUJERES UNIDAS</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="E294" t="inlineStr">
         <is>
-          <t>662 - COOPERATIVA DE AHORRO Y CREDITO SAN ANTONIO LTDA. IMBABURA</t>
+          <t>1662 - COOPERATIVA DE AHORRO Y CREDITO SAN ANTONIO LTDA. IMBABURA</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="E295" t="inlineStr">
         <is>
-          <t>663 - COOPERATIVA DE AHORRO Y CREDITO HUAYCO PUNGO</t>
+          <t>1663 - COOPERATIVA DE AHORRO Y CREDITO HUAYCO PUNGO</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="E296" t="inlineStr">
         <is>
-          <t>664 - COOPERATIVA DE AHORRO Y CREDITO ANDINA LTDA.</t>
+          <t>1664 - COOPERATIVA DE AHORRO Y CREDITO ANDINA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="E297" t="inlineStr">
         <is>
-          <t>665 - COOPERATIVA DE AHORRO Y CREDITO 15 DE AGOSTO DE PILACOTO</t>
+          <t>1665 - COOPERATIVA DE AHORRO Y CREDITO 15 DE AGOSTO DE PILACOTO</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="E298" t="inlineStr">
         <is>
-          <t>666 - COOPERATIVA DE AHORRO Y CREDITO PILAHUIN</t>
+          <t>1666 - COOPERATIVA DE AHORRO Y CREDITO PILAHUIN</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="E299" t="inlineStr">
         <is>
-          <t>667 - COOPERATIVA DE AHORRO Y CREDITO PUCARA LTDA.</t>
+          <t>1667 - COOPERATIVA DE AHORRO Y CREDITO PUCARA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="E300" t="inlineStr">
         <is>
-          <t>668 - COOPERATIVA DE AHORRO Y CREDITO SINCHI RUNA LTDA.</t>
+          <t>1668 - COOPERATIVA DE AHORRO Y CREDITO SINCHI RUNA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="E301" t="inlineStr">
         <is>
-          <t>669 - COOPERATIVA DE AHORRO Y CREDITO CRISTO REY</t>
+          <t>1669 - COOPERATIVA DE AHORRO Y CREDITO CRISTO REY</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="E302" t="inlineStr">
         <is>
-          <t>670 - COOPERATIVA DE AHORRO Y CREDITO SEMILLA DEL PROGRESO LTDA.</t>
+          <t>1670 - COOPERATIVA DE AHORRO Y CREDITO SEMILLA DEL PROGRESO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="E303" t="inlineStr">
         <is>
-          <t>671 - COOPERATIVA DE AHORRO Y CREDITO CARIAMANGA LTDA.</t>
+          <t>1671 - COOPERATIVA DE AHORRO Y CREDITO CARIAMANGA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="E304" t="inlineStr">
         <is>
-          <t>672 - COOPERATIVA DE AHORRO Y CREDITO DE LA CAMARA DE COMERCIO DE PINDAL CADECOPI</t>
+          <t>1672 - COOPERATIVA DE AHORRO Y CREDITO DE LA CAMARA DE COMERCIO DE PINDAL CADECOPI</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="E305" t="inlineStr">
         <is>
-          <t>673 - COOPERATIVA DE AHORRO Y CREDITO GONZANAMA</t>
+          <t>1673 - COOPERATIVA DE AHORRO Y CREDITO GONZANAMA</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="E306" t="inlineStr">
         <is>
-          <t>674 - COOPERATIVA DE AHORRO Y CREDITO QUILANGA LTDA.</t>
+          <t>1674 - COOPERATIVA DE AHORRO Y CREDITO QUILANGA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="E307" t="inlineStr">
         <is>
-          <t>675 - COOPERATIVA DE AHORRO Y CREDITO MARCABELI LTDA</t>
+          <t>1675 - COOPERATIVA DE AHORRO Y CREDITO MARCABELI LTDA</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="E308" t="inlineStr">
         <is>
-          <t>676 - COOPERATIVA DE AHORRO Y CREDITO AGRICOLA JUNIN</t>
+          <t>1676 - COOPERATIVA DE AHORRO Y CREDITO AGRICOLA JUNIN</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="E309" t="inlineStr">
         <is>
-          <t>677 - COOPERATIVA DE AHORRO Y CREDITO PUERTO LOPEZ LTDA.</t>
+          <t>1677 - COOPERATIVA DE AHORRO Y CREDITO PUERTO LOPEZ LTDA.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="E310" t="inlineStr">
         <is>
-          <t>678 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO DEL CANTON BOLIVAR LTDA.</t>
+          <t>1678 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO DEL CANTON BOLIVAR LTDA.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="E311" t="inlineStr">
         <is>
-          <t>679 - COOPERATIVA DE AHORRO Y CREDITO NUEVA ESPERANZA LTDA</t>
+          <t>1679 - COOPERATIVA DE AHORRO Y CREDITO NUEVA ESPERANZA LTDA</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="E312" t="inlineStr">
         <is>
-          <t>680 - COOPERATIVA DE AHORRO Y CREDITO SAN JORGE LTDA</t>
+          <t>1680 - COOPERATIVA DE AHORRO Y CREDITO SAN JORGE LTDA</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="E313" t="inlineStr">
         <is>
-          <t>682 - COOPERATIVA DE AHORRO Y CREDITO ACCION Y DESARROLLO LTDA</t>
+          <t>1682 - COOPERATIVA DE AHORRO Y CREDITO ACCION Y DESARROLLO LTDA</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="E314" t="inlineStr">
         <is>
-          <t>683 - COOPERATIVA DE AHORRO Y CREDITO EDUCADORES DE CHIMBORAZO</t>
+          <t>1683 - COOPERATIVA DE AHORRO Y CREDITO EDUCADORES DE CHIMBORAZO</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="E315" t="inlineStr">
         <is>
-          <t>684 - COOPERATIVA DE AHORRO Y CREDITO MINGA LTDA</t>
+          <t>1684 - COOPERATIVA DE AHORRO Y CREDITO MINGA LTDA</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="E316" t="inlineStr">
         <is>
-          <t>685 - COOPERATIVA DE AHORRO Y CREDITO 4 DE OCTUBRE</t>
+          <t>1685 - COOPERATIVA DE AHORRO Y CREDITO 4 DE OCTUBRE</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="E317" t="inlineStr">
         <is>
-          <t>686 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO INDIGENA DE GUAMOTE LTDA</t>
+          <t>1686 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO INDIGENA DE GUAMOTE LTDA</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="E318" t="inlineStr">
         <is>
-          <t>687 - COOPERATIVA DE AHORRO Y CREDITO FERNANDO DAQUILEMA</t>
+          <t>1687 - COOPERATIVA DE AHORRO Y CREDITO FERNANDO DAQUILEMA</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="E319" t="inlineStr">
         <is>
-          <t>688 - COOPERATIVA DE AHORRO Y CREDITO SUMAC LLACTA LTDA.</t>
+          <t>1688 - COOPERATIVA DE AHORRO Y CREDITO SUMAC LLACTA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="E320" t="inlineStr">
         <is>
-          <t>689 - COOPERATIVA DE AHORRO Y CREDITO SAN GABRIEL LTDA.</t>
+          <t>1689 - COOPERATIVA DE AHORRO Y CREDITO SAN GABRIEL LTDA.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="E321" t="inlineStr">
         <is>
-          <t>690 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO JOYA DE LOS SACHAS LTDA</t>
+          <t>1690 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO JOYA DE LOS SACHAS LTDA</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="E322" t="inlineStr">
         <is>
-          <t>691 - COOPERATIVA DE AHORRO Y CREDITO PUERTO FRANCISCO DE ORELLANA</t>
+          <t>1691 - COOPERATIVA DE AHORRO Y CREDITO PUERTO FRANCISCO DE ORELLANA</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="E323" t="inlineStr">
         <is>
-          <t>692 - COOPERATIVA DE AHORRO Y CREDITO CRECIENDO JUNTOS LTDA.</t>
+          <t>1692 - COOPERATIVA DE AHORRO Y CREDITO CRECIENDO JUNTOS LTDA.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="E324" t="inlineStr">
         <is>
-          <t>693 - COOPERATIVA DE AHORRO Y CREDITO EL COMERCIANTE LTDA.</t>
+          <t>1693 - COOPERATIVA DE AHORRO Y CREDITO EL COMERCIANTE LTDA.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="E325" t="inlineStr">
         <is>
-          <t>694 - COOPERATIVA DE AHORRO Y CREDITO EL DISCAPACITADO</t>
+          <t>1694 - COOPERATIVA DE AHORRO Y CREDITO EL DISCAPACITADO</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="E326" t="inlineStr">
         <is>
-          <t>695 - COOPERATIVA DE AHORRO Y CREDITO EL MIGRANTE SOLIDARIO</t>
+          <t>1695 - COOPERATIVA DE AHORRO Y CREDITO EL MIGRANTE SOLIDARIO</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="E327" t="inlineStr">
         <is>
-          <t>696 - COOPERATIVA DE AHORRO Y CREDITO EL TESORO PILLAREÑO</t>
+          <t>1696 - COOPERATIVA DE AHORRO Y CREDITO EL TESORO PILLAREÑO</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="E328" t="inlineStr">
         <is>
-          <t>697 - COOPERATIVA DE AHORRO Y CREDITO EL TRANSPORTISTA CACET</t>
+          <t>1697 - COOPERATIVA DE AHORRO Y CREDITO EL TRANSPORTISTA CACET</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="E329" t="inlineStr">
         <is>
-          <t>698 - COOPERATIVA DE AHORRO Y CREDITO EMPLEADOS BANCARIOS DE EL ORO LTDA</t>
+          <t>1698 - COOPERATIVA DE AHORRO Y CREDITO EMPLEADOS BANCARIOS DE EL ORO LTDA</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="E330" t="inlineStr">
         <is>
-          <t>699 - COOPERATIVA DE AHORRO Y CREDITO ESPERANZA Y PROGRESO DEL VALLE</t>
+          <t>1699 - COOPERATIVA DE AHORRO Y CREDITO ESPERANZA Y PROGRESO DEL VALLE</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="E331" t="inlineStr">
         <is>
-          <t>700 - COOPERATIVA DE AHORRO Y CREDITO FASAYÑAN LTDA.</t>
+          <t>1700 - COOPERATIVA DE AHORRO Y CREDITO FASAYÑAN LTDA.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="E332" t="inlineStr">
         <is>
-          <t>701 - COOPERATIVA DE AHORRO Y CREDITO FRANDESC LTDA</t>
+          <t>1701 - COOPERATIVA DE AHORRO Y CREDITO FRANDESC LTDA</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="E333" t="inlineStr">
         <is>
-          <t>702 - COOP DE AHORRO Y CREDITO FUERZA ENTRE NOSOTROS PARA IMPULSAR EL EXITO FENIX</t>
+          <t>1702 - COOP DE AHORRO Y CREDITO FUERZA ENTRE NOSOTROS PARA IMPULSAR EL EXITO FENIX</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="E334" t="inlineStr">
         <is>
-          <t>703 - COOPERATIVA DE AHORRO Y CREDITO FUNDAR</t>
+          <t>1703 - COOPERATIVA DE AHORRO Y CREDITO FUNDAR</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="E335" t="inlineStr">
         <is>
-          <t>704 - COOPERATIVA DE AHORRO Y CREDITO GAÑANSOL LTDA.COOP. GAÑANSOL</t>
+          <t>1704 - COOPERATIVA DE AHORRO Y CREDITO GAÑANSOL LTDA.COOP. GAÑANSOL</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="E336" t="inlineStr">
         <is>
-          <t>705 - COOPERATIVA DE AHORRO Y CREDITO GENESIS LTDA</t>
+          <t>1705 - COOPERATIVA DE AHORRO Y CREDITO GENESIS LTDA</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="E337" t="inlineStr">
         <is>
-          <t>706 - COOPERATIVA DE AHORRO Y CREDITO GUACHAPALA</t>
+          <t>1706 - COOPERATIVA DE AHORRO Y CREDITO GUACHAPALA</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="E338" t="inlineStr">
         <is>
-          <t>707 - COOPERATIVA DE AHORRO Y CREDITO GUARUMAL DEL CENTRO LTDA.</t>
+          <t>1707 - COOPERATIVA DE AHORRO Y CREDITO GUARUMAL DEL CENTRO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="E339" t="inlineStr">
         <is>
-          <t>708 - COOPERATIVA DE AHORRO Y CREDITO GUEL LTDA.</t>
+          <t>1708 - COOPERATIVA DE AHORRO Y CREDITO GUEL LTDA.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="E340" t="inlineStr">
         <is>
-          <t>709 - COOPERATIVA DE AHORRO Y CREDITO HUINARA LTDA.</t>
+          <t>1709 - COOPERATIVA DE AHORRO Y CREDITO HUINARA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="E341" t="inlineStr">
         <is>
-          <t>710 - COOPERATIVA DE AHORRO Y CREDITO ILINIZA LTDA.</t>
+          <t>1710 - COOPERATIVA DE AHORRO Y CREDITO ILINIZA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="E342" t="inlineStr">
         <is>
-          <t>711 - COOPERATIVA DE AHORRO Y CREDITO INDIGENA SAC PELILEO LTDA.</t>
+          <t>1711 - COOPERATIVA DE AHORRO Y CREDITO INDIGENA SAC PELILEO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="E343" t="inlineStr">
         <is>
-          <t>712 - COOPERATIVA DE AHORRO Y CREDITO INTERCULTURAL TARPUK RUNA LTDA.</t>
+          <t>1712 - COOPERATIVA DE AHORRO Y CREDITO INTERCULTURAL TARPUK RUNA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="E344" t="inlineStr">
         <is>
-          <t>713 - COOPERATIVA DE AHORRO Y CREDITO INTERCULTURAL TAWANTINSUYU LTDA.</t>
+          <t>1713 - COOPERATIVA DE AHORRO Y CREDITO INTERCULTURAL TAWANTINSUYU LTDA.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="E345" t="inlineStr">
         <is>
-          <t>714 - COOPERATIVA DE AHORRO Y CREDITO INTI WASI LTDA INTICOOP</t>
+          <t>1714 - COOPERATIVA DE AHORRO Y CREDITO INTI WASI LTDA INTICOOP</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="E346" t="inlineStr">
         <is>
-          <t>715 - COOPERATIVA DE AHORRO Y CREDITO JOYOCOTO LTDA</t>
+          <t>1715 - COOPERATIVA DE AHORRO Y CREDITO JOYOCOTO LTDA</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="E347" t="inlineStr">
         <is>
-          <t>716 - COOPERATIVA DE AHORRO Y CREDITO JUVENTUD UNIDA LTDA.</t>
+          <t>1716 - COOPERATIVA DE AHORRO Y CREDITO JUVENTUD UNIDA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="E348" t="inlineStr">
         <is>
-          <t>717 - COOPERATIVA DE AHORRO Y CREDITO MUSHUC RUNA</t>
+          <t>1717 - COOPERATIVA DE AHORRO Y CREDITO MUSHUC RUNA</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="E349" t="inlineStr">
         <is>
-          <t>718 - COOPERATIVA DE AHORRO Y CREDITO KURI WASI LTDA</t>
+          <t>1718 - COOPERATIVA DE AHORRO Y CREDITO KURI WASI LTDA</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="E350" t="inlineStr">
         <is>
-          <t>719 - COOPERATIVA DE AHORRO Y CREDITO KURIÑAN</t>
+          <t>1719 - COOPERATIVA DE AHORRO Y CREDITO KURIÑAN</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="E351" t="inlineStr">
         <is>
-          <t>720 - COOPERATIVA DE AHORRO Y CREDITO LA BENEFICA LTDA.</t>
+          <t>1720 - COOPERATIVA DE AHORRO Y CREDITO LA BENEFICA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="E352" t="inlineStr">
         <is>
-          <t>721 - COOPERATIVA DE AHORRO Y CREDITO LA FLORESTA LTDA</t>
+          <t>1721 - COOPERATIVA DE AHORRO Y CREDITO LA FLORESTA LTDA</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="E353" t="inlineStr">
         <is>
-          <t>722 - COOPERATIVA DE AHORRO Y CREDITO LA FLORIDA</t>
+          <t>1722 - COOPERATIVA DE AHORRO Y CREDITO LA FLORIDA</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="E354" t="inlineStr">
         <is>
-          <t>723 - COOPERATIVA DE AHORRO Y CREDITO LA INMACULADA DE SAN PLACIDO LTDA.</t>
+          <t>1723 - COOPERATIVA DE AHORRO Y CREDITO LA INMACULADA DE SAN PLACIDO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="E355" t="inlineStr">
         <is>
-          <t>724 - COOPERATIVA DE AHORRO Y CREDITO LA LIBERTAD LTDA</t>
+          <t>1724 - COOPERATIVA DE AHORRO Y CREDITO LA LIBERTAD LTDA</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="E356" t="inlineStr">
         <is>
-          <t>725 - COOPERATIVA DE AHORRO Y CREDITO LA UNION LTDA</t>
+          <t>1725 - COOPERATIVA DE AHORRO Y CREDITO LA UNION LTDA</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="E357" t="inlineStr">
         <is>
-          <t>726 - COOPERATIVA DE AHORRO Y CREDITO LAS LAGUNAS</t>
+          <t>1726 - COOPERATIVA DE AHORRO Y CREDITO LAS LAGUNAS</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="E358" t="inlineStr">
         <is>
-          <t>727 - COOPERATIVA DE AHORRO Y CREDITO LOS ANDES LATINOS LTDA.</t>
+          <t>1727 - COOPERATIVA DE AHORRO Y CREDITO LOS ANDES LATINOS LTDA.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="E359" t="inlineStr">
         <is>
-          <t>728 - COOPERATIVA DE AHORRO Y CREDITO LOS CHASQUIS PASTOCALLE LTDA.</t>
+          <t>1728 - COOPERATIVA DE AHORRO Y CREDITO LOS CHASQUIS PASTOCALLE LTDA.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="E360" t="inlineStr">
         <is>
-          <t>729 - COOPERATIVA DE AHORRO Y CREDITO LUZ DEL VALLE</t>
+          <t>1729 - COOPERATIVA DE AHORRO Y CREDITO LUZ DEL VALLE</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="E361" t="inlineStr">
         <is>
-          <t>730 - COOPERATIVA DE AHORRO Y CREDITO MACODES LTDA</t>
+          <t>1730 - COOPERATIVA DE AHORRO Y CREDITO MACODES LTDA</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="E362" t="inlineStr">
         <is>
-          <t>731 - COOPERATIVA DE AHORRO Y CREDITO MARIA AUXILIADORA DE QUIROGA LTDA.</t>
+          <t>1731 - COOPERATIVA DE AHORRO Y CREDITO MARIA AUXILIADORA DE QUIROGA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="E363" t="inlineStr">
         <is>
-          <t>732 - COOPERATIVA DE AHORRO Y CREDITO MICROEMPRESARIAL SUCRE</t>
+          <t>1732 - COOPERATIVA DE AHORRO Y CREDITO MICROEMPRESARIAL SUCRE</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="E364" t="inlineStr">
         <is>
-          <t>733 - COOPERATIVA DE AHORRO Y CREDITO MIGRANTES &amp; EMPRENDEDORES LTDA</t>
+          <t>1733 - COOPERATIVA DE AHORRO Y CREDITO MIGRANTES &amp; EMPRENDEDORES LTDA</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="E365" t="inlineStr">
         <is>
-          <t>734 - COOPERATIVA DE AHORRO Y CREDITO MULTICULTURAL BANCO INDIGENA LTDA.</t>
+          <t>1734 - COOPERATIVA DE AHORRO Y CREDITO MULTICULTURAL BANCO INDIGENA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="E366" t="inlineStr">
         <is>
-          <t>735 - COOPERATIVA DE AHORRO Y CREDITO MUSHUG CAUSAY LTDA</t>
+          <t>1735 - COOPERATIVA DE AHORRO Y CREDITO MUSHUG CAUSAY LTDA</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" t="inlineStr">
         <is>
-          <t>736 - COOPERATIVA DE AHORRO Y CREDITO MUSHUK PAKARI LTDA</t>
+          <t>1736 - COOPERATIVA DE AHORRO Y CREDITO MUSHUK PAKARI LTDA</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="E368" t="inlineStr">
         <is>
-          <t>737 - COOPERATIVA DE AHORRO Y CREDITO MUSHUK PAKARIK LTDA.</t>
+          <t>1737 - COOPERATIVA DE AHORRO Y CREDITO MUSHUK PAKARIK LTDA.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="E369" t="inlineStr">
         <is>
-          <t>738 - COOPERATIVA DE AHORRO Y CREDITO MUSHUK YUYAY</t>
+          <t>1738 - COOPERATIVA DE AHORRO Y CREDITO MUSHUK YUYAY</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="E370" t="inlineStr">
         <is>
-          <t>739 - COOPERATIVA DE AHORRO Y CREDITO MUSHUKWASI</t>
+          <t>1739 - COOPERATIVA DE AHORRO Y CREDITO MUSHUKWASI</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" t="inlineStr">
         <is>
-          <t>740 - COOPERATIVA DE AHORRO Y CREDITO NUEVA FUERZA ALIANZA LTDA</t>
+          <t>1740 - COOPERATIVA DE AHORRO Y CREDITO NUEVA FUERZA ALIANZA LTDA</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="E372" t="inlineStr">
         <is>
-          <t>741 - COOPERATIVA AHORRO Y CREDITO DE LA PEQUEÑA EMPRESA CACPE LOJA LTDA.</t>
+          <t>1741 - COOPERATIVA AHORRO Y CREDITO DE LA PEQUEÑA EMPRESA CACPE LOJA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="E373" t="inlineStr">
         <is>
-          <t>742 - COOPERATIVA DE AHORRO Y CREDITO ÑUKA LLAKTA LTDA</t>
+          <t>1742 - COOPERATIVA DE AHORRO Y CREDITO ÑUKA LLAKTA LTDA</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="E374" t="inlineStr">
         <is>
-          <t>743 - COOPERATIVA DE AHORRO Y CREDITO OCIPSA</t>
+          <t>1743 - COOPERATIVA DE AHORRO Y CREDITO OCIPSA</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="E375" t="inlineStr">
         <is>
-          <t>744 - COOPERATIVA DE AHORRO Y CREDITO OLMEDO LTDA.</t>
+          <t>1744 - COOPERATIVA DE AHORRO Y CREDITO OLMEDO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="E376" t="inlineStr">
         <is>
-          <t>745 - COOPERATIVA DE AHORRO Y CREDITO PADRE VICENTE PONCE RUBIO</t>
+          <t>1745 - COOPERATIVA DE AHORRO Y CREDITO PADRE VICENTE PONCE RUBIO</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="E377" t="inlineStr">
         <is>
-          <t>746 - COOPERATIVA DE AHORRO Y CREDITO POPULAR Y SOLIDARIA</t>
+          <t>1746 - COOPERATIVA DE AHORRO Y CREDITO POPULAR Y SOLIDARIA</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="E378" t="inlineStr">
         <is>
-          <t>748 - COOP. DE AHORRO Y CREDITO PRODUCCION AHORRO INVERSION SERVICIO P.A.I.S. LTDA</t>
+          <t>1748 - COOP. DE AHORRO Y CREDITO PRODUCCION AHORRO INVERSION SERVICIO P.A.I.S. LTDA</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="E379" t="inlineStr">
         <is>
-          <t>749 - COOPERATIVA DE AHORRO Y CREDITO PRODUCCION Y DESARROLLO AGRICOLA COOPRODESA LTDA</t>
+          <t>1749 - COOPERATIVA DE AHORRO Y CREDITO PRODUCCION Y DESARROLLO AGRICOLA COOPRODESA LTDA</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="E380" t="inlineStr">
         <is>
-          <t>750 - COOPERATIVA DE AHORRO Y CREDITO PROFUTURO LTDA</t>
+          <t>1750 - COOPERATIVA DE AHORRO Y CREDITO PROFUTURO LTDA</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="E381" t="inlineStr">
         <is>
-          <t>751 - COOPERATIVA DE AHORRO Y CREDITO PUJILI LTDA.</t>
+          <t>1751 - COOPERATIVA DE AHORRO Y CREDITO PUJILI LTDA.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="E382" t="inlineStr">
         <is>
-          <t>752 - COOPERATIVA DE AHORRO Y CREDITO RIOCHICO</t>
+          <t>1752 - COOPERATIVA DE AHORRO Y CREDITO RIOCHICO</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="E383" t="inlineStr">
         <is>
-          <t>753 - COOPERATIVA DE AHORRO Y CREDITO 9 DE OCTUBRE</t>
+          <t>1753 - COOPERATIVA DE AHORRO Y CREDITO 9 DE OCTUBRE</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="E384" t="inlineStr">
         <is>
-          <t>754 - COOPERATIVA DE AHORRO Y CREDITO SALASACA</t>
+          <t>1754 - COOPERATIVA DE AHORRO Y CREDITO SALASACA</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="E385" t="inlineStr">
         <is>
-          <t>755 - COOPERATIVA DE AHORRO Y CREDITO SALATE LTDA.</t>
+          <t>1755 - COOPERATIVA DE AHORRO Y CREDITO SALATE LTDA.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="E386" t="inlineStr">
         <is>
-          <t>756 - COOPERATIVA DE AHORRO Y CREDITO SALINAS LIMITADA</t>
+          <t>1756 - COOPERATIVA DE AHORRO Y CREDITO SALINAS LIMITADA</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="E387" t="inlineStr">
         <is>
-          <t>757 - COOPERATIVA DE AHORRO Y CREDITO SAN ANTONIO DE TOACASO</t>
+          <t>1757 - COOPERATIVA DE AHORRO Y CREDITO SAN ANTONIO DE TOACASO</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="E388" t="inlineStr">
         <is>
-          <t>758 - COOPERATIVA DE AHORRO Y CREDITO SAN ANTONIO LTDA.</t>
+          <t>1758 - COOPERATIVA DE AHORRO Y CREDITO SAN ANTONIO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="E389" t="inlineStr">
         <is>
-          <t>759 - COOPERATIVA DE AHORRO Y CREDITO SAN BARTOLO LTDA.</t>
+          <t>1759 - COOPERATIVA DE AHORRO Y CREDITO SAN BARTOLO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="E390" t="inlineStr">
         <is>
-          <t>760 - COOPERATIVA DE AHORRO Y CREDITO SAN BARTOLOME LTDA.</t>
+          <t>1760 - COOPERATIVA DE AHORRO Y CREDITO SAN BARTOLOME LTDA.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="E391" t="inlineStr">
         <is>
-          <t>761 - COOPERATIVA DE AHORRO Y CREDITO SAN FERNANDO LIMITADA</t>
+          <t>1761 - COOPERATIVA DE AHORRO Y CREDITO SAN FERNANDO LIMITADA</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="E392" t="inlineStr">
         <is>
-          <t>762 - COOPERATIVA DE AHORRO Y CREDITO SAN ISIDRO LTDA.</t>
+          <t>1762 - COOPERATIVA DE AHORRO Y CREDITO SAN ISIDRO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="E393" t="inlineStr">
         <is>
-          <t>763 - COOPERATIVA DE AHORRO Y CREDITO SAN JOSE - AIRO</t>
+          <t>1763 - COOPERATIVA DE AHORRO Y CREDITO SAN JOSE - AIRO</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="E394" t="inlineStr">
         <is>
-          <t>764 - COOPERATIVA DE AHORRO Y CREDITO SAN MARCOS</t>
+          <t>1764 - COOPERATIVA DE AHORRO Y CREDITO SAN MARCOS</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="E395" t="inlineStr">
         <is>
-          <t>765 - COOPERATIVA DE AHORRO Y CREDITO SAN MARTIN DE TISALEO LTDA</t>
+          <t>1765 - COOPERATIVA DE AHORRO Y CREDITO SAN MARTIN DE TISALEO LTDA</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="E396" t="inlineStr">
         <is>
-          <t>766 - COOPERATIVA DE AHORRO Y CREDITO SAN MIGUEL DE PALLATANGA</t>
+          <t>1766 - COOPERATIVA DE AHORRO Y CREDITO SAN MIGUEL DE PALLATANGA</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="E397" t="inlineStr">
         <is>
-          <t>767 - COOPERATIVA DE AHORRO Y CREDITO SAN PEDRO DE PELILEO LTDA.</t>
+          <t>1767 - COOPERATIVA DE AHORRO Y CREDITO SAN PEDRO DE PELILEO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="E398" t="inlineStr">
         <is>
-          <t>768 - COOPERATIVA DE AHORRO Y CREDITO SAN PEDRO LTDA.</t>
+          <t>1768 - COOPERATIVA DE AHORRO Y CREDITO SAN PEDRO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="E399" t="inlineStr">
         <is>
-          <t>769 - COOPERATIVA DE AHORRO Y CREDITO SAN SANTIAGO DE MOLLETURO</t>
+          <t>1769 - COOPERATIVA DE AHORRO Y CREDITO SAN SANTIAGO DE MOLLETURO</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="E400" t="inlineStr">
         <is>
-          <t>770 - COOPERATIVA DE AHORRO Y CREDITO SAN SEBASTIAN - LOJA</t>
+          <t>1770 - COOPERATIVA DE AHORRO Y CREDITO SAN SEBASTIAN - LOJA</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="E401" t="inlineStr">
         <is>
-          <t>771 - COOPERATIVA DE AHORRO Y CREDITO SANTA ISABEL LTDA</t>
+          <t>1771 - COOPERATIVA DE AHORRO Y CREDITO SANTA ISABEL LTDA</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="E402" t="inlineStr">
         <is>
-          <t>772 - COOPERATIVA DE AHORRO Y CREDITO SARAGUROS</t>
+          <t>1772 - COOPERATIVA DE AHORRO Y CREDITO SARAGUROS</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="E403" t="inlineStr">
         <is>
-          <t>773 - COOPERATIVA DE AHORRO Y CREDITO SERVIDORES MUNICIPALES DE CUENCA</t>
+          <t>1773 - COOPERATIVA DE AHORRO Y CREDITO SERVIDORES MUNICIPALES DE CUENCA</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="E404" t="inlineStr">
         <is>
-          <t>774 - COOPERATIVA DE AHORRO Y CREDITO SIMON BOLIVAR</t>
+          <t>1774 - COOPERATIVA DE AHORRO Y CREDITO SIMON BOLIVAR</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="E405" t="inlineStr">
         <is>
-          <t>775 - COOPERATIVA DE AHORRO Y CREDITO SOCIO AMIGO COOPSA</t>
+          <t>1775 - COOPERATIVA DE AHORRO Y CREDITO SOCIO AMIGO COOPSA</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="E406" t="inlineStr">
         <is>
-          <t>776 - COOPERATIVA DE AHORRO Y CREDITO SOL DE LOS ANDES LTDA</t>
+          <t>1776 - COOPERATIVA DE AHORRO Y CREDITO SOL DE LOS ANDES LTDA</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="E407" t="inlineStr">
         <is>
-          <t>777 - COOPERATIVA DE AHORRO Y CREDITO SOLIDARIA LTDA</t>
+          <t>1777 - COOPERATIVA DE AHORRO Y CREDITO SOLIDARIA LTDA</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="E408" t="inlineStr">
         <is>
-          <t>778 - COOPERATIVA DE AHORRO Y CREDITO SOLIDARIA LTDA. GUALAQUIZA</t>
+          <t>1778 - COOPERATIVA DE AHORRO Y CREDITO SOLIDARIA LTDA. GUALAQUIZA</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="E409" t="inlineStr">
         <is>
-          <t>779 - COOPERATIVA DE AHORRO Y CREDITO SOLIDARIDAD Y PROGRESO ORIENTAL</t>
+          <t>1779 - COOPERATIVA DE AHORRO Y CREDITO SOLIDARIDAD Y PROGRESO ORIENTAL</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="E410" t="inlineStr">
         <is>
-          <t>780 - COOPERATIVA DE AHORRO Y CREDITO SUMAK SAMY LTDA.</t>
+          <t>1780 - COOPERATIVA DE AHORRO Y CREDITO SUMAK SAMY LTDA.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="E411" t="inlineStr">
         <is>
-          <t>781 - COOPERATIVA DE AHORRO Y CREDITO UNIBLOCK Y SERVICIOS LTDA.</t>
+          <t>1781 - COOPERATIVA DE AHORRO Y CREDITO UNIBLOCK Y SERVICIOS LTDA.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="E412" t="inlineStr">
         <is>
-          <t>782 - COOPERATIVA DE AHORRO Y CREDITO UNIOTAVALO LTDA</t>
+          <t>1782 - COOPERATIVA DE AHORRO Y CREDITO UNIOTAVALO LTDA</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="E413" t="inlineStr">
         <is>
-          <t>783 - COOPERATIVA DE AHORRO Y CREDITO WARMIKUNAPAK RIKCHARI LTDA.</t>
+          <t>1783 - COOPERATIVA DE AHORRO Y CREDITO WARMIKUNAPAK RIKCHARI LTDA.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="E414" t="inlineStr">
         <is>
-          <t>784 - COOPERATIVA DE AHORRO Y CREDITO WUAMANLOMA LTDA.</t>
+          <t>1784 - COOPERATIVA DE AHORRO Y CREDITO WUAMANLOMA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="E415" t="inlineStr">
         <is>
-          <t>785 - COOPERATIVA DE SERVICIOS MULTIPLES AGRO VIDA COOSEMAV</t>
+          <t>1785 - COOPERATIVA DE SERVICIOS MULTIPLES AGRO VIDA COOSEMAV</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="E416" t="inlineStr">
         <is>
-          <t>786 - COOPERTATIVA DE AHORRO Y CREDITO UNION QUISAPINCHA LTDA.</t>
+          <t>1786 - COOPERTATIVA DE AHORRO Y CREDITO UNION QUISAPINCHA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="E417" t="inlineStr">
         <is>
-          <t>787 - COOPJADAN LTDA, COOPERATIVA DE AHORRO Y CREDITO JADAN</t>
+          <t>1787 - COOPJADAN LTDA, COOPERATIVA DE AHORRO Y CREDITO JADAN</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="E418" t="inlineStr">
         <is>
-          <t>788 - COOPERATIVA DE AHORRO Y CREDITO CACPE MANABI</t>
+          <t>1788 - COOPERATIVA DE AHORRO Y CREDITO CACPE MANABI</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="E419" t="inlineStr">
         <is>
-          <t>789 - COOPERATIVA DE AHORRO Y CREDITO CRECER WIÑARI LTDA.</t>
+          <t>1789 - COOPERATIVA DE AHORRO Y CREDITO CRECER WIÑARI LTDA.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="E420" t="inlineStr">
         <is>
-          <t>790 - COOP. AHORRO Y CREDITO DEL SINDICATO DE CHOFERES PROFESIONALES DEL AZUAY LTDA.</t>
+          <t>1790 - COOP. AHORRO Y CREDITO DEL SINDICATO DE CHOFERES PROFESIONALES DEL AZUAY LTDA.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="E421" t="inlineStr">
         <is>
-          <t>791 - COOPERATIVA DE AHORRO Y CREDITO EMPRENDEDORES 'COOPEMPRENDER' LIMITADA</t>
+          <t>1791 - COOPERATIVA DE AHORRO Y CREDITO EMPRENDEDORES 'COOPEMPRENDER' LIMITADA</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="E422" t="inlineStr">
         <is>
-          <t>792 - COOPERATIVA DE AHORRO Y CREDITO NUEVA LOJA LTDA.</t>
+          <t>1792 - COOPERATIVA DE AHORRO Y CREDITO NUEVA LOJA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="E423" t="inlineStr">
         <is>
-          <t>793 - COOPERATIVA DE AHORRO Y CREDITO SAN JUAN DE COTOGCHOA</t>
+          <t>1793 - COOPERATIVA DE AHORRO Y CREDITO SAN JUAN DE COTOGCHOA</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="E424" t="inlineStr">
         <is>
-          <t>802 - COOPERATIVA DE AHORRO Y CREDITO MAS AHORRO SOLIDARIO MASCOOP</t>
+          <t>1802 - COOPERATIVA DE AHORRO Y CREDITO MAS AHORRO SOLIDARIO MASCOOP</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="E425" t="inlineStr">
         <is>
-          <t>815 - COOPERATIVA DE AHORRO Y CREDITO TIENDA DE DINERO LTDA.</t>
+          <t>1815 - COOPERATIVA DE AHORRO Y CREDITO TIENDA DE DINERO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="E426" t="inlineStr">
         <is>
-          <t>816 - COOPERATIVA DE AHORRO Y CREDITO VILCABAMBA CACVIL</t>
+          <t>1816 - COOPERATIVA DE AHORRO Y CREDITO VILCABAMBA CACVIL</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="E427" t="inlineStr">
         <is>
-          <t>869 - AUSTROBANK OVERSEAS PANAMA S.A</t>
+          <t>1869 - AUSTROBANK OVERSEAS PANAMA S.A</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="E428" t="inlineStr">
         <is>
-          <t>900 - EXTERNALIZACIÓN DE SERVICIOS S.A. EXSERSA</t>
+          <t>1900 - EXTERNALIZACIÓN DE SERVICIOS S.A. EXSERSA</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="E429" t="inlineStr">
         <is>
-          <t>901 - BANCO DEL INSTITUTO ECUATORIANO DE SEGURIDAD SOCIAL</t>
+          <t>1901 - BANCO DEL INSTITUTO ECUATORIANO DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="E430" t="inlineStr">
         <is>
-          <t>903 - COOPERATIVA DE AHORRO Y CREDITO 23 DE MAYO LTDA.</t>
+          <t>1903 - COOPERATIVA DE AHORRO Y CREDITO 23 DE MAYO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="E431" t="inlineStr">
         <is>
-          <t>904 - COOPERATIVA DE AHORRO Y CRÉDITO COCA LTDA</t>
+          <t>1904 - COOPERATIVA DE AHORRO Y CRÉDITO COCA LTDA</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="E432" t="inlineStr">
         <is>
-          <t>905 - COOPERATIVA  DE AHORRO Y CRÉDITO PILAHUIN TIO LTDA</t>
+          <t>1905 - COOPERATIVA  DE AHORRO Y CRÉDITO PILAHUIN TIO LTDA</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="E433" t="inlineStr">
         <is>
-          <t>906 - COOPERATIVA  DE AHORRO Y CRÉDITO HUAICANA LTDA</t>
+          <t>1906 - COOPERATIVA  DE AHORRO Y CRÉDITO HUAICANA LTDA</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="E434" t="inlineStr">
         <is>
-          <t>907 - COOPERATIVA DE AHORRO Y CREDITO  CREDISUR LTDA.</t>
+          <t>1907 - COOPERATIVA DE AHORRO Y CREDITO  CREDISUR LTDA.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="E435" t="inlineStr">
         <is>
-          <t>908 - COOPERATIVA DE AHORRO Y CREDITO  MAQUITA CUSHUNCHIC LTDA.</t>
+          <t>1908 - COOPERATIVA DE AHORRO Y CREDITO  MAQUITA CUSHUNCHIC LTDA.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="E436" t="inlineStr">
         <is>
-          <t>909 - COOPERATIVA DE AHORRO Y CREDITO  GENERAL RUMIÑAHUI</t>
+          <t>1909 - COOPERATIVA DE AHORRO Y CREDITO  GENERAL RUMIÑAHUI</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="E437" t="inlineStr">
         <is>
-          <t>910 - COOPERATIVA DE AHORRO Y CREDITO  CASAG LTDA</t>
+          <t>1910 - COOPERATIVA DE AHORRO Y CREDITO  CASAG LTDA</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="E438" t="inlineStr">
         <is>
-          <t>911 - COOPERATIVA DE AHORRO Y CREDITO  FOCLA</t>
+          <t>1911 - COOPERATIVA DE AHORRO Y CREDITO  FOCLA</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="E439" t="inlineStr">
         <is>
-          <t>912 - COOPERATIVA DE AHORRO Y CREDITO  FINANCIERA INDIGENA LTDA.</t>
+          <t>1912 - COOPERATIVA DE AHORRO Y CREDITO  FINANCIERA INDIGENA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="E440" t="inlineStr">
         <is>
-          <t>913 - SOCIEDAD FINANCIERA VISIONFUND ECUADOR S.A.</t>
+          <t>1913 - SOCIEDAD FINANCIERA VISIONFUND ECUADOR S.A.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="E441" t="inlineStr">
         <is>
-          <t>915 - BANCO-D-MIRO S.A.</t>
+          <t>1915 - BANCO-D-MIRO S.A.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="E442" t="inlineStr">
         <is>
-          <t>916 - COOPERATIVA  DE AHORRO Y CREDITO HUAQUILLAS LTDA.</t>
+          <t>1916 - COOPERATIVA  DE AHORRO Y CREDITO HUAQUILLAS LTDA.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="E443" t="inlineStr">
         <is>
-          <t>917 - COOPERATIVA DE AHORRO Y CREDITO  DEL COL. FISC. EXPER. VICENTE ROCAFUERTE</t>
+          <t>1917 - COOPERATIVA DE AHORRO Y CREDITO  DEL COL. FISC. EXPER. VICENTE ROCAFUERTE</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="E444" t="inlineStr">
         <is>
-          <t>918 - BANCO PARA LA ASISTENCIA COMUNITARIA FINCA S.A.</t>
+          <t>1918 - BANCO PARA LA ASISTENCIA COMUNITARIA FINCA S.A.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="E445" t="inlineStr">
         <is>
-          <t>920 - COOPERATIVA DE AHORRO Y CREDITO  ECUAFUTURO LTDA.</t>
+          <t>1920 - COOPERATIVA DE AHORRO Y CREDITO  ECUAFUTURO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="E446" t="inlineStr">
         <is>
-          <t>921 - COOPERATIVA DE AHORRO Y CREDITO  MAQUITA CUSHUN LTDA.</t>
+          <t>1921 - COOPERATIVA DE AHORRO Y CREDITO  MAQUITA CUSHUN LTDA.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="E447" t="inlineStr">
         <is>
-          <t>922 - COOPERATIVA DE AHORRO Y CREDITO  VALLES DEL LIRIO</t>
+          <t>1922 - COOPERATIVA DE AHORRO Y CREDITO  VALLES DEL LIRIO</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="E448" t="inlineStr">
         <is>
-          <t>923 - COOPERATIVA  ESFUERZO UNIDO PARA EL DESARR. DEL CHILCO LA ESPERANZA</t>
+          <t>1923 - COOPERATIVA  ESFUERZO UNIDO PARA EL DESARR. DEL CHILCO LA ESPERANZA</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="E449" t="inlineStr">
         <is>
-          <t>924 - COOPERATIVA  A. Y C. CARROCEROS DE TUNGURAHUA</t>
+          <t>1924 - COOPERATIVA  A. Y C. CARROCEROS DE TUNGURAHUA</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="E450" t="inlineStr">
         <is>
-          <t>925 - COOPERATIVA DE AHORRO Y CREDITO  INKA KIPU LTDA.</t>
+          <t>1925 - COOPERATIVA DE AHORRO Y CREDITO  INKA KIPU LTDA.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="E451" t="inlineStr">
         <is>
-          <t>926 - COOPERATIVA  DE AHORRO Y CRÉDITO 'SIMIATUG LTDA'</t>
+          <t>1926 - COOPERATIVA  DE AHORRO Y CRÉDITO 'SIMIATUG LTDA'</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="E452" t="inlineStr">
         <is>
-          <t>928 - COOPERATIVA DE AHORRO Y CREDITO  PIJAL</t>
+          <t>1928 - COOPERATIVA DE AHORRO Y CREDITO  PIJAL</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="E453" t="inlineStr">
         <is>
-          <t>929 - COOPERATIVA DE AHORRO Y CREDITO  ESCENCIA INDIGENA LTDA.</t>
+          <t>1929 - COOPERATIVA DE AHORRO Y CREDITO  ESCENCIA INDIGENA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="E454" t="inlineStr">
         <is>
-          <t>930 - COOPERATIVA DE AHORRO Y CREDITO  SANTA ROSA DE PATUTAN LTDA.</t>
+          <t>1930 - COOPERATIVA DE AHORRO Y CREDITO  SANTA ROSA DE PATUTAN LTDA.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="E455" t="inlineStr">
         <is>
-          <t>931 - COOPERATIVA  DE AHORRO Y CREDITO SAN MIGUEL DE SIGCHOS</t>
+          <t>1931 - COOPERATIVA  DE AHORRO Y CREDITO SAN MIGUEL DE SIGCHOS</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="E456" t="inlineStr">
         <is>
-          <t>932 - COOPERATIVA DE AHORRO Y CREDITO  SIERRA CENTRO LTDA.</t>
+          <t>1932 - COOPERATIVA DE AHORRO Y CREDITO  SIERRA CENTRO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="E457" t="inlineStr">
         <is>
-          <t>933 - COOPERATIVA DE AHORRO Y CREDITO  UNION MERCEDARIA LTDA.</t>
+          <t>1933 - COOPERATIVA DE AHORRO Y CREDITO  UNION MERCEDARIA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="E458" t="inlineStr">
         <is>
-          <t>935 - COOPERATIVA  DE AHORRO Y CREDITO CREDIAMIGO LTDA. LOJA (MIES)</t>
+          <t>1935 - COOPERATIVA  DE AHORRO Y CREDITO CREDIAMIGO LTDA. LOJA (MIES)</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="E459" t="inlineStr">
         <is>
-          <t>936 - COOPERATIVA DE AHORRO Y CREDITO FORTUNA (MIES)</t>
+          <t>1936 - COOPERATIVA DE AHORRO Y CREDITO FORTUNA (MIES)</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="E460" t="inlineStr">
         <is>
-          <t>937 - COOPERATIVA DE AHORRO Y CREDITO DE LOS PROFESIONALES DEL VOLANTE UNION LTDA</t>
+          <t>1937 - COOPERATIVA DE AHORRO Y CREDITO DE LOS PROFESIONALES DEL VOLANTE UNION LTDA</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="E461" t="inlineStr">
         <is>
-          <t>938 - COOPERATIVA DE AHORRO Y CREDITO CACPE CELICA</t>
+          <t>1938 - COOPERATIVA DE AHORRO Y CREDITO CACPE CELICA</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="E462" t="inlineStr">
         <is>
-          <t>939 - COOPERATIVA DE AHORRO Y CREDITO CATAMAYO LTDA. (MIES)</t>
+          <t>1939 - COOPERATIVA DE AHORRO Y CREDITO CATAMAYO LTDA. (MIES)</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="E463" t="inlineStr">
         <is>
-          <t>940 - COOPERATIVA DE AHORRO Y CREDITO  DE LA PEQ. EMPRESA CACPE MACARÁ</t>
+          <t>1940 - COOPERATIVA DE AHORRO Y CREDITO  DE LA PEQ. EMPRESA CACPE MACARÁ</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="E464" t="inlineStr">
         <is>
-          <t>941 - COOPERATIVA  AHO.Y CRED.NUEVOS HORIZONTES EL ORO LTDA.</t>
+          <t>1941 - COOPERATIVA  AHO.Y CRED.NUEVOS HORIZONTES EL ORO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="E465" t="inlineStr">
         <is>
-          <t>942 - COOPERATIVA DE AHORRO Y CREDITO  16 DE JUNIO</t>
+          <t>1942 - COOPERATIVA DE AHORRO Y CREDITO  16 DE JUNIO</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="E466" t="inlineStr">
         <is>
-          <t>943 - COOPERATIVA DE AHORRO Y CREDITO  FUTURO Y PROGRESO DE GALAPAGOS LTDA.</t>
+          <t>1943 - COOPERATIVA DE AHORRO Y CREDITO  FUTURO Y PROGRESO DE GALAPAGOS LTDA.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="E467" t="inlineStr">
         <is>
-          <t>944 - COOPERATIVA DE AHORRO Y CREDITO  LUCHA CAMPESINA LTDA.</t>
+          <t>1944 - COOPERATIVA DE AHORRO Y CREDITO  LUCHA CAMPESINA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="E468" t="inlineStr">
         <is>
-          <t>945 - COOPERATIVA DE AHORRO Y CREDITO  GUAMOTE LTDA.</t>
+          <t>1945 - COOPERATIVA DE AHORRO Y CREDITO  GUAMOTE LTDA.</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="E469" t="inlineStr">
         <is>
-          <t>946 - COOPERATIVA DE AHORRO Y CREDITO  EDUCADORES TULCAN LTDA.</t>
+          <t>1946 - COOPERATIVA DE AHORRO Y CREDITO  EDUCADORES TULCAN LTDA.</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="E470" t="inlineStr">
         <is>
-          <t>947 - COOPERATIVA DE AHORRO Y CREDITO COOPAC AUSTRO LTDA</t>
+          <t>1947 - COOPERATIVA DE AHORRO Y CREDITO COOPAC AUSTRO LTDA</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="E471" t="inlineStr">
         <is>
-          <t>948 - COOPERATIVA DE AHORRO Y CREDITO INDIGENA ALFA Y OMEGA LTDA</t>
+          <t>1948 - COOPERATIVA DE AHORRO Y CREDITO INDIGENA ALFA Y OMEGA LTDA</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="E472" t="inlineStr">
         <is>
-          <t>949 - COOPERATIVA DE AHORRO Y CREDITO CHIBULEO</t>
+          <t>1949 - COOPERATIVA DE AHORRO Y CREDITO CHIBULEO</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="E473" t="inlineStr">
         <is>
-          <t>950 - COOPERATIVA DE AHORRO Y CREDITO KISAPINCHA LTDA.</t>
+          <t>1950 - COOPERATIVA DE AHORRO Y CREDITO KISAPINCHA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="E474" t="inlineStr">
         <is>
-          <t>951 - COOPERATIVA DE AHORRO Y CREDITO VIRGEN DEL CISNE</t>
+          <t>1951 - COOPERATIVA DE AHORRO Y CREDITO VIRGEN DEL CISNE</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="E475" t="inlineStr">
         <is>
-          <t>952 - COOPERATIVA AHORRO Y CREDITO 26 DE SEPTIEMBRE LAZARO CONDO</t>
+          <t>1952 - COOPERATIVA AHORRO Y CREDITO 26 DE SEPTIEMBRE LAZARO CONDO</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="E476" t="inlineStr">
         <is>
-          <t>953 - COOPERATIVA AHORRO Y CREDITO AFRO ECUATORIANA DE LA PEQUEÑA EMPRESA LTDA CACAEPE</t>
+          <t>1953 - COOPERATIVA AHORRO Y CREDITO AFRO ECUATORIANA DE LA PEQUEÑA EMPRESA LTDA CACAEPE</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="E477" t="inlineStr">
         <is>
-          <t>954 - COOPERATIVA AHORRO Y CREDITO UNION EL EJIDO</t>
+          <t>1954 - COOPERATIVA AHORRO Y CREDITO UNION EL EJIDO</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="E478" t="inlineStr">
         <is>
-          <t>955 - COOPERATIVA DE AHORRO Y CREDITO 13 DE ABRIL</t>
+          <t>1955 - COOPERATIVA DE AHORRO Y CREDITO 13 DE ABRIL</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="E479" t="inlineStr">
         <is>
-          <t>956 - COOPERATIVA DE AHORRO Y CREDITO 15 DE DICIEMBRE LINDERO LTDA</t>
+          <t>1956 - COOPERATIVA DE AHORRO Y CREDITO 15 DE DICIEMBRE LINDERO LTDA</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="E480" t="inlineStr">
         <is>
-          <t>957 - COOPERATIVA DE AHORRO Y CREDITO 15 DE MAYO LTDA</t>
+          <t>1957 - COOPERATIVA DE AHORRO Y CREDITO 15 DE MAYO LTDA</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="E481" t="inlineStr">
         <is>
-          <t>958 - COOPERATIVA DE AHORRO Y CREDITO 20 DE FEBRERO LTDA.</t>
+          <t>1958 - COOPERATIVA DE AHORRO Y CREDITO 20 DE FEBRERO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="E482" t="inlineStr">
         <is>
-          <t>959 - COOPERATIVA DE AHORRO Y CREDITO 21 DE NOVIEMBRE LTDA.</t>
+          <t>1959 - COOPERATIVA DE AHORRO Y CREDITO 21 DE NOVIEMBRE LTDA.</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="E483" t="inlineStr">
         <is>
-          <t>960 - COOPERATIVA DE AHORRO Y CREDITO 22 DE JUNIO</t>
+          <t>1960 - COOPERATIVA DE AHORRO Y CREDITO 22 DE JUNIO</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="E484" t="inlineStr">
         <is>
-          <t>962 - COOPERATIVA DE AHORRO Y CREDITO 27 DE ABRIL</t>
+          <t>1962 - COOPERATIVA DE AHORRO Y CREDITO 27 DE ABRIL</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="E485" t="inlineStr">
         <is>
-          <t>963 - COOPERATIVA DE AHORRO Y CREDITO 4 DE OCTUBRE SAN FRANCISCO DE CHAMBO</t>
+          <t>1963 - COOPERATIVA DE AHORRO Y CREDITO 4 DE OCTUBRE SAN FRANCISCO DE CHAMBO</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="E486" t="inlineStr">
         <is>
-          <t>964 - COOPERATIVA DE AHORRO Y CREDITO ABDON CALDERON LTDA.</t>
+          <t>1964 - COOPERATIVA DE AHORRO Y CREDITO ABDON CALDERON LTDA.</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="E487" t="inlineStr">
         <is>
-          <t>965 - COOPERATIVA DE AHORRO Y CREDITO ACCION TUNGURAHUA LTDA.</t>
+          <t>1965 - COOPERATIVA DE AHORRO Y CREDITO ACCION TUNGURAHUA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="E488" t="inlineStr">
         <is>
-          <t>966 - COOPERATIVA DE AHORRO Y CREDITO AGRO PRODUCTIVA MANABI LTDA.</t>
+          <t>1966 - COOPERATIVA DE AHORRO Y CREDITO AGRO PRODUCTIVA MANABI LTDA.</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="E489" t="inlineStr">
         <is>
-          <t>967 - COOPERATIVA DE AHORRO Y CREDITO AGUILAS DE CRISTO</t>
+          <t>1967 - COOPERATIVA DE AHORRO Y CREDITO AGUILAS DE CRISTO</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="E490" t="inlineStr">
         <is>
-          <t>968 - COOPERATIVA DE AHORRO Y CREDITO ALLI TARPUC</t>
+          <t>1968 - COOPERATIVA DE AHORRO Y CREDITO ALLI TARPUC</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="E491" t="inlineStr">
         <is>
-          <t>969 - COOPERATIVA DE AHORRO Y CREDITO BASHALAN LTDA</t>
+          <t>1969 - COOPERATIVA DE AHORRO Y CREDITO BASHALAN LTDA</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="E492" t="inlineStr">
         <is>
-          <t>970 - COOPERATIVA DE AHORRO Y CREDITO BUENA FE LTDA.</t>
+          <t>1970 - COOPERATIVA DE AHORRO Y CREDITO BUENA FE LTDA.</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="E493" t="inlineStr">
         <is>
-          <t>971 - COOPERATIVA DE AHORRO Y CREDITO CACIQUE GURITAVE</t>
+          <t>1971 - COOPERATIVA DE AHORRO Y CREDITO CACIQUE GURITAVE</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="E494" t="inlineStr">
         <is>
-          <t>972 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO DE RIOBAMBA LTDA</t>
+          <t>1972 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO DE RIOBAMBA LTDA</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="E495" t="inlineStr">
         <is>
-          <t>973 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO DE SANTO DOMINGO</t>
+          <t>1973 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO DE SANTO DOMINGO</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="E496" t="inlineStr">
         <is>
-          <t>974 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO DEL CANTON EL CARMEN LTDA.</t>
+          <t>1974 - COOPERATIVA DE AHORRO Y CREDITO CAMARA DE COMERCIO DEL CANTON EL CARMEN LTDA.</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="E497" t="inlineStr">
         <is>
-          <t>975 - COOPERATIVA DE AHORRO Y CREDITO CAÑAR LTDA.</t>
+          <t>1975 - COOPERATIVA DE AHORRO Y CREDITO CAÑAR LTDA.</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="E498" t="inlineStr">
         <is>
-          <t>976 - COOPERATIVA DE AHORRO Y CREDITO CHOCO TUNGURAHUA RUNA LTDA.</t>
+          <t>1976 - COOPERATIVA DE AHORRO Y CREDITO CHOCO TUNGURAHUA RUNA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="E499" t="inlineStr">
         <is>
-          <t>977 - COOPERATIVA DE AHORRO Y CREDITO COLEGIO DE INGENIEROS CIVILES DEL AZUAY C.I.C.A.</t>
+          <t>1977 - COOPERATIVA DE AHORRO Y CREDITO COLEGIO DE INGENIEROS CIVILES DEL AZUAY C.I.C.A.</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="E500" t="inlineStr">
         <is>
-          <t>978 - COOPERATIVA DE AHORRO Y CREDITO COOPARTAMOS LTDA.</t>
+          <t>1978 - COOPERATIVA DE AHORRO Y CREDITO COOPARTAMOS LTDA.</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="E501" t="inlineStr">
         <is>
-          <t>979 - COOPERATIVA DE AHORRO Y CREDITO COOPINDIGENA LTDA.</t>
+          <t>1979 - COOPERATIVA DE AHORRO Y CREDITO COOPINDIGENA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="E502" t="inlineStr">
         <is>
-          <t>980 - COOPERATIVA DE AHORRO Y CREDITO COOPTOPAXI LTDA.</t>
+          <t>1980 - COOPERATIVA DE AHORRO Y CREDITO COOPTOPAXI LTDA.</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="E503" t="inlineStr">
         <is>
-          <t>981 - COOPERATIVA DE AHORRO Y CREDITO CORDILLERA DE LOS ANDES LTDA.</t>
+          <t>1981 - COOPERATIVA DE AHORRO Y CREDITO CORDILLERA DE LOS ANDES LTDA.</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="E504" t="inlineStr">
         <is>
-          <t>982 - COOPERATIVA DE AHORRO Y CREDITO CORPORACION CENTRO LTDA.</t>
+          <t>1982 - COOPERATIVA DE AHORRO Y CREDITO CORPORACION CENTRO LTDA.</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="E505" t="inlineStr">
         <is>
-          <t>983 - COOPERATIVA DE AHORRO Y CREDITO CREA LTDA.</t>
+          <t>1983 - COOPERATIVA DE AHORRO Y CREDITO CREA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="E506" t="inlineStr">
         <is>
-          <t>984 - COOPERATIVA DE AHORRO Y CREDITO CREDI UNION LTDA</t>
+          <t>1984 - COOPERATIVA DE AHORRO Y CREDITO CREDI UNION LTDA</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="E507" t="inlineStr">
         <is>
-          <t>985 - COOPERATIVA DE AHORRO Y CREDITO CREDIL LTDA.</t>
+          <t>1985 - COOPERATIVA DE AHORRO Y CREDITO CREDIL LTDA.</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="E508" t="inlineStr">
         <is>
-          <t>986 - COOPERATIVA DE AHORRO Y CREDITO CUNA DE LA NACIONALIDAD LTDA.</t>
+          <t>1986 - COOPERATIVA DE AHORRO Y CREDITO CUNA DE LA NACIONALIDAD LTDA.</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="E509" t="inlineStr">
         <is>
-          <t>987 - COOPERATIVA DE AHORRO Y CREDITO DE LA CAMARA DE COMERCIO DE GONZANAMA</t>
+          <t>1987 - COOPERATIVA DE AHORRO Y CREDITO DE LA CAMARA DE COMERCIO DE GONZANAMA</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="E510" t="inlineStr">
         <is>
-          <t>990 - COOPERATIVA DE AHORRO Y CREDITO DE LA MICROEMPRESA DE CHIMBORAZO LTDA</t>
+          <t>1990 - COOPERATIVA DE AHORRO Y CREDITO DE LA MICROEMPRESA DE CHIMBORAZO LTDA</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="E511" t="inlineStr">
         <is>
-          <t>991 - COOP DE AHORRO Y CREDITO DE LA PEQUEÑA Y MEDIANA EMPRESA COOPYMEC-MACARA</t>
+          <t>1991 - COOP DE AHORRO Y CREDITO DE LA PEQUEÑA Y MEDIANA EMPRESA COOPYMEC-MACARA</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="E512" t="inlineStr">
         <is>
-          <t>992 - COOPERATIVA DE AHORRO Y CREDITO DE VIVIENDA Y DESARROLLO CASA FACIL LTDA</t>
+          <t>1992 - COOPERATIVA DE AHORRO Y CREDITO DE VIVIENDA Y DESARROLLO CASA FACIL LTDA</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="E513" t="inlineStr">
         <is>
-          <t>993 - COOPERATIVA DE AHORRO Y CREDITO DEL AZUAY</t>
+          <t>1993 - COOPERATIVA DE AHORRO Y CREDITO DEL AZUAY</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="E514" t="inlineStr">
         <is>
-          <t>994 - COOPERATIVA DE AHORRO Y CREDITO DEL EMIGRANTE ECUATORIANO Y SU FAMILIA LTDA.</t>
+          <t>1994 - COOPERATIVA DE AHORRO Y CREDITO DEL EMIGRANTE ECUATORIANO Y SU FAMILIA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="E515" t="inlineStr">
         <is>
-          <t>995 - COOPERATIVA DE AHORRO Y CREDITO SAN PEDRO DE TABOADA LTDA.</t>
+          <t>1995 - COOPERATIVA DE AHORRO Y CREDITO SAN PEDRO DE TABOADA LTDA.</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="E516" t="inlineStr">
         <is>
-          <t>996 - COOPERATIVA DE AHORRO Y CREDITO DESARROLLO POPULAR LTDA.</t>
+          <t>1996 - COOPERATIVA DE AHORRO Y CREDITO DESARROLLO POPULAR LTDA.</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="E517" t="inlineStr">
         <is>
-          <t>997 - COOPERATIVA DE AHORRO Y CREDITO ECONOMIA DEL SUR ECOSUR</t>
+          <t>1997 - COOPERATIVA DE AHORRO Y CREDITO ECONOMIA DEL SUR ECOSUR</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="E518" t="inlineStr">
         <is>
-          <t>998 - COOPERATIVA DE AHORRO Y CREDITO EDUCADORES DE EL ORO LTDA</t>
+          <t>1998 - COOPERATIVA DE AHORRO Y CREDITO EDUCADORES DE EL ORO LTDA</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="E519" t="inlineStr">
         <is>
-          <t>999 - COOPERATIVA DE AHORRO Y CREDITO EDUCADORES DE ZAMORA CHINCHIPE LTDA.</t>
+          <t>1999 - COOPERATIVA DE AHORRO Y CREDITO EDUCADORES DE ZAMORA CHINCHIPE LTDA.</t>
         </is>
       </c>
     </row>
@@ -9398,20 +9423,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -9469,20 +9496,30 @@
       </c>
       <c r="H5" s="25" t="inlineStr">
         <is>
+          <t>Regularizacion activos</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t>Anio fiscal adquisicion</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="inlineStr">
+        <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
@@ -9509,7 +9546,11 @@
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr"/>
+      <c r="E6" s="59" t="inlineStr">
+        <is>
+          <t>1029 - BANCO PICHINCHA C.A.</t>
+        </is>
+      </c>
       <c r="F6" s="59" t="inlineStr">
         <is>
           <t>DOLARES</t>
@@ -9520,18 +9561,20 @@
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H6" s="60" t="n">
+      <c r="H6" s="59" t="inlineStr"/>
+      <c r="I6" s="59" t="inlineStr"/>
+      <c r="J6" s="60" t="n">
         <v>130.2</v>
       </c>
-      <c r="I6" s="61" t="n">
+      <c r="K6" s="61" t="n">
         <v>130.2</v>
       </c>
-      <c r="J6" s="60">
-        <f>I6-H6</f>
-        <v/>
-      </c>
-      <c r="K6" s="62">
-        <f>IF(H6=0,"",(I6-H6)/H6)</f>
+      <c r="L6" s="60">
+        <f>K6-J6</f>
+        <v/>
+      </c>
+      <c r="M6" s="62">
+        <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
@@ -9556,7 +9599,11 @@
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E7" s="63" t="inlineStr"/>
+      <c r="E7" s="63" t="inlineStr">
+        <is>
+          <t>1029 - BANCO PICHINCHA C.A.</t>
+        </is>
+      </c>
       <c r="F7" s="63" t="inlineStr">
         <is>
           <t>DOLARES</t>
@@ -9567,18 +9614,20 @@
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H7" s="64" t="n">
+      <c r="H7" s="63" t="inlineStr"/>
+      <c r="I7" s="63" t="inlineStr"/>
+      <c r="J7" s="64" t="n">
         <v>5590.32</v>
       </c>
-      <c r="I7" s="61" t="n">
+      <c r="K7" s="61" t="n">
         <v>5590.32</v>
       </c>
-      <c r="J7" s="64">
-        <f>I7-H7</f>
-        <v/>
-      </c>
-      <c r="K7" s="65">
-        <f>IF(H7=0,"",(I7-H7)/H7)</f>
+      <c r="L7" s="64">
+        <f>K7-J7</f>
+        <v/>
+      </c>
+      <c r="M7" s="65">
+        <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
@@ -9603,7 +9652,11 @@
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr"/>
+      <c r="E8" s="59" t="inlineStr">
+        <is>
+          <t>1418 - BANCO PROMERICA S.A.</t>
+        </is>
+      </c>
       <c r="F8" s="59" t="inlineStr">
         <is>
           <t>DOLARES</t>
@@ -9614,18 +9667,20 @@
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H8" s="60" t="n">
+      <c r="H8" s="59" t="inlineStr"/>
+      <c r="I8" s="59" t="inlineStr"/>
+      <c r="J8" s="60" t="n">
         <v>53237.31</v>
       </c>
-      <c r="I8" s="61" t="n">
+      <c r="K8" s="61" t="n">
         <v>53237.31</v>
       </c>
-      <c r="J8" s="60">
-        <f>I8-H8</f>
-        <v/>
-      </c>
-      <c r="K8" s="62">
-        <f>IF(H8=0,"",(I8-H8)/H8)</f>
+      <c r="L8" s="60">
+        <f>K8-J8</f>
+        <v/>
+      </c>
+      <c r="M8" s="62">
+        <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
@@ -9665,18 +9720,20 @@
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H9" s="64" t="n">
+      <c r="H9" s="63" t="inlineStr"/>
+      <c r="I9" s="63" t="inlineStr"/>
+      <c r="J9" s="64" t="n">
         <v>189049.31</v>
       </c>
-      <c r="I9" s="61" t="n">
+      <c r="K9" s="61" t="n">
         <v>189049.31</v>
       </c>
-      <c r="J9" s="64">
-        <f>I9-H9</f>
-        <v/>
-      </c>
-      <c r="K9" s="65">
-        <f>IF(H9=0,"",(I9-H9)/H9)</f>
+      <c r="L9" s="64">
+        <f>K9-J9</f>
+        <v/>
+      </c>
+      <c r="M9" s="65">
+        <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
@@ -9692,30 +9749,32 @@
       <c r="E10" s="66" t="n"/>
       <c r="F10" s="66" t="n"/>
       <c r="G10" s="66" t="n"/>
-      <c r="H10" s="30">
-        <f>SUM(H6:H9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="30">
-        <f>SUM(I6:I9)</f>
-        <v/>
-      </c>
+      <c r="H10" s="66" t="n"/>
+      <c r="I10" s="66" t="n"/>
       <c r="J10" s="30">
-        <f>I10-H10</f>
-        <v/>
-      </c>
-      <c r="K10" s="31">
-        <f>IF(H10=0,"",(I10-H10)/H10)</f>
+        <f>SUM(J6:J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="30">
+        <f>SUM(K6:K9)</f>
+        <v/>
+      </c>
+      <c r="L10" s="30">
+        <f>K10-J10</f>
+        <v/>
+      </c>
+      <c r="M10" s="31">
+        <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation sqref="A6:A9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$A$2:$A$4</formula1>
     </dataValidation>
@@ -9734,6 +9793,9 @@
     <dataValidation sqref="G6:G9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$F$2:$F$3</formula1>
     </dataValidation>
+    <dataValidation sqref="H6:H9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Catalogos!$Q$2:$Q$3</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9745,20 +9807,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -9816,20 +9880,30 @@
       </c>
       <c r="H5" s="25" t="inlineStr">
         <is>
+          <t>Regularizacion activos</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t>Anio fiscal adquisicion</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="inlineStr">
+        <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
@@ -9843,18 +9917,20 @@
       <c r="E6" s="59" t="inlineStr"/>
       <c r="F6" s="59" t="inlineStr"/>
       <c r="G6" s="59" t="inlineStr"/>
-      <c r="H6" s="61" t="n">
+      <c r="H6" s="59" t="inlineStr"/>
+      <c r="I6" s="59" t="inlineStr"/>
+      <c r="J6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="61" t="n">
+      <c r="K6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="60">
-        <f>I6-H6</f>
-        <v/>
-      </c>
-      <c r="K6" s="62">
-        <f>IF(H6=0,"",(I6-H6)/H6)</f>
+      <c r="L6" s="60">
+        <f>K6-J6</f>
+        <v/>
+      </c>
+      <c r="M6" s="62">
+        <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
@@ -9866,18 +9942,20 @@
       <c r="E7" s="63" t="inlineStr"/>
       <c r="F7" s="63" t="inlineStr"/>
       <c r="G7" s="63" t="inlineStr"/>
-      <c r="H7" s="61" t="n">
+      <c r="H7" s="63" t="inlineStr"/>
+      <c r="I7" s="63" t="inlineStr"/>
+      <c r="J7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="61" t="n">
+      <c r="K7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="64">
-        <f>I7-H7</f>
-        <v/>
-      </c>
-      <c r="K7" s="65">
-        <f>IF(H7=0,"",(I7-H7)/H7)</f>
+      <c r="L7" s="64">
+        <f>K7-J7</f>
+        <v/>
+      </c>
+      <c r="M7" s="65">
+        <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
@@ -9889,18 +9967,20 @@
       <c r="E8" s="59" t="inlineStr"/>
       <c r="F8" s="59" t="inlineStr"/>
       <c r="G8" s="59" t="inlineStr"/>
-      <c r="H8" s="61" t="n">
+      <c r="H8" s="59" t="inlineStr"/>
+      <c r="I8" s="59" t="inlineStr"/>
+      <c r="J8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="61" t="n">
+      <c r="K8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="60">
-        <f>I8-H8</f>
-        <v/>
-      </c>
-      <c r="K8" s="62">
-        <f>IF(H8=0,"",(I8-H8)/H8)</f>
+      <c r="L8" s="60">
+        <f>K8-J8</f>
+        <v/>
+      </c>
+      <c r="M8" s="62">
+        <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
@@ -9912,18 +9992,20 @@
       <c r="E9" s="63" t="inlineStr"/>
       <c r="F9" s="63" t="inlineStr"/>
       <c r="G9" s="63" t="inlineStr"/>
-      <c r="H9" s="61" t="n">
+      <c r="H9" s="63" t="inlineStr"/>
+      <c r="I9" s="63" t="inlineStr"/>
+      <c r="J9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="61" t="n">
+      <c r="K9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="64">
-        <f>I9-H9</f>
-        <v/>
-      </c>
-      <c r="K9" s="65">
-        <f>IF(H9=0,"",(I9-H9)/H9)</f>
+      <c r="L9" s="64">
+        <f>K9-J9</f>
+        <v/>
+      </c>
+      <c r="M9" s="65">
+        <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
@@ -9935,18 +10017,20 @@
       <c r="E10" s="59" t="inlineStr"/>
       <c r="F10" s="59" t="inlineStr"/>
       <c r="G10" s="59" t="inlineStr"/>
-      <c r="H10" s="61" t="n">
+      <c r="H10" s="59" t="inlineStr"/>
+      <c r="I10" s="59" t="inlineStr"/>
+      <c r="J10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="61" t="n">
+      <c r="K10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="60">
-        <f>I10-H10</f>
-        <v/>
-      </c>
-      <c r="K10" s="62">
-        <f>IF(H10=0,"",(I10-H10)/H10)</f>
+      <c r="L10" s="60">
+        <f>K10-J10</f>
+        <v/>
+      </c>
+      <c r="M10" s="62">
+        <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
     </row>
@@ -9958,18 +10042,20 @@
       <c r="E11" s="63" t="inlineStr"/>
       <c r="F11" s="63" t="inlineStr"/>
       <c r="G11" s="63" t="inlineStr"/>
-      <c r="H11" s="61" t="n">
+      <c r="H11" s="63" t="inlineStr"/>
+      <c r="I11" s="63" t="inlineStr"/>
+      <c r="J11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="61" t="n">
+      <c r="K11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="64">
-        <f>I11-H11</f>
-        <v/>
-      </c>
-      <c r="K11" s="65">
-        <f>IF(H11=0,"",(I11-H11)/H11)</f>
+      <c r="L11" s="64">
+        <f>K11-J11</f>
+        <v/>
+      </c>
+      <c r="M11" s="65">
+        <f>IF(J11=0,"",(K11-J11)/J11)</f>
         <v/>
       </c>
     </row>
@@ -9981,18 +10067,20 @@
       <c r="E12" s="59" t="inlineStr"/>
       <c r="F12" s="59" t="inlineStr"/>
       <c r="G12" s="59" t="inlineStr"/>
-      <c r="H12" s="61" t="n">
+      <c r="H12" s="59" t="inlineStr"/>
+      <c r="I12" s="59" t="inlineStr"/>
+      <c r="J12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="61" t="n">
+      <c r="K12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="60">
-        <f>I12-H12</f>
-        <v/>
-      </c>
-      <c r="K12" s="62">
-        <f>IF(H12=0,"",(I12-H12)/H12)</f>
+      <c r="L12" s="60">
+        <f>K12-J12</f>
+        <v/>
+      </c>
+      <c r="M12" s="62">
+        <f>IF(J12=0,"",(K12-J12)/J12)</f>
         <v/>
       </c>
     </row>
@@ -10004,18 +10092,20 @@
       <c r="E13" s="63" t="inlineStr"/>
       <c r="F13" s="63" t="inlineStr"/>
       <c r="G13" s="63" t="inlineStr"/>
-      <c r="H13" s="61" t="n">
+      <c r="H13" s="63" t="inlineStr"/>
+      <c r="I13" s="63" t="inlineStr"/>
+      <c r="J13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="61" t="n">
+      <c r="K13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="64">
-        <f>I13-H13</f>
-        <v/>
-      </c>
-      <c r="K13" s="65">
-        <f>IF(H13=0,"",(I13-H13)/H13)</f>
+      <c r="L13" s="64">
+        <f>K13-J13</f>
+        <v/>
+      </c>
+      <c r="M13" s="65">
+        <f>IF(J13=0,"",(K13-J13)/J13)</f>
         <v/>
       </c>
     </row>
@@ -10031,30 +10121,32 @@
       <c r="E14" s="66" t="n"/>
       <c r="F14" s="66" t="n"/>
       <c r="G14" s="66" t="n"/>
-      <c r="H14" s="30">
-        <f>SUM(H6:H13)</f>
-        <v/>
-      </c>
-      <c r="I14" s="30">
-        <f>SUM(I6:I13)</f>
-        <v/>
-      </c>
+      <c r="H14" s="66" t="n"/>
+      <c r="I14" s="66" t="n"/>
       <c r="J14" s="30">
-        <f>I14-H14</f>
-        <v/>
-      </c>
-      <c r="K14" s="31">
-        <f>IF(H14=0,"",(I14-H14)/H14)</f>
+        <f>SUM(J6:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="30">
+        <f>SUM(K6:K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="30">
+        <f>K14-J14</f>
+        <v/>
+      </c>
+      <c r="M14" s="31">
+        <f>IF(J14=0,"",(K14-J14)/J14)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="A6:A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$G$2:$G$4</formula1>
     </dataValidation>
@@ -10067,6 +10159,9 @@
     <dataValidation sqref="G6:G13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$F$2:$F$3</formula1>
     </dataValidation>
+    <dataValidation sqref="H6:H13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Catalogos!$Q$2:$Q$3</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10078,25 +10173,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>4.1.3   CUENTAS POR COBRAR</t>
+          <t>4.1.3   CREDITOS, DOCUMENTOS Y CUENTAS POR COBRAR</t>
         </is>
       </c>
     </row>
@@ -10123,40 +10221,55 @@
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
+          <t>Tipo de identificacion</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
           <t>N. de identificacion</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>Regularizacion activos</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t>Anio fiscal adquisicion</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
@@ -10169,18 +10282,21 @@
       <c r="D6" s="59" t="inlineStr"/>
       <c r="E6" s="59" t="inlineStr"/>
       <c r="F6" s="59" t="inlineStr"/>
-      <c r="G6" s="61" t="n">
+      <c r="G6" s="59" t="inlineStr"/>
+      <c r="H6" s="59" t="inlineStr"/>
+      <c r="I6" s="59" t="inlineStr"/>
+      <c r="J6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="61" t="n">
+      <c r="K6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="60">
-        <f>H6-G6</f>
-        <v/>
-      </c>
-      <c r="J6" s="62">
-        <f>IF(G6=0,"",(H6-G6)/G6)</f>
+      <c r="L6" s="60">
+        <f>K6-J6</f>
+        <v/>
+      </c>
+      <c r="M6" s="62">
+        <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
@@ -10191,18 +10307,21 @@
       <c r="D7" s="63" t="inlineStr"/>
       <c r="E7" s="63" t="inlineStr"/>
       <c r="F7" s="63" t="inlineStr"/>
-      <c r="G7" s="61" t="n">
+      <c r="G7" s="63" t="inlineStr"/>
+      <c r="H7" s="63" t="inlineStr"/>
+      <c r="I7" s="63" t="inlineStr"/>
+      <c r="J7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="61" t="n">
+      <c r="K7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="64">
-        <f>H7-G7</f>
-        <v/>
-      </c>
-      <c r="J7" s="65">
-        <f>IF(G7=0,"",(H7-G7)/G7)</f>
+      <c r="L7" s="64">
+        <f>K7-J7</f>
+        <v/>
+      </c>
+      <c r="M7" s="65">
+        <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
@@ -10213,18 +10332,21 @@
       <c r="D8" s="59" t="inlineStr"/>
       <c r="E8" s="59" t="inlineStr"/>
       <c r="F8" s="59" t="inlineStr"/>
-      <c r="G8" s="61" t="n">
+      <c r="G8" s="59" t="inlineStr"/>
+      <c r="H8" s="59" t="inlineStr"/>
+      <c r="I8" s="59" t="inlineStr"/>
+      <c r="J8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="61" t="n">
+      <c r="K8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="60">
-        <f>H8-G8</f>
-        <v/>
-      </c>
-      <c r="J8" s="62">
-        <f>IF(G8=0,"",(H8-G8)/G8)</f>
+      <c r="L8" s="60">
+        <f>K8-J8</f>
+        <v/>
+      </c>
+      <c r="M8" s="62">
+        <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
@@ -10235,18 +10357,21 @@
       <c r="D9" s="63" t="inlineStr"/>
       <c r="E9" s="63" t="inlineStr"/>
       <c r="F9" s="63" t="inlineStr"/>
-      <c r="G9" s="61" t="n">
+      <c r="G9" s="63" t="inlineStr"/>
+      <c r="H9" s="63" t="inlineStr"/>
+      <c r="I9" s="63" t="inlineStr"/>
+      <c r="J9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="61" t="n">
+      <c r="K9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="64">
-        <f>H9-G9</f>
-        <v/>
-      </c>
-      <c r="J9" s="65">
-        <f>IF(G9=0,"",(H9-G9)/G9)</f>
+      <c r="L9" s="64">
+        <f>K9-J9</f>
+        <v/>
+      </c>
+      <c r="M9" s="65">
+        <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
@@ -10257,18 +10382,21 @@
       <c r="D10" s="59" t="inlineStr"/>
       <c r="E10" s="59" t="inlineStr"/>
       <c r="F10" s="59" t="inlineStr"/>
-      <c r="G10" s="61" t="n">
+      <c r="G10" s="59" t="inlineStr"/>
+      <c r="H10" s="59" t="inlineStr"/>
+      <c r="I10" s="59" t="inlineStr"/>
+      <c r="J10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="61" t="n">
+      <c r="K10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="60">
-        <f>H10-G10</f>
-        <v/>
-      </c>
-      <c r="J10" s="62">
-        <f>IF(G10=0,"",(H10-G10)/G10)</f>
+      <c r="L10" s="60">
+        <f>K10-J10</f>
+        <v/>
+      </c>
+      <c r="M10" s="62">
+        <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
     </row>
@@ -10279,18 +10407,21 @@
       <c r="D11" s="63" t="inlineStr"/>
       <c r="E11" s="63" t="inlineStr"/>
       <c r="F11" s="63" t="inlineStr"/>
-      <c r="G11" s="61" t="n">
+      <c r="G11" s="63" t="inlineStr"/>
+      <c r="H11" s="63" t="inlineStr"/>
+      <c r="I11" s="63" t="inlineStr"/>
+      <c r="J11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="61" t="n">
+      <c r="K11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="64">
-        <f>H11-G11</f>
-        <v/>
-      </c>
-      <c r="J11" s="65">
-        <f>IF(G11=0,"",(H11-G11)/G11)</f>
+      <c r="L11" s="64">
+        <f>K11-J11</f>
+        <v/>
+      </c>
+      <c r="M11" s="65">
+        <f>IF(J11=0,"",(K11-J11)/J11)</f>
         <v/>
       </c>
     </row>
@@ -10301,18 +10432,21 @@
       <c r="D12" s="59" t="inlineStr"/>
       <c r="E12" s="59" t="inlineStr"/>
       <c r="F12" s="59" t="inlineStr"/>
-      <c r="G12" s="61" t="n">
+      <c r="G12" s="59" t="inlineStr"/>
+      <c r="H12" s="59" t="inlineStr"/>
+      <c r="I12" s="59" t="inlineStr"/>
+      <c r="J12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="61" t="n">
+      <c r="K12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="60">
-        <f>H12-G12</f>
-        <v/>
-      </c>
-      <c r="J12" s="62">
-        <f>IF(G12=0,"",(H12-G12)/G12)</f>
+      <c r="L12" s="60">
+        <f>K12-J12</f>
+        <v/>
+      </c>
+      <c r="M12" s="62">
+        <f>IF(J12=0,"",(K12-J12)/J12)</f>
         <v/>
       </c>
     </row>
@@ -10323,18 +10457,21 @@
       <c r="D13" s="63" t="inlineStr"/>
       <c r="E13" s="63" t="inlineStr"/>
       <c r="F13" s="63" t="inlineStr"/>
-      <c r="G13" s="61" t="n">
+      <c r="G13" s="63" t="inlineStr"/>
+      <c r="H13" s="63" t="inlineStr"/>
+      <c r="I13" s="63" t="inlineStr"/>
+      <c r="J13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="61" t="n">
+      <c r="K13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="64">
-        <f>H13-G13</f>
-        <v/>
-      </c>
-      <c r="J13" s="65">
-        <f>IF(G13=0,"",(H13-G13)/G13)</f>
+      <c r="L13" s="64">
+        <f>K13-J13</f>
+        <v/>
+      </c>
+      <c r="M13" s="65">
+        <f>IF(J13=0,"",(K13-J13)/J13)</f>
         <v/>
       </c>
     </row>
@@ -10349,41 +10486,50 @@
       <c r="D14" s="66" t="n"/>
       <c r="E14" s="66" t="n"/>
       <c r="F14" s="66" t="n"/>
-      <c r="G14" s="30">
-        <f>SUM(G6:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="30">
-        <f>SUM(H6:H13)</f>
-        <v/>
-      </c>
-      <c r="I14" s="30">
-        <f>H14-G14</f>
-        <v/>
-      </c>
-      <c r="J14" s="31">
-        <f>IF(G14=0,"",(H14-G14)/G14)</f>
+      <c r="G14" s="66" t="n"/>
+      <c r="H14" s="66" t="n"/>
+      <c r="I14" s="66" t="n"/>
+      <c r="J14" s="30">
+        <f>SUM(J6:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="30">
+        <f>SUM(K6:K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="30">
+        <f>K14-J14</f>
+        <v/>
+      </c>
+      <c r="M14" s="31">
+        <f>IF(J14=0,"",(K14-J14)/J14)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="6">
     <dataValidation sqref="B6:B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$H$2:$H$3</formula1>
     </dataValidation>
-    <dataValidation sqref="D6:D13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Catalogos!$P$2:$P$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="E6:E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$C$2:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="E6:E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6:F13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$D$2:$D$258</formula1>
     </dataValidation>
-    <dataValidation sqref="F6:F13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$F$2:$F$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Catalogos!$Q$2:$Q$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10396,17 +10542,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -10444,25 +10591,30 @@
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t>Detalle / observacion</t>
+          <t>Regularizacion activos</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
+          <t>Anio fiscal adquisicion</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
@@ -10473,18 +10625,19 @@
       <c r="B6" s="59" t="inlineStr"/>
       <c r="C6" s="59" t="inlineStr"/>
       <c r="D6" s="59" t="inlineStr"/>
-      <c r="E6" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" s="59" t="inlineStr"/>
       <c r="F6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="60">
-        <f>F6-E6</f>
-        <v/>
-      </c>
-      <c r="H6" s="62">
-        <f>IF(E6=0,"",(F6-E6)/E6)</f>
+      <c r="G6" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="60">
+        <f>G6-F6</f>
+        <v/>
+      </c>
+      <c r="I6" s="62">
+        <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
@@ -10493,18 +10646,19 @@
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="63" t="inlineStr"/>
       <c r="D7" s="63" t="inlineStr"/>
-      <c r="E7" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" s="63" t="inlineStr"/>
       <c r="F7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="64">
-        <f>F7-E7</f>
-        <v/>
-      </c>
-      <c r="H7" s="65">
-        <f>IF(E7=0,"",(F7-E7)/E7)</f>
+      <c r="G7" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="64">
+        <f>G7-F7</f>
+        <v/>
+      </c>
+      <c r="I7" s="65">
+        <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
     </row>
@@ -10513,18 +10667,19 @@
       <c r="B8" s="59" t="inlineStr"/>
       <c r="C8" s="59" t="inlineStr"/>
       <c r="D8" s="59" t="inlineStr"/>
-      <c r="E8" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" s="59" t="inlineStr"/>
       <c r="F8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="60">
-        <f>F8-E8</f>
-        <v/>
-      </c>
-      <c r="H8" s="62">
-        <f>IF(E8=0,"",(F8-E8)/E8)</f>
+      <c r="G8" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="60">
+        <f>G8-F8</f>
+        <v/>
+      </c>
+      <c r="I8" s="62">
+        <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
@@ -10533,18 +10688,19 @@
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="63" t="inlineStr"/>
       <c r="D9" s="63" t="inlineStr"/>
-      <c r="E9" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" s="63" t="inlineStr"/>
       <c r="F9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="64">
-        <f>F9-E9</f>
-        <v/>
-      </c>
-      <c r="H9" s="65">
-        <f>IF(E9=0,"",(F9-E9)/E9)</f>
+      <c r="G9" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="64">
+        <f>G9-F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="65">
+        <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
     </row>
@@ -10553,18 +10709,19 @@
       <c r="B10" s="59" t="inlineStr"/>
       <c r="C10" s="59" t="inlineStr"/>
       <c r="D10" s="59" t="inlineStr"/>
-      <c r="E10" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" s="59" t="inlineStr"/>
       <c r="F10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="60">
-        <f>F10-E10</f>
-        <v/>
-      </c>
-      <c r="H10" s="62">
-        <f>IF(E10=0,"",(F10-E10)/E10)</f>
+      <c r="G10" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="60">
+        <f>G10-F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="62">
+        <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
@@ -10573,18 +10730,19 @@
       <c r="B11" s="63" t="inlineStr"/>
       <c r="C11" s="63" t="inlineStr"/>
       <c r="D11" s="63" t="inlineStr"/>
-      <c r="E11" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" s="63" t="inlineStr"/>
       <c r="F11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="64">
-        <f>F11-E11</f>
-        <v/>
-      </c>
-      <c r="H11" s="65">
-        <f>IF(E11=0,"",(F11-E11)/E11)</f>
+      <c r="G11" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="64">
+        <f>G11-F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="65">
+        <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
     </row>
@@ -10593,18 +10751,19 @@
       <c r="B12" s="59" t="inlineStr"/>
       <c r="C12" s="59" t="inlineStr"/>
       <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" s="59" t="inlineStr"/>
       <c r="F12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="60">
-        <f>F12-E12</f>
-        <v/>
-      </c>
-      <c r="H12" s="62">
-        <f>IF(E12=0,"",(F12-E12)/E12)</f>
+      <c r="G12" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="60">
+        <f>G12-F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="62">
+        <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
@@ -10613,18 +10772,19 @@
       <c r="B13" s="63" t="inlineStr"/>
       <c r="C13" s="63" t="inlineStr"/>
       <c r="D13" s="63" t="inlineStr"/>
-      <c r="E13" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" s="63" t="inlineStr"/>
       <c r="F13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="64">
-        <f>F13-E13</f>
-        <v/>
-      </c>
-      <c r="H13" s="65">
-        <f>IF(E13=0,"",(F13-E13)/E13)</f>
+      <c r="G13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="64">
+        <f>G13-F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="65">
+        <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
@@ -10637,30 +10797,31 @@
       <c r="B14" s="66" t="n"/>
       <c r="C14" s="66" t="n"/>
       <c r="D14" s="66" t="n"/>
-      <c r="E14" s="30">
-        <f>SUM(E6:E13)</f>
-        <v/>
-      </c>
+      <c r="E14" s="66" t="n"/>
       <c r="F14" s="30">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>F14-E14</f>
-        <v/>
-      </c>
-      <c r="H14" s="31">
-        <f>IF(E14=0,"",(F14-E14)/E14)</f>
+        <f>SUM(G6:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="30">
+        <f>G14-F14</f>
+        <v/>
+      </c>
+      <c r="I14" s="31">
+        <f>IF(F14=0,"",(G14-F14)/F14)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="A6:A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$I$2:$I$7</formula1>
     </dataValidation>
@@ -10669,6 +10830,9 @@
     </dataValidation>
     <dataValidation sqref="C6:C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$D$2:$D$258</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6:D13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Catalogos!$Q$2:$Q$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10681,17 +10845,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -10734,20 +10900,30 @@
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
+          <t>Regularizacion activos</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>Anio fiscal adquisicion</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
@@ -10774,18 +10950,20 @@
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E6" s="60" t="n">
+      <c r="E6" s="59" t="inlineStr"/>
+      <c r="F6" s="59" t="inlineStr"/>
+      <c r="G6" s="60" t="n">
         <v>12000</v>
       </c>
-      <c r="F6" s="61" t="n">
+      <c r="H6" s="61" t="n">
         <v>12000</v>
       </c>
-      <c r="G6" s="60">
-        <f>F6-E6</f>
-        <v/>
-      </c>
-      <c r="H6" s="62">
-        <f>IF(E6=0,"",(F6-E6)/E6)</f>
+      <c r="I6" s="60">
+        <f>H6-G6</f>
+        <v/>
+      </c>
+      <c r="J6" s="62">
+        <f>IF(G6=0,"",(H6-G6)/G6)</f>
         <v/>
       </c>
     </row>
@@ -10810,18 +10988,20 @@
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E7" s="64" t="n">
+      <c r="E7" s="63" t="inlineStr"/>
+      <c r="F7" s="63" t="inlineStr"/>
+      <c r="G7" s="64" t="n">
         <v>20000</v>
       </c>
-      <c r="F7" s="61" t="n">
+      <c r="H7" s="61" t="n">
         <v>20000</v>
       </c>
-      <c r="G7" s="64">
-        <f>F7-E7</f>
-        <v/>
-      </c>
-      <c r="H7" s="65">
-        <f>IF(E7=0,"",(F7-E7)/E7)</f>
+      <c r="I7" s="64">
+        <f>H7-G7</f>
+        <v/>
+      </c>
+      <c r="J7" s="65">
+        <f>IF(G7=0,"",(H7-G7)/G7)</f>
         <v/>
       </c>
     </row>
@@ -10846,18 +11026,20 @@
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E8" s="60" t="n">
+      <c r="E8" s="59" t="inlineStr"/>
+      <c r="F8" s="59" t="inlineStr"/>
+      <c r="G8" s="60" t="n">
         <v>32000</v>
       </c>
-      <c r="F8" s="61" t="n">
+      <c r="H8" s="61" t="n">
         <v>32000</v>
       </c>
-      <c r="G8" s="60">
-        <f>F8-E8</f>
-        <v/>
-      </c>
-      <c r="H8" s="62">
-        <f>IF(E8=0,"",(F8-E8)/E8)</f>
+      <c r="I8" s="60">
+        <f>H8-G8</f>
+        <v/>
+      </c>
+      <c r="J8" s="62">
+        <f>IF(G8=0,"",(H8-G8)/G8)</f>
         <v/>
       </c>
     </row>
@@ -10870,30 +11052,32 @@
       <c r="B9" s="66" t="n"/>
       <c r="C9" s="66" t="n"/>
       <c r="D9" s="66" t="n"/>
-      <c r="E9" s="30">
-        <f>SUM(E6:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="30">
-        <f>SUM(F6:F8)</f>
-        <v/>
-      </c>
+      <c r="E9" s="66" t="n"/>
+      <c r="F9" s="66" t="n"/>
       <c r="G9" s="30">
-        <f>F9-E9</f>
-        <v/>
-      </c>
-      <c r="H9" s="31">
-        <f>IF(E9=0,"",(F9-E9)/E9)</f>
+        <f>SUM(G6:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="30">
+        <f>SUM(H6:H8)</f>
+        <v/>
+      </c>
+      <c r="I9" s="30">
+        <f>H9-G9</f>
+        <v/>
+      </c>
+      <c r="J9" s="31">
+        <f>IF(G9=0,"",(H9-G9)/G9)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="A6:A8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$J$2:$J$4</formula1>
     </dataValidation>
@@ -10902,6 +11086,9 @@
     </dataValidation>
     <dataValidation sqref="D6:D8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$D$2:$D$258</formula1>
+    </dataValidation>
+    <dataValidation sqref="E6:E8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Catalogos!$Q$2:$Q$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10914,17 +11101,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -10962,25 +11150,30 @@
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t>Detalle / observacion</t>
+          <t>Regularizacion activos</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
+          <t>Anio fiscal adquisicion</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
@@ -10991,18 +11184,19 @@
       <c r="B6" s="59" t="inlineStr"/>
       <c r="C6" s="59" t="inlineStr"/>
       <c r="D6" s="59" t="inlineStr"/>
-      <c r="E6" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" s="59" t="inlineStr"/>
       <c r="F6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="60">
-        <f>F6-E6</f>
-        <v/>
-      </c>
-      <c r="H6" s="62">
-        <f>IF(E6=0,"",(F6-E6)/E6)</f>
+      <c r="G6" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="60">
+        <f>G6-F6</f>
+        <v/>
+      </c>
+      <c r="I6" s="62">
+        <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
@@ -11011,18 +11205,19 @@
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="63" t="inlineStr"/>
       <c r="D7" s="63" t="inlineStr"/>
-      <c r="E7" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" s="63" t="inlineStr"/>
       <c r="F7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="64">
-        <f>F7-E7</f>
-        <v/>
-      </c>
-      <c r="H7" s="65">
-        <f>IF(E7=0,"",(F7-E7)/E7)</f>
+      <c r="G7" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="64">
+        <f>G7-F7</f>
+        <v/>
+      </c>
+      <c r="I7" s="65">
+        <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
     </row>
@@ -11031,18 +11226,19 @@
       <c r="B8" s="59" t="inlineStr"/>
       <c r="C8" s="59" t="inlineStr"/>
       <c r="D8" s="59" t="inlineStr"/>
-      <c r="E8" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" s="59" t="inlineStr"/>
       <c r="F8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="60">
-        <f>F8-E8</f>
-        <v/>
-      </c>
-      <c r="H8" s="62">
-        <f>IF(E8=0,"",(F8-E8)/E8)</f>
+      <c r="G8" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="60">
+        <f>G8-F8</f>
+        <v/>
+      </c>
+      <c r="I8" s="62">
+        <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
@@ -11051,18 +11247,19 @@
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="63" t="inlineStr"/>
       <c r="D9" s="63" t="inlineStr"/>
-      <c r="E9" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" s="63" t="inlineStr"/>
       <c r="F9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="64">
-        <f>F9-E9</f>
-        <v/>
-      </c>
-      <c r="H9" s="65">
-        <f>IF(E9=0,"",(F9-E9)/E9)</f>
+      <c r="G9" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="64">
+        <f>G9-F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="65">
+        <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
     </row>
@@ -11071,18 +11268,19 @@
       <c r="B10" s="59" t="inlineStr"/>
       <c r="C10" s="59" t="inlineStr"/>
       <c r="D10" s="59" t="inlineStr"/>
-      <c r="E10" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" s="59" t="inlineStr"/>
       <c r="F10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="60">
-        <f>F10-E10</f>
-        <v/>
-      </c>
-      <c r="H10" s="62">
-        <f>IF(E10=0,"",(F10-E10)/E10)</f>
+      <c r="G10" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="60">
+        <f>G10-F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="62">
+        <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
@@ -11091,18 +11289,19 @@
       <c r="B11" s="63" t="inlineStr"/>
       <c r="C11" s="63" t="inlineStr"/>
       <c r="D11" s="63" t="inlineStr"/>
-      <c r="E11" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" s="63" t="inlineStr"/>
       <c r="F11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="64">
-        <f>F11-E11</f>
-        <v/>
-      </c>
-      <c r="H11" s="65">
-        <f>IF(E11=0,"",(F11-E11)/E11)</f>
+      <c r="G11" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="64">
+        <f>G11-F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="65">
+        <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
     </row>
@@ -11111,18 +11310,19 @@
       <c r="B12" s="59" t="inlineStr"/>
       <c r="C12" s="59" t="inlineStr"/>
       <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" s="59" t="inlineStr"/>
       <c r="F12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="60">
-        <f>F12-E12</f>
-        <v/>
-      </c>
-      <c r="H12" s="62">
-        <f>IF(E12=0,"",(F12-E12)/E12)</f>
+      <c r="G12" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="60">
+        <f>G12-F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="62">
+        <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
@@ -11131,18 +11331,19 @@
       <c r="B13" s="63" t="inlineStr"/>
       <c r="C13" s="63" t="inlineStr"/>
       <c r="D13" s="63" t="inlineStr"/>
-      <c r="E13" s="61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" s="63" t="inlineStr"/>
       <c r="F13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="64">
-        <f>F13-E13</f>
-        <v/>
-      </c>
-      <c r="H13" s="65">
-        <f>IF(E13=0,"",(F13-E13)/E13)</f>
+      <c r="G13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="64">
+        <f>G13-F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="65">
+        <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
@@ -11155,30 +11356,31 @@
       <c r="B14" s="66" t="n"/>
       <c r="C14" s="66" t="n"/>
       <c r="D14" s="66" t="n"/>
-      <c r="E14" s="30">
-        <f>SUM(E6:E13)</f>
-        <v/>
-      </c>
+      <c r="E14" s="66" t="n"/>
       <c r="F14" s="30">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>F14-E14</f>
-        <v/>
-      </c>
-      <c r="H14" s="31">
-        <f>IF(E14=0,"",(F14-E14)/E14)</f>
+        <f>SUM(G6:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="30">
+        <f>G14-F14</f>
+        <v/>
+      </c>
+      <c r="I14" s="31">
+        <f>IF(F14=0,"",(G14-F14)/F14)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="A6:A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$K$2:$K$9</formula1>
     </dataValidation>
@@ -11187,6 +11389,9 @@
     </dataValidation>
     <dataValidation sqref="C6:C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$D$2:$D$258</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6:D13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Catalogos!$Q$2:$Q$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11199,20 +11404,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -11270,20 +11477,30 @@
       </c>
       <c r="H5" s="25" t="inlineStr">
         <is>
+          <t>Regularizacion activos</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t>Anio fiscal adquisicion</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="inlineStr">
+        <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
@@ -11325,18 +11542,20 @@
           <t>1042203018</t>
         </is>
       </c>
-      <c r="H6" s="60" t="n">
+      <c r="H6" s="59" t="inlineStr"/>
+      <c r="I6" s="59" t="inlineStr"/>
+      <c r="J6" s="60" t="n">
         <v>267340.8</v>
       </c>
-      <c r="I6" s="61" t="n">
+      <c r="K6" s="61" t="n">
         <v>267340.8</v>
       </c>
-      <c r="J6" s="60">
-        <f>I6-H6</f>
-        <v/>
-      </c>
-      <c r="K6" s="62">
-        <f>IF(H6=0,"",(I6-H6)/H6)</f>
+      <c r="L6" s="60">
+        <f>K6-J6</f>
+        <v/>
+      </c>
+      <c r="M6" s="62">
+        <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
@@ -11376,18 +11595,20 @@
           <t>1012005008000000000</t>
         </is>
       </c>
-      <c r="H7" s="64" t="n">
+      <c r="H7" s="63" t="inlineStr"/>
+      <c r="I7" s="63" t="inlineStr"/>
+      <c r="J7" s="64" t="n">
         <v>198118.55</v>
       </c>
-      <c r="I7" s="61" t="n">
+      <c r="K7" s="61" t="n">
         <v>198118.55</v>
       </c>
-      <c r="J7" s="64">
-        <f>I7-H7</f>
-        <v/>
-      </c>
-      <c r="K7" s="65">
-        <f>IF(H7=0,"",(I7-H7)/H7)</f>
+      <c r="L7" s="64">
+        <f>K7-J7</f>
+        <v/>
+      </c>
+      <c r="M7" s="65">
+        <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
@@ -11423,18 +11644,20 @@
           <t>1042203018</t>
         </is>
       </c>
-      <c r="H8" s="60" t="n">
+      <c r="H8" s="59" t="inlineStr"/>
+      <c r="I8" s="59" t="inlineStr"/>
+      <c r="J8" s="60" t="n">
         <v>33634.04</v>
       </c>
-      <c r="I8" s="61" t="n">
+      <c r="K8" s="61" t="n">
         <v>33634.04</v>
       </c>
-      <c r="J8" s="60">
-        <f>I8-H8</f>
-        <v/>
-      </c>
-      <c r="K8" s="62">
-        <f>IF(H8=0,"",(I8-H8)/H8)</f>
+      <c r="L8" s="60">
+        <f>K8-J8</f>
+        <v/>
+      </c>
+      <c r="M8" s="62">
+        <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
@@ -11470,18 +11693,20 @@
           <t>1012005008000000000</t>
         </is>
       </c>
-      <c r="H9" s="64" t="n">
+      <c r="H9" s="63" t="inlineStr"/>
+      <c r="I9" s="63" t="inlineStr"/>
+      <c r="J9" s="64" t="n">
         <v>82624.22</v>
       </c>
-      <c r="I9" s="61" t="n">
+      <c r="K9" s="61" t="n">
         <v>82624.22</v>
       </c>
-      <c r="J9" s="64">
-        <f>I9-H9</f>
-        <v/>
-      </c>
-      <c r="K9" s="65">
-        <f>IF(H9=0,"",(I9-H9)/H9)</f>
+      <c r="L9" s="64">
+        <f>K9-J9</f>
+        <v/>
+      </c>
+      <c r="M9" s="65">
+        <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
@@ -11497,32 +11722,34 @@
       <c r="E10" s="66" t="n"/>
       <c r="F10" s="66" t="n"/>
       <c r="G10" s="66" t="n"/>
-      <c r="H10" s="30">
-        <f>SUM(H6:H9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="30">
-        <f>SUM(I6:I9)</f>
-        <v/>
-      </c>
+      <c r="H10" s="66" t="n"/>
+      <c r="I10" s="66" t="n"/>
       <c r="J10" s="30">
-        <f>I10-H10</f>
-        <v/>
-      </c>
-      <c r="K10" s="31">
-        <f>IF(H10=0,"",(I10-H10)/H10)</f>
+        <f>SUM(J6:J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="30">
+        <f>SUM(K6:K9)</f>
+        <v/>
+      </c>
+      <c r="L10" s="30">
+        <f>K10-J10</f>
+        <v/>
+      </c>
+      <c r="M10" s="31">
+        <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="A6:A9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Catalogos!$L$2:$L$9</formula1>
+      <formula1>Catalogos!$L$2:$L$10</formula1>
     </dataValidation>
     <dataValidation sqref="B6:B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$C$2:$C$3</formula1>
@@ -11536,6 +11763,9 @@
     <dataValidation sqref="E6:E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$N$2:$N$222</formula1>
     </dataValidation>
+    <dataValidation sqref="H6:H9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Catalogos!$Q$2:$Q$3</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11547,16 +11777,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -11589,25 +11821,35 @@
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>Detalle / observacion</t>
+          <t>Descripcion</t>
         </is>
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
+          <t>Regularizacion activos</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>Anio fiscal adquisicion</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
@@ -11617,18 +11859,20 @@
       <c r="A6" s="59" t="inlineStr"/>
       <c r="B6" s="59" t="inlineStr"/>
       <c r="C6" s="59" t="inlineStr"/>
-      <c r="D6" s="61" t="n">
+      <c r="D6" s="59" t="inlineStr"/>
+      <c r="E6" s="59" t="inlineStr"/>
+      <c r="F6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="61" t="n">
+      <c r="G6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="60">
-        <f>E6-D6</f>
-        <v/>
-      </c>
-      <c r="G6" s="62">
-        <f>IF(D6=0,"",(E6-D6)/D6)</f>
+      <c r="H6" s="60">
+        <f>G6-F6</f>
+        <v/>
+      </c>
+      <c r="I6" s="62">
+        <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
@@ -11636,18 +11880,20 @@
       <c r="A7" s="63" t="inlineStr"/>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="63" t="inlineStr"/>
-      <c r="D7" s="61" t="n">
+      <c r="D7" s="63" t="inlineStr"/>
+      <c r="E7" s="63" t="inlineStr"/>
+      <c r="F7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="61" t="n">
+      <c r="G7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="64">
-        <f>E7-D7</f>
-        <v/>
-      </c>
-      <c r="G7" s="65">
-        <f>IF(D7=0,"",(E7-D7)/D7)</f>
+      <c r="H7" s="64">
+        <f>G7-F7</f>
+        <v/>
+      </c>
+      <c r="I7" s="65">
+        <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
     </row>
@@ -11655,18 +11901,20 @@
       <c r="A8" s="59" t="inlineStr"/>
       <c r="B8" s="59" t="inlineStr"/>
       <c r="C8" s="59" t="inlineStr"/>
-      <c r="D8" s="61" t="n">
+      <c r="D8" s="59" t="inlineStr"/>
+      <c r="E8" s="59" t="inlineStr"/>
+      <c r="F8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="61" t="n">
+      <c r="G8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="60">
-        <f>E8-D8</f>
-        <v/>
-      </c>
-      <c r="G8" s="62">
-        <f>IF(D8=0,"",(E8-D8)/D8)</f>
+      <c r="H8" s="60">
+        <f>G8-F8</f>
+        <v/>
+      </c>
+      <c r="I8" s="62">
+        <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
@@ -11674,18 +11922,20 @@
       <c r="A9" s="63" t="inlineStr"/>
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="63" t="inlineStr"/>
-      <c r="D9" s="61" t="n">
+      <c r="D9" s="63" t="inlineStr"/>
+      <c r="E9" s="63" t="inlineStr"/>
+      <c r="F9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="61" t="n">
+      <c r="G9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="64">
-        <f>E9-D9</f>
-        <v/>
-      </c>
-      <c r="G9" s="65">
-        <f>IF(D9=0,"",(E9-D9)/D9)</f>
+      <c r="H9" s="64">
+        <f>G9-F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="65">
+        <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
     </row>
@@ -11693,18 +11943,20 @@
       <c r="A10" s="59" t="inlineStr"/>
       <c r="B10" s="59" t="inlineStr"/>
       <c r="C10" s="59" t="inlineStr"/>
-      <c r="D10" s="61" t="n">
+      <c r="D10" s="59" t="inlineStr"/>
+      <c r="E10" s="59" t="inlineStr"/>
+      <c r="F10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="61" t="n">
+      <c r="G10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="60">
-        <f>E10-D10</f>
-        <v/>
-      </c>
-      <c r="G10" s="62">
-        <f>IF(D10=0,"",(E10-D10)/D10)</f>
+      <c r="H10" s="60">
+        <f>G10-F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="62">
+        <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
@@ -11712,18 +11964,20 @@
       <c r="A11" s="63" t="inlineStr"/>
       <c r="B11" s="63" t="inlineStr"/>
       <c r="C11" s="63" t="inlineStr"/>
-      <c r="D11" s="61" t="n">
+      <c r="D11" s="63" t="inlineStr"/>
+      <c r="E11" s="63" t="inlineStr"/>
+      <c r="F11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="61" t="n">
+      <c r="G11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="64">
-        <f>E11-D11</f>
-        <v/>
-      </c>
-      <c r="G11" s="65">
-        <f>IF(D11=0,"",(E11-D11)/D11)</f>
+      <c r="H11" s="64">
+        <f>G11-F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="65">
+        <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
     </row>
@@ -11731,18 +11985,20 @@
       <c r="A12" s="59" t="inlineStr"/>
       <c r="B12" s="59" t="inlineStr"/>
       <c r="C12" s="59" t="inlineStr"/>
-      <c r="D12" s="61" t="n">
+      <c r="D12" s="59" t="inlineStr"/>
+      <c r="E12" s="59" t="inlineStr"/>
+      <c r="F12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="61" t="n">
+      <c r="G12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="60">
-        <f>E12-D12</f>
-        <v/>
-      </c>
-      <c r="G12" s="62">
-        <f>IF(D12=0,"",(E12-D12)/D12)</f>
+      <c r="H12" s="60">
+        <f>G12-F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="62">
+        <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
@@ -11750,18 +12006,20 @@
       <c r="A13" s="63" t="inlineStr"/>
       <c r="B13" s="63" t="inlineStr"/>
       <c r="C13" s="63" t="inlineStr"/>
-      <c r="D13" s="61" t="n">
+      <c r="D13" s="63" t="inlineStr"/>
+      <c r="E13" s="63" t="inlineStr"/>
+      <c r="F13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="61" t="n">
+      <c r="G13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="64">
-        <f>E13-D13</f>
-        <v/>
-      </c>
-      <c r="G13" s="65">
-        <f>IF(D13=0,"",(E13-D13)/D13)</f>
+      <c r="H13" s="64">
+        <f>G13-F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="65">
+        <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
@@ -11773,36 +12031,41 @@
       </c>
       <c r="B14" s="66" t="n"/>
       <c r="C14" s="66" t="n"/>
-      <c r="D14" s="30">
-        <f>SUM(D6:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="30">
-        <f>SUM(E6:E13)</f>
-        <v/>
-      </c>
+      <c r="D14" s="66" t="n"/>
+      <c r="E14" s="66" t="n"/>
       <c r="F14" s="30">
-        <f>E14-D14</f>
-        <v/>
-      </c>
-      <c r="G14" s="31">
-        <f>IF(D14=0,"",(E14-D14)/D14)</f>
+        <f>SUM(F6:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="30">
+        <f>SUM(G6:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="30">
+        <f>G14-F14</f>
+        <v/>
+      </c>
+      <c r="I14" s="31">
+        <f>IF(F14=0,"",(G14-F14)/F14)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="A6:A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation sqref="B6:B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogos!$D$2:$D$258</formula1>
     </dataValidation>
+    <dataValidation sqref="D6:D13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Catalogos!$Q$2:$Q$3</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -18,8 +18,10 @@
     <sheet name="Otros Activos" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Pasivos" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Justificacion" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Datos del XML" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Catalogos" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet name="Generar XML" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Datos del XML" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="_Mapa" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet name="Catalogos" sheetId="15" state="hidden" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +34,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -119,6 +121,16 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="007A7A7A"/>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -215,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -425,6 +437,12 @@
     <xf numFmtId="164" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -434,8 +452,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2539,6 +2555,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GENERAR XML PARA EL SRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Convierte este libro en el archivo XML de la Declaracion Patrimonial, listo para subir al portal del SRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="5" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="77" t="inlineStr">
+        <is>
+          <t>►   GENERAR XML</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="78" t="inlineStr">
+        <is>
+          <t>Dibuje el boton sobre este recuadro y asignele la macro GenerarXmlSRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="79" t="inlineStr">
+        <is>
+          <t>CONFIGURACION POR UNICA VEZ (activa el boton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="80" t="inlineStr">
+        <is>
+          <t>1. Abra el editor de macros con la tecla  Alt + F11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="80" t="inlineStr">
+        <is>
+          <t>2. Menu Archivo &gt; Importar archivo... y seleccione el archivo GenerarXmlSRI.bas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="80" t="inlineStr">
+        <is>
+          <t>3. Cierre el editor y guarde este libro como  'Libro de Excel habilitado para macros (*.xlsm)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="80" t="inlineStr">
+        <is>
+          <t>4. Active la pestana Programador:  Archivo &gt; Opciones &gt; Personalizar cinta de opciones &gt; marque 'Programador'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="80" t="inlineStr">
+        <is>
+          <t>5. Programador &gt; Insertar &gt; Boton (control de formulario) y dibujelo sobre el recuadro verde de arriba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="80" t="inlineStr">
+        <is>
+          <t>6. Cuando Excel lo solicite, asigne la macro  GenerarXmlSRI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="80" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="79" t="inlineStr">
+        <is>
+          <t>USO DIARIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="80" t="inlineStr">
+        <is>
+          <t>7. Llene las columnas amarillas de cada modulo y la hoja Justificacion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="80" t="inlineStr">
+        <is>
+          <t>8. Pulse el boton GENERAR XML, indique el anio y elija donde guardar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="80" t="inlineStr">
+        <is>
+          <t>9. El archivo .xml queda listo para subir al portal del SRI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="80" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="80" t="inlineStr">
+        <is>
+          <t>Alternativa sin macros:  ejecutar  python tools/generar_xml_sri.py  desde la terminal.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B5:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2557,108 +2728,108 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>IDENTIFICACION</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="78" t="inlineStr">
+      <c r="A6" s="82" t="inlineStr">
         <is>
           <t>Anio de la declaracion</t>
         </is>
       </c>
-      <c r="B6" s="79" t="n">
+      <c r="B6" s="83" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="78" t="inlineStr">
+      <c r="A7" s="82" t="inlineStr">
         <is>
           <t>Tipo de declaracion</t>
         </is>
       </c>
-      <c r="B7" s="79" t="inlineStr">
+      <c r="B7" s="83" t="inlineStr">
         <is>
           <t>SOC - Sociedad conyugal o union de hecho</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="78" t="inlineStr">
+      <c r="A8" s="82" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="B8" s="79" t="inlineStr">
+      <c r="B8" s="83" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="78" t="inlineStr">
+      <c r="A9" s="82" t="inlineStr">
         <is>
           <t>Numero de identificacion</t>
         </is>
       </c>
-      <c r="B9" s="79" t="inlineStr">
+      <c r="B9" s="83" t="inlineStr">
         <is>
           <t>1709164899001</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="78" t="inlineStr">
+      <c r="A10" s="82" t="inlineStr">
         <is>
           <t>Nombre del declarante</t>
         </is>
       </c>
-      <c r="B10" s="79" t="inlineStr">
+      <c r="B10" s="83" t="inlineStr">
         <is>
           <t>GONZALEZ NAVAS MARCO VINICIO</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="78" t="inlineStr">
+      <c r="A11" s="82" t="inlineStr">
         <is>
           <t>Identificacion del conyuge</t>
         </is>
       </c>
-      <c r="B11" s="79" t="inlineStr">
+      <c r="B11" s="83" t="inlineStr">
         <is>
           <t>C - Cedula</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="78" t="inlineStr">
+      <c r="A12" s="82" t="inlineStr">
         <is>
           <t>Numero ident. conyuge</t>
         </is>
       </c>
-      <c r="B12" s="79" t="inlineStr">
+      <c r="B12" s="83" t="inlineStr">
         <is>
           <t>1709784225</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="78" t="inlineStr">
+      <c r="A13" s="82" t="inlineStr">
         <is>
           <t>Nombre del conyuge</t>
         </is>
       </c>
-      <c r="B13" s="79" t="inlineStr">
+      <c r="B13" s="83" t="inlineStr">
         <is>
           <t>HIDALGO LOZA ROSA CONSUELO</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="78" t="inlineStr">
+      <c r="A14" s="82" t="inlineStr">
         <is>
           <t>Total creditos / cuentas por cobrar</t>
         </is>
@@ -2668,14 +2839,14 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="77" t="inlineStr">
+      <c r="A16" s="81" t="inlineStr">
         <is>
           <t>PATRIMONIO NETO (enlazado a la hoja Dashboard)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="78" t="inlineStr">
+      <c r="A17" s="82" t="inlineStr">
         <is>
           <t>Patrimonio neto 2025</t>
         </is>
@@ -2686,7 +2857,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="78" t="inlineStr">
+      <c r="A18" s="82" t="inlineStr">
         <is>
           <t>Patrimonio neto 2026 (proyectado)</t>
         </is>
@@ -2697,7 +2868,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="78" t="inlineStr">
+      <c r="A19" s="82" t="inlineStr">
         <is>
           <t>Variacion proyectada</t>
         </is>
@@ -2708,7 +2879,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="78" t="inlineStr">
+      <c r="A20" s="82" t="inlineStr">
         <is>
           <t>Variacion % proyectada</t>
         </is>
@@ -2719,14 +2890,14 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="77" t="inlineStr">
+      <c r="A22" s="81" t="inlineStr">
         <is>
           <t>PATRIMONIO DECLARADO EN EL XML</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="78" t="inlineStr">
+      <c r="A23" s="82" t="inlineStr">
         <is>
           <t>Patrimonio total declarado</t>
         </is>
@@ -2736,7 +2907,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="78" t="inlineStr">
+      <c r="A24" s="82" t="inlineStr">
         <is>
           <t>Atribuible a hijos no emancipados</t>
         </is>
@@ -2746,7 +2917,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="78" t="inlineStr">
+      <c r="A25" s="82" t="inlineStr">
         <is>
           <t>Patrimonio en la sociedad conyugal</t>
         </is>
@@ -2756,7 +2927,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="78" t="inlineStr">
+      <c r="A26" s="82" t="inlineStr">
         <is>
           <t>Patrimonio individual del declarante</t>
         </is>
@@ -2766,7 +2937,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="78" t="inlineStr">
+      <c r="A27" s="82" t="inlineStr">
         <is>
           <t>Patrimonio del anio anterior</t>
         </is>
@@ -2776,7 +2947,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="78" t="inlineStr">
+      <c r="A28" s="82" t="inlineStr">
         <is>
           <t>Crecimiento / decremento patrimonial</t>
         </is>
@@ -2786,21 +2957,21 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="80" t="inlineStr">
+      <c r="A30" s="79" t="inlineStr">
         <is>
           <t>Justificacion de la variacion (ver hoja Justificacion)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="81" t="inlineStr">
+      <c r="A31" s="80" t="inlineStr">
         <is>
           <t>- 1 - Ingresos locales</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="81" t="inlineStr">
+      <c r="A32" s="80" t="inlineStr">
         <is>
           <t>- 6 - Otros</t>
         </is>
@@ -2825,7 +2996,3250 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>hoja</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>contenedor</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>detalle</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>clase</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ordenXml</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>xmlTag</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>descIndex</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>detalleDinero</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>dineroEn</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>detalleDinero</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>tipoInversion</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>detalleDinero</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>detalleDinero</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>pais</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>detalleDinero</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>_ifi</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>detalleDinero</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>tipoMoneda</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>detalleDinero</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>saldo</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>detalleDinero</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>partesRelacionadas</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>detalleDinero</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>regularizacionActivos</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>dinero</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>detalleDinero</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>anioFiscalAdquisicion</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Derechos de Capital</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>inversiones</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>detalleInversiones</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>tipoInversion</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Derechos de Capital</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>inversiones</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>detalleInversiones</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Derechos de Capital</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>inversiones</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>detalleInversiones</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Derechos de Capital</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>inversiones</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>detalleInversiones</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>codpais</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Derechos de Capital</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>inversiones</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>detalleInversiones</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>nombempresa</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Derechos de Capital</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>inversiones</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>detalleInversiones</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>porcentpart</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Derechos de Capital</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>inversiones</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>detalleInversiones</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>numAcc</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Derechos de Capital</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>inversiones</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>detalleInversiones</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>relacionadas</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Derechos de Capital</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>inversiones</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>detalleInversiones</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>regularizacionActivos</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Derechos de Capital</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>inversiones</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>detalleInversiones</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>anioFiscalAdquisicion</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cxc</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cuentas por Cobrar</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ctasXCobrar</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>detalleCtasXCobrar</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>nombreDeudor</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cxc</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cuentas por Cobrar</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ctasXCobrar</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>detalleCtasXCobrar</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>tipoDeudor</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cxc</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cuentas por Cobrar</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ctasXCobrar</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>detalleCtasXCobrar</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>tipoIdentificacion</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cxc</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cuentas por Cobrar</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ctasXCobrar</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>detalleCtasXCobrar</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>numeroIdentificacion</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cxc</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cuentas por Cobrar</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ctasXCobrar</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>detalleCtasXCobrar</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cxc</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cuentas por Cobrar</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ctasXCobrar</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>detalleCtasXCobrar</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>pais</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cxc</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cuentas por Cobrar</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ctasXCobrar</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>detalleCtasXCobrar</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>partesRelacionadas</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cxc</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cuentas por Cobrar</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ctasXCobrar</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>detalleCtasXCobrar</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>saldo</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cxc</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cuentas por Cobrar</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ctasXCobrar</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>detalleCtasXCobrar</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>regularizacionActivos</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cxc</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cuentas por Cobrar</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ctasXCobrar</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>detalleCtasXCobrar</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>anioFiscalAdquisicion</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>muebles</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bienes Muebles</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>otrosBienes</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>detalleOtrosBienes</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>tipoBien</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>muebles</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bienes Muebles</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>otrosBienes</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>detalleOtrosBienes</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>muebles</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bienes Muebles</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>otrosBienes</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>detalleOtrosBienes</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>pais</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>muebles</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bienes Muebles</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>otrosBienes</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>detalleOtrosBienes</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>muebles</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bienes Muebles</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>otrosBienes</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>detalleOtrosBienes</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>regularizacionActivos</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>muebles</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Bienes Muebles</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>otrosBienes</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>detalleOtrosBienes</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>anioFiscalAdquisicion</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Vehiculos</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>detalleVehiculos</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>tipoVehiculo</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Vehiculos</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>detalleVehiculos</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Vehiculos</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>detalleVehiculos</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Vehiculos</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>detalleVehiculos</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>pais</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Vehiculos</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>detalleVehiculos</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Vehiculos</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>detalleVehiculos</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>regularizacionActivos</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Vehiculos</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>vehiculos</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>detalleVehiculos</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>anioFiscalAdquisicion</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>derechos</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Derechos</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>derechos</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>detalleDerechos</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>tipoDerecho</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>derechos</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Derechos</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>derechos</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>detalleDerechos</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>derechos</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Derechos</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>derechos</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>detalleDerechos</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>pais</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>derechos</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Derechos</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>derechos</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>detalleDerechos</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>derechos</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Derechos</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>derechos</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>detalleDerechos</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>regularizacionActivos</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>derechos</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Derechos</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>derechos</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>detalleDerechos</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>anioFiscalAdquisicion</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>inmuebles</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Bienes Inmuebles</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>bienesInmuebles</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>detalleBienesInmuebles</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>tipoInmueble</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>inmuebles</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Bienes Inmuebles</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>bienesInmuebles</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>detalleBienesInmuebles</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>5</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>inmuebles</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Bienes Inmuebles</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>bienesInmuebles</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>detalleBienesInmuebles</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>codPais</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>inmuebles</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Bienes Inmuebles</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>bienesInmuebles</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>detalleBienesInmuebles</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>provincia</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>inmuebles</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Bienes Inmuebles</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>bienesInmuebles</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>detalleBienesInmuebles</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>canton</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>inmuebles</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Bienes Inmuebles</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>bienesInmuebles</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>detalleBienesInmuebles</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>fechaInscripcion</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>inmuebles</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Bienes Inmuebles</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>bienesInmuebles</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>detalleBienesInmuebles</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>claveCat</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>inmuebles</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Bienes Inmuebles</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>bienesInmuebles</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>detalleBienesInmuebles</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>5</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>inmuebles</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Bienes Inmuebles</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>bienesInmuebles</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>detalleBienesInmuebles</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>regularizacionActivos</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>inmuebles</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Bienes Inmuebles</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>bienesInmuebles</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>detalleBienesInmuebles</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>anioFiscalAdquisicion</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>otros</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Otros Activos</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>otrosActivos</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>detalleOtrosActivos</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>7</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>otros</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Otros Activos</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>otrosActivos</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>detalleOtrosActivos</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>7</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>pais</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>otros</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Otros Activos</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>otrosActivos</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>detalleOtrosActivos</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>7</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>otros</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Otros Activos</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>otrosActivos</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>detalleOtrosActivos</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>7</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>valorTotal</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>otros</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Otros Activos</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>otrosActivos</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>detalleOtrosActivos</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>7</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>regularizacionActivos</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>otros</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Otros Activos</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>otrosActivos</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>detalleOtrosActivos</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>7</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>anioFiscalAdquisicion</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pasivos</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>detallePasivo</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>6</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>tipoAcreedor</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pasivos</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>detallePasivo</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>6</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>domicilioAcreedor</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pasivos</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>detallePasivo</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>6</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>valorDeuda</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Pasivos</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>detallePasivo</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>6</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>paisAcreedor</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pasivos</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>detallePasivo</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>nombreAcreedor</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Pasivos</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>detallePasivo</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>6</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>tipoIdentificacionAcreedor</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pasivos</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>detallePasivo</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>6</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>numeroIdentificacionAcreedor</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Pasivos</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>detallePasivo</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>6</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>numeroRegistroBancoCentral</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pasivos</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>detallePasivo</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>pasivo</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>6</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>partesRelacionadas</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2835,97 +6249,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="82" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>DINERO_EN</t>
         </is>
       </c>
-      <c r="B1" s="82" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>TIPO_INVERSION</t>
         </is>
       </c>
-      <c r="C1" s="82" t="inlineStr">
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>UBICACION</t>
         </is>
       </c>
-      <c r="D1" s="82" t="inlineStr">
+      <c r="D1" s="84" t="inlineStr">
         <is>
           <t>PAIS</t>
         </is>
       </c>
-      <c r="E1" s="82" t="inlineStr">
+      <c r="E1" s="84" t="inlineStr">
         <is>
           <t>INSTITUCION_FINANCIERA</t>
         </is>
       </c>
-      <c r="F1" s="82" t="inlineStr">
+      <c r="F1" s="84" t="inlineStr">
         <is>
           <t>PARTES_RELACIONADAS</t>
         </is>
       </c>
-      <c r="G1" s="82" t="inlineStr">
+      <c r="G1" s="84" t="inlineStr">
         <is>
           <t>TIPO_DRC</t>
         </is>
       </c>
-      <c r="H1" s="82" t="inlineStr">
+      <c r="H1" s="84" t="inlineStr">
         <is>
           <t>TIPO_PERSONA</t>
         </is>
       </c>
-      <c r="I1" s="82" t="inlineStr">
+      <c r="I1" s="84" t="inlineStr">
         <is>
           <t>TIPO_BIEN_MUEBLE</t>
         </is>
       </c>
-      <c r="J1" s="82" t="inlineStr">
+      <c r="J1" s="84" t="inlineStr">
         <is>
           <t>TIPO_VEHICULO</t>
         </is>
       </c>
-      <c r="K1" s="82" t="inlineStr">
+      <c r="K1" s="84" t="inlineStr">
         <is>
           <t>TIPO_DERECHO</t>
         </is>
       </c>
-      <c r="L1" s="82" t="inlineStr">
+      <c r="L1" s="84" t="inlineStr">
         <is>
           <t>TIPO_INMUEBLE</t>
         </is>
       </c>
-      <c r="M1" s="82" t="inlineStr">
+      <c r="M1" s="84" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="N1" s="82" t="inlineStr">
+      <c r="N1" s="84" t="inlineStr">
         <is>
           <t>CANTON</t>
         </is>
       </c>
-      <c r="O1" s="82" t="inlineStr">
+      <c r="O1" s="84" t="inlineStr">
         <is>
           <t>TIPO_ACREEDOR</t>
         </is>
       </c>
-      <c r="P1" s="82" t="inlineStr">
+      <c r="P1" s="84" t="inlineStr">
         <is>
           <t>TIPO_IDENTIFICACION</t>
         </is>
       </c>
-      <c r="Q1" s="82" t="inlineStr">
+      <c r="Q1" s="84" t="inlineStr">
         <is>
           <t>REGULARIZACION</t>
         </is>
       </c>
-      <c r="R1" s="82" t="inlineStr">
+      <c r="R1" s="84" t="inlineStr">
         <is>
           <t>JUSTIF_INCREMENTO</t>
         </is>
       </c>
-      <c r="S1" s="82" t="inlineStr">
+      <c r="S1" s="84" t="inlineStr">
         <is>
           <t>JUSTIF_DECREMENTO</t>
         </is>

--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -2555,7 +2555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2599,95 +2599,81 @@
     <row r="7">
       <c r="B7" s="78" t="inlineStr">
         <is>
-          <t>Dibuje el boton sobre este recuadro y asignele la macro GenerarXmlSRI</t>
+          <t>En el archivo .xlsm el boton verde ya esta vinculado a la macro GenerarXmlSRI.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="79" t="inlineStr">
         <is>
-          <t>CONFIGURACION POR UNICA VEZ (activa el boton)</t>
+          <t>COMO USAR ESTE ARCHIVO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="80" t="inlineStr">
         <is>
-          <t>1. Abra el editor de macros con la tecla  Alt + F11.</t>
+          <t>1. Al abrir el archivo .xlsm, pulse 'Habilitar contenido' en la barra de seguridad de Excel.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="80" t="inlineStr">
         <is>
-          <t>2. Menu Archivo &gt; Importar archivo... y seleccione el archivo GenerarXmlSRI.bas.</t>
+          <t>2. Llene las columnas amarillas de cada modulo (Dinero, Vehiculos, etc.) y la hoja Justificacion.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="80" t="inlineStr">
         <is>
-          <t>3. Cierre el editor y guarde este libro como  'Libro de Excel habilitado para macros (*.xlsm)'.</t>
+          <t>3. Pulse el boton verde GENERAR XML, indique el anio y elija donde guardar el archivo.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="80" t="inlineStr">
         <is>
-          <t>4. Active la pestana Programador:  Archivo &gt; Opciones &gt; Personalizar cinta de opciones &gt; marque 'Programador'.</t>
+          <t>4. El archivo .xml queda listo para subir al portal del SRI.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="80" t="inlineStr">
-        <is>
-          <t>5. Programador &gt; Insertar &gt; Boton (control de formulario) y dibujelo sobre el recuadro verde de arriba.</t>
-        </is>
-      </c>
+      <c r="B14" s="80" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="80" t="inlineStr">
-        <is>
-          <t>6. Cuando Excel lo solicite, asigne la macro  GenerarXmlSRI.</t>
+      <c r="B15" s="79" t="inlineStr">
+        <is>
+          <t>SI EXCEL BLOQUEA LAS MACROS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="80" t="inlineStr"/>
+      <c r="B16" s="80" t="inlineStr">
+        <is>
+          <t>- Cierre Excel. En el Explorador, clic derecho sobre el archivo &gt; Propiedades.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="79" t="inlineStr">
-        <is>
-          <t>USO DIARIO</t>
+      <c r="B17" s="80" t="inlineStr">
+        <is>
+          <t>- Al final de la pestana General marque 'Desbloquear' y pulse Aceptar.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="80" t="inlineStr">
         <is>
-          <t>7. Llene las columnas amarillas de cada modulo y la hoja Justificacion.</t>
+          <t>- Vuelva a abrirlo y pulse 'Habilitar contenido'. Conserve siempre la extension .xlsm.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="80" t="inlineStr">
-        <is>
-          <t>8. Pulse el boton GENERAR XML, indique el anio y elija donde guardar.</t>
-        </is>
-      </c>
+      <c r="B19" s="80" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="80" t="inlineStr">
-        <is>
-          <t>9. El archivo .xml queda listo para subir al portal del SRI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="80" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="80" t="inlineStr">
         <is>
           <t>Alternativa sin macros:  ejecutar  python tools/generar_xml_sri.py  desde la terminal.</t>
         </is>

--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;0.0%"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,6 +116,11 @@
     <font>
       <b val="1"/>
       <color rgb="0020507D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -227,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -236,8 +241,14 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -415,13 +426,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -437,11 +448,11 @@
     <xf numFmtId="164" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -648,144 +659,6 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Composicion de activos 2025</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Dashboard'!$B$12:$B$19</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dashboard'!$D$12:$D$19</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showPercent val="1"/>
-        </dLbls>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Variacion proyectada (2025 -&gt; 2026)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Dashboard'!F37</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Dashboard'!$B$38:$B$40</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dashboard'!$F$38:$F$40</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
               <a:t>Distribucion del incremento patrimonial</a:t>
             </a:r>
           </a:p>
@@ -829,7 +702,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -918,10 +791,10 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3060000"/>
+    <ext cx="7200000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -931,50 +804,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5040000" cy="3240000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="3060000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1321,7 +1150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1332,6 +1161,10 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1350,663 +1183,676 @@
     </row>
     <row r="3" ht="5" customHeight="1">
       <c r="A3" s="3" t="n"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>TIPO DE GRAFICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Columnas</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n"/>
     </row>
     <row r="5" ht="6" customHeight="1">
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="5" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>TOTAL ACTIVOS</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>TOTAL PASIVOS</t>
         </is>
       </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>PATRIMONIO NETO</t>
         </is>
       </c>
-      <c r="G6" s="13" t="n"/>
+      <c r="G6" s="15" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="14">
+      <c r="B7" s="16">
         <f>D20</f>
         <v/>
       </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="15">
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="17">
         <f>D25</f>
         <v/>
       </c>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="16">
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="18">
         <f>D31</f>
         <v/>
       </c>
-      <c r="G7" s="13" t="n"/>
+      <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Var. proyectada</t>
         </is>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="20">
         <f>G20</f>
         <v/>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>Var. proyectada</t>
         </is>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="22">
         <f>G25</f>
         <v/>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Var. proyectada</t>
         </is>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="24">
         <f>G31</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>ACTIVOS</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Dinero e inversiones</t>
         </is>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="29">
         <f>'Dinero'!J10</f>
         <v/>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="29">
         <f>'Dinero'!K10</f>
         <v/>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="29">
         <f>E12-D12</f>
         <v/>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="30">
         <f>IF(D12=0,"",(E12-D12)/D12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Derechos representativos de capital</t>
         </is>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="29">
         <f>'Derechos de Capital'!J14</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="29">
         <f>'Derechos de Capital'!K14</f>
         <v/>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="29">
         <f>E13-D13</f>
         <v/>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="30">
         <f>IF(D13=0,"",(E13-D13)/D13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Cuentas por cobrar</t>
         </is>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="29">
         <f>'Cuentas por Cobrar'!J14</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="29">
         <f>'Cuentas por Cobrar'!K14</f>
         <v/>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="29">
         <f>E14-D14</f>
         <v/>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="30">
         <f>IF(D14=0,"",(E14-D14)/D14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>Bienes muebles</t>
         </is>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="29">
         <f>'Bienes Muebles'!F14</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="29">
         <f>'Bienes Muebles'!G14</f>
         <v/>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="29">
         <f>E15-D15</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="30">
         <f>IF(D15=0,"",(E15-D15)/D15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Vehiculos, naves y aeronaves</t>
         </is>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="29">
         <f>'Vehiculos'!G9</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="29">
         <f>'Vehiculos'!H9</f>
         <v/>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="29">
         <f>E16-D16</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="30">
         <f>IF(D16=0,"",(E16-D16)/D16)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>Derechos (usufructo, uso, etc.)</t>
         </is>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="29">
         <f>'Derechos'!F14</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="29">
         <f>'Derechos'!G14</f>
         <v/>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="29">
         <f>E17-D17</f>
         <v/>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="30">
         <f>IF(D17=0,"",(E17-D17)/D17)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Bienes inmuebles</t>
         </is>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="29">
         <f>'Bienes Inmuebles'!J10</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="29">
         <f>'Bienes Inmuebles'!K10</f>
         <v/>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="29">
         <f>E18-D18</f>
         <v/>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="30">
         <f>IF(D18=0,"",(E18-D18)/D18)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Otros activos</t>
         </is>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="29">
         <f>'Otros Activos'!F14</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="29">
         <f>'Otros Activos'!G14</f>
         <v/>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="29">
         <f>E19-D19</f>
         <v/>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="30">
         <f>IF(D19=0,"",(E19-D19)/D19)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>TOTAL ACTIVOS</t>
         </is>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="32">
         <f>SUM(D12:D19)</f>
         <v/>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="32">
         <f>SUM(E12:E19)</f>
         <v/>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="32">
         <f>E20-D20</f>
         <v/>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="33">
         <f>IF(D20=0,"",(E20-D20)/D20)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>PASIVOS</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="C23" s="26" t="n"/>
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="F23" s="25" t="inlineStr">
+      <c r="F23" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G23" s="25" t="inlineStr">
+      <c r="G23" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="33" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Deudas y obligaciones</t>
         </is>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="36">
         <f>'Pasivos'!I8</f>
         <v/>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="36">
         <f>'Pasivos'!J8</f>
         <v/>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="36">
         <f>E24-D24</f>
         <v/>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="37">
         <f>IF(D24=0,"",(E24-D24)/D24)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="36" t="inlineStr">
+      <c r="B25" s="38" t="inlineStr">
         <is>
           <t>TOTAL PASIVOS</t>
         </is>
       </c>
-      <c r="D25" s="37">
+      <c r="D25" s="39">
         <f>SUM(D24:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="37">
+      <c r="E25" s="39">
         <f>SUM(E24:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="37">
+      <c r="F25" s="39">
         <f>E25-D25</f>
         <v/>
       </c>
-      <c r="G25" s="38">
+      <c r="G25" s="40">
         <f>IF(D25=0,"",(E25-D25)/D25)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="39" t="inlineStr">
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>PATRIMONIO NETO</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="F28" s="25" t="inlineStr">
+      <c r="F28" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G28" s="25" t="inlineStr">
+      <c r="G28" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="B29" s="40" t="inlineStr">
+      <c r="B29" s="42" t="inlineStr">
         <is>
           <t>(+) Total activos</t>
         </is>
       </c>
-      <c r="D29" s="41">
+      <c r="D29" s="43">
         <f>D20</f>
         <v/>
       </c>
-      <c r="E29" s="41">
+      <c r="E29" s="43">
         <f>E20</f>
         <v/>
       </c>
-      <c r="F29" s="41">
+      <c r="F29" s="43">
         <f>E29-D29</f>
         <v/>
       </c>
-      <c r="G29" s="42">
+      <c r="G29" s="44">
         <f>IF(D29=0,"",(E29-D29)/D29)</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="40" t="inlineStr">
+      <c r="B30" s="42" t="inlineStr">
         <is>
           <t>(-) Total pasivos</t>
         </is>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="43">
         <f>D25</f>
         <v/>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="43">
         <f>E25</f>
         <v/>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="43">
         <f>E30-D30</f>
         <v/>
       </c>
-      <c r="G30" s="42">
+      <c r="G30" s="44">
         <f>IF(D30=0,"",(E30-D30)/D30)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="43" t="inlineStr">
+      <c r="B31" s="45" t="inlineStr">
         <is>
           <t>(=) PATRIMONIO NETO</t>
         </is>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="46">
         <f>D29-D30</f>
         <v/>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="46">
         <f>E29-E30</f>
         <v/>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="46">
         <f>E31-D31</f>
         <v/>
       </c>
-      <c r="G31" s="45">
+      <c r="G31" s="47">
         <f>IF(D31=0,"",(E31-D31)/D31)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="46" t="inlineStr">
+      <c r="B32" s="48" t="inlineStr">
         <is>
           <t>Patrimonio declarado en el XML (2025)</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="47" t="n">
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="49" t="n">
         <v>883285.5600000001</v>
       </c>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="46" t="inlineStr">
+      <c r="B33" s="48" t="inlineStr">
         <is>
           <t>Patrimonio neto del anio anterior</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="47" t="n">
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="49" t="n">
         <v>801569.97</v>
       </c>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="46" t="inlineStr">
+      <c r="B34" s="48" t="inlineStr">
         <is>
           <t>Crecimiento / decremento patrimonial (XML)</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="47" t="n">
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="49" t="n">
         <v>81715.59</v>
       </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="48" t="inlineStr">
+      <c r="B36" s="50" t="inlineStr">
         <is>
           <t>CONSOLIDADO</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C37" s="24" t="n"/>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="27" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="F37" s="25" t="inlineStr">
+      <c r="F37" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G37" s="25" t="inlineStr">
+      <c r="G37" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="B38" s="49" t="inlineStr">
+      <c r="B38" s="51" t="inlineStr">
         <is>
           <t>Activos</t>
         </is>
       </c>
-      <c r="D38" s="50">
+      <c r="D38" s="52">
         <f>D20</f>
         <v/>
       </c>
-      <c r="E38" s="50">
+      <c r="E38" s="52">
         <f>E20</f>
         <v/>
       </c>
-      <c r="F38" s="50">
+      <c r="F38" s="52">
         <f>E38-D38</f>
         <v/>
       </c>
-      <c r="G38" s="51">
+      <c r="G38" s="53">
         <f>IF(D38=0,"",(E38-D38)/D38)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="B39" s="52" t="inlineStr">
+      <c r="B39" s="54" t="inlineStr">
         <is>
           <t>Pasivos</t>
         </is>
       </c>
-      <c r="D39" s="53">
+      <c r="D39" s="55">
         <f>D25</f>
         <v/>
       </c>
-      <c r="E39" s="53">
+      <c r="E39" s="55">
         <f>E25</f>
         <v/>
       </c>
-      <c r="F39" s="53">
+      <c r="F39" s="55">
         <f>E39-D39</f>
         <v/>
       </c>
-      <c r="G39" s="54">
+      <c r="G39" s="56">
         <f>IF(D39=0,"",(E39-D39)/D39)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="B40" s="55" t="inlineStr">
+      <c r="B40" s="57" t="inlineStr">
         <is>
           <t>Patrimonio neto</t>
         </is>
       </c>
-      <c r="D40" s="56">
+      <c r="D40" s="58">
         <f>D31</f>
         <v/>
       </c>
-      <c r="E40" s="56">
+      <c r="E40" s="58">
         <f>E31</f>
         <v/>
       </c>
-      <c r="F40" s="56">
+      <c r="F40" s="58">
         <f>E40-D40</f>
         <v/>
       </c>
-      <c r="G40" s="57">
+      <c r="G40" s="59">
         <f>IF(D40=0,"",(E40-D40)/D40)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="58" t="inlineStr">
+      <c r="B42" s="60" t="inlineStr">
         <is>
           <t>Edite las columnas amarillas en las hojas de cada modulo; las tarjetas, secciones y graficos se recalculan solos.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="42">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
@@ -2039,15 +1885,22 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="I4:J4"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B22:G22"/>
+    <mergeCell ref="I3:L3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="B32:C32"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="I4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Columnas,Barras,Pastel,Anillo,Lineas,Area"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2094,197 +1947,197 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Tipo de acreedor</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Domicilio del acreedor</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Nombre del acreedor</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>N. de identificacion</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>N. registro Banco Central</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>DINERS CLUB DEL ECUADOR</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="61" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="61" t="inlineStr">
         <is>
           <t>1792260957001</t>
         </is>
       </c>
-      <c r="G6" s="59" t="inlineStr"/>
-      <c r="H6" s="59" t="inlineStr">
+      <c r="G6" s="61" t="inlineStr"/>
+      <c r="H6" s="61" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="I6" s="60" t="n">
+      <c r="I6" s="62" t="n">
         <v>4891.88</v>
       </c>
-      <c r="J6" s="61" t="n">
+      <c r="J6" s="63" t="n">
         <v>4891.88</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="62">
         <f>J6-I6</f>
         <v/>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="64">
         <f>IF(I6=0,"",(J6-I6)/I6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C7" s="63" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D7" s="63" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>BANCO DEL PICHINCHA</t>
         </is>
       </c>
-      <c r="E7" s="63" t="inlineStr">
+      <c r="E7" s="65" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
-      <c r="F7" s="63" t="inlineStr">
+      <c r="F7" s="65" t="inlineStr">
         <is>
           <t>1790010937001</t>
         </is>
       </c>
-      <c r="G7" s="63" t="inlineStr"/>
-      <c r="H7" s="63" t="inlineStr">
+      <c r="G7" s="65" t="inlineStr"/>
+      <c r="H7" s="65" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="I7" s="64" t="n">
+      <c r="I7" s="66" t="n">
         <v>5547.31</v>
       </c>
-      <c r="J7" s="61" t="n">
+      <c r="J7" s="63" t="n">
         <v>5547.31</v>
       </c>
-      <c r="K7" s="64">
+      <c r="K7" s="66">
         <f>J7-I7</f>
         <v/>
       </c>
-      <c r="L7" s="65">
+      <c r="L7" s="67">
         <f>IF(I7=0,"",(J7-I7)/I7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="69" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="67" t="n"/>
-      <c r="C8" s="67" t="n"/>
-      <c r="D8" s="67" t="n"/>
-      <c r="E8" s="67" t="n"/>
-      <c r="F8" s="67" t="n"/>
-      <c r="G8" s="67" t="n"/>
-      <c r="H8" s="67" t="n"/>
-      <c r="I8" s="37">
+      <c r="B8" s="69" t="n"/>
+      <c r="C8" s="69" t="n"/>
+      <c r="D8" s="69" t="n"/>
+      <c r="E8" s="69" t="n"/>
+      <c r="F8" s="69" t="n"/>
+      <c r="G8" s="69" t="n"/>
+      <c r="H8" s="69" t="n"/>
+      <c r="I8" s="39">
         <f>SUM(I6:I7)</f>
         <v/>
       </c>
-      <c r="J8" s="37">
+      <c r="J8" s="39">
         <f>SUM(J6:J7)</f>
         <v/>
       </c>
-      <c r="K8" s="37">
+      <c r="K8" s="39">
         <f>J8-I8</f>
         <v/>
       </c>
-      <c r="L8" s="38">
+      <c r="L8" s="40">
         <f>IF(I8=0,"",(J8-I8)/I8)</f>
         <v/>
       </c>
@@ -2352,166 +2205,166 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="6" customHeight="1">
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="5" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>INCREMENTO PATRIMONIAL</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>TOTAL JUSTIFICADO</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>DIFERENCIA</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
+      <c r="G6" s="13" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="16">
+      <c r="B7" s="18">
         <f>E15</f>
         <v/>
       </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="14">
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="16">
         <f>E14</f>
         <v/>
       </c>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="15">
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="17">
         <f>E16</f>
         <v/>
       </c>
-      <c r="G7" s="11" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Declarado en el XML 2025</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Suma de montos asignados</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>Debe quedar en $0.00</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n"/>
+      <c r="G8" s="13" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
         <is>
           <t>DISTRIBUCION DEL INCREMENTO PATRIMONIAL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Concepto declarado (Tabla del SRI)</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>Monto asignado</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>% del total</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="68" t="inlineStr">
+      <c r="B12" s="70" t="inlineStr">
         <is>
           <t>1 - Ingresos locales</t>
         </is>
       </c>
-      <c r="E12" s="61" t="n">
+      <c r="E12" s="63" t="n">
         <v>40857.79</v>
       </c>
-      <c r="F12" s="62">
+      <c r="F12" s="64">
         <f>IF($E$14=0,"",E12/$E$14)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="68" t="inlineStr">
+      <c r="B13" s="70" t="inlineStr">
         <is>
           <t>6 - Otros</t>
         </is>
       </c>
-      <c r="E13" s="61" t="n">
+      <c r="E13" s="63" t="n">
         <v>40857.79</v>
       </c>
-      <c r="F13" s="62">
+      <c r="F13" s="64">
         <f>IF($E$14=0,"",E13/$E$14)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="69" t="inlineStr">
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>TOTAL JUSTIFICADO</t>
         </is>
       </c>
-      <c r="E14" s="70">
+      <c r="E14" s="72">
         <f>SUM(E12:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="71">
+      <c r="F14" s="73">
         <f>IF(E14=0,"",1)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="72" t="inlineStr">
+      <c r="B15" s="74" t="inlineStr">
         <is>
           <t>Incremento patrimonial declarado (XML)</t>
         </is>
       </c>
-      <c r="C15" s="73" t="n"/>
-      <c r="D15" s="73" t="n"/>
-      <c r="E15" s="74" t="n">
+      <c r="C15" s="75" t="n"/>
+      <c r="D15" s="75" t="n"/>
+      <c r="E15" s="76" t="n">
         <v>81715.59</v>
       </c>
-      <c r="F15" s="73" t="n"/>
+      <c r="F15" s="75" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="75" t="inlineStr">
+      <c r="B16" s="77" t="inlineStr">
         <is>
           <t>Diferencia por justificar (debe ser $0.00)</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="76">
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="78">
         <f>E15-E14</f>
         <v/>
       </c>
-      <c r="F16" s="13" t="n"/>
+      <c r="F16" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="58" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>Escoja el concepto en la lista desplegable (catalogo del SRI) y asigne el monto en la columna amarilla.</t>
         </is>
@@ -2583,97 +2436,97 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="77" t="inlineStr">
+      <c r="B5" s="79" t="inlineStr">
         <is>
           <t>►   GENERAR XML</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="78" t="inlineStr">
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>En el archivo .xlsm el boton verde ya esta vinculado a la macro GenerarXmlSRI.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="79" t="inlineStr">
+      <c r="B9" s="81" t="inlineStr">
         <is>
           <t>COMO USAR ESTE ARCHIVO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="80" t="inlineStr">
+      <c r="B10" s="82" t="inlineStr">
         <is>
           <t>1. Al abrir el archivo .xlsm, pulse 'Habilitar contenido' en la barra de seguridad de Excel.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="80" t="inlineStr">
+      <c r="B11" s="82" t="inlineStr">
         <is>
           <t>2. Llene las columnas amarillas de cada modulo (Dinero, Vehiculos, etc.) y la hoja Justificacion.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="80" t="inlineStr">
+      <c r="B12" s="82" t="inlineStr">
         <is>
           <t>3. Pulse el boton verde GENERAR XML, indique el anio y elija donde guardar el archivo.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="80" t="inlineStr">
+      <c r="B13" s="82" t="inlineStr">
         <is>
           <t>4. El archivo .xml queda listo para subir al portal del SRI.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="80" t="inlineStr"/>
+      <c r="B14" s="82" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="79" t="inlineStr">
+      <c r="B15" s="81" t="inlineStr">
         <is>
           <t>SI EXCEL BLOQUEA LAS MACROS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="80" t="inlineStr">
+      <c r="B16" s="82" t="inlineStr">
         <is>
           <t>- Cierre Excel. En el Explorador, clic derecho sobre el archivo &gt; Propiedades.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="80" t="inlineStr">
+      <c r="B17" s="82" t="inlineStr">
         <is>
           <t>- Al final de la pestana General marque 'Desbloquear' y pulse Aceptar.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="80" t="inlineStr">
+      <c r="B18" s="82" t="inlineStr">
         <is>
           <t>- Vuelva a abrirlo y pulse 'Habilitar contenido'. Conserve siempre la extension .xlsm.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="80" t="inlineStr"/>
+      <c r="B19" s="82" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="B20" s="80" t="inlineStr">
+      <c r="B20" s="82" t="inlineStr">
         <is>
           <t>Alternativa sin macros:  ejecutar  python tools/generar_xml_sri.py  desde la terminal.</t>
         </is>
@@ -2714,257 +2567,257 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="81" t="inlineStr">
+      <c r="A5" s="83" t="inlineStr">
         <is>
           <t>IDENTIFICACION</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="82" t="inlineStr">
+      <c r="A6" s="84" t="inlineStr">
         <is>
           <t>Anio de la declaracion</t>
         </is>
       </c>
-      <c r="B6" s="83" t="n">
+      <c r="B6" s="85" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="82" t="inlineStr">
+      <c r="A7" s="84" t="inlineStr">
         <is>
           <t>Tipo de declaracion</t>
         </is>
       </c>
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="85" t="inlineStr">
         <is>
           <t>SOC - Sociedad conyugal o union de hecho</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="82" t="inlineStr">
+      <c r="A8" s="84" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="B8" s="83" t="inlineStr">
+      <c r="B8" s="85" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="82" t="inlineStr">
+      <c r="A9" s="84" t="inlineStr">
         <is>
           <t>Numero de identificacion</t>
         </is>
       </c>
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="85" t="inlineStr">
         <is>
           <t>1709164899001</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="82" t="inlineStr">
+      <c r="A10" s="84" t="inlineStr">
         <is>
           <t>Nombre del declarante</t>
         </is>
       </c>
-      <c r="B10" s="83" t="inlineStr">
+      <c r="B10" s="85" t="inlineStr">
         <is>
           <t>GONZALEZ NAVAS MARCO VINICIO</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="82" t="inlineStr">
+      <c r="A11" s="84" t="inlineStr">
         <is>
           <t>Identificacion del conyuge</t>
         </is>
       </c>
-      <c r="B11" s="83" t="inlineStr">
+      <c r="B11" s="85" t="inlineStr">
         <is>
           <t>C - Cedula</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="82" t="inlineStr">
+      <c r="A12" s="84" t="inlineStr">
         <is>
           <t>Numero ident. conyuge</t>
         </is>
       </c>
-      <c r="B12" s="83" t="inlineStr">
+      <c r="B12" s="85" t="inlineStr">
         <is>
           <t>1709784225</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="82" t="inlineStr">
+      <c r="A13" s="84" t="inlineStr">
         <is>
           <t>Nombre del conyuge</t>
         </is>
       </c>
-      <c r="B13" s="83" t="inlineStr">
+      <c r="B13" s="85" t="inlineStr">
         <is>
           <t>HIDALGO LOZA ROSA CONSUELO</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="82" t="inlineStr">
+      <c r="A14" s="84" t="inlineStr">
         <is>
           <t>Total creditos / cuentas por cobrar</t>
         </is>
       </c>
-      <c r="B14" s="60" t="n">
+      <c r="B14" s="62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="81" t="inlineStr">
+      <c r="A16" s="83" t="inlineStr">
         <is>
           <t>PATRIMONIO NETO (enlazado a la hoja Dashboard)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="82" t="inlineStr">
+      <c r="A17" s="84" t="inlineStr">
         <is>
           <t>Patrimonio neto 2025</t>
         </is>
       </c>
-      <c r="B17" s="60">
+      <c r="B17" s="62">
         <f>Dashboard!D31</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="82" t="inlineStr">
+      <c r="A18" s="84" t="inlineStr">
         <is>
           <t>Patrimonio neto 2026 (proyectado)</t>
         </is>
       </c>
-      <c r="B18" s="60">
+      <c r="B18" s="62">
         <f>Dashboard!E31</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="82" t="inlineStr">
+      <c r="A19" s="84" t="inlineStr">
         <is>
           <t>Variacion proyectada</t>
         </is>
       </c>
-      <c r="B19" s="60">
+      <c r="B19" s="62">
         <f>Dashboard!F31</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="82" t="inlineStr">
+      <c r="A20" s="84" t="inlineStr">
         <is>
           <t>Variacion % proyectada</t>
         </is>
       </c>
-      <c r="B20" s="62">
+      <c r="B20" s="64">
         <f>Dashboard!G31</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="81" t="inlineStr">
+      <c r="A22" s="83" t="inlineStr">
         <is>
           <t>PATRIMONIO DECLARADO EN EL XML</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="82" t="inlineStr">
+      <c r="A23" s="84" t="inlineStr">
         <is>
           <t>Patrimonio total declarado</t>
         </is>
       </c>
-      <c r="B23" s="60" t="n">
+      <c r="B23" s="62" t="n">
         <v>883285.5600000001</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="82" t="inlineStr">
+      <c r="A24" s="84" t="inlineStr">
         <is>
           <t>Atribuible a hijos no emancipados</t>
         </is>
       </c>
-      <c r="B24" s="60" t="n">
+      <c r="B24" s="62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="82" t="inlineStr">
+      <c r="A25" s="84" t="inlineStr">
         <is>
           <t>Patrimonio en la sociedad conyugal</t>
         </is>
       </c>
-      <c r="B25" s="60" t="n">
+      <c r="B25" s="62" t="n">
         <v>883285.5600000001</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="82" t="inlineStr">
+      <c r="A26" s="84" t="inlineStr">
         <is>
           <t>Patrimonio individual del declarante</t>
         </is>
       </c>
-      <c r="B26" s="60" t="n">
+      <c r="B26" s="62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="82" t="inlineStr">
+      <c r="A27" s="84" t="inlineStr">
         <is>
           <t>Patrimonio del anio anterior</t>
         </is>
       </c>
-      <c r="B27" s="60" t="n">
+      <c r="B27" s="62" t="n">
         <v>801569.97</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="82" t="inlineStr">
+      <c r="A28" s="84" t="inlineStr">
         <is>
           <t>Crecimiento / decremento patrimonial</t>
         </is>
       </c>
-      <c r="B28" s="60" t="n">
+      <c r="B28" s="62" t="n">
         <v>81715.59</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="79" t="inlineStr">
+      <c r="A30" s="81" t="inlineStr">
         <is>
           <t>Justificacion de la variacion (ver hoja Justificacion)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="80" t="inlineStr">
+      <c r="A31" s="82" t="inlineStr">
         <is>
           <t>- 1 - Ingresos locales</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="80" t="inlineStr">
+      <c r="A32" s="82" t="inlineStr">
         <is>
           <t>- 6 - Otros</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="58" t="inlineStr">
+      <c r="A34" s="60" t="inlineStr">
         <is>
           <t>Catalogos del SRI integrados (Tablas 1-19 del archivo CATALOGO.xls). El XML se genera con generar_xml_sri.py.</t>
         </is>
@@ -6235,97 +6088,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="84" t="inlineStr">
+      <c r="A1" s="86" t="inlineStr">
         <is>
           <t>DINERO_EN</t>
         </is>
       </c>
-      <c r="B1" s="84" t="inlineStr">
+      <c r="B1" s="86" t="inlineStr">
         <is>
           <t>TIPO_INVERSION</t>
         </is>
       </c>
-      <c r="C1" s="84" t="inlineStr">
+      <c r="C1" s="86" t="inlineStr">
         <is>
           <t>UBICACION</t>
         </is>
       </c>
-      <c r="D1" s="84" t="inlineStr">
+      <c r="D1" s="86" t="inlineStr">
         <is>
           <t>PAIS</t>
         </is>
       </c>
-      <c r="E1" s="84" t="inlineStr">
+      <c r="E1" s="86" t="inlineStr">
         <is>
           <t>INSTITUCION_FINANCIERA</t>
         </is>
       </c>
-      <c r="F1" s="84" t="inlineStr">
+      <c r="F1" s="86" t="inlineStr">
         <is>
           <t>PARTES_RELACIONADAS</t>
         </is>
       </c>
-      <c r="G1" s="84" t="inlineStr">
+      <c r="G1" s="86" t="inlineStr">
         <is>
           <t>TIPO_DRC</t>
         </is>
       </c>
-      <c r="H1" s="84" t="inlineStr">
+      <c r="H1" s="86" t="inlineStr">
         <is>
           <t>TIPO_PERSONA</t>
         </is>
       </c>
-      <c r="I1" s="84" t="inlineStr">
+      <c r="I1" s="86" t="inlineStr">
         <is>
           <t>TIPO_BIEN_MUEBLE</t>
         </is>
       </c>
-      <c r="J1" s="84" t="inlineStr">
+      <c r="J1" s="86" t="inlineStr">
         <is>
           <t>TIPO_VEHICULO</t>
         </is>
       </c>
-      <c r="K1" s="84" t="inlineStr">
+      <c r="K1" s="86" t="inlineStr">
         <is>
           <t>TIPO_DERECHO</t>
         </is>
       </c>
-      <c r="L1" s="84" t="inlineStr">
+      <c r="L1" s="86" t="inlineStr">
         <is>
           <t>TIPO_INMUEBLE</t>
         </is>
       </c>
-      <c r="M1" s="84" t="inlineStr">
+      <c r="M1" s="86" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="N1" s="84" t="inlineStr">
+      <c r="N1" s="86" t="inlineStr">
         <is>
           <t>CANTON</t>
         </is>
       </c>
-      <c r="O1" s="84" t="inlineStr">
+      <c r="O1" s="86" t="inlineStr">
         <is>
           <t>TIPO_ACREEDOR</t>
         </is>
       </c>
-      <c r="P1" s="84" t="inlineStr">
+      <c r="P1" s="86" t="inlineStr">
         <is>
           <t>TIPO_IDENTIFICACION</t>
         </is>
       </c>
-      <c r="Q1" s="84" t="inlineStr">
+      <c r="Q1" s="86" t="inlineStr">
         <is>
           <t>REGULARIZACION</t>
         </is>
       </c>
-      <c r="R1" s="84" t="inlineStr">
+      <c r="R1" s="86" t="inlineStr">
         <is>
           <t>JUSTIF_INCREMENTO</t>
         </is>
       </c>
-      <c r="S1" s="84" t="inlineStr">
+      <c r="S1" s="86" t="inlineStr">
         <is>
           <t>JUSTIF_DECREMENTO</t>
         </is>
@@ -12859,311 +12712,311 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Dinero en</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Tipo de inversion</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Institucion financiera</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Tipo de moneda</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>3 - Cuenta de ahorros</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="61" t="inlineStr">
         <is>
           <t>1029 - BANCO PICHINCHA C.A.</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="61" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G6" s="59" t="inlineStr">
+      <c r="G6" s="61" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H6" s="59" t="inlineStr"/>
-      <c r="I6" s="59" t="inlineStr"/>
-      <c r="J6" s="60" t="n">
+      <c r="H6" s="61" t="inlineStr"/>
+      <c r="I6" s="61" t="inlineStr"/>
+      <c r="J6" s="62" t="n">
         <v>130.2</v>
       </c>
-      <c r="K6" s="61" t="n">
+      <c r="K6" s="63" t="n">
         <v>130.2</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="62">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="64">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>4 - Cuenta corriente</t>
         </is>
       </c>
-      <c r="C7" s="63" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D7" s="63" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E7" s="63" t="inlineStr">
+      <c r="E7" s="65" t="inlineStr">
         <is>
           <t>1029 - BANCO PICHINCHA C.A.</t>
         </is>
       </c>
-      <c r="F7" s="63" t="inlineStr">
+      <c r="F7" s="65" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G7" s="63" t="inlineStr">
+      <c r="G7" s="65" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H7" s="63" t="inlineStr"/>
-      <c r="I7" s="63" t="inlineStr"/>
-      <c r="J7" s="64" t="n">
+      <c r="H7" s="65" t="inlineStr"/>
+      <c r="I7" s="65" t="inlineStr"/>
+      <c r="J7" s="66" t="n">
         <v>5590.32</v>
       </c>
-      <c r="K7" s="61" t="n">
+      <c r="K7" s="63" t="n">
         <v>5590.32</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="66">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="65">
+      <c r="M7" s="67">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>3 - Cuenta de ahorros</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="61" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E8" s="61" t="inlineStr">
         <is>
           <t>1418 - BANCO PROMERICA S.A.</t>
         </is>
       </c>
-      <c r="F8" s="59" t="inlineStr">
+      <c r="F8" s="61" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G8" s="59" t="inlineStr">
+      <c r="G8" s="61" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H8" s="59" t="inlineStr"/>
-      <c r="I8" s="59" t="inlineStr"/>
-      <c r="J8" s="60" t="n">
+      <c r="H8" s="61" t="inlineStr"/>
+      <c r="I8" s="61" t="inlineStr"/>
+      <c r="J8" s="62" t="n">
         <v>53237.31</v>
       </c>
-      <c r="K8" s="61" t="n">
+      <c r="K8" s="63" t="n">
         <v>53237.31</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="62">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="62">
+      <c r="M8" s="64">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B9" s="63" t="inlineStr">
+      <c r="B9" s="65" t="inlineStr">
         <is>
           <t>2 - Inversiones financieras</t>
         </is>
       </c>
-      <c r="C9" s="63" t="inlineStr">
+      <c r="C9" s="65" t="inlineStr">
         <is>
           <t>EXT - En el exterior</t>
         </is>
       </c>
-      <c r="D9" s="63" t="inlineStr">
+      <c r="D9" s="65" t="inlineStr">
         <is>
           <t>118 - PANAMA</t>
         </is>
       </c>
-      <c r="E9" s="63" t="inlineStr">
+      <c r="E9" s="65" t="inlineStr">
         <is>
           <t>BANCO PICHINCHA CA</t>
         </is>
       </c>
-      <c r="F9" s="63" t="inlineStr">
+      <c r="F9" s="65" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G9" s="63" t="inlineStr">
+      <c r="G9" s="65" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H9" s="63" t="inlineStr"/>
-      <c r="I9" s="63" t="inlineStr"/>
-      <c r="J9" s="64" t="n">
+      <c r="H9" s="65" t="inlineStr"/>
+      <c r="I9" s="65" t="inlineStr"/>
+      <c r="J9" s="66" t="n">
         <v>189049.31</v>
       </c>
-      <c r="K9" s="61" t="n">
+      <c r="K9" s="63" t="n">
         <v>189049.31</v>
       </c>
-      <c r="L9" s="64">
+      <c r="L9" s="66">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="65">
+      <c r="M9" s="67">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="66" t="n"/>
-      <c r="C10" s="66" t="n"/>
-      <c r="D10" s="66" t="n"/>
-      <c r="E10" s="66" t="n"/>
-      <c r="F10" s="66" t="n"/>
-      <c r="G10" s="66" t="n"/>
-      <c r="H10" s="66" t="n"/>
-      <c r="I10" s="66" t="n"/>
-      <c r="J10" s="30">
+      <c r="B10" s="68" t="n"/>
+      <c r="C10" s="68" t="n"/>
+      <c r="D10" s="68" t="n"/>
+      <c r="E10" s="68" t="n"/>
+      <c r="F10" s="68" t="n"/>
+      <c r="G10" s="68" t="n"/>
+      <c r="H10" s="68" t="n"/>
+      <c r="I10" s="68" t="n"/>
+      <c r="J10" s="32">
         <f>SUM(J6:J9)</f>
         <v/>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="32">
         <f>SUM(K6:K9)</f>
         <v/>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="32">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="31">
+      <c r="M10" s="33">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
@@ -13243,299 +13096,299 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Tipo de inversion</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Empresa / Administradora / Fideicomiso</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>% de participacion</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>N. de acciones / participaciones</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr"/>
-      <c r="C6" s="59" t="inlineStr"/>
-      <c r="D6" s="59" t="inlineStr"/>
-      <c r="E6" s="59" t="inlineStr"/>
-      <c r="F6" s="59" t="inlineStr"/>
-      <c r="G6" s="59" t="inlineStr"/>
-      <c r="H6" s="59" t="inlineStr"/>
-      <c r="I6" s="59" t="inlineStr"/>
-      <c r="J6" s="61" t="n">
+      <c r="A6" s="61" t="inlineStr"/>
+      <c r="B6" s="61" t="inlineStr"/>
+      <c r="C6" s="61" t="inlineStr"/>
+      <c r="D6" s="61" t="inlineStr"/>
+      <c r="E6" s="61" t="inlineStr"/>
+      <c r="F6" s="61" t="inlineStr"/>
+      <c r="G6" s="61" t="inlineStr"/>
+      <c r="H6" s="61" t="inlineStr"/>
+      <c r="I6" s="61" t="inlineStr"/>
+      <c r="J6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="61" t="n">
+      <c r="K6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="62">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="64">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr"/>
-      <c r="C7" s="63" t="inlineStr"/>
-      <c r="D7" s="63" t="inlineStr"/>
-      <c r="E7" s="63" t="inlineStr"/>
-      <c r="F7" s="63" t="inlineStr"/>
-      <c r="G7" s="63" t="inlineStr"/>
-      <c r="H7" s="63" t="inlineStr"/>
-      <c r="I7" s="63" t="inlineStr"/>
-      <c r="J7" s="61" t="n">
+      <c r="A7" s="65" t="inlineStr"/>
+      <c r="B7" s="65" t="inlineStr"/>
+      <c r="C7" s="65" t="inlineStr"/>
+      <c r="D7" s="65" t="inlineStr"/>
+      <c r="E7" s="65" t="inlineStr"/>
+      <c r="F7" s="65" t="inlineStr"/>
+      <c r="G7" s="65" t="inlineStr"/>
+      <c r="H7" s="65" t="inlineStr"/>
+      <c r="I7" s="65" t="inlineStr"/>
+      <c r="J7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="61" t="n">
+      <c r="K7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="66">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="65">
+      <c r="M7" s="67">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr"/>
-      <c r="B8" s="59" t="inlineStr"/>
-      <c r="C8" s="59" t="inlineStr"/>
-      <c r="D8" s="59" t="inlineStr"/>
-      <c r="E8" s="59" t="inlineStr"/>
-      <c r="F8" s="59" t="inlineStr"/>
-      <c r="G8" s="59" t="inlineStr"/>
-      <c r="H8" s="59" t="inlineStr"/>
-      <c r="I8" s="59" t="inlineStr"/>
-      <c r="J8" s="61" t="n">
+      <c r="A8" s="61" t="inlineStr"/>
+      <c r="B8" s="61" t="inlineStr"/>
+      <c r="C8" s="61" t="inlineStr"/>
+      <c r="D8" s="61" t="inlineStr"/>
+      <c r="E8" s="61" t="inlineStr"/>
+      <c r="F8" s="61" t="inlineStr"/>
+      <c r="G8" s="61" t="inlineStr"/>
+      <c r="H8" s="61" t="inlineStr"/>
+      <c r="I8" s="61" t="inlineStr"/>
+      <c r="J8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="61" t="n">
+      <c r="K8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="62">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="62">
+      <c r="M8" s="64">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr"/>
-      <c r="C9" s="63" t="inlineStr"/>
-      <c r="D9" s="63" t="inlineStr"/>
-      <c r="E9" s="63" t="inlineStr"/>
-      <c r="F9" s="63" t="inlineStr"/>
-      <c r="G9" s="63" t="inlineStr"/>
-      <c r="H9" s="63" t="inlineStr"/>
-      <c r="I9" s="63" t="inlineStr"/>
-      <c r="J9" s="61" t="n">
+      <c r="A9" s="65" t="inlineStr"/>
+      <c r="B9" s="65" t="inlineStr"/>
+      <c r="C9" s="65" t="inlineStr"/>
+      <c r="D9" s="65" t="inlineStr"/>
+      <c r="E9" s="65" t="inlineStr"/>
+      <c r="F9" s="65" t="inlineStr"/>
+      <c r="G9" s="65" t="inlineStr"/>
+      <c r="H9" s="65" t="inlineStr"/>
+      <c r="I9" s="65" t="inlineStr"/>
+      <c r="J9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="61" t="n">
+      <c r="K9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="64">
+      <c r="L9" s="66">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="65">
+      <c r="M9" s="67">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr"/>
-      <c r="B10" s="59" t="inlineStr"/>
-      <c r="C10" s="59" t="inlineStr"/>
-      <c r="D10" s="59" t="inlineStr"/>
-      <c r="E10" s="59" t="inlineStr"/>
-      <c r="F10" s="59" t="inlineStr"/>
-      <c r="G10" s="59" t="inlineStr"/>
-      <c r="H10" s="59" t="inlineStr"/>
-      <c r="I10" s="59" t="inlineStr"/>
-      <c r="J10" s="61" t="n">
+      <c r="A10" s="61" t="inlineStr"/>
+      <c r="B10" s="61" t="inlineStr"/>
+      <c r="C10" s="61" t="inlineStr"/>
+      <c r="D10" s="61" t="inlineStr"/>
+      <c r="E10" s="61" t="inlineStr"/>
+      <c r="F10" s="61" t="inlineStr"/>
+      <c r="G10" s="61" t="inlineStr"/>
+      <c r="H10" s="61" t="inlineStr"/>
+      <c r="I10" s="61" t="inlineStr"/>
+      <c r="J10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="61" t="n">
+      <c r="K10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="60">
+      <c r="L10" s="62">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="62">
+      <c r="M10" s="64">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="63" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr"/>
-      <c r="C11" s="63" t="inlineStr"/>
-      <c r="D11" s="63" t="inlineStr"/>
-      <c r="E11" s="63" t="inlineStr"/>
-      <c r="F11" s="63" t="inlineStr"/>
-      <c r="G11" s="63" t="inlineStr"/>
-      <c r="H11" s="63" t="inlineStr"/>
-      <c r="I11" s="63" t="inlineStr"/>
-      <c r="J11" s="61" t="n">
+      <c r="A11" s="65" t="inlineStr"/>
+      <c r="B11" s="65" t="inlineStr"/>
+      <c r="C11" s="65" t="inlineStr"/>
+      <c r="D11" s="65" t="inlineStr"/>
+      <c r="E11" s="65" t="inlineStr"/>
+      <c r="F11" s="65" t="inlineStr"/>
+      <c r="G11" s="65" t="inlineStr"/>
+      <c r="H11" s="65" t="inlineStr"/>
+      <c r="I11" s="65" t="inlineStr"/>
+      <c r="J11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="61" t="n">
+      <c r="K11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="64">
+      <c r="L11" s="66">
         <f>K11-J11</f>
         <v/>
       </c>
-      <c r="M11" s="65">
+      <c r="M11" s="67">
         <f>IF(J11=0,"",(K11-J11)/J11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr"/>
-      <c r="B12" s="59" t="inlineStr"/>
-      <c r="C12" s="59" t="inlineStr"/>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr"/>
-      <c r="F12" s="59" t="inlineStr"/>
-      <c r="G12" s="59" t="inlineStr"/>
-      <c r="H12" s="59" t="inlineStr"/>
-      <c r="I12" s="59" t="inlineStr"/>
-      <c r="J12" s="61" t="n">
+      <c r="A12" s="61" t="inlineStr"/>
+      <c r="B12" s="61" t="inlineStr"/>
+      <c r="C12" s="61" t="inlineStr"/>
+      <c r="D12" s="61" t="inlineStr"/>
+      <c r="E12" s="61" t="inlineStr"/>
+      <c r="F12" s="61" t="inlineStr"/>
+      <c r="G12" s="61" t="inlineStr"/>
+      <c r="H12" s="61" t="inlineStr"/>
+      <c r="I12" s="61" t="inlineStr"/>
+      <c r="J12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="61" t="n">
+      <c r="K12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="60">
+      <c r="L12" s="62">
         <f>K12-J12</f>
         <v/>
       </c>
-      <c r="M12" s="62">
+      <c r="M12" s="64">
         <f>IF(J12=0,"",(K12-J12)/J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr"/>
-      <c r="C13" s="63" t="inlineStr"/>
-      <c r="D13" s="63" t="inlineStr"/>
-      <c r="E13" s="63" t="inlineStr"/>
-      <c r="F13" s="63" t="inlineStr"/>
-      <c r="G13" s="63" t="inlineStr"/>
-      <c r="H13" s="63" t="inlineStr"/>
-      <c r="I13" s="63" t="inlineStr"/>
-      <c r="J13" s="61" t="n">
+      <c r="A13" s="65" t="inlineStr"/>
+      <c r="B13" s="65" t="inlineStr"/>
+      <c r="C13" s="65" t="inlineStr"/>
+      <c r="D13" s="65" t="inlineStr"/>
+      <c r="E13" s="65" t="inlineStr"/>
+      <c r="F13" s="65" t="inlineStr"/>
+      <c r="G13" s="65" t="inlineStr"/>
+      <c r="H13" s="65" t="inlineStr"/>
+      <c r="I13" s="65" t="inlineStr"/>
+      <c r="J13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="61" t="n">
+      <c r="K13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="64">
+      <c r="L13" s="66">
         <f>K13-J13</f>
         <v/>
       </c>
-      <c r="M13" s="65">
+      <c r="M13" s="67">
         <f>IF(J13=0,"",(K13-J13)/J13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="66" t="n"/>
-      <c r="G14" s="66" t="n"/>
-      <c r="H14" s="66" t="n"/>
-      <c r="I14" s="66" t="n"/>
-      <c r="J14" s="30">
+      <c r="B14" s="68" t="n"/>
+      <c r="C14" s="68" t="n"/>
+      <c r="D14" s="68" t="n"/>
+      <c r="E14" s="68" t="n"/>
+      <c r="F14" s="68" t="n"/>
+      <c r="G14" s="68" t="n"/>
+      <c r="H14" s="68" t="n"/>
+      <c r="I14" s="68" t="n"/>
+      <c r="J14" s="32">
         <f>SUM(J6:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="32">
         <f>SUM(K6:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="30">
+      <c r="L14" s="32">
         <f>K14-J14</f>
         <v/>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="33">
         <f>IF(J14=0,"",(K14-J14)/J14)</f>
         <v/>
       </c>
@@ -13609,299 +13462,299 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Nombre del deudor</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Tipo de deudor</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>N. de identificacion</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr"/>
-      <c r="C6" s="59" t="inlineStr"/>
-      <c r="D6" s="59" t="inlineStr"/>
-      <c r="E6" s="59" t="inlineStr"/>
-      <c r="F6" s="59" t="inlineStr"/>
-      <c r="G6" s="59" t="inlineStr"/>
-      <c r="H6" s="59" t="inlineStr"/>
-      <c r="I6" s="59" t="inlineStr"/>
-      <c r="J6" s="61" t="n">
+      <c r="A6" s="61" t="inlineStr"/>
+      <c r="B6" s="61" t="inlineStr"/>
+      <c r="C6" s="61" t="inlineStr"/>
+      <c r="D6" s="61" t="inlineStr"/>
+      <c r="E6" s="61" t="inlineStr"/>
+      <c r="F6" s="61" t="inlineStr"/>
+      <c r="G6" s="61" t="inlineStr"/>
+      <c r="H6" s="61" t="inlineStr"/>
+      <c r="I6" s="61" t="inlineStr"/>
+      <c r="J6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="61" t="n">
+      <c r="K6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="62">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="64">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr"/>
-      <c r="C7" s="63" t="inlineStr"/>
-      <c r="D7" s="63" t="inlineStr"/>
-      <c r="E7" s="63" t="inlineStr"/>
-      <c r="F7" s="63" t="inlineStr"/>
-      <c r="G7" s="63" t="inlineStr"/>
-      <c r="H7" s="63" t="inlineStr"/>
-      <c r="I7" s="63" t="inlineStr"/>
-      <c r="J7" s="61" t="n">
+      <c r="A7" s="65" t="inlineStr"/>
+      <c r="B7" s="65" t="inlineStr"/>
+      <c r="C7" s="65" t="inlineStr"/>
+      <c r="D7" s="65" t="inlineStr"/>
+      <c r="E7" s="65" t="inlineStr"/>
+      <c r="F7" s="65" t="inlineStr"/>
+      <c r="G7" s="65" t="inlineStr"/>
+      <c r="H7" s="65" t="inlineStr"/>
+      <c r="I7" s="65" t="inlineStr"/>
+      <c r="J7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="61" t="n">
+      <c r="K7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="66">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="65">
+      <c r="M7" s="67">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr"/>
-      <c r="B8" s="59" t="inlineStr"/>
-      <c r="C8" s="59" t="inlineStr"/>
-      <c r="D8" s="59" t="inlineStr"/>
-      <c r="E8" s="59" t="inlineStr"/>
-      <c r="F8" s="59" t="inlineStr"/>
-      <c r="G8" s="59" t="inlineStr"/>
-      <c r="H8" s="59" t="inlineStr"/>
-      <c r="I8" s="59" t="inlineStr"/>
-      <c r="J8" s="61" t="n">
+      <c r="A8" s="61" t="inlineStr"/>
+      <c r="B8" s="61" t="inlineStr"/>
+      <c r="C8" s="61" t="inlineStr"/>
+      <c r="D8" s="61" t="inlineStr"/>
+      <c r="E8" s="61" t="inlineStr"/>
+      <c r="F8" s="61" t="inlineStr"/>
+      <c r="G8" s="61" t="inlineStr"/>
+      <c r="H8" s="61" t="inlineStr"/>
+      <c r="I8" s="61" t="inlineStr"/>
+      <c r="J8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="61" t="n">
+      <c r="K8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="62">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="62">
+      <c r="M8" s="64">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr"/>
-      <c r="C9" s="63" t="inlineStr"/>
-      <c r="D9" s="63" t="inlineStr"/>
-      <c r="E9" s="63" t="inlineStr"/>
-      <c r="F9" s="63" t="inlineStr"/>
-      <c r="G9" s="63" t="inlineStr"/>
-      <c r="H9" s="63" t="inlineStr"/>
-      <c r="I9" s="63" t="inlineStr"/>
-      <c r="J9" s="61" t="n">
+      <c r="A9" s="65" t="inlineStr"/>
+      <c r="B9" s="65" t="inlineStr"/>
+      <c r="C9" s="65" t="inlineStr"/>
+      <c r="D9" s="65" t="inlineStr"/>
+      <c r="E9" s="65" t="inlineStr"/>
+      <c r="F9" s="65" t="inlineStr"/>
+      <c r="G9" s="65" t="inlineStr"/>
+      <c r="H9" s="65" t="inlineStr"/>
+      <c r="I9" s="65" t="inlineStr"/>
+      <c r="J9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="61" t="n">
+      <c r="K9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="64">
+      <c r="L9" s="66">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="65">
+      <c r="M9" s="67">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr"/>
-      <c r="B10" s="59" t="inlineStr"/>
-      <c r="C10" s="59" t="inlineStr"/>
-      <c r="D10" s="59" t="inlineStr"/>
-      <c r="E10" s="59" t="inlineStr"/>
-      <c r="F10" s="59" t="inlineStr"/>
-      <c r="G10" s="59" t="inlineStr"/>
-      <c r="H10" s="59" t="inlineStr"/>
-      <c r="I10" s="59" t="inlineStr"/>
-      <c r="J10" s="61" t="n">
+      <c r="A10" s="61" t="inlineStr"/>
+      <c r="B10" s="61" t="inlineStr"/>
+      <c r="C10" s="61" t="inlineStr"/>
+      <c r="D10" s="61" t="inlineStr"/>
+      <c r="E10" s="61" t="inlineStr"/>
+      <c r="F10" s="61" t="inlineStr"/>
+      <c r="G10" s="61" t="inlineStr"/>
+      <c r="H10" s="61" t="inlineStr"/>
+      <c r="I10" s="61" t="inlineStr"/>
+      <c r="J10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="61" t="n">
+      <c r="K10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="60">
+      <c r="L10" s="62">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="62">
+      <c r="M10" s="64">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="63" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr"/>
-      <c r="C11" s="63" t="inlineStr"/>
-      <c r="D11" s="63" t="inlineStr"/>
-      <c r="E11" s="63" t="inlineStr"/>
-      <c r="F11" s="63" t="inlineStr"/>
-      <c r="G11" s="63" t="inlineStr"/>
-      <c r="H11" s="63" t="inlineStr"/>
-      <c r="I11" s="63" t="inlineStr"/>
-      <c r="J11" s="61" t="n">
+      <c r="A11" s="65" t="inlineStr"/>
+      <c r="B11" s="65" t="inlineStr"/>
+      <c r="C11" s="65" t="inlineStr"/>
+      <c r="D11" s="65" t="inlineStr"/>
+      <c r="E11" s="65" t="inlineStr"/>
+      <c r="F11" s="65" t="inlineStr"/>
+      <c r="G11" s="65" t="inlineStr"/>
+      <c r="H11" s="65" t="inlineStr"/>
+      <c r="I11" s="65" t="inlineStr"/>
+      <c r="J11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="61" t="n">
+      <c r="K11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="64">
+      <c r="L11" s="66">
         <f>K11-J11</f>
         <v/>
       </c>
-      <c r="M11" s="65">
+      <c r="M11" s="67">
         <f>IF(J11=0,"",(K11-J11)/J11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr"/>
-      <c r="B12" s="59" t="inlineStr"/>
-      <c r="C12" s="59" t="inlineStr"/>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr"/>
-      <c r="F12" s="59" t="inlineStr"/>
-      <c r="G12" s="59" t="inlineStr"/>
-      <c r="H12" s="59" t="inlineStr"/>
-      <c r="I12" s="59" t="inlineStr"/>
-      <c r="J12" s="61" t="n">
+      <c r="A12" s="61" t="inlineStr"/>
+      <c r="B12" s="61" t="inlineStr"/>
+      <c r="C12" s="61" t="inlineStr"/>
+      <c r="D12" s="61" t="inlineStr"/>
+      <c r="E12" s="61" t="inlineStr"/>
+      <c r="F12" s="61" t="inlineStr"/>
+      <c r="G12" s="61" t="inlineStr"/>
+      <c r="H12" s="61" t="inlineStr"/>
+      <c r="I12" s="61" t="inlineStr"/>
+      <c r="J12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="61" t="n">
+      <c r="K12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="60">
+      <c r="L12" s="62">
         <f>K12-J12</f>
         <v/>
       </c>
-      <c r="M12" s="62">
+      <c r="M12" s="64">
         <f>IF(J12=0,"",(K12-J12)/J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr"/>
-      <c r="C13" s="63" t="inlineStr"/>
-      <c r="D13" s="63" t="inlineStr"/>
-      <c r="E13" s="63" t="inlineStr"/>
-      <c r="F13" s="63" t="inlineStr"/>
-      <c r="G13" s="63" t="inlineStr"/>
-      <c r="H13" s="63" t="inlineStr"/>
-      <c r="I13" s="63" t="inlineStr"/>
-      <c r="J13" s="61" t="n">
+      <c r="A13" s="65" t="inlineStr"/>
+      <c r="B13" s="65" t="inlineStr"/>
+      <c r="C13" s="65" t="inlineStr"/>
+      <c r="D13" s="65" t="inlineStr"/>
+      <c r="E13" s="65" t="inlineStr"/>
+      <c r="F13" s="65" t="inlineStr"/>
+      <c r="G13" s="65" t="inlineStr"/>
+      <c r="H13" s="65" t="inlineStr"/>
+      <c r="I13" s="65" t="inlineStr"/>
+      <c r="J13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="61" t="n">
+      <c r="K13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="64">
+      <c r="L13" s="66">
         <f>K13-J13</f>
         <v/>
       </c>
-      <c r="M13" s="65">
+      <c r="M13" s="67">
         <f>IF(J13=0,"",(K13-J13)/J13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="66" t="n"/>
-      <c r="G14" s="66" t="n"/>
-      <c r="H14" s="66" t="n"/>
-      <c r="I14" s="66" t="n"/>
-      <c r="J14" s="30">
+      <c r="B14" s="68" t="n"/>
+      <c r="C14" s="68" t="n"/>
+      <c r="D14" s="68" t="n"/>
+      <c r="E14" s="68" t="n"/>
+      <c r="F14" s="68" t="n"/>
+      <c r="G14" s="68" t="n"/>
+      <c r="H14" s="68" t="n"/>
+      <c r="I14" s="68" t="n"/>
+      <c r="J14" s="32">
         <f>SUM(J6:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="32">
         <f>SUM(K6:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="30">
+      <c r="L14" s="32">
         <f>K14-J14</f>
         <v/>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="33">
         <f>IF(J14=0,"",(K14-J14)/J14)</f>
         <v/>
       </c>
@@ -13974,243 +13827,243 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Tipo de bien</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr"/>
-      <c r="C6" s="59" t="inlineStr"/>
-      <c r="D6" s="59" t="inlineStr"/>
-      <c r="E6" s="59" t="inlineStr"/>
-      <c r="F6" s="61" t="n">
+      <c r="A6" s="61" t="inlineStr"/>
+      <c r="B6" s="61" t="inlineStr"/>
+      <c r="C6" s="61" t="inlineStr"/>
+      <c r="D6" s="61" t="inlineStr"/>
+      <c r="E6" s="61" t="inlineStr"/>
+      <c r="F6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="61" t="n">
+      <c r="G6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="62">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="64">
         <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr"/>
-      <c r="C7" s="63" t="inlineStr"/>
-      <c r="D7" s="63" t="inlineStr"/>
-      <c r="E7" s="63" t="inlineStr"/>
-      <c r="F7" s="61" t="n">
+      <c r="A7" s="65" t="inlineStr"/>
+      <c r="B7" s="65" t="inlineStr"/>
+      <c r="C7" s="65" t="inlineStr"/>
+      <c r="D7" s="65" t="inlineStr"/>
+      <c r="E7" s="65" t="inlineStr"/>
+      <c r="F7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="61" t="n">
+      <c r="G7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="64">
+      <c r="H7" s="66">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="65">
+      <c r="I7" s="67">
         <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr"/>
-      <c r="B8" s="59" t="inlineStr"/>
-      <c r="C8" s="59" t="inlineStr"/>
-      <c r="D8" s="59" t="inlineStr"/>
-      <c r="E8" s="59" t="inlineStr"/>
-      <c r="F8" s="61" t="n">
+      <c r="A8" s="61" t="inlineStr"/>
+      <c r="B8" s="61" t="inlineStr"/>
+      <c r="C8" s="61" t="inlineStr"/>
+      <c r="D8" s="61" t="inlineStr"/>
+      <c r="E8" s="61" t="inlineStr"/>
+      <c r="F8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="61" t="n">
+      <c r="G8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="62">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="64">
         <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr"/>
-      <c r="C9" s="63" t="inlineStr"/>
-      <c r="D9" s="63" t="inlineStr"/>
-      <c r="E9" s="63" t="inlineStr"/>
-      <c r="F9" s="61" t="n">
+      <c r="A9" s="65" t="inlineStr"/>
+      <c r="B9" s="65" t="inlineStr"/>
+      <c r="C9" s="65" t="inlineStr"/>
+      <c r="D9" s="65" t="inlineStr"/>
+      <c r="E9" s="65" t="inlineStr"/>
+      <c r="F9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="61" t="n">
+      <c r="G9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="64">
+      <c r="H9" s="66">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="65">
+      <c r="I9" s="67">
         <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr"/>
-      <c r="B10" s="59" t="inlineStr"/>
-      <c r="C10" s="59" t="inlineStr"/>
-      <c r="D10" s="59" t="inlineStr"/>
-      <c r="E10" s="59" t="inlineStr"/>
-      <c r="F10" s="61" t="n">
+      <c r="A10" s="61" t="inlineStr"/>
+      <c r="B10" s="61" t="inlineStr"/>
+      <c r="C10" s="61" t="inlineStr"/>
+      <c r="D10" s="61" t="inlineStr"/>
+      <c r="E10" s="61" t="inlineStr"/>
+      <c r="F10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="61" t="n">
+      <c r="G10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="60">
+      <c r="H10" s="62">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="62">
+      <c r="I10" s="64">
         <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="63" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr"/>
-      <c r="C11" s="63" t="inlineStr"/>
-      <c r="D11" s="63" t="inlineStr"/>
-      <c r="E11" s="63" t="inlineStr"/>
-      <c r="F11" s="61" t="n">
+      <c r="A11" s="65" t="inlineStr"/>
+      <c r="B11" s="65" t="inlineStr"/>
+      <c r="C11" s="65" t="inlineStr"/>
+      <c r="D11" s="65" t="inlineStr"/>
+      <c r="E11" s="65" t="inlineStr"/>
+      <c r="F11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="61" t="n">
+      <c r="G11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="66">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="65">
+      <c r="I11" s="67">
         <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr"/>
-      <c r="B12" s="59" t="inlineStr"/>
-      <c r="C12" s="59" t="inlineStr"/>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr"/>
-      <c r="F12" s="61" t="n">
+      <c r="A12" s="61" t="inlineStr"/>
+      <c r="B12" s="61" t="inlineStr"/>
+      <c r="C12" s="61" t="inlineStr"/>
+      <c r="D12" s="61" t="inlineStr"/>
+      <c r="E12" s="61" t="inlineStr"/>
+      <c r="F12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="61" t="n">
+      <c r="G12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="60">
+      <c r="H12" s="62">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="62">
+      <c r="I12" s="64">
         <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr"/>
-      <c r="C13" s="63" t="inlineStr"/>
-      <c r="D13" s="63" t="inlineStr"/>
-      <c r="E13" s="63" t="inlineStr"/>
-      <c r="F13" s="61" t="n">
+      <c r="A13" s="65" t="inlineStr"/>
+      <c r="B13" s="65" t="inlineStr"/>
+      <c r="C13" s="65" t="inlineStr"/>
+      <c r="D13" s="65" t="inlineStr"/>
+      <c r="E13" s="65" t="inlineStr"/>
+      <c r="F13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="61" t="n">
+      <c r="G13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="64">
+      <c r="H13" s="66">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="65">
+      <c r="I13" s="67">
         <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="30">
+      <c r="B14" s="68" t="n"/>
+      <c r="C14" s="68" t="n"/>
+      <c r="D14" s="68" t="n"/>
+      <c r="E14" s="68" t="n"/>
+      <c r="F14" s="32">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="32">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="32">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="33">
         <f>IF(F14=0,"",(G14-F14)/F14)</f>
         <v/>
       </c>
@@ -14278,195 +14131,195 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Tipo de vehiculo</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Registro / placa / chasis</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>1 - Vehiculos motorizados terrestres</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>PBO7092</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr"/>
-      <c r="F6" s="59" t="inlineStr"/>
-      <c r="G6" s="60" t="n">
+      <c r="E6" s="61" t="inlineStr"/>
+      <c r="F6" s="61" t="inlineStr"/>
+      <c r="G6" s="62" t="n">
         <v>12000</v>
       </c>
-      <c r="H6" s="61" t="n">
+      <c r="H6" s="63" t="n">
         <v>12000</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="62">
         <f>H6-G6</f>
         <v/>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="64">
         <f>IF(G6=0,"",(H6-G6)/G6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>1 - Vehiculos motorizados terrestres</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>PBF9690</t>
         </is>
       </c>
-      <c r="C7" s="63" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D7" s="63" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E7" s="63" t="inlineStr"/>
-      <c r="F7" s="63" t="inlineStr"/>
-      <c r="G7" s="64" t="n">
+      <c r="E7" s="65" t="inlineStr"/>
+      <c r="F7" s="65" t="inlineStr"/>
+      <c r="G7" s="66" t="n">
         <v>20000</v>
       </c>
-      <c r="H7" s="61" t="n">
+      <c r="H7" s="63" t="n">
         <v>20000</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="66">
         <f>H7-G7</f>
         <v/>
       </c>
-      <c r="J7" s="65">
+      <c r="J7" s="67">
         <f>IF(G7=0,"",(H7-G7)/G7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>1 - Vehiculos motorizados terrestres</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>PFC8683</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="61" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr"/>
-      <c r="F8" s="59" t="inlineStr"/>
-      <c r="G8" s="60" t="n">
+      <c r="E8" s="61" t="inlineStr"/>
+      <c r="F8" s="61" t="inlineStr"/>
+      <c r="G8" s="62" t="n">
         <v>32000</v>
       </c>
-      <c r="H8" s="61" t="n">
+      <c r="H8" s="63" t="n">
         <v>32000</v>
       </c>
-      <c r="I8" s="60">
+      <c r="I8" s="62">
         <f>H8-G8</f>
         <v/>
       </c>
-      <c r="J8" s="62">
+      <c r="J8" s="64">
         <f>IF(G8=0,"",(H8-G8)/G8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="66" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="66" t="n"/>
-      <c r="C9" s="66" t="n"/>
-      <c r="D9" s="66" t="n"/>
-      <c r="E9" s="66" t="n"/>
-      <c r="F9" s="66" t="n"/>
-      <c r="G9" s="30">
+      <c r="B9" s="68" t="n"/>
+      <c r="C9" s="68" t="n"/>
+      <c r="D9" s="68" t="n"/>
+      <c r="E9" s="68" t="n"/>
+      <c r="F9" s="68" t="n"/>
+      <c r="G9" s="32">
         <f>SUM(G6:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="32">
         <f>SUM(H6:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="32">
         <f>H9-G9</f>
         <v/>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="33">
         <f>IF(G9=0,"",(H9-G9)/G9)</f>
         <v/>
       </c>
@@ -14533,243 +14386,243 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Tipo de derecho</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr"/>
-      <c r="C6" s="59" t="inlineStr"/>
-      <c r="D6" s="59" t="inlineStr"/>
-      <c r="E6" s="59" t="inlineStr"/>
-      <c r="F6" s="61" t="n">
+      <c r="A6" s="61" t="inlineStr"/>
+      <c r="B6" s="61" t="inlineStr"/>
+      <c r="C6" s="61" t="inlineStr"/>
+      <c r="D6" s="61" t="inlineStr"/>
+      <c r="E6" s="61" t="inlineStr"/>
+      <c r="F6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="61" t="n">
+      <c r="G6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="62">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="64">
         <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr"/>
-      <c r="C7" s="63" t="inlineStr"/>
-      <c r="D7" s="63" t="inlineStr"/>
-      <c r="E7" s="63" t="inlineStr"/>
-      <c r="F7" s="61" t="n">
+      <c r="A7" s="65" t="inlineStr"/>
+      <c r="B7" s="65" t="inlineStr"/>
+      <c r="C7" s="65" t="inlineStr"/>
+      <c r="D7" s="65" t="inlineStr"/>
+      <c r="E7" s="65" t="inlineStr"/>
+      <c r="F7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="61" t="n">
+      <c r="G7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="64">
+      <c r="H7" s="66">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="65">
+      <c r="I7" s="67">
         <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr"/>
-      <c r="B8" s="59" t="inlineStr"/>
-      <c r="C8" s="59" t="inlineStr"/>
-      <c r="D8" s="59" t="inlineStr"/>
-      <c r="E8" s="59" t="inlineStr"/>
-      <c r="F8" s="61" t="n">
+      <c r="A8" s="61" t="inlineStr"/>
+      <c r="B8" s="61" t="inlineStr"/>
+      <c r="C8" s="61" t="inlineStr"/>
+      <c r="D8" s="61" t="inlineStr"/>
+      <c r="E8" s="61" t="inlineStr"/>
+      <c r="F8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="61" t="n">
+      <c r="G8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="62">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="64">
         <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr"/>
-      <c r="C9" s="63" t="inlineStr"/>
-      <c r="D9" s="63" t="inlineStr"/>
-      <c r="E9" s="63" t="inlineStr"/>
-      <c r="F9" s="61" t="n">
+      <c r="A9" s="65" t="inlineStr"/>
+      <c r="B9" s="65" t="inlineStr"/>
+      <c r="C9" s="65" t="inlineStr"/>
+      <c r="D9" s="65" t="inlineStr"/>
+      <c r="E9" s="65" t="inlineStr"/>
+      <c r="F9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="61" t="n">
+      <c r="G9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="64">
+      <c r="H9" s="66">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="65">
+      <c r="I9" s="67">
         <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr"/>
-      <c r="B10" s="59" t="inlineStr"/>
-      <c r="C10" s="59" t="inlineStr"/>
-      <c r="D10" s="59" t="inlineStr"/>
-      <c r="E10" s="59" t="inlineStr"/>
-      <c r="F10" s="61" t="n">
+      <c r="A10" s="61" t="inlineStr"/>
+      <c r="B10" s="61" t="inlineStr"/>
+      <c r="C10" s="61" t="inlineStr"/>
+      <c r="D10" s="61" t="inlineStr"/>
+      <c r="E10" s="61" t="inlineStr"/>
+      <c r="F10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="61" t="n">
+      <c r="G10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="60">
+      <c r="H10" s="62">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="62">
+      <c r="I10" s="64">
         <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="63" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr"/>
-      <c r="C11" s="63" t="inlineStr"/>
-      <c r="D11" s="63" t="inlineStr"/>
-      <c r="E11" s="63" t="inlineStr"/>
-      <c r="F11" s="61" t="n">
+      <c r="A11" s="65" t="inlineStr"/>
+      <c r="B11" s="65" t="inlineStr"/>
+      <c r="C11" s="65" t="inlineStr"/>
+      <c r="D11" s="65" t="inlineStr"/>
+      <c r="E11" s="65" t="inlineStr"/>
+      <c r="F11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="61" t="n">
+      <c r="G11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="66">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="65">
+      <c r="I11" s="67">
         <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr"/>
-      <c r="B12" s="59" t="inlineStr"/>
-      <c r="C12" s="59" t="inlineStr"/>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr"/>
-      <c r="F12" s="61" t="n">
+      <c r="A12" s="61" t="inlineStr"/>
+      <c r="B12" s="61" t="inlineStr"/>
+      <c r="C12" s="61" t="inlineStr"/>
+      <c r="D12" s="61" t="inlineStr"/>
+      <c r="E12" s="61" t="inlineStr"/>
+      <c r="F12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="61" t="n">
+      <c r="G12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="60">
+      <c r="H12" s="62">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="62">
+      <c r="I12" s="64">
         <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr"/>
-      <c r="C13" s="63" t="inlineStr"/>
-      <c r="D13" s="63" t="inlineStr"/>
-      <c r="E13" s="63" t="inlineStr"/>
-      <c r="F13" s="61" t="n">
+      <c r="A13" s="65" t="inlineStr"/>
+      <c r="B13" s="65" t="inlineStr"/>
+      <c r="C13" s="65" t="inlineStr"/>
+      <c r="D13" s="65" t="inlineStr"/>
+      <c r="E13" s="65" t="inlineStr"/>
+      <c r="F13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="61" t="n">
+      <c r="G13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="64">
+      <c r="H13" s="66">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="65">
+      <c r="I13" s="67">
         <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="30">
+      <c r="B14" s="68" t="n"/>
+      <c r="C14" s="68" t="n"/>
+      <c r="D14" s="68" t="n"/>
+      <c r="E14" s="68" t="n"/>
+      <c r="F14" s="32">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="32">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="32">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="33">
         <f>IF(F14=0,"",(G14-F14)/F14)</f>
         <v/>
       </c>
@@ -14840,303 +14693,303 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Tipo de inmueble</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Canton</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Fecha de inscripcion</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Clave catastral</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>3 - Terreno</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="61" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="61" t="inlineStr">
         <is>
           <t>22/10/2008</t>
         </is>
       </c>
-      <c r="G6" s="59" t="inlineStr">
+      <c r="G6" s="61" t="inlineStr">
         <is>
           <t>1042203018</t>
         </is>
       </c>
-      <c r="H6" s="59" t="inlineStr"/>
-      <c r="I6" s="59" t="inlineStr"/>
-      <c r="J6" s="60" t="n">
+      <c r="H6" s="61" t="inlineStr"/>
+      <c r="I6" s="61" t="inlineStr"/>
+      <c r="J6" s="62" t="n">
         <v>267340.8</v>
       </c>
-      <c r="K6" s="61" t="n">
+      <c r="K6" s="63" t="n">
         <v>267340.8</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="62">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="64">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>1 - Casa</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C7" s="63" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D7" s="63" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E7" s="63" t="inlineStr">
+      <c r="E7" s="65" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F7" s="63" t="inlineStr">
+      <c r="F7" s="65" t="inlineStr">
         <is>
           <t>13/03/1997</t>
         </is>
       </c>
-      <c r="G7" s="63" t="inlineStr">
+      <c r="G7" s="65" t="inlineStr">
         <is>
           <t>1012005008000000000</t>
         </is>
       </c>
-      <c r="H7" s="63" t="inlineStr"/>
-      <c r="I7" s="63" t="inlineStr"/>
-      <c r="J7" s="64" t="n">
+      <c r="H7" s="65" t="inlineStr"/>
+      <c r="I7" s="65" t="inlineStr"/>
+      <c r="J7" s="66" t="n">
         <v>198118.55</v>
       </c>
-      <c r="K7" s="61" t="n">
+      <c r="K7" s="63" t="n">
         <v>198118.55</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="66">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="65">
+      <c r="M7" s="67">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>1 - Casa</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="61" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E8" s="61" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F8" s="59" t="inlineStr"/>
-      <c r="G8" s="59" t="inlineStr">
+      <c r="F8" s="61" t="inlineStr"/>
+      <c r="G8" s="61" t="inlineStr">
         <is>
           <t>1042203018</t>
         </is>
       </c>
-      <c r="H8" s="59" t="inlineStr"/>
-      <c r="I8" s="59" t="inlineStr"/>
-      <c r="J8" s="60" t="n">
+      <c r="H8" s="61" t="inlineStr"/>
+      <c r="I8" s="61" t="inlineStr"/>
+      <c r="J8" s="62" t="n">
         <v>33634.04</v>
       </c>
-      <c r="K8" s="61" t="n">
+      <c r="K8" s="63" t="n">
         <v>33634.04</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="62">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="62">
+      <c r="M8" s="64">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>3 - Terreno</t>
         </is>
       </c>
-      <c r="B9" s="63" t="inlineStr">
+      <c r="B9" s="65" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C9" s="63" t="inlineStr">
+      <c r="C9" s="65" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D9" s="63" t="inlineStr">
+      <c r="D9" s="65" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E9" s="63" t="inlineStr">
+      <c r="E9" s="65" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F9" s="63" t="inlineStr"/>
-      <c r="G9" s="63" t="inlineStr">
+      <c r="F9" s="65" t="inlineStr"/>
+      <c r="G9" s="65" t="inlineStr">
         <is>
           <t>1012005008000000000</t>
         </is>
       </c>
-      <c r="H9" s="63" t="inlineStr"/>
-      <c r="I9" s="63" t="inlineStr"/>
-      <c r="J9" s="64" t="n">
+      <c r="H9" s="65" t="inlineStr"/>
+      <c r="I9" s="65" t="inlineStr"/>
+      <c r="J9" s="66" t="n">
         <v>82624.22</v>
       </c>
-      <c r="K9" s="61" t="n">
+      <c r="K9" s="63" t="n">
         <v>82624.22</v>
       </c>
-      <c r="L9" s="64">
+      <c r="L9" s="66">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="65">
+      <c r="M9" s="67">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="66" t="n"/>
-      <c r="C10" s="66" t="n"/>
-      <c r="D10" s="66" t="n"/>
-      <c r="E10" s="66" t="n"/>
-      <c r="F10" s="66" t="n"/>
-      <c r="G10" s="66" t="n"/>
-      <c r="H10" s="66" t="n"/>
-      <c r="I10" s="66" t="n"/>
-      <c r="J10" s="30">
+      <c r="B10" s="68" t="n"/>
+      <c r="C10" s="68" t="n"/>
+      <c r="D10" s="68" t="n"/>
+      <c r="E10" s="68" t="n"/>
+      <c r="F10" s="68" t="n"/>
+      <c r="G10" s="68" t="n"/>
+      <c r="H10" s="68" t="n"/>
+      <c r="I10" s="68" t="n"/>
+      <c r="J10" s="32">
         <f>SUM(J6:J9)</f>
         <v/>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="32">
         <f>SUM(K6:K9)</f>
         <v/>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="32">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="31">
+      <c r="M10" s="33">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
@@ -15209,243 +15062,243 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Descripcion</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr"/>
-      <c r="C6" s="59" t="inlineStr"/>
-      <c r="D6" s="59" t="inlineStr"/>
-      <c r="E6" s="59" t="inlineStr"/>
-      <c r="F6" s="61" t="n">
+      <c r="A6" s="61" t="inlineStr"/>
+      <c r="B6" s="61" t="inlineStr"/>
+      <c r="C6" s="61" t="inlineStr"/>
+      <c r="D6" s="61" t="inlineStr"/>
+      <c r="E6" s="61" t="inlineStr"/>
+      <c r="F6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="61" t="n">
+      <c r="G6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="62">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="64">
         <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr"/>
-      <c r="C7" s="63" t="inlineStr"/>
-      <c r="D7" s="63" t="inlineStr"/>
-      <c r="E7" s="63" t="inlineStr"/>
-      <c r="F7" s="61" t="n">
+      <c r="A7" s="65" t="inlineStr"/>
+      <c r="B7" s="65" t="inlineStr"/>
+      <c r="C7" s="65" t="inlineStr"/>
+      <c r="D7" s="65" t="inlineStr"/>
+      <c r="E7" s="65" t="inlineStr"/>
+      <c r="F7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="61" t="n">
+      <c r="G7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="64">
+      <c r="H7" s="66">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="65">
+      <c r="I7" s="67">
         <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr"/>
-      <c r="B8" s="59" t="inlineStr"/>
-      <c r="C8" s="59" t="inlineStr"/>
-      <c r="D8" s="59" t="inlineStr"/>
-      <c r="E8" s="59" t="inlineStr"/>
-      <c r="F8" s="61" t="n">
+      <c r="A8" s="61" t="inlineStr"/>
+      <c r="B8" s="61" t="inlineStr"/>
+      <c r="C8" s="61" t="inlineStr"/>
+      <c r="D8" s="61" t="inlineStr"/>
+      <c r="E8" s="61" t="inlineStr"/>
+      <c r="F8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="61" t="n">
+      <c r="G8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="62">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="64">
         <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr"/>
-      <c r="C9" s="63" t="inlineStr"/>
-      <c r="D9" s="63" t="inlineStr"/>
-      <c r="E9" s="63" t="inlineStr"/>
-      <c r="F9" s="61" t="n">
+      <c r="A9" s="65" t="inlineStr"/>
+      <c r="B9" s="65" t="inlineStr"/>
+      <c r="C9" s="65" t="inlineStr"/>
+      <c r="D9" s="65" t="inlineStr"/>
+      <c r="E9" s="65" t="inlineStr"/>
+      <c r="F9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="61" t="n">
+      <c r="G9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="64">
+      <c r="H9" s="66">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="65">
+      <c r="I9" s="67">
         <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr"/>
-      <c r="B10" s="59" t="inlineStr"/>
-      <c r="C10" s="59" t="inlineStr"/>
-      <c r="D10" s="59" t="inlineStr"/>
-      <c r="E10" s="59" t="inlineStr"/>
-      <c r="F10" s="61" t="n">
+      <c r="A10" s="61" t="inlineStr"/>
+      <c r="B10" s="61" t="inlineStr"/>
+      <c r="C10" s="61" t="inlineStr"/>
+      <c r="D10" s="61" t="inlineStr"/>
+      <c r="E10" s="61" t="inlineStr"/>
+      <c r="F10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="61" t="n">
+      <c r="G10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="60">
+      <c r="H10" s="62">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="62">
+      <c r="I10" s="64">
         <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="63" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr"/>
-      <c r="C11" s="63" t="inlineStr"/>
-      <c r="D11" s="63" t="inlineStr"/>
-      <c r="E11" s="63" t="inlineStr"/>
-      <c r="F11" s="61" t="n">
+      <c r="A11" s="65" t="inlineStr"/>
+      <c r="B11" s="65" t="inlineStr"/>
+      <c r="C11" s="65" t="inlineStr"/>
+      <c r="D11" s="65" t="inlineStr"/>
+      <c r="E11" s="65" t="inlineStr"/>
+      <c r="F11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="61" t="n">
+      <c r="G11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="66">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="65">
+      <c r="I11" s="67">
         <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr"/>
-      <c r="B12" s="59" t="inlineStr"/>
-      <c r="C12" s="59" t="inlineStr"/>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr"/>
-      <c r="F12" s="61" t="n">
+      <c r="A12" s="61" t="inlineStr"/>
+      <c r="B12" s="61" t="inlineStr"/>
+      <c r="C12" s="61" t="inlineStr"/>
+      <c r="D12" s="61" t="inlineStr"/>
+      <c r="E12" s="61" t="inlineStr"/>
+      <c r="F12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="61" t="n">
+      <c r="G12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="60">
+      <c r="H12" s="62">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="62">
+      <c r="I12" s="64">
         <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr"/>
-      <c r="C13" s="63" t="inlineStr"/>
-      <c r="D13" s="63" t="inlineStr"/>
-      <c r="E13" s="63" t="inlineStr"/>
-      <c r="F13" s="61" t="n">
+      <c r="A13" s="65" t="inlineStr"/>
+      <c r="B13" s="65" t="inlineStr"/>
+      <c r="C13" s="65" t="inlineStr"/>
+      <c r="D13" s="65" t="inlineStr"/>
+      <c r="E13" s="65" t="inlineStr"/>
+      <c r="F13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="61" t="n">
+      <c r="G13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="64">
+      <c r="H13" s="66">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="65">
+      <c r="I13" s="67">
         <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="30">
+      <c r="B14" s="68" t="n"/>
+      <c r="C14" s="68" t="n"/>
+      <c r="D14" s="68" t="n"/>
+      <c r="E14" s="68" t="n"/>
+      <c r="F14" s="32">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="32">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="32">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="33">
         <f>IF(F14=0,"",(G14-F14)/F14)</f>
         <v/>
       </c>

--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -2197,7 +2197,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Conceptos declarados en el XML  -  ejercicio 2025  (TABLA 14 - incremento)</t>
+          <t>Conceptos declarados en el XML  -  ejercicio 2025  (catalogo Tabla 14 del SRI)</t>
         </is>
       </c>
     </row>

--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;0.0%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,10 +122,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
@@ -232,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -423,18 +419,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -442,17 +426,14 @@
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -647,144 +628,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Distribucion del incremento patrimonial</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Justificacion'!$B$12:$B$13</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Justificacion'!$E$12:$E$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showPercent val="1"/>
-        </dLbls>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Monto asignado por concepto</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Justificacion'!E11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Justificacion'!$B$12:$B$13</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Justificacion'!$E$12:$E$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -804,55 +647,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="3240000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2175,16 +1969,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2197,208 +1989,148 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Conceptos declarados en el XML  -  ejercicio 2025  (catalogo Tabla 14 del SRI)</t>
+          <t>Marque 'Si' los conceptos que justifican la variacion patrimonial  -  ejercicio 2025</t>
         </is>
       </c>
     </row>
     <row r="3" ht="5" customHeight="1">
       <c r="A3" s="3" t="n"/>
     </row>
-    <row r="5" ht="6" customHeight="1">
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>INCREMENTO PATRIMONIAL</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>TOTAL JUSTIFICADO</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>DIFERENCIA</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="n"/>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="18">
-        <f>E15</f>
-        <v/>
-      </c>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="16">
-        <f>E14</f>
-        <v/>
-      </c>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="17">
-        <f>E16</f>
-        <v/>
-      </c>
-      <c r="G7" s="13" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>Declarado en el XML 2025</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>Suma de montos asignados</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>Debe quedar en $0.00</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="n"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="70" t="inlineStr">
+        <is>
+          <t>Incremento patrimonial declarado en el XML</t>
+        </is>
+      </c>
+      <c r="C5" s="71" t="n"/>
+      <c r="D5" s="71" t="n"/>
+      <c r="E5" s="72" t="n">
+        <v>81715.59</v>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Concepto (Tabla 14 del SRI)</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>Justifica la variacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="73" t="inlineStr">
+        <is>
+          <t>1 - Ingresos locales</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="73" t="inlineStr">
+        <is>
+          <t>2 - Ingresos exterior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="50" t="inlineStr">
-        <is>
-          <t>DISTRIBUCION DEL INCREMENTO PATRIMONIAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>Concepto declarado (Tabla del SRI)</t>
-        </is>
-      </c>
-      <c r="E11" s="27" t="inlineStr">
-        <is>
-          <t>Monto asignado</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="inlineStr">
-        <is>
-          <t>% del total</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="70" t="inlineStr">
-        <is>
-          <t>1 - Ingresos locales</t>
-        </is>
-      </c>
-      <c r="E12" s="63" t="n">
-        <v>40857.79</v>
-      </c>
-      <c r="F12" s="64">
-        <f>IF($E$14=0,"",E12/$E$14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="70" t="inlineStr">
+      <c r="B10" s="73" t="inlineStr">
+        <is>
+          <t>3 - Herencias, legados o donaciones</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="73" t="inlineStr">
+        <is>
+          <t>4 - Loterias o rifas</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="73" t="inlineStr">
+        <is>
+          <t>5 - Ganancias de capital</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="73" t="inlineStr">
         <is>
           <t>6 - Otros</t>
         </is>
       </c>
-      <c r="E13" s="63" t="n">
-        <v>40857.79</v>
-      </c>
-      <c r="F13" s="64">
-        <f>IF($E$14=0,"",E13/$E$14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="71" t="inlineStr">
-        <is>
-          <t>TOTAL JUSTIFICADO</t>
-        </is>
-      </c>
-      <c r="E14" s="72">
-        <f>SUM(E12:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="73">
-        <f>IF(E14=0,"",1)</f>
-        <v/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="74" t="inlineStr">
-        <is>
-          <t>Incremento patrimonial declarado (XML)</t>
-        </is>
-      </c>
-      <c r="C15" s="75" t="n"/>
-      <c r="D15" s="75" t="n"/>
-      <c r="E15" s="76" t="n">
-        <v>81715.59</v>
-      </c>
-      <c r="F15" s="75" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="77" t="inlineStr">
-        <is>
-          <t>Diferencia por justificar (debe ser $0.00)</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="78">
-        <f>E15-E14</f>
-        <v/>
-      </c>
-      <c r="F16" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="60" t="inlineStr">
-        <is>
-          <t>Escoja el concepto en la lista desplegable (catalogo del SRI) y asigne el monto en la columna amarilla.</t>
+      <c r="B15" s="60" t="inlineStr">
+        <is>
+          <t>Esta hoja reproduce la seccion Justificacion del formulario del SRI. Marque 'Si' en los conceptos que apliquen; el generador de XML los toma de aqui.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="11">
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="B13:D13"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B12:B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Catalogos!$R$2:$R$7</formula1>
+    <dataValidation sqref="E8:E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Si,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2436,7 +2168,7 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="79" t="inlineStr">
+      <c r="B5" s="74" t="inlineStr">
         <is>
           <t>►   GENERAR XML</t>
         </is>
@@ -2450,83 +2182,83 @@
       <c r="D6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="80" t="inlineStr">
+      <c r="B7" s="75" t="inlineStr">
         <is>
           <t>En el archivo .xlsm el boton verde ya esta vinculado a la macro GenerarXmlSRI.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="81" t="inlineStr">
+      <c r="B9" s="76" t="inlineStr">
         <is>
           <t>COMO USAR ESTE ARCHIVO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="82" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>1. Al abrir el archivo .xlsm, pulse 'Habilitar contenido' en la barra de seguridad de Excel.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="82" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>2. Llene las columnas amarillas de cada modulo (Dinero, Vehiculos, etc.) y la hoja Justificacion.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="82" t="inlineStr">
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>3. Pulse el boton verde GENERAR XML, indique el anio y elija donde guardar el archivo.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="82" t="inlineStr">
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>4. El archivo .xml queda listo para subir al portal del SRI.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="82" t="inlineStr"/>
+      <c r="B14" s="77" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="81" t="inlineStr">
+      <c r="B15" s="76" t="inlineStr">
         <is>
           <t>SI EXCEL BLOQUEA LAS MACROS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="82" t="inlineStr">
+      <c r="B16" s="77" t="inlineStr">
         <is>
           <t>- Cierre Excel. En el Explorador, clic derecho sobre el archivo &gt; Propiedades.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="82" t="inlineStr">
+      <c r="B17" s="77" t="inlineStr">
         <is>
           <t>- Al final de la pestana General marque 'Desbloquear' y pulse Aceptar.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="82" t="inlineStr">
+      <c r="B18" s="77" t="inlineStr">
         <is>
           <t>- Vuelva a abrirlo y pulse 'Habilitar contenido'. Conserve siempre la extension .xlsm.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="82" t="inlineStr"/>
+      <c r="B19" s="77" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="B20" s="82" t="inlineStr">
+      <c r="B20" s="77" t="inlineStr">
         <is>
           <t>Alternativa sin macros:  ejecutar  python tools/generar_xml_sri.py  desde la terminal.</t>
         </is>
@@ -2567,108 +2299,108 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="83" t="inlineStr">
+      <c r="A5" s="78" t="inlineStr">
         <is>
           <t>IDENTIFICACION</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="84" t="inlineStr">
+      <c r="A6" s="79" t="inlineStr">
         <is>
           <t>Anio de la declaracion</t>
         </is>
       </c>
-      <c r="B6" s="85" t="n">
+      <c r="B6" s="80" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="84" t="inlineStr">
+      <c r="A7" s="79" t="inlineStr">
         <is>
           <t>Tipo de declaracion</t>
         </is>
       </c>
-      <c r="B7" s="85" t="inlineStr">
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>SOC - Sociedad conyugal o union de hecho</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="84" t="inlineStr">
+      <c r="A8" s="79" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="B8" s="85" t="inlineStr">
+      <c r="B8" s="80" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="84" t="inlineStr">
+      <c r="A9" s="79" t="inlineStr">
         <is>
           <t>Numero de identificacion</t>
         </is>
       </c>
-      <c r="B9" s="85" t="inlineStr">
+      <c r="B9" s="80" t="inlineStr">
         <is>
           <t>1709164899001</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="84" t="inlineStr">
+      <c r="A10" s="79" t="inlineStr">
         <is>
           <t>Nombre del declarante</t>
         </is>
       </c>
-      <c r="B10" s="85" t="inlineStr">
+      <c r="B10" s="80" t="inlineStr">
         <is>
           <t>GONZALEZ NAVAS MARCO VINICIO</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="84" t="inlineStr">
+      <c r="A11" s="79" t="inlineStr">
         <is>
           <t>Identificacion del conyuge</t>
         </is>
       </c>
-      <c r="B11" s="85" t="inlineStr">
+      <c r="B11" s="80" t="inlineStr">
         <is>
           <t>C - Cedula</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="84" t="inlineStr">
+      <c r="A12" s="79" t="inlineStr">
         <is>
           <t>Numero ident. conyuge</t>
         </is>
       </c>
-      <c r="B12" s="85" t="inlineStr">
+      <c r="B12" s="80" t="inlineStr">
         <is>
           <t>1709784225</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="84" t="inlineStr">
+      <c r="A13" s="79" t="inlineStr">
         <is>
           <t>Nombre del conyuge</t>
         </is>
       </c>
-      <c r="B13" s="85" t="inlineStr">
+      <c r="B13" s="80" t="inlineStr">
         <is>
           <t>HIDALGO LOZA ROSA CONSUELO</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="84" t="inlineStr">
+      <c r="A14" s="79" t="inlineStr">
         <is>
           <t>Total creditos / cuentas por cobrar</t>
         </is>
@@ -2678,14 +2410,14 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="83" t="inlineStr">
+      <c r="A16" s="78" t="inlineStr">
         <is>
           <t>PATRIMONIO NETO (enlazado a la hoja Dashboard)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="84" t="inlineStr">
+      <c r="A17" s="79" t="inlineStr">
         <is>
           <t>Patrimonio neto 2025</t>
         </is>
@@ -2696,7 +2428,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="84" t="inlineStr">
+      <c r="A18" s="79" t="inlineStr">
         <is>
           <t>Patrimonio neto 2026 (proyectado)</t>
         </is>
@@ -2707,7 +2439,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="84" t="inlineStr">
+      <c r="A19" s="79" t="inlineStr">
         <is>
           <t>Variacion proyectada</t>
         </is>
@@ -2718,7 +2450,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="84" t="inlineStr">
+      <c r="A20" s="79" t="inlineStr">
         <is>
           <t>Variacion % proyectada</t>
         </is>
@@ -2729,14 +2461,14 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="83" t="inlineStr">
+      <c r="A22" s="78" t="inlineStr">
         <is>
           <t>PATRIMONIO DECLARADO EN EL XML</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="84" t="inlineStr">
+      <c r="A23" s="79" t="inlineStr">
         <is>
           <t>Patrimonio total declarado</t>
         </is>
@@ -2746,7 +2478,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="84" t="inlineStr">
+      <c r="A24" s="79" t="inlineStr">
         <is>
           <t>Atribuible a hijos no emancipados</t>
         </is>
@@ -2756,7 +2488,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="84" t="inlineStr">
+      <c r="A25" s="79" t="inlineStr">
         <is>
           <t>Patrimonio en la sociedad conyugal</t>
         </is>
@@ -2766,7 +2498,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="84" t="inlineStr">
+      <c r="A26" s="79" t="inlineStr">
         <is>
           <t>Patrimonio individual del declarante</t>
         </is>
@@ -2776,7 +2508,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="84" t="inlineStr">
+      <c r="A27" s="79" t="inlineStr">
         <is>
           <t>Patrimonio del anio anterior</t>
         </is>
@@ -2786,7 +2518,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="84" t="inlineStr">
+      <c r="A28" s="79" t="inlineStr">
         <is>
           <t>Crecimiento / decremento patrimonial</t>
         </is>
@@ -2796,21 +2528,21 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="81" t="inlineStr">
+      <c r="A30" s="76" t="inlineStr">
         <is>
           <t>Justificacion de la variacion (ver hoja Justificacion)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="82" t="inlineStr">
+      <c r="A31" s="77" t="inlineStr">
         <is>
           <t>- 1 - Ingresos locales</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="82" t="inlineStr">
+      <c r="A32" s="77" t="inlineStr">
         <is>
           <t>- 6 - Otros</t>
         </is>
@@ -6088,97 +5820,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="86" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>DINERO_EN</t>
         </is>
       </c>
-      <c r="B1" s="86" t="inlineStr">
+      <c r="B1" s="81" t="inlineStr">
         <is>
           <t>TIPO_INVERSION</t>
         </is>
       </c>
-      <c r="C1" s="86" t="inlineStr">
+      <c r="C1" s="81" t="inlineStr">
         <is>
           <t>UBICACION</t>
         </is>
       </c>
-      <c r="D1" s="86" t="inlineStr">
+      <c r="D1" s="81" t="inlineStr">
         <is>
           <t>PAIS</t>
         </is>
       </c>
-      <c r="E1" s="86" t="inlineStr">
+      <c r="E1" s="81" t="inlineStr">
         <is>
           <t>INSTITUCION_FINANCIERA</t>
         </is>
       </c>
-      <c r="F1" s="86" t="inlineStr">
+      <c r="F1" s="81" t="inlineStr">
         <is>
           <t>PARTES_RELACIONADAS</t>
         </is>
       </c>
-      <c r="G1" s="86" t="inlineStr">
+      <c r="G1" s="81" t="inlineStr">
         <is>
           <t>TIPO_DRC</t>
         </is>
       </c>
-      <c r="H1" s="86" t="inlineStr">
+      <c r="H1" s="81" t="inlineStr">
         <is>
           <t>TIPO_PERSONA</t>
         </is>
       </c>
-      <c r="I1" s="86" t="inlineStr">
+      <c r="I1" s="81" t="inlineStr">
         <is>
           <t>TIPO_BIEN_MUEBLE</t>
         </is>
       </c>
-      <c r="J1" s="86" t="inlineStr">
+      <c r="J1" s="81" t="inlineStr">
         <is>
           <t>TIPO_VEHICULO</t>
         </is>
       </c>
-      <c r="K1" s="86" t="inlineStr">
+      <c r="K1" s="81" t="inlineStr">
         <is>
           <t>TIPO_DERECHO</t>
         </is>
       </c>
-      <c r="L1" s="86" t="inlineStr">
+      <c r="L1" s="81" t="inlineStr">
         <is>
           <t>TIPO_INMUEBLE</t>
         </is>
       </c>
-      <c r="M1" s="86" t="inlineStr">
+      <c r="M1" s="81" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="N1" s="86" t="inlineStr">
+      <c r="N1" s="81" t="inlineStr">
         <is>
           <t>CANTON</t>
         </is>
       </c>
-      <c r="O1" s="86" t="inlineStr">
+      <c r="O1" s="81" t="inlineStr">
         <is>
           <t>TIPO_ACREEDOR</t>
         </is>
       </c>
-      <c r="P1" s="86" t="inlineStr">
+      <c r="P1" s="81" t="inlineStr">
         <is>
           <t>TIPO_IDENTIFICACION</t>
         </is>
       </c>
-      <c r="Q1" s="86" t="inlineStr">
+      <c r="Q1" s="81" t="inlineStr">
         <is>
           <t>REGULARIZACION</t>
         </is>
       </c>
-      <c r="R1" s="86" t="inlineStr">
+      <c r="R1" s="81" t="inlineStr">
         <is>
           <t>JUSTIF_INCREMENTO</t>
         </is>
       </c>
-      <c r="S1" s="86" t="inlineStr">
+      <c r="S1" s="81" t="inlineStr">
         <is>
           <t>JUSTIF_DECREMENTO</t>
         </is>

--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;0.0%"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,11 +116,6 @@
     <font>
       <b val="1"/>
       <color rgb="0020507D"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -228,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -237,14 +232,8 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -429,11 +418,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -534,7 +526,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Activos / Pasivos / Patrimonio: 2025 vs 2026</a:t>
+              <a:t>Concentracion de activos: 2025 vs 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -549,7 +541,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!D37</f>
+              <f>'Dashboard'!D11</f>
             </strRef>
           </tx>
           <spPr>
@@ -559,12 +551,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$38:$B$40</f>
+              <f>'Dashboard'!$B$12:$B$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$38:$D$40</f>
+              <f>'Dashboard'!$D$12:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -573,7 +565,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!E37</f>
+              <f>'Dashboard'!E11</f>
             </strRef>
           </tx>
           <spPr>
@@ -583,12 +575,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$38:$B$40</f>
+              <f>'Dashboard'!$B$12:$B$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$38:$E$40</f>
+              <f>'Dashboard'!$E$12:$E$19</f>
             </numRef>
           </val>
         </ser>
@@ -628,16 +620,71 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Composicion: activos, pasivos y patrimonio</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$B$38:$B$40</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$D$38:$D$40</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showPercent val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="4320000"/>
+    <ext cx="6840000" cy="3420000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -647,6 +694,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -944,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -955,10 +1024,6 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -977,676 +1042,663 @@
     </row>
     <row r="3" ht="5" customHeight="1">
       <c r="A3" s="3" t="n"/>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>TIPO DE GRAFICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>Columnas</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="n"/>
     </row>
     <row r="5" ht="6" customHeight="1">
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="9" t="n"/>
-      <c r="G5" s="6" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>TOTAL ACTIVOS</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>TOTAL PASIVOS</t>
         </is>
       </c>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>PATRIMONIO NETO</t>
         </is>
       </c>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="13" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="16">
+      <c r="B7" s="14">
         <f>D20</f>
         <v/>
       </c>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="17">
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="15">
         <f>D25</f>
         <v/>
       </c>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="18">
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="16">
         <f>D31</f>
         <v/>
       </c>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Var. proyectada</t>
         </is>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="18">
         <f>G20</f>
         <v/>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Var. proyectada</t>
         </is>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="20">
         <f>G25</f>
         <v/>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>Var. proyectada</t>
         </is>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <f>G31</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>ACTIVOS</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="F11" s="27" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G11" s="27" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Dinero e inversiones</t>
         </is>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="27">
         <f>'Dinero'!J10</f>
         <v/>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="27">
         <f>'Dinero'!K10</f>
         <v/>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="27">
         <f>E12-D12</f>
         <v/>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="28">
         <f>IF(D12=0,"",(E12-D12)/D12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>Derechos representativos de capital</t>
         </is>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="27">
         <f>'Derechos de Capital'!J14</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="27">
         <f>'Derechos de Capital'!K14</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="27">
         <f>E13-D13</f>
         <v/>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="28">
         <f>IF(D13=0,"",(E13-D13)/D13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Cuentas por cobrar</t>
         </is>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="27">
         <f>'Cuentas por Cobrar'!J14</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="27">
         <f>'Cuentas por Cobrar'!K14</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="27">
         <f>E14-D14</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="28">
         <f>IF(D14=0,"",(E14-D14)/D14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Bienes muebles</t>
         </is>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="27">
         <f>'Bienes Muebles'!F14</f>
         <v/>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="27">
         <f>'Bienes Muebles'!G14</f>
         <v/>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="27">
         <f>E15-D15</f>
         <v/>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="28">
         <f>IF(D15=0,"",(E15-D15)/D15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Vehiculos, naves y aeronaves</t>
         </is>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="27">
         <f>'Vehiculos'!G9</f>
         <v/>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="27">
         <f>'Vehiculos'!H9</f>
         <v/>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="27">
         <f>E16-D16</f>
         <v/>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="28">
         <f>IF(D16=0,"",(E16-D16)/D16)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Derechos (usufructo, uso, etc.)</t>
         </is>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="27">
         <f>'Derechos'!F14</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="27">
         <f>'Derechos'!G14</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="27">
         <f>E17-D17</f>
         <v/>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="28">
         <f>IF(D17=0,"",(E17-D17)/D17)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Bienes inmuebles</t>
         </is>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="27">
         <f>'Bienes Inmuebles'!J10</f>
         <v/>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="27">
         <f>'Bienes Inmuebles'!K10</f>
         <v/>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="27">
         <f>E18-D18</f>
         <v/>
       </c>
-      <c r="G18" s="30">
+      <c r="G18" s="28">
         <f>IF(D18=0,"",(E18-D18)/D18)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Otros activos</t>
         </is>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="27">
         <f>'Otros Activos'!F14</f>
         <v/>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="27">
         <f>'Otros Activos'!G14</f>
         <v/>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="27">
         <f>E19-D19</f>
         <v/>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="28">
         <f>IF(D19=0,"",(E19-D19)/D19)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="31" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>TOTAL ACTIVOS</t>
         </is>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="30">
         <f>SUM(D12:D19)</f>
         <v/>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="30">
         <f>SUM(E12:E19)</f>
         <v/>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="30">
         <f>E20-D20</f>
         <v/>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="31">
         <f>IF(D20=0,"",(E20-D20)/D20)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>PASIVOS</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C23" s="26" t="n"/>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="E23" s="27" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="F23" s="27" t="inlineStr">
+      <c r="F23" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G23" s="27" t="inlineStr">
+      <c r="G23" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Deudas y obligaciones</t>
         </is>
       </c>
-      <c r="D24" s="36">
+      <c r="D24" s="34">
         <f>'Pasivos'!I8</f>
         <v/>
       </c>
-      <c r="E24" s="36">
+      <c r="E24" s="34">
         <f>'Pasivos'!J8</f>
         <v/>
       </c>
-      <c r="F24" s="36">
+      <c r="F24" s="34">
         <f>E24-D24</f>
         <v/>
       </c>
-      <c r="G24" s="37">
+      <c r="G24" s="35">
         <f>IF(D24=0,"",(E24-D24)/D24)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>TOTAL PASIVOS</t>
         </is>
       </c>
-      <c r="D25" s="39">
+      <c r="D25" s="37">
         <f>SUM(D24:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="39">
+      <c r="E25" s="37">
         <f>SUM(E24:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="39">
+      <c r="F25" s="37">
         <f>E25-D25</f>
         <v/>
       </c>
-      <c r="G25" s="40">
+      <c r="G25" s="38">
         <f>IF(D25=0,"",(E25-D25)/D25)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="41" t="inlineStr">
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>PATRIMONIO NETO</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C28" s="26" t="n"/>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="E28" s="25" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="F28" s="27" t="inlineStr">
+      <c r="F28" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G28" s="27" t="inlineStr">
+      <c r="G28" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="B29" s="42" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>(+) Total activos</t>
         </is>
       </c>
-      <c r="D29" s="43">
+      <c r="D29" s="41">
         <f>D20</f>
         <v/>
       </c>
-      <c r="E29" s="43">
+      <c r="E29" s="41">
         <f>E20</f>
         <v/>
       </c>
-      <c r="F29" s="43">
+      <c r="F29" s="41">
         <f>E29-D29</f>
         <v/>
       </c>
-      <c r="G29" s="44">
+      <c r="G29" s="42">
         <f>IF(D29=0,"",(E29-D29)/D29)</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="42" t="inlineStr">
+      <c r="B30" s="40" t="inlineStr">
         <is>
           <t>(-) Total pasivos</t>
         </is>
       </c>
-      <c r="D30" s="43">
+      <c r="D30" s="41">
         <f>D25</f>
         <v/>
       </c>
-      <c r="E30" s="43">
+      <c r="E30" s="41">
         <f>E25</f>
         <v/>
       </c>
-      <c r="F30" s="43">
+      <c r="F30" s="41">
         <f>E30-D30</f>
         <v/>
       </c>
-      <c r="G30" s="44">
+      <c r="G30" s="42">
         <f>IF(D30=0,"",(E30-D30)/D30)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="45" t="inlineStr">
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>(=) PATRIMONIO NETO</t>
         </is>
       </c>
-      <c r="D31" s="46">
+      <c r="D31" s="44">
         <f>D29-D30</f>
         <v/>
       </c>
-      <c r="E31" s="46">
+      <c r="E31" s="44">
         <f>E29-E30</f>
         <v/>
       </c>
-      <c r="F31" s="46">
+      <c r="F31" s="44">
         <f>E31-D31</f>
         <v/>
       </c>
-      <c r="G31" s="47">
+      <c r="G31" s="45">
         <f>IF(D31=0,"",(E31-D31)/D31)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="48" t="inlineStr">
+      <c r="B32" s="46" t="inlineStr">
         <is>
           <t>Patrimonio declarado en el XML (2025)</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="49" t="n">
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="47" t="n">
         <v>883285.5600000001</v>
       </c>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="48" t="inlineStr">
+      <c r="B33" s="46" t="inlineStr">
         <is>
           <t>Patrimonio neto del anio anterior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="49" t="n">
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="47" t="n">
         <v>801569.97</v>
       </c>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="48" t="inlineStr">
+      <c r="B34" s="46" t="inlineStr">
         <is>
           <t>Crecimiento / decremento patrimonial (XML)</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="49" t="n">
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="47" t="n">
         <v>81715.59</v>
       </c>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="6" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="50" t="inlineStr">
+      <c r="B36" s="48" t="inlineStr">
         <is>
           <t>CONSOLIDADO</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="B37" s="26" t="inlineStr">
+      <c r="B37" s="24" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C37" s="26" t="n"/>
-      <c r="D37" s="27" t="inlineStr">
+      <c r="C37" s="24" t="n"/>
+      <c r="D37" s="25" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="E37" s="27" t="inlineStr">
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="F37" s="27" t="inlineStr">
+      <c r="F37" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G37" s="27" t="inlineStr">
+      <c r="G37" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="B38" s="51" t="inlineStr">
+      <c r="B38" s="49" t="inlineStr">
         <is>
           <t>Activos</t>
         </is>
       </c>
-      <c r="D38" s="52">
+      <c r="D38" s="50">
         <f>D20</f>
         <v/>
       </c>
-      <c r="E38" s="52">
+      <c r="E38" s="50">
         <f>E20</f>
         <v/>
       </c>
-      <c r="F38" s="52">
+      <c r="F38" s="50">
         <f>E38-D38</f>
         <v/>
       </c>
-      <c r="G38" s="53">
+      <c r="G38" s="51">
         <f>IF(D38=0,"",(E38-D38)/D38)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="B39" s="54" t="inlineStr">
+      <c r="B39" s="52" t="inlineStr">
         <is>
           <t>Pasivos</t>
         </is>
       </c>
-      <c r="D39" s="55">
+      <c r="D39" s="53">
         <f>D25</f>
         <v/>
       </c>
-      <c r="E39" s="55">
+      <c r="E39" s="53">
         <f>E25</f>
         <v/>
       </c>
-      <c r="F39" s="55">
+      <c r="F39" s="53">
         <f>E39-D39</f>
         <v/>
       </c>
-      <c r="G39" s="56">
+      <c r="G39" s="54">
         <f>IF(D39=0,"",(E39-D39)/D39)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="B40" s="57" t="inlineStr">
+      <c r="B40" s="55" t="inlineStr">
         <is>
           <t>Patrimonio neto</t>
         </is>
       </c>
-      <c r="D40" s="58">
+      <c r="D40" s="56">
         <f>D31</f>
         <v/>
       </c>
-      <c r="E40" s="58">
+      <c r="E40" s="56">
         <f>E31</f>
         <v/>
       </c>
-      <c r="F40" s="58">
+      <c r="F40" s="56">
         <f>E40-D40</f>
         <v/>
       </c>
-      <c r="G40" s="59">
+      <c r="G40" s="57">
         <f>IF(D40=0,"",(E40-D40)/D40)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="60" t="inlineStr">
+      <c r="B42" s="58" t="inlineStr">
         <is>
           <t>Edite las columnas amarillas en las hojas de cada modulo; las tarjetas, secciones y graficos se recalculan solos.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="40">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
@@ -1679,22 +1731,15 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="I4:J4"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B22:G22"/>
-    <mergeCell ref="I3:L3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="B32:C32"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="I4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Columnas,Barras,Pastel,Anillo,Lineas,Area"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1741,197 +1786,197 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Tipo de acreedor</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Domicilio del acreedor</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Nombre del acreedor</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>N. de identificacion</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>N. registro Banco Central</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="L5" s="27" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>DINERS CLUB DEL ECUADOR</t>
         </is>
       </c>
-      <c r="E6" s="61" t="inlineStr">
+      <c r="E6" s="59" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
-      <c r="F6" s="61" t="inlineStr">
+      <c r="F6" s="59" t="inlineStr">
         <is>
           <t>1792260957001</t>
         </is>
       </c>
-      <c r="G6" s="61" t="inlineStr"/>
-      <c r="H6" s="61" t="inlineStr">
+      <c r="G6" s="59" t="inlineStr"/>
+      <c r="H6" s="59" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="I6" s="62" t="n">
+      <c r="I6" s="60" t="n">
         <v>4891.88</v>
       </c>
-      <c r="J6" s="63" t="n">
+      <c r="J6" s="61" t="n">
         <v>4891.88</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="60">
         <f>J6-I6</f>
         <v/>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="62">
         <f>IF(I6=0,"",(J6-I6)/I6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B7" s="65" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="63" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D7" s="65" t="inlineStr">
+      <c r="D7" s="63" t="inlineStr">
         <is>
           <t>BANCO DEL PICHINCHA</t>
         </is>
       </c>
-      <c r="E7" s="65" t="inlineStr">
+      <c r="E7" s="63" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
-      <c r="F7" s="65" t="inlineStr">
+      <c r="F7" s="63" t="inlineStr">
         <is>
           <t>1790010937001</t>
         </is>
       </c>
-      <c r="G7" s="65" t="inlineStr"/>
-      <c r="H7" s="65" t="inlineStr">
+      <c r="G7" s="63" t="inlineStr"/>
+      <c r="H7" s="63" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="I7" s="66" t="n">
+      <c r="I7" s="64" t="n">
         <v>5547.31</v>
       </c>
-      <c r="J7" s="63" t="n">
+      <c r="J7" s="61" t="n">
         <v>5547.31</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="64">
         <f>J7-I7</f>
         <v/>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="65">
         <f>IF(I7=0,"",(J7-I7)/I7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="69" t="inlineStr">
+      <c r="A8" s="67" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="69" t="n"/>
-      <c r="C8" s="69" t="n"/>
-      <c r="D8" s="69" t="n"/>
-      <c r="E8" s="69" t="n"/>
-      <c r="F8" s="69" t="n"/>
-      <c r="G8" s="69" t="n"/>
-      <c r="H8" s="69" t="n"/>
-      <c r="I8" s="39">
+      <c r="B8" s="67" t="n"/>
+      <c r="C8" s="67" t="n"/>
+      <c r="D8" s="67" t="n"/>
+      <c r="E8" s="67" t="n"/>
+      <c r="F8" s="67" t="n"/>
+      <c r="G8" s="67" t="n"/>
+      <c r="H8" s="67" t="n"/>
+      <c r="I8" s="37">
         <f>SUM(I6:I7)</f>
         <v/>
       </c>
-      <c r="J8" s="39">
+      <c r="J8" s="37">
         <f>SUM(J6:J7)</f>
         <v/>
       </c>
-      <c r="K8" s="39">
+      <c r="K8" s="37">
         <f>J8-I8</f>
         <v/>
       </c>
-      <c r="L8" s="40">
+      <c r="L8" s="38">
         <f>IF(I8=0,"",(J8-I8)/I8)</f>
         <v/>
       </c>
@@ -1997,115 +2042,115 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="B5" s="70" t="inlineStr">
+      <c r="B5" s="68" t="inlineStr">
         <is>
           <t>Incremento patrimonial declarado en el XML</t>
         </is>
       </c>
-      <c r="C5" s="71" t="n"/>
-      <c r="D5" s="71" t="n"/>
-      <c r="E5" s="72" t="n">
+      <c r="C5" s="69" t="n"/>
+      <c r="D5" s="69" t="n"/>
+      <c r="E5" s="70" t="n">
         <v>81715.59</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Concepto (Tabla 14 del SRI)</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>Justifica la variacion</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="73" t="inlineStr">
+      <c r="B8" s="71" t="inlineStr">
         <is>
           <t>1 - Ingresos locales</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="72" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="73" t="inlineStr">
+      <c r="B9" s="71" t="inlineStr">
         <is>
           <t>2 - Ingresos exterior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="72" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="73" t="inlineStr">
+      <c r="B10" s="71" t="inlineStr">
         <is>
           <t>3 - Herencias, legados o donaciones</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="72" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="73" t="inlineStr">
+      <c r="B11" s="71" t="inlineStr">
         <is>
           <t>4 - Loterias o rifas</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="72" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="73" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>5 - Ganancias de capital</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="72" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="73" t="inlineStr">
+      <c r="B13" s="71" t="inlineStr">
         <is>
           <t>6 - Otros</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="72" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="58" t="inlineStr">
         <is>
           <t>Esta hoja reproduce la seccion Justificacion del formulario del SRI. Marque 'Si' en los conceptos que apliquen; el generador de XML los toma de aqui.</t>
         </is>
@@ -2168,97 +2213,97 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="74" t="inlineStr">
+      <c r="B5" s="73" t="inlineStr">
         <is>
           <t>►   GENERAR XML</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="75" t="inlineStr">
+      <c r="B7" s="74" t="inlineStr">
         <is>
           <t>En el archivo .xlsm el boton verde ya esta vinculado a la macro GenerarXmlSRI.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="75" t="inlineStr">
         <is>
           <t>COMO USAR ESTE ARCHIVO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="77" t="inlineStr">
+      <c r="B10" s="76" t="inlineStr">
         <is>
           <t>1. Al abrir el archivo .xlsm, pulse 'Habilitar contenido' en la barra de seguridad de Excel.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="77" t="inlineStr">
+      <c r="B11" s="76" t="inlineStr">
         <is>
           <t>2. Llene las columnas amarillas de cada modulo (Dinero, Vehiculos, etc.) y la hoja Justificacion.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="77" t="inlineStr">
+      <c r="B12" s="76" t="inlineStr">
         <is>
           <t>3. Pulse el boton verde GENERAR XML, indique el anio y elija donde guardar el archivo.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="77" t="inlineStr">
+      <c r="B13" s="76" t="inlineStr">
         <is>
           <t>4. El archivo .xml queda listo para subir al portal del SRI.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="77" t="inlineStr"/>
+      <c r="B14" s="76" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="76" t="inlineStr">
+      <c r="B15" s="75" t="inlineStr">
         <is>
           <t>SI EXCEL BLOQUEA LAS MACROS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="77" t="inlineStr">
+      <c r="B16" s="76" t="inlineStr">
         <is>
           <t>- Cierre Excel. En el Explorador, clic derecho sobre el archivo &gt; Propiedades.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="77" t="inlineStr">
+      <c r="B17" s="76" t="inlineStr">
         <is>
           <t>- Al final de la pestana General marque 'Desbloquear' y pulse Aceptar.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="77" t="inlineStr">
+      <c r="B18" s="76" t="inlineStr">
         <is>
           <t>- Vuelva a abrirlo y pulse 'Habilitar contenido'. Conserve siempre la extension .xlsm.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="77" t="inlineStr"/>
+      <c r="B19" s="76" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="B20" s="77" t="inlineStr">
+      <c r="B20" s="76" t="inlineStr">
         <is>
           <t>Alternativa sin macros:  ejecutar  python tools/generar_xml_sri.py  desde la terminal.</t>
         </is>
@@ -2299,257 +2344,257 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="78" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>IDENTIFICACION</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="79" t="inlineStr">
+      <c r="A6" s="78" t="inlineStr">
         <is>
           <t>Anio de la declaracion</t>
         </is>
       </c>
-      <c r="B6" s="80" t="n">
+      <c r="B6" s="79" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="79" t="inlineStr">
+      <c r="A7" s="78" t="inlineStr">
         <is>
           <t>Tipo de declaracion</t>
         </is>
       </c>
-      <c r="B7" s="80" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>SOC - Sociedad conyugal o union de hecho</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="79" t="inlineStr">
+      <c r="A8" s="78" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="B8" s="80" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="79" t="inlineStr">
+      <c r="A9" s="78" t="inlineStr">
         <is>
           <t>Numero de identificacion</t>
         </is>
       </c>
-      <c r="B9" s="80" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>1709164899001</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="79" t="inlineStr">
+      <c r="A10" s="78" t="inlineStr">
         <is>
           <t>Nombre del declarante</t>
         </is>
       </c>
-      <c r="B10" s="80" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>GONZALEZ NAVAS MARCO VINICIO</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="79" t="inlineStr">
+      <c r="A11" s="78" t="inlineStr">
         <is>
           <t>Identificacion del conyuge</t>
         </is>
       </c>
-      <c r="B11" s="80" t="inlineStr">
+      <c r="B11" s="79" t="inlineStr">
         <is>
           <t>C - Cedula</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="79" t="inlineStr">
+      <c r="A12" s="78" t="inlineStr">
         <is>
           <t>Numero ident. conyuge</t>
         </is>
       </c>
-      <c r="B12" s="80" t="inlineStr">
+      <c r="B12" s="79" t="inlineStr">
         <is>
           <t>1709784225</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="79" t="inlineStr">
+      <c r="A13" s="78" t="inlineStr">
         <is>
           <t>Nombre del conyuge</t>
         </is>
       </c>
-      <c r="B13" s="80" t="inlineStr">
+      <c r="B13" s="79" t="inlineStr">
         <is>
           <t>HIDALGO LOZA ROSA CONSUELO</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="79" t="inlineStr">
+      <c r="A14" s="78" t="inlineStr">
         <is>
           <t>Total creditos / cuentas por cobrar</t>
         </is>
       </c>
-      <c r="B14" s="62" t="n">
+      <c r="B14" s="60" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="78" t="inlineStr">
+      <c r="A16" s="77" t="inlineStr">
         <is>
           <t>PATRIMONIO NETO (enlazado a la hoja Dashboard)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="79" t="inlineStr">
+      <c r="A17" s="78" t="inlineStr">
         <is>
           <t>Patrimonio neto 2025</t>
         </is>
       </c>
-      <c r="B17" s="62">
+      <c r="B17" s="60">
         <f>Dashboard!D31</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="79" t="inlineStr">
+      <c r="A18" s="78" t="inlineStr">
         <is>
           <t>Patrimonio neto 2026 (proyectado)</t>
         </is>
       </c>
-      <c r="B18" s="62">
+      <c r="B18" s="60">
         <f>Dashboard!E31</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="79" t="inlineStr">
+      <c r="A19" s="78" t="inlineStr">
         <is>
           <t>Variacion proyectada</t>
         </is>
       </c>
-      <c r="B19" s="62">
+      <c r="B19" s="60">
         <f>Dashboard!F31</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="79" t="inlineStr">
+      <c r="A20" s="78" t="inlineStr">
         <is>
           <t>Variacion % proyectada</t>
         </is>
       </c>
-      <c r="B20" s="64">
+      <c r="B20" s="62">
         <f>Dashboard!G31</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="78" t="inlineStr">
+      <c r="A22" s="77" t="inlineStr">
         <is>
           <t>PATRIMONIO DECLARADO EN EL XML</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="79" t="inlineStr">
+      <c r="A23" s="78" t="inlineStr">
         <is>
           <t>Patrimonio total declarado</t>
         </is>
       </c>
-      <c r="B23" s="62" t="n">
+      <c r="B23" s="60" t="n">
         <v>883285.5600000001</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="79" t="inlineStr">
+      <c r="A24" s="78" t="inlineStr">
         <is>
           <t>Atribuible a hijos no emancipados</t>
         </is>
       </c>
-      <c r="B24" s="62" t="n">
+      <c r="B24" s="60" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="79" t="inlineStr">
+      <c r="A25" s="78" t="inlineStr">
         <is>
           <t>Patrimonio en la sociedad conyugal</t>
         </is>
       </c>
-      <c r="B25" s="62" t="n">
+      <c r="B25" s="60" t="n">
         <v>883285.5600000001</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="79" t="inlineStr">
+      <c r="A26" s="78" t="inlineStr">
         <is>
           <t>Patrimonio individual del declarante</t>
         </is>
       </c>
-      <c r="B26" s="62" t="n">
+      <c r="B26" s="60" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="79" t="inlineStr">
+      <c r="A27" s="78" t="inlineStr">
         <is>
           <t>Patrimonio del anio anterior</t>
         </is>
       </c>
-      <c r="B27" s="62" t="n">
+      <c r="B27" s="60" t="n">
         <v>801569.97</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="79" t="inlineStr">
+      <c r="A28" s="78" t="inlineStr">
         <is>
           <t>Crecimiento / decremento patrimonial</t>
         </is>
       </c>
-      <c r="B28" s="62" t="n">
+      <c r="B28" s="60" t="n">
         <v>81715.59</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="76" t="inlineStr">
+      <c r="A30" s="75" t="inlineStr">
         <is>
           <t>Justificacion de la variacion (ver hoja Justificacion)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="77" t="inlineStr">
+      <c r="A31" s="76" t="inlineStr">
         <is>
           <t>- 1 - Ingresos locales</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="77" t="inlineStr">
+      <c r="A32" s="76" t="inlineStr">
         <is>
           <t>- 6 - Otros</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="60" t="inlineStr">
+      <c r="A34" s="58" t="inlineStr">
         <is>
           <t>Catalogos del SRI integrados (Tablas 1-19 del archivo CATALOGO.xls). El XML se genera con generar_xml_sri.py.</t>
         </is>
@@ -5820,97 +5865,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="81" t="inlineStr">
+      <c r="A1" s="80" t="inlineStr">
         <is>
           <t>DINERO_EN</t>
         </is>
       </c>
-      <c r="B1" s="81" t="inlineStr">
+      <c r="B1" s="80" t="inlineStr">
         <is>
           <t>TIPO_INVERSION</t>
         </is>
       </c>
-      <c r="C1" s="81" t="inlineStr">
+      <c r="C1" s="80" t="inlineStr">
         <is>
           <t>UBICACION</t>
         </is>
       </c>
-      <c r="D1" s="81" t="inlineStr">
+      <c r="D1" s="80" t="inlineStr">
         <is>
           <t>PAIS</t>
         </is>
       </c>
-      <c r="E1" s="81" t="inlineStr">
+      <c r="E1" s="80" t="inlineStr">
         <is>
           <t>INSTITUCION_FINANCIERA</t>
         </is>
       </c>
-      <c r="F1" s="81" t="inlineStr">
+      <c r="F1" s="80" t="inlineStr">
         <is>
           <t>PARTES_RELACIONADAS</t>
         </is>
       </c>
-      <c r="G1" s="81" t="inlineStr">
+      <c r="G1" s="80" t="inlineStr">
         <is>
           <t>TIPO_DRC</t>
         </is>
       </c>
-      <c r="H1" s="81" t="inlineStr">
+      <c r="H1" s="80" t="inlineStr">
         <is>
           <t>TIPO_PERSONA</t>
         </is>
       </c>
-      <c r="I1" s="81" t="inlineStr">
+      <c r="I1" s="80" t="inlineStr">
         <is>
           <t>TIPO_BIEN_MUEBLE</t>
         </is>
       </c>
-      <c r="J1" s="81" t="inlineStr">
+      <c r="J1" s="80" t="inlineStr">
         <is>
           <t>TIPO_VEHICULO</t>
         </is>
       </c>
-      <c r="K1" s="81" t="inlineStr">
+      <c r="K1" s="80" t="inlineStr">
         <is>
           <t>TIPO_DERECHO</t>
         </is>
       </c>
-      <c r="L1" s="81" t="inlineStr">
+      <c r="L1" s="80" t="inlineStr">
         <is>
           <t>TIPO_INMUEBLE</t>
         </is>
       </c>
-      <c r="M1" s="81" t="inlineStr">
+      <c r="M1" s="80" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="N1" s="81" t="inlineStr">
+      <c r="N1" s="80" t="inlineStr">
         <is>
           <t>CANTON</t>
         </is>
       </c>
-      <c r="O1" s="81" t="inlineStr">
+      <c r="O1" s="80" t="inlineStr">
         <is>
           <t>TIPO_ACREEDOR</t>
         </is>
       </c>
-      <c r="P1" s="81" t="inlineStr">
+      <c r="P1" s="80" t="inlineStr">
         <is>
           <t>TIPO_IDENTIFICACION</t>
         </is>
       </c>
-      <c r="Q1" s="81" t="inlineStr">
+      <c r="Q1" s="80" t="inlineStr">
         <is>
           <t>REGULARIZACION</t>
         </is>
       </c>
-      <c r="R1" s="81" t="inlineStr">
+      <c r="R1" s="80" t="inlineStr">
         <is>
           <t>JUSTIF_INCREMENTO</t>
         </is>
       </c>
-      <c r="S1" s="81" t="inlineStr">
+      <c r="S1" s="80" t="inlineStr">
         <is>
           <t>JUSTIF_DECREMENTO</t>
         </is>
@@ -12444,311 +12489,311 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Dinero en</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Tipo de inversion</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Institucion financiera</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Tipo de moneda</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="L5" s="27" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>3 - Cuenta de ahorros</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E6" s="61" t="inlineStr">
+      <c r="E6" s="59" t="inlineStr">
         <is>
           <t>1029 - BANCO PICHINCHA C.A.</t>
         </is>
       </c>
-      <c r="F6" s="61" t="inlineStr">
+      <c r="F6" s="59" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G6" s="61" t="inlineStr">
+      <c r="G6" s="59" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H6" s="61" t="inlineStr"/>
-      <c r="I6" s="61" t="inlineStr"/>
-      <c r="J6" s="62" t="n">
+      <c r="H6" s="59" t="inlineStr"/>
+      <c r="I6" s="59" t="inlineStr"/>
+      <c r="J6" s="60" t="n">
         <v>130.2</v>
       </c>
-      <c r="K6" s="63" t="n">
+      <c r="K6" s="61" t="n">
         <v>130.2</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="60">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="62">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B7" s="65" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>4 - Cuenta corriente</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="63" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D7" s="65" t="inlineStr">
+      <c r="D7" s="63" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E7" s="65" t="inlineStr">
+      <c r="E7" s="63" t="inlineStr">
         <is>
           <t>1029 - BANCO PICHINCHA C.A.</t>
         </is>
       </c>
-      <c r="F7" s="65" t="inlineStr">
+      <c r="F7" s="63" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G7" s="65" t="inlineStr">
+      <c r="G7" s="63" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H7" s="65" t="inlineStr"/>
-      <c r="I7" s="65" t="inlineStr"/>
-      <c r="J7" s="66" t="n">
+      <c r="H7" s="63" t="inlineStr"/>
+      <c r="I7" s="63" t="inlineStr"/>
+      <c r="J7" s="64" t="n">
         <v>5590.32</v>
       </c>
-      <c r="K7" s="63" t="n">
+      <c r="K7" s="61" t="n">
         <v>5590.32</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="64">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="65">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>3 - Cuenta de ahorros</t>
         </is>
       </c>
-      <c r="C8" s="61" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E8" s="61" t="inlineStr">
+      <c r="E8" s="59" t="inlineStr">
         <is>
           <t>1418 - BANCO PROMERICA S.A.</t>
         </is>
       </c>
-      <c r="F8" s="61" t="inlineStr">
+      <c r="F8" s="59" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G8" s="61" t="inlineStr">
+      <c r="G8" s="59" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H8" s="61" t="inlineStr"/>
-      <c r="I8" s="61" t="inlineStr"/>
-      <c r="J8" s="62" t="n">
+      <c r="H8" s="59" t="inlineStr"/>
+      <c r="I8" s="59" t="inlineStr"/>
+      <c r="J8" s="60" t="n">
         <v>53237.31</v>
       </c>
-      <c r="K8" s="63" t="n">
+      <c r="K8" s="61" t="n">
         <v>53237.31</v>
       </c>
-      <c r="L8" s="62">
+      <c r="L8" s="60">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="64">
+      <c r="M8" s="62">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr">
+      <c r="A9" s="63" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B9" s="65" t="inlineStr">
+      <c r="B9" s="63" t="inlineStr">
         <is>
           <t>2 - Inversiones financieras</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
+      <c r="C9" s="63" t="inlineStr">
         <is>
           <t>EXT - En el exterior</t>
         </is>
       </c>
-      <c r="D9" s="65" t="inlineStr">
+      <c r="D9" s="63" t="inlineStr">
         <is>
           <t>118 - PANAMA</t>
         </is>
       </c>
-      <c r="E9" s="65" t="inlineStr">
+      <c r="E9" s="63" t="inlineStr">
         <is>
           <t>BANCO PICHINCHA CA</t>
         </is>
       </c>
-      <c r="F9" s="65" t="inlineStr">
+      <c r="F9" s="63" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G9" s="65" t="inlineStr">
+      <c r="G9" s="63" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H9" s="65" t="inlineStr"/>
-      <c r="I9" s="65" t="inlineStr"/>
-      <c r="J9" s="66" t="n">
+      <c r="H9" s="63" t="inlineStr"/>
+      <c r="I9" s="63" t="inlineStr"/>
+      <c r="J9" s="64" t="n">
         <v>189049.31</v>
       </c>
-      <c r="K9" s="63" t="n">
+      <c r="K9" s="61" t="n">
         <v>189049.31</v>
       </c>
-      <c r="L9" s="66">
+      <c r="L9" s="64">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="67">
+      <c r="M9" s="65">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="68" t="n"/>
-      <c r="C10" s="68" t="n"/>
-      <c r="D10" s="68" t="n"/>
-      <c r="E10" s="68" t="n"/>
-      <c r="F10" s="68" t="n"/>
-      <c r="G10" s="68" t="n"/>
-      <c r="H10" s="68" t="n"/>
-      <c r="I10" s="68" t="n"/>
-      <c r="J10" s="32">
+      <c r="B10" s="66" t="n"/>
+      <c r="C10" s="66" t="n"/>
+      <c r="D10" s="66" t="n"/>
+      <c r="E10" s="66" t="n"/>
+      <c r="F10" s="66" t="n"/>
+      <c r="G10" s="66" t="n"/>
+      <c r="H10" s="66" t="n"/>
+      <c r="I10" s="66" t="n"/>
+      <c r="J10" s="30">
         <f>SUM(J6:J9)</f>
         <v/>
       </c>
-      <c r="K10" s="32">
+      <c r="K10" s="30">
         <f>SUM(K6:K9)</f>
         <v/>
       </c>
-      <c r="L10" s="32">
+      <c r="L10" s="30">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="33">
+      <c r="M10" s="31">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
@@ -12828,299 +12873,299 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Tipo de inversion</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Empresa / Administradora / Fideicomiso</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>% de participacion</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>N. de acciones / participaciones</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="L5" s="27" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr"/>
-      <c r="B6" s="61" t="inlineStr"/>
-      <c r="C6" s="61" t="inlineStr"/>
-      <c r="D6" s="61" t="inlineStr"/>
-      <c r="E6" s="61" t="inlineStr"/>
-      <c r="F6" s="61" t="inlineStr"/>
-      <c r="G6" s="61" t="inlineStr"/>
-      <c r="H6" s="61" t="inlineStr"/>
-      <c r="I6" s="61" t="inlineStr"/>
-      <c r="J6" s="63" t="n">
+      <c r="A6" s="59" t="inlineStr"/>
+      <c r="B6" s="59" t="inlineStr"/>
+      <c r="C6" s="59" t="inlineStr"/>
+      <c r="D6" s="59" t="inlineStr"/>
+      <c r="E6" s="59" t="inlineStr"/>
+      <c r="F6" s="59" t="inlineStr"/>
+      <c r="G6" s="59" t="inlineStr"/>
+      <c r="H6" s="59" t="inlineStr"/>
+      <c r="I6" s="59" t="inlineStr"/>
+      <c r="J6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="63" t="n">
+      <c r="K6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="60">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="62">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr"/>
-      <c r="B7" s="65" t="inlineStr"/>
-      <c r="C7" s="65" t="inlineStr"/>
-      <c r="D7" s="65" t="inlineStr"/>
-      <c r="E7" s="65" t="inlineStr"/>
-      <c r="F7" s="65" t="inlineStr"/>
-      <c r="G7" s="65" t="inlineStr"/>
-      <c r="H7" s="65" t="inlineStr"/>
-      <c r="I7" s="65" t="inlineStr"/>
-      <c r="J7" s="63" t="n">
+      <c r="A7" s="63" t="inlineStr"/>
+      <c r="B7" s="63" t="inlineStr"/>
+      <c r="C7" s="63" t="inlineStr"/>
+      <c r="D7" s="63" t="inlineStr"/>
+      <c r="E7" s="63" t="inlineStr"/>
+      <c r="F7" s="63" t="inlineStr"/>
+      <c r="G7" s="63" t="inlineStr"/>
+      <c r="H7" s="63" t="inlineStr"/>
+      <c r="I7" s="63" t="inlineStr"/>
+      <c r="J7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="63" t="n">
+      <c r="K7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="64">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="65">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr"/>
-      <c r="B8" s="61" t="inlineStr"/>
-      <c r="C8" s="61" t="inlineStr"/>
-      <c r="D8" s="61" t="inlineStr"/>
-      <c r="E8" s="61" t="inlineStr"/>
-      <c r="F8" s="61" t="inlineStr"/>
-      <c r="G8" s="61" t="inlineStr"/>
-      <c r="H8" s="61" t="inlineStr"/>
-      <c r="I8" s="61" t="inlineStr"/>
-      <c r="J8" s="63" t="n">
+      <c r="A8" s="59" t="inlineStr"/>
+      <c r="B8" s="59" t="inlineStr"/>
+      <c r="C8" s="59" t="inlineStr"/>
+      <c r="D8" s="59" t="inlineStr"/>
+      <c r="E8" s="59" t="inlineStr"/>
+      <c r="F8" s="59" t="inlineStr"/>
+      <c r="G8" s="59" t="inlineStr"/>
+      <c r="H8" s="59" t="inlineStr"/>
+      <c r="I8" s="59" t="inlineStr"/>
+      <c r="J8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="63" t="n">
+      <c r="K8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="62">
+      <c r="L8" s="60">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="64">
+      <c r="M8" s="62">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr"/>
-      <c r="B9" s="65" t="inlineStr"/>
-      <c r="C9" s="65" t="inlineStr"/>
-      <c r="D9" s="65" t="inlineStr"/>
-      <c r="E9" s="65" t="inlineStr"/>
-      <c r="F9" s="65" t="inlineStr"/>
-      <c r="G9" s="65" t="inlineStr"/>
-      <c r="H9" s="65" t="inlineStr"/>
-      <c r="I9" s="65" t="inlineStr"/>
-      <c r="J9" s="63" t="n">
+      <c r="A9" s="63" t="inlineStr"/>
+      <c r="B9" s="63" t="inlineStr"/>
+      <c r="C9" s="63" t="inlineStr"/>
+      <c r="D9" s="63" t="inlineStr"/>
+      <c r="E9" s="63" t="inlineStr"/>
+      <c r="F9" s="63" t="inlineStr"/>
+      <c r="G9" s="63" t="inlineStr"/>
+      <c r="H9" s="63" t="inlineStr"/>
+      <c r="I9" s="63" t="inlineStr"/>
+      <c r="J9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="63" t="n">
+      <c r="K9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="66">
+      <c r="L9" s="64">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="67">
+      <c r="M9" s="65">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="inlineStr"/>
-      <c r="B10" s="61" t="inlineStr"/>
-      <c r="C10" s="61" t="inlineStr"/>
-      <c r="D10" s="61" t="inlineStr"/>
-      <c r="E10" s="61" t="inlineStr"/>
-      <c r="F10" s="61" t="inlineStr"/>
-      <c r="G10" s="61" t="inlineStr"/>
-      <c r="H10" s="61" t="inlineStr"/>
-      <c r="I10" s="61" t="inlineStr"/>
-      <c r="J10" s="63" t="n">
+      <c r="A10" s="59" t="inlineStr"/>
+      <c r="B10" s="59" t="inlineStr"/>
+      <c r="C10" s="59" t="inlineStr"/>
+      <c r="D10" s="59" t="inlineStr"/>
+      <c r="E10" s="59" t="inlineStr"/>
+      <c r="F10" s="59" t="inlineStr"/>
+      <c r="G10" s="59" t="inlineStr"/>
+      <c r="H10" s="59" t="inlineStr"/>
+      <c r="I10" s="59" t="inlineStr"/>
+      <c r="J10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="63" t="n">
+      <c r="K10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="62">
+      <c r="L10" s="60">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="64">
+      <c r="M10" s="62">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="inlineStr"/>
-      <c r="B11" s="65" t="inlineStr"/>
-      <c r="C11" s="65" t="inlineStr"/>
-      <c r="D11" s="65" t="inlineStr"/>
-      <c r="E11" s="65" t="inlineStr"/>
-      <c r="F11" s="65" t="inlineStr"/>
-      <c r="G11" s="65" t="inlineStr"/>
-      <c r="H11" s="65" t="inlineStr"/>
-      <c r="I11" s="65" t="inlineStr"/>
-      <c r="J11" s="63" t="n">
+      <c r="A11" s="63" t="inlineStr"/>
+      <c r="B11" s="63" t="inlineStr"/>
+      <c r="C11" s="63" t="inlineStr"/>
+      <c r="D11" s="63" t="inlineStr"/>
+      <c r="E11" s="63" t="inlineStr"/>
+      <c r="F11" s="63" t="inlineStr"/>
+      <c r="G11" s="63" t="inlineStr"/>
+      <c r="H11" s="63" t="inlineStr"/>
+      <c r="I11" s="63" t="inlineStr"/>
+      <c r="J11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="63" t="n">
+      <c r="K11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="66">
+      <c r="L11" s="64">
         <f>K11-J11</f>
         <v/>
       </c>
-      <c r="M11" s="67">
+      <c r="M11" s="65">
         <f>IF(J11=0,"",(K11-J11)/J11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="inlineStr"/>
-      <c r="B12" s="61" t="inlineStr"/>
-      <c r="C12" s="61" t="inlineStr"/>
-      <c r="D12" s="61" t="inlineStr"/>
-      <c r="E12" s="61" t="inlineStr"/>
-      <c r="F12" s="61" t="inlineStr"/>
-      <c r="G12" s="61" t="inlineStr"/>
-      <c r="H12" s="61" t="inlineStr"/>
-      <c r="I12" s="61" t="inlineStr"/>
-      <c r="J12" s="63" t="n">
+      <c r="A12" s="59" t="inlineStr"/>
+      <c r="B12" s="59" t="inlineStr"/>
+      <c r="C12" s="59" t="inlineStr"/>
+      <c r="D12" s="59" t="inlineStr"/>
+      <c r="E12" s="59" t="inlineStr"/>
+      <c r="F12" s="59" t="inlineStr"/>
+      <c r="G12" s="59" t="inlineStr"/>
+      <c r="H12" s="59" t="inlineStr"/>
+      <c r="I12" s="59" t="inlineStr"/>
+      <c r="J12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="63" t="n">
+      <c r="K12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="62">
+      <c r="L12" s="60">
         <f>K12-J12</f>
         <v/>
       </c>
-      <c r="M12" s="64">
+      <c r="M12" s="62">
         <f>IF(J12=0,"",(K12-J12)/J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="65" t="inlineStr"/>
-      <c r="B13" s="65" t="inlineStr"/>
-      <c r="C13" s="65" t="inlineStr"/>
-      <c r="D13" s="65" t="inlineStr"/>
-      <c r="E13" s="65" t="inlineStr"/>
-      <c r="F13" s="65" t="inlineStr"/>
-      <c r="G13" s="65" t="inlineStr"/>
-      <c r="H13" s="65" t="inlineStr"/>
-      <c r="I13" s="65" t="inlineStr"/>
-      <c r="J13" s="63" t="n">
+      <c r="A13" s="63" t="inlineStr"/>
+      <c r="B13" s="63" t="inlineStr"/>
+      <c r="C13" s="63" t="inlineStr"/>
+      <c r="D13" s="63" t="inlineStr"/>
+      <c r="E13" s="63" t="inlineStr"/>
+      <c r="F13" s="63" t="inlineStr"/>
+      <c r="G13" s="63" t="inlineStr"/>
+      <c r="H13" s="63" t="inlineStr"/>
+      <c r="I13" s="63" t="inlineStr"/>
+      <c r="J13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="63" t="n">
+      <c r="K13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="66">
+      <c r="L13" s="64">
         <f>K13-J13</f>
         <v/>
       </c>
-      <c r="M13" s="67">
+      <c r="M13" s="65">
         <f>IF(J13=0,"",(K13-J13)/J13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="68" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="68" t="n"/>
-      <c r="E14" s="68" t="n"/>
-      <c r="F14" s="68" t="n"/>
-      <c r="G14" s="68" t="n"/>
-      <c r="H14" s="68" t="n"/>
-      <c r="I14" s="68" t="n"/>
-      <c r="J14" s="32">
+      <c r="B14" s="66" t="n"/>
+      <c r="C14" s="66" t="n"/>
+      <c r="D14" s="66" t="n"/>
+      <c r="E14" s="66" t="n"/>
+      <c r="F14" s="66" t="n"/>
+      <c r="G14" s="66" t="n"/>
+      <c r="H14" s="66" t="n"/>
+      <c r="I14" s="66" t="n"/>
+      <c r="J14" s="30">
         <f>SUM(J6:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="30">
         <f>SUM(K6:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="30">
         <f>K14-J14</f>
         <v/>
       </c>
-      <c r="M14" s="33">
+      <c r="M14" s="31">
         <f>IF(J14=0,"",(K14-J14)/J14)</f>
         <v/>
       </c>
@@ -13194,299 +13239,299 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Nombre del deudor</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Tipo de deudor</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>N. de identificacion</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="L5" s="27" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr"/>
-      <c r="B6" s="61" t="inlineStr"/>
-      <c r="C6" s="61" t="inlineStr"/>
-      <c r="D6" s="61" t="inlineStr"/>
-      <c r="E6" s="61" t="inlineStr"/>
-      <c r="F6" s="61" t="inlineStr"/>
-      <c r="G6" s="61" t="inlineStr"/>
-      <c r="H6" s="61" t="inlineStr"/>
-      <c r="I6" s="61" t="inlineStr"/>
-      <c r="J6" s="63" t="n">
+      <c r="A6" s="59" t="inlineStr"/>
+      <c r="B6" s="59" t="inlineStr"/>
+      <c r="C6" s="59" t="inlineStr"/>
+      <c r="D6" s="59" t="inlineStr"/>
+      <c r="E6" s="59" t="inlineStr"/>
+      <c r="F6" s="59" t="inlineStr"/>
+      <c r="G6" s="59" t="inlineStr"/>
+      <c r="H6" s="59" t="inlineStr"/>
+      <c r="I6" s="59" t="inlineStr"/>
+      <c r="J6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="63" t="n">
+      <c r="K6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="60">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="62">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr"/>
-      <c r="B7" s="65" t="inlineStr"/>
-      <c r="C7" s="65" t="inlineStr"/>
-      <c r="D7" s="65" t="inlineStr"/>
-      <c r="E7" s="65" t="inlineStr"/>
-      <c r="F7" s="65" t="inlineStr"/>
-      <c r="G7" s="65" t="inlineStr"/>
-      <c r="H7" s="65" t="inlineStr"/>
-      <c r="I7" s="65" t="inlineStr"/>
-      <c r="J7" s="63" t="n">
+      <c r="A7" s="63" t="inlineStr"/>
+      <c r="B7" s="63" t="inlineStr"/>
+      <c r="C7" s="63" t="inlineStr"/>
+      <c r="D7" s="63" t="inlineStr"/>
+      <c r="E7" s="63" t="inlineStr"/>
+      <c r="F7" s="63" t="inlineStr"/>
+      <c r="G7" s="63" t="inlineStr"/>
+      <c r="H7" s="63" t="inlineStr"/>
+      <c r="I7" s="63" t="inlineStr"/>
+      <c r="J7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="63" t="n">
+      <c r="K7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="64">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="65">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr"/>
-      <c r="B8" s="61" t="inlineStr"/>
-      <c r="C8" s="61" t="inlineStr"/>
-      <c r="D8" s="61" t="inlineStr"/>
-      <c r="E8" s="61" t="inlineStr"/>
-      <c r="F8" s="61" t="inlineStr"/>
-      <c r="G8" s="61" t="inlineStr"/>
-      <c r="H8" s="61" t="inlineStr"/>
-      <c r="I8" s="61" t="inlineStr"/>
-      <c r="J8" s="63" t="n">
+      <c r="A8" s="59" t="inlineStr"/>
+      <c r="B8" s="59" t="inlineStr"/>
+      <c r="C8" s="59" t="inlineStr"/>
+      <c r="D8" s="59" t="inlineStr"/>
+      <c r="E8" s="59" t="inlineStr"/>
+      <c r="F8" s="59" t="inlineStr"/>
+      <c r="G8" s="59" t="inlineStr"/>
+      <c r="H8" s="59" t="inlineStr"/>
+      <c r="I8" s="59" t="inlineStr"/>
+      <c r="J8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="63" t="n">
+      <c r="K8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="62">
+      <c r="L8" s="60">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="64">
+      <c r="M8" s="62">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr"/>
-      <c r="B9" s="65" t="inlineStr"/>
-      <c r="C9" s="65" t="inlineStr"/>
-      <c r="D9" s="65" t="inlineStr"/>
-      <c r="E9" s="65" t="inlineStr"/>
-      <c r="F9" s="65" t="inlineStr"/>
-      <c r="G9" s="65" t="inlineStr"/>
-      <c r="H9" s="65" t="inlineStr"/>
-      <c r="I9" s="65" t="inlineStr"/>
-      <c r="J9" s="63" t="n">
+      <c r="A9" s="63" t="inlineStr"/>
+      <c r="B9" s="63" t="inlineStr"/>
+      <c r="C9" s="63" t="inlineStr"/>
+      <c r="D9" s="63" t="inlineStr"/>
+      <c r="E9" s="63" t="inlineStr"/>
+      <c r="F9" s="63" t="inlineStr"/>
+      <c r="G9" s="63" t="inlineStr"/>
+      <c r="H9" s="63" t="inlineStr"/>
+      <c r="I9" s="63" t="inlineStr"/>
+      <c r="J9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="63" t="n">
+      <c r="K9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="66">
+      <c r="L9" s="64">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="67">
+      <c r="M9" s="65">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="inlineStr"/>
-      <c r="B10" s="61" t="inlineStr"/>
-      <c r="C10" s="61" t="inlineStr"/>
-      <c r="D10" s="61" t="inlineStr"/>
-      <c r="E10" s="61" t="inlineStr"/>
-      <c r="F10" s="61" t="inlineStr"/>
-      <c r="G10" s="61" t="inlineStr"/>
-      <c r="H10" s="61" t="inlineStr"/>
-      <c r="I10" s="61" t="inlineStr"/>
-      <c r="J10" s="63" t="n">
+      <c r="A10" s="59" t="inlineStr"/>
+      <c r="B10" s="59" t="inlineStr"/>
+      <c r="C10" s="59" t="inlineStr"/>
+      <c r="D10" s="59" t="inlineStr"/>
+      <c r="E10" s="59" t="inlineStr"/>
+      <c r="F10" s="59" t="inlineStr"/>
+      <c r="G10" s="59" t="inlineStr"/>
+      <c r="H10" s="59" t="inlineStr"/>
+      <c r="I10" s="59" t="inlineStr"/>
+      <c r="J10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="63" t="n">
+      <c r="K10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="62">
+      <c r="L10" s="60">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="64">
+      <c r="M10" s="62">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="inlineStr"/>
-      <c r="B11" s="65" t="inlineStr"/>
-      <c r="C11" s="65" t="inlineStr"/>
-      <c r="D11" s="65" t="inlineStr"/>
-      <c r="E11" s="65" t="inlineStr"/>
-      <c r="F11" s="65" t="inlineStr"/>
-      <c r="G11" s="65" t="inlineStr"/>
-      <c r="H11" s="65" t="inlineStr"/>
-      <c r="I11" s="65" t="inlineStr"/>
-      <c r="J11" s="63" t="n">
+      <c r="A11" s="63" t="inlineStr"/>
+      <c r="B11" s="63" t="inlineStr"/>
+      <c r="C11" s="63" t="inlineStr"/>
+      <c r="D11" s="63" t="inlineStr"/>
+      <c r="E11" s="63" t="inlineStr"/>
+      <c r="F11" s="63" t="inlineStr"/>
+      <c r="G11" s="63" t="inlineStr"/>
+      <c r="H11" s="63" t="inlineStr"/>
+      <c r="I11" s="63" t="inlineStr"/>
+      <c r="J11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="63" t="n">
+      <c r="K11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="66">
+      <c r="L11" s="64">
         <f>K11-J11</f>
         <v/>
       </c>
-      <c r="M11" s="67">
+      <c r="M11" s="65">
         <f>IF(J11=0,"",(K11-J11)/J11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="inlineStr"/>
-      <c r="B12" s="61" t="inlineStr"/>
-      <c r="C12" s="61" t="inlineStr"/>
-      <c r="D12" s="61" t="inlineStr"/>
-      <c r="E12" s="61" t="inlineStr"/>
-      <c r="F12" s="61" t="inlineStr"/>
-      <c r="G12" s="61" t="inlineStr"/>
-      <c r="H12" s="61" t="inlineStr"/>
-      <c r="I12" s="61" t="inlineStr"/>
-      <c r="J12" s="63" t="n">
+      <c r="A12" s="59" t="inlineStr"/>
+      <c r="B12" s="59" t="inlineStr"/>
+      <c r="C12" s="59" t="inlineStr"/>
+      <c r="D12" s="59" t="inlineStr"/>
+      <c r="E12" s="59" t="inlineStr"/>
+      <c r="F12" s="59" t="inlineStr"/>
+      <c r="G12" s="59" t="inlineStr"/>
+      <c r="H12" s="59" t="inlineStr"/>
+      <c r="I12" s="59" t="inlineStr"/>
+      <c r="J12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="63" t="n">
+      <c r="K12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="62">
+      <c r="L12" s="60">
         <f>K12-J12</f>
         <v/>
       </c>
-      <c r="M12" s="64">
+      <c r="M12" s="62">
         <f>IF(J12=0,"",(K12-J12)/J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="65" t="inlineStr"/>
-      <c r="B13" s="65" t="inlineStr"/>
-      <c r="C13" s="65" t="inlineStr"/>
-      <c r="D13" s="65" t="inlineStr"/>
-      <c r="E13" s="65" t="inlineStr"/>
-      <c r="F13" s="65" t="inlineStr"/>
-      <c r="G13" s="65" t="inlineStr"/>
-      <c r="H13" s="65" t="inlineStr"/>
-      <c r="I13" s="65" t="inlineStr"/>
-      <c r="J13" s="63" t="n">
+      <c r="A13" s="63" t="inlineStr"/>
+      <c r="B13" s="63" t="inlineStr"/>
+      <c r="C13" s="63" t="inlineStr"/>
+      <c r="D13" s="63" t="inlineStr"/>
+      <c r="E13" s="63" t="inlineStr"/>
+      <c r="F13" s="63" t="inlineStr"/>
+      <c r="G13" s="63" t="inlineStr"/>
+      <c r="H13" s="63" t="inlineStr"/>
+      <c r="I13" s="63" t="inlineStr"/>
+      <c r="J13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="63" t="n">
+      <c r="K13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="66">
+      <c r="L13" s="64">
         <f>K13-J13</f>
         <v/>
       </c>
-      <c r="M13" s="67">
+      <c r="M13" s="65">
         <f>IF(J13=0,"",(K13-J13)/J13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="68" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="68" t="n"/>
-      <c r="E14" s="68" t="n"/>
-      <c r="F14" s="68" t="n"/>
-      <c r="G14" s="68" t="n"/>
-      <c r="H14" s="68" t="n"/>
-      <c r="I14" s="68" t="n"/>
-      <c r="J14" s="32">
+      <c r="B14" s="66" t="n"/>
+      <c r="C14" s="66" t="n"/>
+      <c r="D14" s="66" t="n"/>
+      <c r="E14" s="66" t="n"/>
+      <c r="F14" s="66" t="n"/>
+      <c r="G14" s="66" t="n"/>
+      <c r="H14" s="66" t="n"/>
+      <c r="I14" s="66" t="n"/>
+      <c r="J14" s="30">
         <f>SUM(J6:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="30">
         <f>SUM(K6:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="30">
         <f>K14-J14</f>
         <v/>
       </c>
-      <c r="M14" s="33">
+      <c r="M14" s="31">
         <f>IF(J14=0,"",(K14-J14)/J14)</f>
         <v/>
       </c>
@@ -13559,243 +13604,243 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Tipo de bien</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr"/>
-      <c r="B6" s="61" t="inlineStr"/>
-      <c r="C6" s="61" t="inlineStr"/>
-      <c r="D6" s="61" t="inlineStr"/>
-      <c r="E6" s="61" t="inlineStr"/>
-      <c r="F6" s="63" t="n">
+      <c r="A6" s="59" t="inlineStr"/>
+      <c r="B6" s="59" t="inlineStr"/>
+      <c r="C6" s="59" t="inlineStr"/>
+      <c r="D6" s="59" t="inlineStr"/>
+      <c r="E6" s="59" t="inlineStr"/>
+      <c r="F6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="63" t="n">
+      <c r="G6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="62">
+      <c r="H6" s="60">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="62">
         <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr"/>
-      <c r="B7" s="65" t="inlineStr"/>
-      <c r="C7" s="65" t="inlineStr"/>
-      <c r="D7" s="65" t="inlineStr"/>
-      <c r="E7" s="65" t="inlineStr"/>
-      <c r="F7" s="63" t="n">
+      <c r="A7" s="63" t="inlineStr"/>
+      <c r="B7" s="63" t="inlineStr"/>
+      <c r="C7" s="63" t="inlineStr"/>
+      <c r="D7" s="63" t="inlineStr"/>
+      <c r="E7" s="63" t="inlineStr"/>
+      <c r="F7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="63" t="n">
+      <c r="G7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="66">
+      <c r="H7" s="64">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="65">
         <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr"/>
-      <c r="B8" s="61" t="inlineStr"/>
-      <c r="C8" s="61" t="inlineStr"/>
-      <c r="D8" s="61" t="inlineStr"/>
-      <c r="E8" s="61" t="inlineStr"/>
-      <c r="F8" s="63" t="n">
+      <c r="A8" s="59" t="inlineStr"/>
+      <c r="B8" s="59" t="inlineStr"/>
+      <c r="C8" s="59" t="inlineStr"/>
+      <c r="D8" s="59" t="inlineStr"/>
+      <c r="E8" s="59" t="inlineStr"/>
+      <c r="F8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="63" t="n">
+      <c r="G8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="62">
+      <c r="H8" s="60">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="64">
+      <c r="I8" s="62">
         <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr"/>
-      <c r="B9" s="65" t="inlineStr"/>
-      <c r="C9" s="65" t="inlineStr"/>
-      <c r="D9" s="65" t="inlineStr"/>
-      <c r="E9" s="65" t="inlineStr"/>
-      <c r="F9" s="63" t="n">
+      <c r="A9" s="63" t="inlineStr"/>
+      <c r="B9" s="63" t="inlineStr"/>
+      <c r="C9" s="63" t="inlineStr"/>
+      <c r="D9" s="63" t="inlineStr"/>
+      <c r="E9" s="63" t="inlineStr"/>
+      <c r="F9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="63" t="n">
+      <c r="G9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="66">
+      <c r="H9" s="64">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="67">
+      <c r="I9" s="65">
         <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="inlineStr"/>
-      <c r="B10" s="61" t="inlineStr"/>
-      <c r="C10" s="61" t="inlineStr"/>
-      <c r="D10" s="61" t="inlineStr"/>
-      <c r="E10" s="61" t="inlineStr"/>
-      <c r="F10" s="63" t="n">
+      <c r="A10" s="59" t="inlineStr"/>
+      <c r="B10" s="59" t="inlineStr"/>
+      <c r="C10" s="59" t="inlineStr"/>
+      <c r="D10" s="59" t="inlineStr"/>
+      <c r="E10" s="59" t="inlineStr"/>
+      <c r="F10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="63" t="n">
+      <c r="G10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="62">
+      <c r="H10" s="60">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="64">
+      <c r="I10" s="62">
         <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="inlineStr"/>
-      <c r="B11" s="65" t="inlineStr"/>
-      <c r="C11" s="65" t="inlineStr"/>
-      <c r="D11" s="65" t="inlineStr"/>
-      <c r="E11" s="65" t="inlineStr"/>
-      <c r="F11" s="63" t="n">
+      <c r="A11" s="63" t="inlineStr"/>
+      <c r="B11" s="63" t="inlineStr"/>
+      <c r="C11" s="63" t="inlineStr"/>
+      <c r="D11" s="63" t="inlineStr"/>
+      <c r="E11" s="63" t="inlineStr"/>
+      <c r="F11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="63" t="n">
+      <c r="G11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="66">
+      <c r="H11" s="64">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="67">
+      <c r="I11" s="65">
         <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="inlineStr"/>
-      <c r="B12" s="61" t="inlineStr"/>
-      <c r="C12" s="61" t="inlineStr"/>
-      <c r="D12" s="61" t="inlineStr"/>
-      <c r="E12" s="61" t="inlineStr"/>
-      <c r="F12" s="63" t="n">
+      <c r="A12" s="59" t="inlineStr"/>
+      <c r="B12" s="59" t="inlineStr"/>
+      <c r="C12" s="59" t="inlineStr"/>
+      <c r="D12" s="59" t="inlineStr"/>
+      <c r="E12" s="59" t="inlineStr"/>
+      <c r="F12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="63" t="n">
+      <c r="G12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="62">
+      <c r="H12" s="60">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="64">
+      <c r="I12" s="62">
         <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="65" t="inlineStr"/>
-      <c r="B13" s="65" t="inlineStr"/>
-      <c r="C13" s="65" t="inlineStr"/>
-      <c r="D13" s="65" t="inlineStr"/>
-      <c r="E13" s="65" t="inlineStr"/>
-      <c r="F13" s="63" t="n">
+      <c r="A13" s="63" t="inlineStr"/>
+      <c r="B13" s="63" t="inlineStr"/>
+      <c r="C13" s="63" t="inlineStr"/>
+      <c r="D13" s="63" t="inlineStr"/>
+      <c r="E13" s="63" t="inlineStr"/>
+      <c r="F13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="63" t="n">
+      <c r="G13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="66">
+      <c r="H13" s="64">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="67">
+      <c r="I13" s="65">
         <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="68" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="68" t="n"/>
-      <c r="E14" s="68" t="n"/>
-      <c r="F14" s="32">
+      <c r="B14" s="66" t="n"/>
+      <c r="C14" s="66" t="n"/>
+      <c r="D14" s="66" t="n"/>
+      <c r="E14" s="66" t="n"/>
+      <c r="F14" s="30">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="30">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="30">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="33">
+      <c r="I14" s="31">
         <f>IF(F14=0,"",(G14-F14)/F14)</f>
         <v/>
       </c>
@@ -13863,195 +13908,195 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Tipo de vehiculo</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Registro / placa / chasis</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>1 - Vehiculos motorizados terrestres</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>PBO7092</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E6" s="61" t="inlineStr"/>
-      <c r="F6" s="61" t="inlineStr"/>
-      <c r="G6" s="62" t="n">
+      <c r="E6" s="59" t="inlineStr"/>
+      <c r="F6" s="59" t="inlineStr"/>
+      <c r="G6" s="60" t="n">
         <v>12000</v>
       </c>
-      <c r="H6" s="63" t="n">
+      <c r="H6" s="61" t="n">
         <v>12000</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="60">
         <f>H6-G6</f>
         <v/>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="62">
         <f>IF(G6=0,"",(H6-G6)/G6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>1 - Vehiculos motorizados terrestres</t>
         </is>
       </c>
-      <c r="B7" s="65" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>PBF9690</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="63" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D7" s="65" t="inlineStr">
+      <c r="D7" s="63" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E7" s="65" t="inlineStr"/>
-      <c r="F7" s="65" t="inlineStr"/>
-      <c r="G7" s="66" t="n">
+      <c r="E7" s="63" t="inlineStr"/>
+      <c r="F7" s="63" t="inlineStr"/>
+      <c r="G7" s="64" t="n">
         <v>20000</v>
       </c>
-      <c r="H7" s="63" t="n">
+      <c r="H7" s="61" t="n">
         <v>20000</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="64">
         <f>H7-G7</f>
         <v/>
       </c>
-      <c r="J7" s="67">
+      <c r="J7" s="65">
         <f>IF(G7=0,"",(H7-G7)/G7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>1 - Vehiculos motorizados terrestres</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>PFC8683</t>
         </is>
       </c>
-      <c r="C8" s="61" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E8" s="61" t="inlineStr"/>
-      <c r="F8" s="61" t="inlineStr"/>
-      <c r="G8" s="62" t="n">
+      <c r="E8" s="59" t="inlineStr"/>
+      <c r="F8" s="59" t="inlineStr"/>
+      <c r="G8" s="60" t="n">
         <v>32000</v>
       </c>
-      <c r="H8" s="63" t="n">
+      <c r="H8" s="61" t="n">
         <v>32000</v>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="60">
         <f>H8-G8</f>
         <v/>
       </c>
-      <c r="J8" s="64">
+      <c r="J8" s="62">
         <f>IF(G8=0,"",(H8-G8)/G8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="66" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="68" t="n"/>
-      <c r="C9" s="68" t="n"/>
-      <c r="D9" s="68" t="n"/>
-      <c r="E9" s="68" t="n"/>
-      <c r="F9" s="68" t="n"/>
-      <c r="G9" s="32">
+      <c r="B9" s="66" t="n"/>
+      <c r="C9" s="66" t="n"/>
+      <c r="D9" s="66" t="n"/>
+      <c r="E9" s="66" t="n"/>
+      <c r="F9" s="66" t="n"/>
+      <c r="G9" s="30">
         <f>SUM(G6:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="30">
         <f>SUM(H6:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="30">
         <f>H9-G9</f>
         <v/>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="31">
         <f>IF(G9=0,"",(H9-G9)/G9)</f>
         <v/>
       </c>
@@ -14118,243 +14163,243 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Tipo de derecho</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr"/>
-      <c r="B6" s="61" t="inlineStr"/>
-      <c r="C6" s="61" t="inlineStr"/>
-      <c r="D6" s="61" t="inlineStr"/>
-      <c r="E6" s="61" t="inlineStr"/>
-      <c r="F6" s="63" t="n">
+      <c r="A6" s="59" t="inlineStr"/>
+      <c r="B6" s="59" t="inlineStr"/>
+      <c r="C6" s="59" t="inlineStr"/>
+      <c r="D6" s="59" t="inlineStr"/>
+      <c r="E6" s="59" t="inlineStr"/>
+      <c r="F6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="63" t="n">
+      <c r="G6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="62">
+      <c r="H6" s="60">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="62">
         <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr"/>
-      <c r="B7" s="65" t="inlineStr"/>
-      <c r="C7" s="65" t="inlineStr"/>
-      <c r="D7" s="65" t="inlineStr"/>
-      <c r="E7" s="65" t="inlineStr"/>
-      <c r="F7" s="63" t="n">
+      <c r="A7" s="63" t="inlineStr"/>
+      <c r="B7" s="63" t="inlineStr"/>
+      <c r="C7" s="63" t="inlineStr"/>
+      <c r="D7" s="63" t="inlineStr"/>
+      <c r="E7" s="63" t="inlineStr"/>
+      <c r="F7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="63" t="n">
+      <c r="G7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="66">
+      <c r="H7" s="64">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="65">
         <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr"/>
-      <c r="B8" s="61" t="inlineStr"/>
-      <c r="C8" s="61" t="inlineStr"/>
-      <c r="D8" s="61" t="inlineStr"/>
-      <c r="E8" s="61" t="inlineStr"/>
-      <c r="F8" s="63" t="n">
+      <c r="A8" s="59" t="inlineStr"/>
+      <c r="B8" s="59" t="inlineStr"/>
+      <c r="C8" s="59" t="inlineStr"/>
+      <c r="D8" s="59" t="inlineStr"/>
+      <c r="E8" s="59" t="inlineStr"/>
+      <c r="F8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="63" t="n">
+      <c r="G8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="62">
+      <c r="H8" s="60">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="64">
+      <c r="I8" s="62">
         <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr"/>
-      <c r="B9" s="65" t="inlineStr"/>
-      <c r="C9" s="65" t="inlineStr"/>
-      <c r="D9" s="65" t="inlineStr"/>
-      <c r="E9" s="65" t="inlineStr"/>
-      <c r="F9" s="63" t="n">
+      <c r="A9" s="63" t="inlineStr"/>
+      <c r="B9" s="63" t="inlineStr"/>
+      <c r="C9" s="63" t="inlineStr"/>
+      <c r="D9" s="63" t="inlineStr"/>
+      <c r="E9" s="63" t="inlineStr"/>
+      <c r="F9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="63" t="n">
+      <c r="G9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="66">
+      <c r="H9" s="64">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="67">
+      <c r="I9" s="65">
         <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="inlineStr"/>
-      <c r="B10" s="61" t="inlineStr"/>
-      <c r="C10" s="61" t="inlineStr"/>
-      <c r="D10" s="61" t="inlineStr"/>
-      <c r="E10" s="61" t="inlineStr"/>
-      <c r="F10" s="63" t="n">
+      <c r="A10" s="59" t="inlineStr"/>
+      <c r="B10" s="59" t="inlineStr"/>
+      <c r="C10" s="59" t="inlineStr"/>
+      <c r="D10" s="59" t="inlineStr"/>
+      <c r="E10" s="59" t="inlineStr"/>
+      <c r="F10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="63" t="n">
+      <c r="G10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="62">
+      <c r="H10" s="60">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="64">
+      <c r="I10" s="62">
         <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="inlineStr"/>
-      <c r="B11" s="65" t="inlineStr"/>
-      <c r="C11" s="65" t="inlineStr"/>
-      <c r="D11" s="65" t="inlineStr"/>
-      <c r="E11" s="65" t="inlineStr"/>
-      <c r="F11" s="63" t="n">
+      <c r="A11" s="63" t="inlineStr"/>
+      <c r="B11" s="63" t="inlineStr"/>
+      <c r="C11" s="63" t="inlineStr"/>
+      <c r="D11" s="63" t="inlineStr"/>
+      <c r="E11" s="63" t="inlineStr"/>
+      <c r="F11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="63" t="n">
+      <c r="G11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="66">
+      <c r="H11" s="64">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="67">
+      <c r="I11" s="65">
         <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="inlineStr"/>
-      <c r="B12" s="61" t="inlineStr"/>
-      <c r="C12" s="61" t="inlineStr"/>
-      <c r="D12" s="61" t="inlineStr"/>
-      <c r="E12" s="61" t="inlineStr"/>
-      <c r="F12" s="63" t="n">
+      <c r="A12" s="59" t="inlineStr"/>
+      <c r="B12" s="59" t="inlineStr"/>
+      <c r="C12" s="59" t="inlineStr"/>
+      <c r="D12" s="59" t="inlineStr"/>
+      <c r="E12" s="59" t="inlineStr"/>
+      <c r="F12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="63" t="n">
+      <c r="G12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="62">
+      <c r="H12" s="60">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="64">
+      <c r="I12" s="62">
         <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="65" t="inlineStr"/>
-      <c r="B13" s="65" t="inlineStr"/>
-      <c r="C13" s="65" t="inlineStr"/>
-      <c r="D13" s="65" t="inlineStr"/>
-      <c r="E13" s="65" t="inlineStr"/>
-      <c r="F13" s="63" t="n">
+      <c r="A13" s="63" t="inlineStr"/>
+      <c r="B13" s="63" t="inlineStr"/>
+      <c r="C13" s="63" t="inlineStr"/>
+      <c r="D13" s="63" t="inlineStr"/>
+      <c r="E13" s="63" t="inlineStr"/>
+      <c r="F13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="63" t="n">
+      <c r="G13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="66">
+      <c r="H13" s="64">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="67">
+      <c r="I13" s="65">
         <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="68" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="68" t="n"/>
-      <c r="E14" s="68" t="n"/>
-      <c r="F14" s="32">
+      <c r="B14" s="66" t="n"/>
+      <c r="C14" s="66" t="n"/>
+      <c r="D14" s="66" t="n"/>
+      <c r="E14" s="66" t="n"/>
+      <c r="F14" s="30">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="30">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="30">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="33">
+      <c r="I14" s="31">
         <f>IF(F14=0,"",(G14-F14)/F14)</f>
         <v/>
       </c>
@@ -14425,303 +14470,303 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Tipo de inmueble</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Canton</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Fecha de inscripcion</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Clave catastral</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="L5" s="27" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>3 - Terreno</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E6" s="61" t="inlineStr">
+      <c r="E6" s="59" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F6" s="61" t="inlineStr">
+      <c r="F6" s="59" t="inlineStr">
         <is>
           <t>22/10/2008</t>
         </is>
       </c>
-      <c r="G6" s="61" t="inlineStr">
+      <c r="G6" s="59" t="inlineStr">
         <is>
           <t>1042203018</t>
         </is>
       </c>
-      <c r="H6" s="61" t="inlineStr"/>
-      <c r="I6" s="61" t="inlineStr"/>
-      <c r="J6" s="62" t="n">
+      <c r="H6" s="59" t="inlineStr"/>
+      <c r="I6" s="59" t="inlineStr"/>
+      <c r="J6" s="60" t="n">
         <v>267340.8</v>
       </c>
-      <c r="K6" s="63" t="n">
+      <c r="K6" s="61" t="n">
         <v>267340.8</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="60">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="62">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>1 - Casa</t>
         </is>
       </c>
-      <c r="B7" s="65" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="63" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D7" s="65" t="inlineStr">
+      <c r="D7" s="63" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E7" s="65" t="inlineStr">
+      <c r="E7" s="63" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F7" s="65" t="inlineStr">
+      <c r="F7" s="63" t="inlineStr">
         <is>
           <t>13/03/1997</t>
         </is>
       </c>
-      <c r="G7" s="65" t="inlineStr">
+      <c r="G7" s="63" t="inlineStr">
         <is>
           <t>1012005008000000000</t>
         </is>
       </c>
-      <c r="H7" s="65" t="inlineStr"/>
-      <c r="I7" s="65" t="inlineStr"/>
-      <c r="J7" s="66" t="n">
+      <c r="H7" s="63" t="inlineStr"/>
+      <c r="I7" s="63" t="inlineStr"/>
+      <c r="J7" s="64" t="n">
         <v>198118.55</v>
       </c>
-      <c r="K7" s="63" t="n">
+      <c r="K7" s="61" t="n">
         <v>198118.55</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="64">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="65">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>1 - Casa</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C8" s="61" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E8" s="61" t="inlineStr">
+      <c r="E8" s="59" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F8" s="61" t="inlineStr"/>
-      <c r="G8" s="61" t="inlineStr">
+      <c r="F8" s="59" t="inlineStr"/>
+      <c r="G8" s="59" t="inlineStr">
         <is>
           <t>1042203018</t>
         </is>
       </c>
-      <c r="H8" s="61" t="inlineStr"/>
-      <c r="I8" s="61" t="inlineStr"/>
-      <c r="J8" s="62" t="n">
+      <c r="H8" s="59" t="inlineStr"/>
+      <c r="I8" s="59" t="inlineStr"/>
+      <c r="J8" s="60" t="n">
         <v>33634.04</v>
       </c>
-      <c r="K8" s="63" t="n">
+      <c r="K8" s="61" t="n">
         <v>33634.04</v>
       </c>
-      <c r="L8" s="62">
+      <c r="L8" s="60">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="64">
+      <c r="M8" s="62">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr">
+      <c r="A9" s="63" t="inlineStr">
         <is>
           <t>3 - Terreno</t>
         </is>
       </c>
-      <c r="B9" s="65" t="inlineStr">
+      <c r="B9" s="63" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
+      <c r="C9" s="63" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D9" s="65" t="inlineStr">
+      <c r="D9" s="63" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E9" s="65" t="inlineStr">
+      <c r="E9" s="63" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F9" s="65" t="inlineStr"/>
-      <c r="G9" s="65" t="inlineStr">
+      <c r="F9" s="63" t="inlineStr"/>
+      <c r="G9" s="63" t="inlineStr">
         <is>
           <t>1012005008000000000</t>
         </is>
       </c>
-      <c r="H9" s="65" t="inlineStr"/>
-      <c r="I9" s="65" t="inlineStr"/>
-      <c r="J9" s="66" t="n">
+      <c r="H9" s="63" t="inlineStr"/>
+      <c r="I9" s="63" t="inlineStr"/>
+      <c r="J9" s="64" t="n">
         <v>82624.22</v>
       </c>
-      <c r="K9" s="63" t="n">
+      <c r="K9" s="61" t="n">
         <v>82624.22</v>
       </c>
-      <c r="L9" s="66">
+      <c r="L9" s="64">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="67">
+      <c r="M9" s="65">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="68" t="n"/>
-      <c r="C10" s="68" t="n"/>
-      <c r="D10" s="68" t="n"/>
-      <c r="E10" s="68" t="n"/>
-      <c r="F10" s="68" t="n"/>
-      <c r="G10" s="68" t="n"/>
-      <c r="H10" s="68" t="n"/>
-      <c r="I10" s="68" t="n"/>
-      <c r="J10" s="32">
+      <c r="B10" s="66" t="n"/>
+      <c r="C10" s="66" t="n"/>
+      <c r="D10" s="66" t="n"/>
+      <c r="E10" s="66" t="n"/>
+      <c r="F10" s="66" t="n"/>
+      <c r="G10" s="66" t="n"/>
+      <c r="H10" s="66" t="n"/>
+      <c r="I10" s="66" t="n"/>
+      <c r="J10" s="30">
         <f>SUM(J6:J9)</f>
         <v/>
       </c>
-      <c r="K10" s="32">
+      <c r="K10" s="30">
         <f>SUM(K6:K9)</f>
         <v/>
       </c>
-      <c r="L10" s="32">
+      <c r="L10" s="30">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="33">
+      <c r="M10" s="31">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
@@ -14794,243 +14839,243 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Descripcion</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr"/>
-      <c r="B6" s="61" t="inlineStr"/>
-      <c r="C6" s="61" t="inlineStr"/>
-      <c r="D6" s="61" t="inlineStr"/>
-      <c r="E6" s="61" t="inlineStr"/>
-      <c r="F6" s="63" t="n">
+      <c r="A6" s="59" t="inlineStr"/>
+      <c r="B6" s="59" t="inlineStr"/>
+      <c r="C6" s="59" t="inlineStr"/>
+      <c r="D6" s="59" t="inlineStr"/>
+      <c r="E6" s="59" t="inlineStr"/>
+      <c r="F6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="63" t="n">
+      <c r="G6" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="62">
+      <c r="H6" s="60">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="62">
         <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr"/>
-      <c r="B7" s="65" t="inlineStr"/>
-      <c r="C7" s="65" t="inlineStr"/>
-      <c r="D7" s="65" t="inlineStr"/>
-      <c r="E7" s="65" t="inlineStr"/>
-      <c r="F7" s="63" t="n">
+      <c r="A7" s="63" t="inlineStr"/>
+      <c r="B7" s="63" t="inlineStr"/>
+      <c r="C7" s="63" t="inlineStr"/>
+      <c r="D7" s="63" t="inlineStr"/>
+      <c r="E7" s="63" t="inlineStr"/>
+      <c r="F7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="63" t="n">
+      <c r="G7" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="66">
+      <c r="H7" s="64">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="65">
         <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr"/>
-      <c r="B8" s="61" t="inlineStr"/>
-      <c r="C8" s="61" t="inlineStr"/>
-      <c r="D8" s="61" t="inlineStr"/>
-      <c r="E8" s="61" t="inlineStr"/>
-      <c r="F8" s="63" t="n">
+      <c r="A8" s="59" t="inlineStr"/>
+      <c r="B8" s="59" t="inlineStr"/>
+      <c r="C8" s="59" t="inlineStr"/>
+      <c r="D8" s="59" t="inlineStr"/>
+      <c r="E8" s="59" t="inlineStr"/>
+      <c r="F8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="63" t="n">
+      <c r="G8" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="62">
+      <c r="H8" s="60">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="64">
+      <c r="I8" s="62">
         <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr"/>
-      <c r="B9" s="65" t="inlineStr"/>
-      <c r="C9" s="65" t="inlineStr"/>
-      <c r="D9" s="65" t="inlineStr"/>
-      <c r="E9" s="65" t="inlineStr"/>
-      <c r="F9" s="63" t="n">
+      <c r="A9" s="63" t="inlineStr"/>
+      <c r="B9" s="63" t="inlineStr"/>
+      <c r="C9" s="63" t="inlineStr"/>
+      <c r="D9" s="63" t="inlineStr"/>
+      <c r="E9" s="63" t="inlineStr"/>
+      <c r="F9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="63" t="n">
+      <c r="G9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="66">
+      <c r="H9" s="64">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="67">
+      <c r="I9" s="65">
         <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="inlineStr"/>
-      <c r="B10" s="61" t="inlineStr"/>
-      <c r="C10" s="61" t="inlineStr"/>
-      <c r="D10" s="61" t="inlineStr"/>
-      <c r="E10" s="61" t="inlineStr"/>
-      <c r="F10" s="63" t="n">
+      <c r="A10" s="59" t="inlineStr"/>
+      <c r="B10" s="59" t="inlineStr"/>
+      <c r="C10" s="59" t="inlineStr"/>
+      <c r="D10" s="59" t="inlineStr"/>
+      <c r="E10" s="59" t="inlineStr"/>
+      <c r="F10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="63" t="n">
+      <c r="G10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="62">
+      <c r="H10" s="60">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="64">
+      <c r="I10" s="62">
         <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="inlineStr"/>
-      <c r="B11" s="65" t="inlineStr"/>
-      <c r="C11" s="65" t="inlineStr"/>
-      <c r="D11" s="65" t="inlineStr"/>
-      <c r="E11" s="65" t="inlineStr"/>
-      <c r="F11" s="63" t="n">
+      <c r="A11" s="63" t="inlineStr"/>
+      <c r="B11" s="63" t="inlineStr"/>
+      <c r="C11" s="63" t="inlineStr"/>
+      <c r="D11" s="63" t="inlineStr"/>
+      <c r="E11" s="63" t="inlineStr"/>
+      <c r="F11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="63" t="n">
+      <c r="G11" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="66">
+      <c r="H11" s="64">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="67">
+      <c r="I11" s="65">
         <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="inlineStr"/>
-      <c r="B12" s="61" t="inlineStr"/>
-      <c r="C12" s="61" t="inlineStr"/>
-      <c r="D12" s="61" t="inlineStr"/>
-      <c r="E12" s="61" t="inlineStr"/>
-      <c r="F12" s="63" t="n">
+      <c r="A12" s="59" t="inlineStr"/>
+      <c r="B12" s="59" t="inlineStr"/>
+      <c r="C12" s="59" t="inlineStr"/>
+      <c r="D12" s="59" t="inlineStr"/>
+      <c r="E12" s="59" t="inlineStr"/>
+      <c r="F12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="63" t="n">
+      <c r="G12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="62">
+      <c r="H12" s="60">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="64">
+      <c r="I12" s="62">
         <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="65" t="inlineStr"/>
-      <c r="B13" s="65" t="inlineStr"/>
-      <c r="C13" s="65" t="inlineStr"/>
-      <c r="D13" s="65" t="inlineStr"/>
-      <c r="E13" s="65" t="inlineStr"/>
-      <c r="F13" s="63" t="n">
+      <c r="A13" s="63" t="inlineStr"/>
+      <c r="B13" s="63" t="inlineStr"/>
+      <c r="C13" s="63" t="inlineStr"/>
+      <c r="D13" s="63" t="inlineStr"/>
+      <c r="E13" s="63" t="inlineStr"/>
+      <c r="F13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="63" t="n">
+      <c r="G13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="66">
+      <c r="H13" s="64">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="67">
+      <c r="I13" s="65">
         <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="68" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="68" t="n"/>
-      <c r="E14" s="68" t="n"/>
-      <c r="F14" s="32">
+      <c r="B14" s="66" t="n"/>
+      <c r="C14" s="66" t="n"/>
+      <c r="D14" s="66" t="n"/>
+      <c r="E14" s="66" t="n"/>
+      <c r="F14" s="30">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="30">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="30">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="33">
+      <c r="I14" s="31">
         <f>IF(F14=0,"",(G14-F14)/F14)</f>
         <v/>
       </c>

--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -526,7 +526,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Concentracion de activos: 2025 vs 2026</a:t>
+              <a:t>Concentracion de activos 2025 (por tipo)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -550,9 +550,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Dashboard'!$B$12:$B$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -560,30 +560,9 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Dashboard'!E11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Dashboard'!$B$12:$B$19</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dashboard'!$E$12:$E$19</f>
-            </numRef>
-          </val>
-        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -611,9 +590,6 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -650,9 +626,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Dashboard'!$B$38:$B$40</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -661,6 +637,10 @@
           </val>
         </ser>
         <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
           <showPercent val="1"/>
         </dLbls>
         <firstSliceAng val="0"/>
@@ -684,7 +664,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3420000"/>
+    <ext cx="7560000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -703,10 +683,10 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3420000"/>
+    <ext cx="5400000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>

--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -223,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -232,6 +232,7 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -526,7 +527,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Concentracion de activos 2025 (por tipo)</a:t>
+              <a:t>Concentracion de activos 2025</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -539,11 +540,6 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Dashboard'!D11</f>
-            </strRef>
-          </tx>
           <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
@@ -551,17 +547,21 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Dashboard'!$B$12:$B$19</f>
+              <f>'Dashboard'!$AA$3:$AA$5</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$12:$D$19</f>
+              <f>'Dashboard'!$AB$3:$AB$5</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
+          <numFmt formatCode="&quot;$&quot;#,##0"/>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
         </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
@@ -664,7 +664,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3600000"/>
+    <ext cx="7560000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -683,10 +683,10 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3600000"/>
+    <ext cx="5760000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -993,7 +993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:AB42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1004,6 +1004,8 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1022,656 +1024,685 @@
     </row>
     <row r="3" ht="5" customHeight="1">
       <c r="A3" s="3" t="n"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Dinero e inversiones</t>
+        </is>
+      </c>
+      <c r="AB3" s="4">
+        <f>D12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Vehiculos, naves y aeronaves</t>
+        </is>
+      </c>
+      <c r="AB4" s="4">
+        <f>D16</f>
+        <v/>
+      </c>
     </row>
     <row r="5" ht="6" customHeight="1">
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Bienes inmuebles</t>
+        </is>
+      </c>
+      <c r="AB5" s="4">
+        <f>D18</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>TOTAL ACTIVOS</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>TOTAL PASIVOS</t>
         </is>
       </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>PATRIMONIO NETO</t>
         </is>
       </c>
-      <c r="G6" s="13" t="n"/>
+      <c r="G6" s="14" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="14">
+      <c r="B7" s="15">
         <f>D20</f>
         <v/>
       </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="15">
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="16">
         <f>D25</f>
         <v/>
       </c>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="16">
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="17">
         <f>D31</f>
         <v/>
       </c>
-      <c r="G7" s="13" t="n"/>
+      <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Var. proyectada</t>
         </is>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>G20</f>
         <v/>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Var. proyectada</t>
         </is>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <f>G25</f>
         <v/>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>Var. proyectada</t>
         </is>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="23">
         <f>G31</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>ACTIVOS</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="C11" s="25" t="n"/>
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Dinero e inversiones</t>
         </is>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="28">
         <f>'Dinero'!J10</f>
         <v/>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="28">
         <f>'Dinero'!K10</f>
         <v/>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="28">
         <f>E12-D12</f>
         <v/>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="29">
         <f>IF(D12=0,"",(E12-D12)/D12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Derechos representativos de capital</t>
         </is>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="28">
         <f>'Derechos de Capital'!J14</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="28">
         <f>'Derechos de Capital'!K14</f>
         <v/>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="28">
         <f>E13-D13</f>
         <v/>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="29">
         <f>IF(D13=0,"",(E13-D13)/D13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>Cuentas por cobrar</t>
         </is>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>'Cuentas por Cobrar'!J14</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>'Cuentas por Cobrar'!K14</f>
         <v/>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="28">
         <f>E14-D14</f>
         <v/>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="29">
         <f>IF(D14=0,"",(E14-D14)/D14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>Bienes muebles</t>
         </is>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="28">
         <f>'Bienes Muebles'!F14</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="28">
         <f>'Bienes Muebles'!G14</f>
         <v/>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="28">
         <f>E15-D15</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="29">
         <f>IF(D15=0,"",(E15-D15)/D15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>Vehiculos, naves y aeronaves</t>
         </is>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>'Vehiculos'!G9</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>'Vehiculos'!H9</f>
         <v/>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="28">
         <f>E16-D16</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>IF(D16=0,"",(E16-D16)/D16)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Derechos (usufructo, uso, etc.)</t>
         </is>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>'Derechos'!F14</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>'Derechos'!G14</f>
         <v/>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="28">
         <f>E17-D17</f>
         <v/>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="29">
         <f>IF(D17=0,"",(E17-D17)/D17)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>Bienes inmuebles</t>
         </is>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>'Bienes Inmuebles'!J10</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>'Bienes Inmuebles'!K10</f>
         <v/>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="28">
         <f>E18-D18</f>
         <v/>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="29">
         <f>IF(D18=0,"",(E18-D18)/D18)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>Otros activos</t>
         </is>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>'Otros Activos'!F14</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>'Otros Activos'!G14</f>
         <v/>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="28">
         <f>E19-D19</f>
         <v/>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="29">
         <f>IF(D19=0,"",(E19-D19)/D19)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>TOTAL ACTIVOS</t>
         </is>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <f>SUM(D12:D19)</f>
         <v/>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <f>SUM(E12:E19)</f>
         <v/>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <f>E20-D20</f>
         <v/>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="32">
         <f>IF(D20=0,"",(E20-D20)/D20)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>PASIVOS</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="F23" s="25" t="inlineStr">
+      <c r="F23" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G23" s="25" t="inlineStr">
+      <c r="G23" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="33" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>Deudas y obligaciones</t>
         </is>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="35">
         <f>'Pasivos'!I8</f>
         <v/>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="35">
         <f>'Pasivos'!J8</f>
         <v/>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="35">
         <f>E24-D24</f>
         <v/>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="36">
         <f>IF(D24=0,"",(E24-D24)/D24)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="36" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>TOTAL PASIVOS</t>
         </is>
       </c>
-      <c r="D25" s="37">
+      <c r="D25" s="38">
         <f>SUM(D24:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="37">
+      <c r="E25" s="38">
         <f>SUM(E24:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="37">
+      <c r="F25" s="38">
         <f>E25-D25</f>
         <v/>
       </c>
-      <c r="G25" s="38">
+      <c r="G25" s="39">
         <f>IF(D25=0,"",(E25-D25)/D25)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="39" t="inlineStr">
+      <c r="B27" s="40" t="inlineStr">
         <is>
           <t>PATRIMONIO NETO</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="F28" s="25" t="inlineStr">
+      <c r="F28" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G28" s="25" t="inlineStr">
+      <c r="G28" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="B29" s="40" t="inlineStr">
+      <c r="B29" s="41" t="inlineStr">
         <is>
           <t>(+) Total activos</t>
         </is>
       </c>
-      <c r="D29" s="41">
+      <c r="D29" s="42">
         <f>D20</f>
         <v/>
       </c>
-      <c r="E29" s="41">
+      <c r="E29" s="42">
         <f>E20</f>
         <v/>
       </c>
-      <c r="F29" s="41">
+      <c r="F29" s="42">
         <f>E29-D29</f>
         <v/>
       </c>
-      <c r="G29" s="42">
+      <c r="G29" s="43">
         <f>IF(D29=0,"",(E29-D29)/D29)</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="40" t="inlineStr">
+      <c r="B30" s="41" t="inlineStr">
         <is>
           <t>(-) Total pasivos</t>
         </is>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="42">
         <f>D25</f>
         <v/>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="42">
         <f>E25</f>
         <v/>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="42">
         <f>E30-D30</f>
         <v/>
       </c>
-      <c r="G30" s="42">
+      <c r="G30" s="43">
         <f>IF(D30=0,"",(E30-D30)/D30)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="43" t="inlineStr">
+      <c r="B31" s="44" t="inlineStr">
         <is>
           <t>(=) PATRIMONIO NETO</t>
         </is>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="45">
         <f>D29-D30</f>
         <v/>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="45">
         <f>E29-E30</f>
         <v/>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="45">
         <f>E31-D31</f>
         <v/>
       </c>
-      <c r="G31" s="45">
+      <c r="G31" s="46">
         <f>IF(D31=0,"",(E31-D31)/D31)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="46" t="inlineStr">
+      <c r="B32" s="47" t="inlineStr">
         <is>
           <t>Patrimonio declarado en el XML (2025)</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="47" t="n">
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="48" t="n">
         <v>883285.5600000001</v>
       </c>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="46" t="inlineStr">
+      <c r="B33" s="47" t="inlineStr">
         <is>
           <t>Patrimonio neto del anio anterior</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="47" t="n">
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="48" t="n">
         <v>801569.97</v>
       </c>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="46" t="inlineStr">
+      <c r="B34" s="47" t="inlineStr">
         <is>
           <t>Crecimiento / decremento patrimonial (XML)</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="47" t="n">
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="48" t="n">
         <v>81715.59</v>
       </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="48" t="inlineStr">
+      <c r="B36" s="49" t="inlineStr">
         <is>
           <t>CONSOLIDADO</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C37" s="24" t="n"/>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="C37" s="25" t="n"/>
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E37" s="26" t="inlineStr">
         <is>
           <t>Total 2026</t>
         </is>
       </c>
-      <c r="F37" s="25" t="inlineStr">
+      <c r="F37" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="G37" s="25" t="inlineStr">
+      <c r="G37" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="B38" s="49" t="inlineStr">
+      <c r="B38" s="50" t="inlineStr">
         <is>
           <t>Activos</t>
         </is>
       </c>
-      <c r="D38" s="50">
+      <c r="D38" s="51">
         <f>D20</f>
         <v/>
       </c>
-      <c r="E38" s="50">
+      <c r="E38" s="51">
         <f>E20</f>
         <v/>
       </c>
-      <c r="F38" s="50">
+      <c r="F38" s="51">
         <f>E38-D38</f>
         <v/>
       </c>
-      <c r="G38" s="51">
+      <c r="G38" s="52">
         <f>IF(D38=0,"",(E38-D38)/D38)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="B39" s="52" t="inlineStr">
+      <c r="B39" s="53" t="inlineStr">
         <is>
           <t>Pasivos</t>
         </is>
       </c>
-      <c r="D39" s="53">
+      <c r="D39" s="54">
         <f>D25</f>
         <v/>
       </c>
-      <c r="E39" s="53">
+      <c r="E39" s="54">
         <f>E25</f>
         <v/>
       </c>
-      <c r="F39" s="53">
+      <c r="F39" s="54">
         <f>E39-D39</f>
         <v/>
       </c>
-      <c r="G39" s="54">
+      <c r="G39" s="55">
         <f>IF(D39=0,"",(E39-D39)/D39)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="B40" s="55" t="inlineStr">
+      <c r="B40" s="56" t="inlineStr">
         <is>
           <t>Patrimonio neto</t>
         </is>
       </c>
-      <c r="D40" s="56">
+      <c r="D40" s="57">
         <f>D31</f>
         <v/>
       </c>
-      <c r="E40" s="56">
+      <c r="E40" s="57">
         <f>E31</f>
         <v/>
       </c>
-      <c r="F40" s="56">
+      <c r="F40" s="57">
         <f>E40-D40</f>
         <v/>
       </c>
-      <c r="G40" s="57">
+      <c r="G40" s="58">
         <f>IF(D40=0,"",(E40-D40)/D40)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="58" t="inlineStr">
+      <c r="B42" s="59" t="inlineStr">
         <is>
           <t>Edite las columnas amarillas en las hojas de cada modulo; las tarjetas, secciones y graficos se recalculan solos.</t>
         </is>
@@ -1766,197 +1797,197 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Tipo de acreedor</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Domicilio del acreedor</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Nombre del acreedor</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>N. de identificacion</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>N. registro Banco Central</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="26" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>DINERS CLUB DEL ECUADOR</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="60" t="inlineStr">
         <is>
           <t>1792260957001</t>
         </is>
       </c>
-      <c r="G6" s="59" t="inlineStr"/>
-      <c r="H6" s="59" t="inlineStr">
+      <c r="G6" s="60" t="inlineStr"/>
+      <c r="H6" s="60" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="I6" s="60" t="n">
+      <c r="I6" s="61" t="n">
         <v>4891.88</v>
       </c>
-      <c r="J6" s="61" t="n">
+      <c r="J6" s="62" t="n">
         <v>4891.88</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="61">
         <f>J6-I6</f>
         <v/>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="63">
         <f>IF(I6=0,"",(J6-I6)/I6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C7" s="63" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D7" s="63" t="inlineStr">
+      <c r="D7" s="64" t="inlineStr">
         <is>
           <t>BANCO DEL PICHINCHA</t>
         </is>
       </c>
-      <c r="E7" s="63" t="inlineStr">
+      <c r="E7" s="64" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
-      <c r="F7" s="63" t="inlineStr">
+      <c r="F7" s="64" t="inlineStr">
         <is>
           <t>1790010937001</t>
         </is>
       </c>
-      <c r="G7" s="63" t="inlineStr"/>
-      <c r="H7" s="63" t="inlineStr">
+      <c r="G7" s="64" t="inlineStr"/>
+      <c r="H7" s="64" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="I7" s="64" t="n">
+      <c r="I7" s="65" t="n">
         <v>5547.31</v>
       </c>
-      <c r="J7" s="61" t="n">
+      <c r="J7" s="62" t="n">
         <v>5547.31</v>
       </c>
-      <c r="K7" s="64">
+      <c r="K7" s="65">
         <f>J7-I7</f>
         <v/>
       </c>
-      <c r="L7" s="65">
+      <c r="L7" s="66">
         <f>IF(I7=0,"",(J7-I7)/I7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="67" t="n"/>
-      <c r="C8" s="67" t="n"/>
-      <c r="D8" s="67" t="n"/>
-      <c r="E8" s="67" t="n"/>
-      <c r="F8" s="67" t="n"/>
-      <c r="G8" s="67" t="n"/>
-      <c r="H8" s="67" t="n"/>
-      <c r="I8" s="37">
+      <c r="B8" s="68" t="n"/>
+      <c r="C8" s="68" t="n"/>
+      <c r="D8" s="68" t="n"/>
+      <c r="E8" s="68" t="n"/>
+      <c r="F8" s="68" t="n"/>
+      <c r="G8" s="68" t="n"/>
+      <c r="H8" s="68" t="n"/>
+      <c r="I8" s="38">
         <f>SUM(I6:I7)</f>
         <v/>
       </c>
-      <c r="J8" s="37">
+      <c r="J8" s="38">
         <f>SUM(J6:J7)</f>
         <v/>
       </c>
-      <c r="K8" s="37">
+      <c r="K8" s="38">
         <f>J8-I8</f>
         <v/>
       </c>
-      <c r="L8" s="38">
+      <c r="L8" s="39">
         <f>IF(I8=0,"",(J8-I8)/I8)</f>
         <v/>
       </c>
@@ -2022,115 +2053,115 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="B5" s="68" t="inlineStr">
+      <c r="B5" s="69" t="inlineStr">
         <is>
           <t>Incremento patrimonial declarado en el XML</t>
         </is>
       </c>
-      <c r="C5" s="69" t="n"/>
-      <c r="D5" s="69" t="n"/>
-      <c r="E5" s="70" t="n">
+      <c r="C5" s="70" t="n"/>
+      <c r="D5" s="70" t="n"/>
+      <c r="E5" s="71" t="n">
         <v>81715.59</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Concepto (Tabla 14 del SRI)</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>Justifica la variacion</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="71" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>1 - Ingresos locales</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="72" t="inlineStr">
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="73" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="71" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>2 - Ingresos exterior</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="72" t="inlineStr">
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="73" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="71" t="inlineStr">
+      <c r="B10" s="72" t="inlineStr">
         <is>
           <t>3 - Herencias, legados o donaciones</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="72" t="inlineStr">
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="73" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="71" t="inlineStr">
+      <c r="B11" s="72" t="inlineStr">
         <is>
           <t>4 - Loterias o rifas</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="72" t="inlineStr">
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="73" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="71" t="inlineStr">
+      <c r="B12" s="72" t="inlineStr">
         <is>
           <t>5 - Ganancias de capital</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="72" t="inlineStr">
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="73" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="71" t="inlineStr">
+      <c r="B13" s="72" t="inlineStr">
         <is>
           <t>6 - Otros</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="72" t="inlineStr">
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="73" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>Esta hoja reproduce la seccion Justificacion del formulario del SRI. Marque 'Si' en los conceptos que apliquen; el generador de XML los toma de aqui.</t>
         </is>
@@ -2193,97 +2224,97 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="73" t="inlineStr">
+      <c r="B5" s="74" t="inlineStr">
         <is>
           <t>►   GENERAR XML</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="75" t="inlineStr">
         <is>
           <t>En el archivo .xlsm el boton verde ya esta vinculado a la macro GenerarXmlSRI.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="75" t="inlineStr">
+      <c r="B9" s="76" t="inlineStr">
         <is>
           <t>COMO USAR ESTE ARCHIVO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="76" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>1. Al abrir el archivo .xlsm, pulse 'Habilitar contenido' en la barra de seguridad de Excel.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="76" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>2. Llene las columnas amarillas de cada modulo (Dinero, Vehiculos, etc.) y la hoja Justificacion.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="76" t="inlineStr">
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>3. Pulse el boton verde GENERAR XML, indique el anio y elija donde guardar el archivo.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="76" t="inlineStr">
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>4. El archivo .xml queda listo para subir al portal del SRI.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="76" t="inlineStr"/>
+      <c r="B14" s="77" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="75" t="inlineStr">
+      <c r="B15" s="76" t="inlineStr">
         <is>
           <t>SI EXCEL BLOQUEA LAS MACROS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="76" t="inlineStr">
+      <c r="B16" s="77" t="inlineStr">
         <is>
           <t>- Cierre Excel. En el Explorador, clic derecho sobre el archivo &gt; Propiedades.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="76" t="inlineStr">
+      <c r="B17" s="77" t="inlineStr">
         <is>
           <t>- Al final de la pestana General marque 'Desbloquear' y pulse Aceptar.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="76" t="inlineStr">
+      <c r="B18" s="77" t="inlineStr">
         <is>
           <t>- Vuelva a abrirlo y pulse 'Habilitar contenido'. Conserve siempre la extension .xlsm.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="76" t="inlineStr"/>
+      <c r="B19" s="77" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="B20" s="76" t="inlineStr">
+      <c r="B20" s="77" t="inlineStr">
         <is>
           <t>Alternativa sin macros:  ejecutar  python tools/generar_xml_sri.py  desde la terminal.</t>
         </is>
@@ -2324,257 +2355,257 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="78" t="inlineStr">
         <is>
           <t>IDENTIFICACION</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="78" t="inlineStr">
+      <c r="A6" s="79" t="inlineStr">
         <is>
           <t>Anio de la declaracion</t>
         </is>
       </c>
-      <c r="B6" s="79" t="n">
+      <c r="B6" s="80" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="78" t="inlineStr">
+      <c r="A7" s="79" t="inlineStr">
         <is>
           <t>Tipo de declaracion</t>
         </is>
       </c>
-      <c r="B7" s="79" t="inlineStr">
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>SOC - Sociedad conyugal o union de hecho</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="78" t="inlineStr">
+      <c r="A8" s="79" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="B8" s="79" t="inlineStr">
+      <c r="B8" s="80" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="78" t="inlineStr">
+      <c r="A9" s="79" t="inlineStr">
         <is>
           <t>Numero de identificacion</t>
         </is>
       </c>
-      <c r="B9" s="79" t="inlineStr">
+      <c r="B9" s="80" t="inlineStr">
         <is>
           <t>1709164899001</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="78" t="inlineStr">
+      <c r="A10" s="79" t="inlineStr">
         <is>
           <t>Nombre del declarante</t>
         </is>
       </c>
-      <c r="B10" s="79" t="inlineStr">
+      <c r="B10" s="80" t="inlineStr">
         <is>
           <t>GONZALEZ NAVAS MARCO VINICIO</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="78" t="inlineStr">
+      <c r="A11" s="79" t="inlineStr">
         <is>
           <t>Identificacion del conyuge</t>
         </is>
       </c>
-      <c r="B11" s="79" t="inlineStr">
+      <c r="B11" s="80" t="inlineStr">
         <is>
           <t>C - Cedula</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="78" t="inlineStr">
+      <c r="A12" s="79" t="inlineStr">
         <is>
           <t>Numero ident. conyuge</t>
         </is>
       </c>
-      <c r="B12" s="79" t="inlineStr">
+      <c r="B12" s="80" t="inlineStr">
         <is>
           <t>1709784225</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="78" t="inlineStr">
+      <c r="A13" s="79" t="inlineStr">
         <is>
           <t>Nombre del conyuge</t>
         </is>
       </c>
-      <c r="B13" s="79" t="inlineStr">
+      <c r="B13" s="80" t="inlineStr">
         <is>
           <t>HIDALGO LOZA ROSA CONSUELO</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="78" t="inlineStr">
+      <c r="A14" s="79" t="inlineStr">
         <is>
           <t>Total creditos / cuentas por cobrar</t>
         </is>
       </c>
-      <c r="B14" s="60" t="n">
+      <c r="B14" s="61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="77" t="inlineStr">
+      <c r="A16" s="78" t="inlineStr">
         <is>
           <t>PATRIMONIO NETO (enlazado a la hoja Dashboard)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="78" t="inlineStr">
+      <c r="A17" s="79" t="inlineStr">
         <is>
           <t>Patrimonio neto 2025</t>
         </is>
       </c>
-      <c r="B17" s="60">
+      <c r="B17" s="61">
         <f>Dashboard!D31</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="78" t="inlineStr">
+      <c r="A18" s="79" t="inlineStr">
         <is>
           <t>Patrimonio neto 2026 (proyectado)</t>
         </is>
       </c>
-      <c r="B18" s="60">
+      <c r="B18" s="61">
         <f>Dashboard!E31</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="78" t="inlineStr">
+      <c r="A19" s="79" t="inlineStr">
         <is>
           <t>Variacion proyectada</t>
         </is>
       </c>
-      <c r="B19" s="60">
+      <c r="B19" s="61">
         <f>Dashboard!F31</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="78" t="inlineStr">
+      <c r="A20" s="79" t="inlineStr">
         <is>
           <t>Variacion % proyectada</t>
         </is>
       </c>
-      <c r="B20" s="62">
+      <c r="B20" s="63">
         <f>Dashboard!G31</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="77" t="inlineStr">
+      <c r="A22" s="78" t="inlineStr">
         <is>
           <t>PATRIMONIO DECLARADO EN EL XML</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="78" t="inlineStr">
+      <c r="A23" s="79" t="inlineStr">
         <is>
           <t>Patrimonio total declarado</t>
         </is>
       </c>
-      <c r="B23" s="60" t="n">
+      <c r="B23" s="61" t="n">
         <v>883285.5600000001</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="78" t="inlineStr">
+      <c r="A24" s="79" t="inlineStr">
         <is>
           <t>Atribuible a hijos no emancipados</t>
         </is>
       </c>
-      <c r="B24" s="60" t="n">
+      <c r="B24" s="61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="78" t="inlineStr">
+      <c r="A25" s="79" t="inlineStr">
         <is>
           <t>Patrimonio en la sociedad conyugal</t>
         </is>
       </c>
-      <c r="B25" s="60" t="n">
+      <c r="B25" s="61" t="n">
         <v>883285.5600000001</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="78" t="inlineStr">
+      <c r="A26" s="79" t="inlineStr">
         <is>
           <t>Patrimonio individual del declarante</t>
         </is>
       </c>
-      <c r="B26" s="60" t="n">
+      <c r="B26" s="61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="78" t="inlineStr">
+      <c r="A27" s="79" t="inlineStr">
         <is>
           <t>Patrimonio del anio anterior</t>
         </is>
       </c>
-      <c r="B27" s="60" t="n">
+      <c r="B27" s="61" t="n">
         <v>801569.97</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="78" t="inlineStr">
+      <c r="A28" s="79" t="inlineStr">
         <is>
           <t>Crecimiento / decremento patrimonial</t>
         </is>
       </c>
-      <c r="B28" s="60" t="n">
+      <c r="B28" s="61" t="n">
         <v>81715.59</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="75" t="inlineStr">
+      <c r="A30" s="76" t="inlineStr">
         <is>
           <t>Justificacion de la variacion (ver hoja Justificacion)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="76" t="inlineStr">
+      <c r="A31" s="77" t="inlineStr">
         <is>
           <t>- 1 - Ingresos locales</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="76" t="inlineStr">
+      <c r="A32" s="77" t="inlineStr">
         <is>
           <t>- 6 - Otros</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="58" t="inlineStr">
+      <c r="A34" s="59" t="inlineStr">
         <is>
           <t>Catalogos del SRI integrados (Tablas 1-19 del archivo CATALOGO.xls). El XML se genera con generar_xml_sri.py.</t>
         </is>
@@ -5845,97 +5876,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="80" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>DINERO_EN</t>
         </is>
       </c>
-      <c r="B1" s="80" t="inlineStr">
+      <c r="B1" s="81" t="inlineStr">
         <is>
           <t>TIPO_INVERSION</t>
         </is>
       </c>
-      <c r="C1" s="80" t="inlineStr">
+      <c r="C1" s="81" t="inlineStr">
         <is>
           <t>UBICACION</t>
         </is>
       </c>
-      <c r="D1" s="80" t="inlineStr">
+      <c r="D1" s="81" t="inlineStr">
         <is>
           <t>PAIS</t>
         </is>
       </c>
-      <c r="E1" s="80" t="inlineStr">
+      <c r="E1" s="81" t="inlineStr">
         <is>
           <t>INSTITUCION_FINANCIERA</t>
         </is>
       </c>
-      <c r="F1" s="80" t="inlineStr">
+      <c r="F1" s="81" t="inlineStr">
         <is>
           <t>PARTES_RELACIONADAS</t>
         </is>
       </c>
-      <c r="G1" s="80" t="inlineStr">
+      <c r="G1" s="81" t="inlineStr">
         <is>
           <t>TIPO_DRC</t>
         </is>
       </c>
-      <c r="H1" s="80" t="inlineStr">
+      <c r="H1" s="81" t="inlineStr">
         <is>
           <t>TIPO_PERSONA</t>
         </is>
       </c>
-      <c r="I1" s="80" t="inlineStr">
+      <c r="I1" s="81" t="inlineStr">
         <is>
           <t>TIPO_BIEN_MUEBLE</t>
         </is>
       </c>
-      <c r="J1" s="80" t="inlineStr">
+      <c r="J1" s="81" t="inlineStr">
         <is>
           <t>TIPO_VEHICULO</t>
         </is>
       </c>
-      <c r="K1" s="80" t="inlineStr">
+      <c r="K1" s="81" t="inlineStr">
         <is>
           <t>TIPO_DERECHO</t>
         </is>
       </c>
-      <c r="L1" s="80" t="inlineStr">
+      <c r="L1" s="81" t="inlineStr">
         <is>
           <t>TIPO_INMUEBLE</t>
         </is>
       </c>
-      <c r="M1" s="80" t="inlineStr">
+      <c r="M1" s="81" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="N1" s="80" t="inlineStr">
+      <c r="N1" s="81" t="inlineStr">
         <is>
           <t>CANTON</t>
         </is>
       </c>
-      <c r="O1" s="80" t="inlineStr">
+      <c r="O1" s="81" t="inlineStr">
         <is>
           <t>TIPO_ACREEDOR</t>
         </is>
       </c>
-      <c r="P1" s="80" t="inlineStr">
+      <c r="P1" s="81" t="inlineStr">
         <is>
           <t>TIPO_IDENTIFICACION</t>
         </is>
       </c>
-      <c r="Q1" s="80" t="inlineStr">
+      <c r="Q1" s="81" t="inlineStr">
         <is>
           <t>REGULARIZACION</t>
         </is>
       </c>
-      <c r="R1" s="80" t="inlineStr">
+      <c r="R1" s="81" t="inlineStr">
         <is>
           <t>JUSTIF_INCREMENTO</t>
         </is>
       </c>
-      <c r="S1" s="80" t="inlineStr">
+      <c r="S1" s="81" t="inlineStr">
         <is>
           <t>JUSTIF_DECREMENTO</t>
         </is>
@@ -12469,311 +12500,311 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Dinero en</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Tipo de inversion</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Institucion financiera</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Tipo de moneda</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>3 - Cuenta de ahorros</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>1029 - BANCO PICHINCHA C.A.</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="60" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G6" s="59" t="inlineStr">
+      <c r="G6" s="60" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H6" s="59" t="inlineStr"/>
-      <c r="I6" s="59" t="inlineStr"/>
-      <c r="J6" s="60" t="n">
+      <c r="H6" s="60" t="inlineStr"/>
+      <c r="I6" s="60" t="inlineStr"/>
+      <c r="J6" s="61" t="n">
         <v>130.2</v>
       </c>
-      <c r="K6" s="61" t="n">
+      <c r="K6" s="62" t="n">
         <v>130.2</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="61">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="63">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>4 - Cuenta corriente</t>
         </is>
       </c>
-      <c r="C7" s="63" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D7" s="63" t="inlineStr">
+      <c r="D7" s="64" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E7" s="63" t="inlineStr">
+      <c r="E7" s="64" t="inlineStr">
         <is>
           <t>1029 - BANCO PICHINCHA C.A.</t>
         </is>
       </c>
-      <c r="F7" s="63" t="inlineStr">
+      <c r="F7" s="64" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G7" s="63" t="inlineStr">
+      <c r="G7" s="64" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H7" s="63" t="inlineStr"/>
-      <c r="I7" s="63" t="inlineStr"/>
-      <c r="J7" s="64" t="n">
+      <c r="H7" s="64" t="inlineStr"/>
+      <c r="I7" s="64" t="inlineStr"/>
+      <c r="J7" s="65" t="n">
         <v>5590.32</v>
       </c>
-      <c r="K7" s="61" t="n">
+      <c r="K7" s="62" t="n">
         <v>5590.32</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="65">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="65">
+      <c r="M7" s="66">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>3 - Cuenta de ahorros</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>1418 - BANCO PROMERICA S.A.</t>
         </is>
       </c>
-      <c r="F8" s="59" t="inlineStr">
+      <c r="F8" s="60" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G8" s="59" t="inlineStr">
+      <c r="G8" s="60" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H8" s="59" t="inlineStr"/>
-      <c r="I8" s="59" t="inlineStr"/>
-      <c r="J8" s="60" t="n">
+      <c r="H8" s="60" t="inlineStr"/>
+      <c r="I8" s="60" t="inlineStr"/>
+      <c r="J8" s="61" t="n">
         <v>53237.31</v>
       </c>
-      <c r="K8" s="61" t="n">
+      <c r="K8" s="62" t="n">
         <v>53237.31</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="61">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="62">
+      <c r="M8" s="63">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B9" s="63" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>2 - Inversiones financieras</t>
         </is>
       </c>
-      <c r="C9" s="63" t="inlineStr">
+      <c r="C9" s="64" t="inlineStr">
         <is>
           <t>EXT - En el exterior</t>
         </is>
       </c>
-      <c r="D9" s="63" t="inlineStr">
+      <c r="D9" s="64" t="inlineStr">
         <is>
           <t>118 - PANAMA</t>
         </is>
       </c>
-      <c r="E9" s="63" t="inlineStr">
+      <c r="E9" s="64" t="inlineStr">
         <is>
           <t>BANCO PICHINCHA CA</t>
         </is>
       </c>
-      <c r="F9" s="63" t="inlineStr">
+      <c r="F9" s="64" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G9" s="63" t="inlineStr">
+      <c r="G9" s="64" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H9" s="63" t="inlineStr"/>
-      <c r="I9" s="63" t="inlineStr"/>
-      <c r="J9" s="64" t="n">
+      <c r="H9" s="64" t="inlineStr"/>
+      <c r="I9" s="64" t="inlineStr"/>
+      <c r="J9" s="65" t="n">
         <v>189049.31</v>
       </c>
-      <c r="K9" s="61" t="n">
+      <c r="K9" s="62" t="n">
         <v>189049.31</v>
       </c>
-      <c r="L9" s="64">
+      <c r="L9" s="65">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="65">
+      <c r="M9" s="66">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="66" t="n"/>
-      <c r="C10" s="66" t="n"/>
-      <c r="D10" s="66" t="n"/>
-      <c r="E10" s="66" t="n"/>
-      <c r="F10" s="66" t="n"/>
-      <c r="G10" s="66" t="n"/>
-      <c r="H10" s="66" t="n"/>
-      <c r="I10" s="66" t="n"/>
-      <c r="J10" s="30">
+      <c r="B10" s="67" t="n"/>
+      <c r="C10" s="67" t="n"/>
+      <c r="D10" s="67" t="n"/>
+      <c r="E10" s="67" t="n"/>
+      <c r="F10" s="67" t="n"/>
+      <c r="G10" s="67" t="n"/>
+      <c r="H10" s="67" t="n"/>
+      <c r="I10" s="67" t="n"/>
+      <c r="J10" s="31">
         <f>SUM(J6:J9)</f>
         <v/>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="31">
         <f>SUM(K6:K9)</f>
         <v/>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="31">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="31">
+      <c r="M10" s="32">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
@@ -12853,299 +12884,299 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Tipo de inversion</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Empresa / Administradora / Fideicomiso</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>% de participacion</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>N. de acciones / participaciones</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr"/>
-      <c r="C6" s="59" t="inlineStr"/>
-      <c r="D6" s="59" t="inlineStr"/>
-      <c r="E6" s="59" t="inlineStr"/>
-      <c r="F6" s="59" t="inlineStr"/>
-      <c r="G6" s="59" t="inlineStr"/>
-      <c r="H6" s="59" t="inlineStr"/>
-      <c r="I6" s="59" t="inlineStr"/>
-      <c r="J6" s="61" t="n">
+      <c r="A6" s="60" t="inlineStr"/>
+      <c r="B6" s="60" t="inlineStr"/>
+      <c r="C6" s="60" t="inlineStr"/>
+      <c r="D6" s="60" t="inlineStr"/>
+      <c r="E6" s="60" t="inlineStr"/>
+      <c r="F6" s="60" t="inlineStr"/>
+      <c r="G6" s="60" t="inlineStr"/>
+      <c r="H6" s="60" t="inlineStr"/>
+      <c r="I6" s="60" t="inlineStr"/>
+      <c r="J6" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="61" t="n">
+      <c r="K6" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="61">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="63">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr"/>
-      <c r="C7" s="63" t="inlineStr"/>
-      <c r="D7" s="63" t="inlineStr"/>
-      <c r="E7" s="63" t="inlineStr"/>
-      <c r="F7" s="63" t="inlineStr"/>
-      <c r="G7" s="63" t="inlineStr"/>
-      <c r="H7" s="63" t="inlineStr"/>
-      <c r="I7" s="63" t="inlineStr"/>
-      <c r="J7" s="61" t="n">
+      <c r="A7" s="64" t="inlineStr"/>
+      <c r="B7" s="64" t="inlineStr"/>
+      <c r="C7" s="64" t="inlineStr"/>
+      <c r="D7" s="64" t="inlineStr"/>
+      <c r="E7" s="64" t="inlineStr"/>
+      <c r="F7" s="64" t="inlineStr"/>
+      <c r="G7" s="64" t="inlineStr"/>
+      <c r="H7" s="64" t="inlineStr"/>
+      <c r="I7" s="64" t="inlineStr"/>
+      <c r="J7" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="61" t="n">
+      <c r="K7" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="65">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="65">
+      <c r="M7" s="66">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr"/>
-      <c r="B8" s="59" t="inlineStr"/>
-      <c r="C8" s="59" t="inlineStr"/>
-      <c r="D8" s="59" t="inlineStr"/>
-      <c r="E8" s="59" t="inlineStr"/>
-      <c r="F8" s="59" t="inlineStr"/>
-      <c r="G8" s="59" t="inlineStr"/>
-      <c r="H8" s="59" t="inlineStr"/>
-      <c r="I8" s="59" t="inlineStr"/>
-      <c r="J8" s="61" t="n">
+      <c r="A8" s="60" t="inlineStr"/>
+      <c r="B8" s="60" t="inlineStr"/>
+      <c r="C8" s="60" t="inlineStr"/>
+      <c r="D8" s="60" t="inlineStr"/>
+      <c r="E8" s="60" t="inlineStr"/>
+      <c r="F8" s="60" t="inlineStr"/>
+      <c r="G8" s="60" t="inlineStr"/>
+      <c r="H8" s="60" t="inlineStr"/>
+      <c r="I8" s="60" t="inlineStr"/>
+      <c r="J8" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="61" t="n">
+      <c r="K8" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="61">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="62">
+      <c r="M8" s="63">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr"/>
-      <c r="C9" s="63" t="inlineStr"/>
-      <c r="D9" s="63" t="inlineStr"/>
-      <c r="E9" s="63" t="inlineStr"/>
-      <c r="F9" s="63" t="inlineStr"/>
-      <c r="G9" s="63" t="inlineStr"/>
-      <c r="H9" s="63" t="inlineStr"/>
-      <c r="I9" s="63" t="inlineStr"/>
-      <c r="J9" s="61" t="n">
+      <c r="A9" s="64" t="inlineStr"/>
+      <c r="B9" s="64" t="inlineStr"/>
+      <c r="C9" s="64" t="inlineStr"/>
+      <c r="D9" s="64" t="inlineStr"/>
+      <c r="E9" s="64" t="inlineStr"/>
+      <c r="F9" s="64" t="inlineStr"/>
+      <c r="G9" s="64" t="inlineStr"/>
+      <c r="H9" s="64" t="inlineStr"/>
+      <c r="I9" s="64" t="inlineStr"/>
+      <c r="J9" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="61" t="n">
+      <c r="K9" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="64">
+      <c r="L9" s="65">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="65">
+      <c r="M9" s="66">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr"/>
-      <c r="B10" s="59" t="inlineStr"/>
-      <c r="C10" s="59" t="inlineStr"/>
-      <c r="D10" s="59" t="inlineStr"/>
-      <c r="E10" s="59" t="inlineStr"/>
-      <c r="F10" s="59" t="inlineStr"/>
-      <c r="G10" s="59" t="inlineStr"/>
-      <c r="H10" s="59" t="inlineStr"/>
-      <c r="I10" s="59" t="inlineStr"/>
-      <c r="J10" s="61" t="n">
+      <c r="A10" s="60" t="inlineStr"/>
+      <c r="B10" s="60" t="inlineStr"/>
+      <c r="C10" s="60" t="inlineStr"/>
+      <c r="D10" s="60" t="inlineStr"/>
+      <c r="E10" s="60" t="inlineStr"/>
+      <c r="F10" s="60" t="inlineStr"/>
+      <c r="G10" s="60" t="inlineStr"/>
+      <c r="H10" s="60" t="inlineStr"/>
+      <c r="I10" s="60" t="inlineStr"/>
+      <c r="J10" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="61" t="n">
+      <c r="K10" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="60">
+      <c r="L10" s="61">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="62">
+      <c r="M10" s="63">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="63" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr"/>
-      <c r="C11" s="63" t="inlineStr"/>
-      <c r="D11" s="63" t="inlineStr"/>
-      <c r="E11" s="63" t="inlineStr"/>
-      <c r="F11" s="63" t="inlineStr"/>
-      <c r="G11" s="63" t="inlineStr"/>
-      <c r="H11" s="63" t="inlineStr"/>
-      <c r="I11" s="63" t="inlineStr"/>
-      <c r="J11" s="61" t="n">
+      <c r="A11" s="64" t="inlineStr"/>
+      <c r="B11" s="64" t="inlineStr"/>
+      <c r="C11" s="64" t="inlineStr"/>
+      <c r="D11" s="64" t="inlineStr"/>
+      <c r="E11" s="64" t="inlineStr"/>
+      <c r="F11" s="64" t="inlineStr"/>
+      <c r="G11" s="64" t="inlineStr"/>
+      <c r="H11" s="64" t="inlineStr"/>
+      <c r="I11" s="64" t="inlineStr"/>
+      <c r="J11" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="61" t="n">
+      <c r="K11" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="64">
+      <c r="L11" s="65">
         <f>K11-J11</f>
         <v/>
       </c>
-      <c r="M11" s="65">
+      <c r="M11" s="66">
         <f>IF(J11=0,"",(K11-J11)/J11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr"/>
-      <c r="B12" s="59" t="inlineStr"/>
-      <c r="C12" s="59" t="inlineStr"/>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr"/>
-      <c r="F12" s="59" t="inlineStr"/>
-      <c r="G12" s="59" t="inlineStr"/>
-      <c r="H12" s="59" t="inlineStr"/>
-      <c r="I12" s="59" t="inlineStr"/>
-      <c r="J12" s="61" t="n">
+      <c r="A12" s="60" t="inlineStr"/>
+      <c r="B12" s="60" t="inlineStr"/>
+      <c r="C12" s="60" t="inlineStr"/>
+      <c r="D12" s="60" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr"/>
+      <c r="F12" s="60" t="inlineStr"/>
+      <c r="G12" s="60" t="inlineStr"/>
+      <c r="H12" s="60" t="inlineStr"/>
+      <c r="I12" s="60" t="inlineStr"/>
+      <c r="J12" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="61" t="n">
+      <c r="K12" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="60">
+      <c r="L12" s="61">
         <f>K12-J12</f>
         <v/>
       </c>
-      <c r="M12" s="62">
+      <c r="M12" s="63">
         <f>IF(J12=0,"",(K12-J12)/J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr"/>
-      <c r="C13" s="63" t="inlineStr"/>
-      <c r="D13" s="63" t="inlineStr"/>
-      <c r="E13" s="63" t="inlineStr"/>
-      <c r="F13" s="63" t="inlineStr"/>
-      <c r="G13" s="63" t="inlineStr"/>
-      <c r="H13" s="63" t="inlineStr"/>
-      <c r="I13" s="63" t="inlineStr"/>
-      <c r="J13" s="61" t="n">
+      <c r="A13" s="64" t="inlineStr"/>
+      <c r="B13" s="64" t="inlineStr"/>
+      <c r="C13" s="64" t="inlineStr"/>
+      <c r="D13" s="64" t="inlineStr"/>
+      <c r="E13" s="64" t="inlineStr"/>
+      <c r="F13" s="64" t="inlineStr"/>
+      <c r="G13" s="64" t="inlineStr"/>
+      <c r="H13" s="64" t="inlineStr"/>
+      <c r="I13" s="64" t="inlineStr"/>
+      <c r="J13" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="61" t="n">
+      <c r="K13" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="64">
+      <c r="L13" s="65">
         <f>K13-J13</f>
         <v/>
       </c>
-      <c r="M13" s="65">
+      <c r="M13" s="66">
         <f>IF(J13=0,"",(K13-J13)/J13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="67" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="66" t="n"/>
-      <c r="G14" s="66" t="n"/>
-      <c r="H14" s="66" t="n"/>
-      <c r="I14" s="66" t="n"/>
-      <c r="J14" s="30">
+      <c r="B14" s="67" t="n"/>
+      <c r="C14" s="67" t="n"/>
+      <c r="D14" s="67" t="n"/>
+      <c r="E14" s="67" t="n"/>
+      <c r="F14" s="67" t="n"/>
+      <c r="G14" s="67" t="n"/>
+      <c r="H14" s="67" t="n"/>
+      <c r="I14" s="67" t="n"/>
+      <c r="J14" s="31">
         <f>SUM(J6:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="31">
         <f>SUM(K6:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="30">
+      <c r="L14" s="31">
         <f>K14-J14</f>
         <v/>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="32">
         <f>IF(J14=0,"",(K14-J14)/J14)</f>
         <v/>
       </c>
@@ -13219,299 +13250,299 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Nombre del deudor</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Tipo de deudor</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>N. de identificacion</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Partes relacionadas</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr"/>
-      <c r="C6" s="59" t="inlineStr"/>
-      <c r="D6" s="59" t="inlineStr"/>
-      <c r="E6" s="59" t="inlineStr"/>
-      <c r="F6" s="59" t="inlineStr"/>
-      <c r="G6" s="59" t="inlineStr"/>
-      <c r="H6" s="59" t="inlineStr"/>
-      <c r="I6" s="59" t="inlineStr"/>
-      <c r="J6" s="61" t="n">
+      <c r="A6" s="60" t="inlineStr"/>
+      <c r="B6" s="60" t="inlineStr"/>
+      <c r="C6" s="60" t="inlineStr"/>
+      <c r="D6" s="60" t="inlineStr"/>
+      <c r="E6" s="60" t="inlineStr"/>
+      <c r="F6" s="60" t="inlineStr"/>
+      <c r="G6" s="60" t="inlineStr"/>
+      <c r="H6" s="60" t="inlineStr"/>
+      <c r="I6" s="60" t="inlineStr"/>
+      <c r="J6" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="61" t="n">
+      <c r="K6" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="61">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="63">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr"/>
-      <c r="C7" s="63" t="inlineStr"/>
-      <c r="D7" s="63" t="inlineStr"/>
-      <c r="E7" s="63" t="inlineStr"/>
-      <c r="F7" s="63" t="inlineStr"/>
-      <c r="G7" s="63" t="inlineStr"/>
-      <c r="H7" s="63" t="inlineStr"/>
-      <c r="I7" s="63" t="inlineStr"/>
-      <c r="J7" s="61" t="n">
+      <c r="A7" s="64" t="inlineStr"/>
+      <c r="B7" s="64" t="inlineStr"/>
+      <c r="C7" s="64" t="inlineStr"/>
+      <c r="D7" s="64" t="inlineStr"/>
+      <c r="E7" s="64" t="inlineStr"/>
+      <c r="F7" s="64" t="inlineStr"/>
+      <c r="G7" s="64" t="inlineStr"/>
+      <c r="H7" s="64" t="inlineStr"/>
+      <c r="I7" s="64" t="inlineStr"/>
+      <c r="J7" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="61" t="n">
+      <c r="K7" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="65">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="65">
+      <c r="M7" s="66">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr"/>
-      <c r="B8" s="59" t="inlineStr"/>
-      <c r="C8" s="59" t="inlineStr"/>
-      <c r="D8" s="59" t="inlineStr"/>
-      <c r="E8" s="59" t="inlineStr"/>
-      <c r="F8" s="59" t="inlineStr"/>
-      <c r="G8" s="59" t="inlineStr"/>
-      <c r="H8" s="59" t="inlineStr"/>
-      <c r="I8" s="59" t="inlineStr"/>
-      <c r="J8" s="61" t="n">
+      <c r="A8" s="60" t="inlineStr"/>
+      <c r="B8" s="60" t="inlineStr"/>
+      <c r="C8" s="60" t="inlineStr"/>
+      <c r="D8" s="60" t="inlineStr"/>
+      <c r="E8" s="60" t="inlineStr"/>
+      <c r="F8" s="60" t="inlineStr"/>
+      <c r="G8" s="60" t="inlineStr"/>
+      <c r="H8" s="60" t="inlineStr"/>
+      <c r="I8" s="60" t="inlineStr"/>
+      <c r="J8" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="61" t="n">
+      <c r="K8" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="61">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="62">
+      <c r="M8" s="63">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr"/>
-      <c r="C9" s="63" t="inlineStr"/>
-      <c r="D9" s="63" t="inlineStr"/>
-      <c r="E9" s="63" t="inlineStr"/>
-      <c r="F9" s="63" t="inlineStr"/>
-      <c r="G9" s="63" t="inlineStr"/>
-      <c r="H9" s="63" t="inlineStr"/>
-      <c r="I9" s="63" t="inlineStr"/>
-      <c r="J9" s="61" t="n">
+      <c r="A9" s="64" t="inlineStr"/>
+      <c r="B9" s="64" t="inlineStr"/>
+      <c r="C9" s="64" t="inlineStr"/>
+      <c r="D9" s="64" t="inlineStr"/>
+      <c r="E9" s="64" t="inlineStr"/>
+      <c r="F9" s="64" t="inlineStr"/>
+      <c r="G9" s="64" t="inlineStr"/>
+      <c r="H9" s="64" t="inlineStr"/>
+      <c r="I9" s="64" t="inlineStr"/>
+      <c r="J9" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="61" t="n">
+      <c r="K9" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="64">
+      <c r="L9" s="65">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="65">
+      <c r="M9" s="66">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr"/>
-      <c r="B10" s="59" t="inlineStr"/>
-      <c r="C10" s="59" t="inlineStr"/>
-      <c r="D10" s="59" t="inlineStr"/>
-      <c r="E10" s="59" t="inlineStr"/>
-      <c r="F10" s="59" t="inlineStr"/>
-      <c r="G10" s="59" t="inlineStr"/>
-      <c r="H10" s="59" t="inlineStr"/>
-      <c r="I10" s="59" t="inlineStr"/>
-      <c r="J10" s="61" t="n">
+      <c r="A10" s="60" t="inlineStr"/>
+      <c r="B10" s="60" t="inlineStr"/>
+      <c r="C10" s="60" t="inlineStr"/>
+      <c r="D10" s="60" t="inlineStr"/>
+      <c r="E10" s="60" t="inlineStr"/>
+      <c r="F10" s="60" t="inlineStr"/>
+      <c r="G10" s="60" t="inlineStr"/>
+      <c r="H10" s="60" t="inlineStr"/>
+      <c r="I10" s="60" t="inlineStr"/>
+      <c r="J10" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="61" t="n">
+      <c r="K10" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="60">
+      <c r="L10" s="61">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="62">
+      <c r="M10" s="63">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="63" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr"/>
-      <c r="C11" s="63" t="inlineStr"/>
-      <c r="D11" s="63" t="inlineStr"/>
-      <c r="E11" s="63" t="inlineStr"/>
-      <c r="F11" s="63" t="inlineStr"/>
-      <c r="G11" s="63" t="inlineStr"/>
-      <c r="H11" s="63" t="inlineStr"/>
-      <c r="I11" s="63" t="inlineStr"/>
-      <c r="J11" s="61" t="n">
+      <c r="A11" s="64" t="inlineStr"/>
+      <c r="B11" s="64" t="inlineStr"/>
+      <c r="C11" s="64" t="inlineStr"/>
+      <c r="D11" s="64" t="inlineStr"/>
+      <c r="E11" s="64" t="inlineStr"/>
+      <c r="F11" s="64" t="inlineStr"/>
+      <c r="G11" s="64" t="inlineStr"/>
+      <c r="H11" s="64" t="inlineStr"/>
+      <c r="I11" s="64" t="inlineStr"/>
+      <c r="J11" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="61" t="n">
+      <c r="K11" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="64">
+      <c r="L11" s="65">
         <f>K11-J11</f>
         <v/>
       </c>
-      <c r="M11" s="65">
+      <c r="M11" s="66">
         <f>IF(J11=0,"",(K11-J11)/J11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr"/>
-      <c r="B12" s="59" t="inlineStr"/>
-      <c r="C12" s="59" t="inlineStr"/>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr"/>
-      <c r="F12" s="59" t="inlineStr"/>
-      <c r="G12" s="59" t="inlineStr"/>
-      <c r="H12" s="59" t="inlineStr"/>
-      <c r="I12" s="59" t="inlineStr"/>
-      <c r="J12" s="61" t="n">
+      <c r="A12" s="60" t="inlineStr"/>
+      <c r="B12" s="60" t="inlineStr"/>
+      <c r="C12" s="60" t="inlineStr"/>
+      <c r="D12" s="60" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr"/>
+      <c r="F12" s="60" t="inlineStr"/>
+      <c r="G12" s="60" t="inlineStr"/>
+      <c r="H12" s="60" t="inlineStr"/>
+      <c r="I12" s="60" t="inlineStr"/>
+      <c r="J12" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="61" t="n">
+      <c r="K12" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="60">
+      <c r="L12" s="61">
         <f>K12-J12</f>
         <v/>
       </c>
-      <c r="M12" s="62">
+      <c r="M12" s="63">
         <f>IF(J12=0,"",(K12-J12)/J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr"/>
-      <c r="C13" s="63" t="inlineStr"/>
-      <c r="D13" s="63" t="inlineStr"/>
-      <c r="E13" s="63" t="inlineStr"/>
-      <c r="F13" s="63" t="inlineStr"/>
-      <c r="G13" s="63" t="inlineStr"/>
-      <c r="H13" s="63" t="inlineStr"/>
-      <c r="I13" s="63" t="inlineStr"/>
-      <c r="J13" s="61" t="n">
+      <c r="A13" s="64" t="inlineStr"/>
+      <c r="B13" s="64" t="inlineStr"/>
+      <c r="C13" s="64" t="inlineStr"/>
+      <c r="D13" s="64" t="inlineStr"/>
+      <c r="E13" s="64" t="inlineStr"/>
+      <c r="F13" s="64" t="inlineStr"/>
+      <c r="G13" s="64" t="inlineStr"/>
+      <c r="H13" s="64" t="inlineStr"/>
+      <c r="I13" s="64" t="inlineStr"/>
+      <c r="J13" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="61" t="n">
+      <c r="K13" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="64">
+      <c r="L13" s="65">
         <f>K13-J13</f>
         <v/>
       </c>
-      <c r="M13" s="65">
+      <c r="M13" s="66">
         <f>IF(J13=0,"",(K13-J13)/J13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="67" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="66" t="n"/>
-      <c r="G14" s="66" t="n"/>
-      <c r="H14" s="66" t="n"/>
-      <c r="I14" s="66" t="n"/>
-      <c r="J14" s="30">
+      <c r="B14" s="67" t="n"/>
+      <c r="C14" s="67" t="n"/>
+      <c r="D14" s="67" t="n"/>
+      <c r="E14" s="67" t="n"/>
+      <c r="F14" s="67" t="n"/>
+      <c r="G14" s="67" t="n"/>
+      <c r="H14" s="67" t="n"/>
+      <c r="I14" s="67" t="n"/>
+      <c r="J14" s="31">
         <f>SUM(J6:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="31">
         <f>SUM(K6:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="30">
+      <c r="L14" s="31">
         <f>K14-J14</f>
         <v/>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="32">
         <f>IF(J14=0,"",(K14-J14)/J14)</f>
         <v/>
       </c>
@@ -13584,243 +13615,243 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Tipo de bien</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr"/>
-      <c r="C6" s="59" t="inlineStr"/>
-      <c r="D6" s="59" t="inlineStr"/>
-      <c r="E6" s="59" t="inlineStr"/>
-      <c r="F6" s="61" t="n">
+      <c r="A6" s="60" t="inlineStr"/>
+      <c r="B6" s="60" t="inlineStr"/>
+      <c r="C6" s="60" t="inlineStr"/>
+      <c r="D6" s="60" t="inlineStr"/>
+      <c r="E6" s="60" t="inlineStr"/>
+      <c r="F6" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="61" t="n">
+      <c r="G6" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="61">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="63">
         <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr"/>
-      <c r="C7" s="63" t="inlineStr"/>
-      <c r="D7" s="63" t="inlineStr"/>
-      <c r="E7" s="63" t="inlineStr"/>
-      <c r="F7" s="61" t="n">
+      <c r="A7" s="64" t="inlineStr"/>
+      <c r="B7" s="64" t="inlineStr"/>
+      <c r="C7" s="64" t="inlineStr"/>
+      <c r="D7" s="64" t="inlineStr"/>
+      <c r="E7" s="64" t="inlineStr"/>
+      <c r="F7" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="61" t="n">
+      <c r="G7" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="64">
+      <c r="H7" s="65">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="65">
+      <c r="I7" s="66">
         <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr"/>
-      <c r="B8" s="59" t="inlineStr"/>
-      <c r="C8" s="59" t="inlineStr"/>
-      <c r="D8" s="59" t="inlineStr"/>
-      <c r="E8" s="59" t="inlineStr"/>
-      <c r="F8" s="61" t="n">
+      <c r="A8" s="60" t="inlineStr"/>
+      <c r="B8" s="60" t="inlineStr"/>
+      <c r="C8" s="60" t="inlineStr"/>
+      <c r="D8" s="60" t="inlineStr"/>
+      <c r="E8" s="60" t="inlineStr"/>
+      <c r="F8" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="61" t="n">
+      <c r="G8" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="61">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="63">
         <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr"/>
-      <c r="C9" s="63" t="inlineStr"/>
-      <c r="D9" s="63" t="inlineStr"/>
-      <c r="E9" s="63" t="inlineStr"/>
-      <c r="F9" s="61" t="n">
+      <c r="A9" s="64" t="inlineStr"/>
+      <c r="B9" s="64" t="inlineStr"/>
+      <c r="C9" s="64" t="inlineStr"/>
+      <c r="D9" s="64" t="inlineStr"/>
+      <c r="E9" s="64" t="inlineStr"/>
+      <c r="F9" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="61" t="n">
+      <c r="G9" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="64">
+      <c r="H9" s="65">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="65">
+      <c r="I9" s="66">
         <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr"/>
-      <c r="B10" s="59" t="inlineStr"/>
-      <c r="C10" s="59" t="inlineStr"/>
-      <c r="D10" s="59" t="inlineStr"/>
-      <c r="E10" s="59" t="inlineStr"/>
-      <c r="F10" s="61" t="n">
+      <c r="A10" s="60" t="inlineStr"/>
+      <c r="B10" s="60" t="inlineStr"/>
+      <c r="C10" s="60" t="inlineStr"/>
+      <c r="D10" s="60" t="inlineStr"/>
+      <c r="E10" s="60" t="inlineStr"/>
+      <c r="F10" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="61" t="n">
+      <c r="G10" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="60">
+      <c r="H10" s="61">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="62">
+      <c r="I10" s="63">
         <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="63" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr"/>
-      <c r="C11" s="63" t="inlineStr"/>
-      <c r="D11" s="63" t="inlineStr"/>
-      <c r="E11" s="63" t="inlineStr"/>
-      <c r="F11" s="61" t="n">
+      <c r="A11" s="64" t="inlineStr"/>
+      <c r="B11" s="64" t="inlineStr"/>
+      <c r="C11" s="64" t="inlineStr"/>
+      <c r="D11" s="64" t="inlineStr"/>
+      <c r="E11" s="64" t="inlineStr"/>
+      <c r="F11" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="61" t="n">
+      <c r="G11" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="65">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="65">
+      <c r="I11" s="66">
         <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr"/>
-      <c r="B12" s="59" t="inlineStr"/>
-      <c r="C12" s="59" t="inlineStr"/>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr"/>
-      <c r="F12" s="61" t="n">
+      <c r="A12" s="60" t="inlineStr"/>
+      <c r="B12" s="60" t="inlineStr"/>
+      <c r="C12" s="60" t="inlineStr"/>
+      <c r="D12" s="60" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr"/>
+      <c r="F12" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="61" t="n">
+      <c r="G12" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="60">
+      <c r="H12" s="61">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="62">
+      <c r="I12" s="63">
         <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr"/>
-      <c r="C13" s="63" t="inlineStr"/>
-      <c r="D13" s="63" t="inlineStr"/>
-      <c r="E13" s="63" t="inlineStr"/>
-      <c r="F13" s="61" t="n">
+      <c r="A13" s="64" t="inlineStr"/>
+      <c r="B13" s="64" t="inlineStr"/>
+      <c r="C13" s="64" t="inlineStr"/>
+      <c r="D13" s="64" t="inlineStr"/>
+      <c r="E13" s="64" t="inlineStr"/>
+      <c r="F13" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="61" t="n">
+      <c r="G13" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="64">
+      <c r="H13" s="65">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="65">
+      <c r="I13" s="66">
         <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="67" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="30">
+      <c r="B14" s="67" t="n"/>
+      <c r="C14" s="67" t="n"/>
+      <c r="D14" s="67" t="n"/>
+      <c r="E14" s="67" t="n"/>
+      <c r="F14" s="31">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="32">
         <f>IF(F14=0,"",(G14-F14)/F14)</f>
         <v/>
       </c>
@@ -13888,195 +13919,195 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Tipo de vehiculo</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Registro / placa / chasis</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>1 - Vehiculos motorizados terrestres</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>PBO7092</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr"/>
-      <c r="F6" s="59" t="inlineStr"/>
-      <c r="G6" s="60" t="n">
+      <c r="E6" s="60" t="inlineStr"/>
+      <c r="F6" s="60" t="inlineStr"/>
+      <c r="G6" s="61" t="n">
         <v>12000</v>
       </c>
-      <c r="H6" s="61" t="n">
+      <c r="H6" s="62" t="n">
         <v>12000</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="61">
         <f>H6-G6</f>
         <v/>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="63">
         <f>IF(G6=0,"",(H6-G6)/G6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>1 - Vehiculos motorizados terrestres</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>PBF9690</t>
         </is>
       </c>
-      <c r="C7" s="63" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D7" s="63" t="inlineStr">
+      <c r="D7" s="64" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E7" s="63" t="inlineStr"/>
-      <c r="F7" s="63" t="inlineStr"/>
-      <c r="G7" s="64" t="n">
+      <c r="E7" s="64" t="inlineStr"/>
+      <c r="F7" s="64" t="inlineStr"/>
+      <c r="G7" s="65" t="n">
         <v>20000</v>
       </c>
-      <c r="H7" s="61" t="n">
+      <c r="H7" s="62" t="n">
         <v>20000</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="65">
         <f>H7-G7</f>
         <v/>
       </c>
-      <c r="J7" s="65">
+      <c r="J7" s="66">
         <f>IF(G7=0,"",(H7-G7)/G7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>1 - Vehiculos motorizados terrestres</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>PFC8683</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr"/>
-      <c r="F8" s="59" t="inlineStr"/>
-      <c r="G8" s="60" t="n">
+      <c r="E8" s="60" t="inlineStr"/>
+      <c r="F8" s="60" t="inlineStr"/>
+      <c r="G8" s="61" t="n">
         <v>32000</v>
       </c>
-      <c r="H8" s="61" t="n">
+      <c r="H8" s="62" t="n">
         <v>32000</v>
       </c>
-      <c r="I8" s="60">
+      <c r="I8" s="61">
         <f>H8-G8</f>
         <v/>
       </c>
-      <c r="J8" s="62">
+      <c r="J8" s="63">
         <f>IF(G8=0,"",(H8-G8)/G8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="66" t="inlineStr">
+      <c r="A9" s="67" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="66" t="n"/>
-      <c r="C9" s="66" t="n"/>
-      <c r="D9" s="66" t="n"/>
-      <c r="E9" s="66" t="n"/>
-      <c r="F9" s="66" t="n"/>
-      <c r="G9" s="30">
+      <c r="B9" s="67" t="n"/>
+      <c r="C9" s="67" t="n"/>
+      <c r="D9" s="67" t="n"/>
+      <c r="E9" s="67" t="n"/>
+      <c r="F9" s="67" t="n"/>
+      <c r="G9" s="31">
         <f>SUM(G6:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <f>SUM(H6:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="31">
         <f>H9-G9</f>
         <v/>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="32">
         <f>IF(G9=0,"",(H9-G9)/G9)</f>
         <v/>
       </c>
@@ -14143,243 +14174,243 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Tipo de derecho</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr"/>
-      <c r="C6" s="59" t="inlineStr"/>
-      <c r="D6" s="59" t="inlineStr"/>
-      <c r="E6" s="59" t="inlineStr"/>
-      <c r="F6" s="61" t="n">
+      <c r="A6" s="60" t="inlineStr"/>
+      <c r="B6" s="60" t="inlineStr"/>
+      <c r="C6" s="60" t="inlineStr"/>
+      <c r="D6" s="60" t="inlineStr"/>
+      <c r="E6" s="60" t="inlineStr"/>
+      <c r="F6" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="61" t="n">
+      <c r="G6" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="61">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="63">
         <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr"/>
-      <c r="C7" s="63" t="inlineStr"/>
-      <c r="D7" s="63" t="inlineStr"/>
-      <c r="E7" s="63" t="inlineStr"/>
-      <c r="F7" s="61" t="n">
+      <c r="A7" s="64" t="inlineStr"/>
+      <c r="B7" s="64" t="inlineStr"/>
+      <c r="C7" s="64" t="inlineStr"/>
+      <c r="D7" s="64" t="inlineStr"/>
+      <c r="E7" s="64" t="inlineStr"/>
+      <c r="F7" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="61" t="n">
+      <c r="G7" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="64">
+      <c r="H7" s="65">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="65">
+      <c r="I7" s="66">
         <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr"/>
-      <c r="B8" s="59" t="inlineStr"/>
-      <c r="C8" s="59" t="inlineStr"/>
-      <c r="D8" s="59" t="inlineStr"/>
-      <c r="E8" s="59" t="inlineStr"/>
-      <c r="F8" s="61" t="n">
+      <c r="A8" s="60" t="inlineStr"/>
+      <c r="B8" s="60" t="inlineStr"/>
+      <c r="C8" s="60" t="inlineStr"/>
+      <c r="D8" s="60" t="inlineStr"/>
+      <c r="E8" s="60" t="inlineStr"/>
+      <c r="F8" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="61" t="n">
+      <c r="G8" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="61">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="63">
         <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr"/>
-      <c r="C9" s="63" t="inlineStr"/>
-      <c r="D9" s="63" t="inlineStr"/>
-      <c r="E9" s="63" t="inlineStr"/>
-      <c r="F9" s="61" t="n">
+      <c r="A9" s="64" t="inlineStr"/>
+      <c r="B9" s="64" t="inlineStr"/>
+      <c r="C9" s="64" t="inlineStr"/>
+      <c r="D9" s="64" t="inlineStr"/>
+      <c r="E9" s="64" t="inlineStr"/>
+      <c r="F9" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="61" t="n">
+      <c r="G9" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="64">
+      <c r="H9" s="65">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="65">
+      <c r="I9" s="66">
         <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr"/>
-      <c r="B10" s="59" t="inlineStr"/>
-      <c r="C10" s="59" t="inlineStr"/>
-      <c r="D10" s="59" t="inlineStr"/>
-      <c r="E10" s="59" t="inlineStr"/>
-      <c r="F10" s="61" t="n">
+      <c r="A10" s="60" t="inlineStr"/>
+      <c r="B10" s="60" t="inlineStr"/>
+      <c r="C10" s="60" t="inlineStr"/>
+      <c r="D10" s="60" t="inlineStr"/>
+      <c r="E10" s="60" t="inlineStr"/>
+      <c r="F10" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="61" t="n">
+      <c r="G10" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="60">
+      <c r="H10" s="61">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="62">
+      <c r="I10" s="63">
         <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="63" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr"/>
-      <c r="C11" s="63" t="inlineStr"/>
-      <c r="D11" s="63" t="inlineStr"/>
-      <c r="E11" s="63" t="inlineStr"/>
-      <c r="F11" s="61" t="n">
+      <c r="A11" s="64" t="inlineStr"/>
+      <c r="B11" s="64" t="inlineStr"/>
+      <c r="C11" s="64" t="inlineStr"/>
+      <c r="D11" s="64" t="inlineStr"/>
+      <c r="E11" s="64" t="inlineStr"/>
+      <c r="F11" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="61" t="n">
+      <c r="G11" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="65">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="65">
+      <c r="I11" s="66">
         <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr"/>
-      <c r="B12" s="59" t="inlineStr"/>
-      <c r="C12" s="59" t="inlineStr"/>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr"/>
-      <c r="F12" s="61" t="n">
+      <c r="A12" s="60" t="inlineStr"/>
+      <c r="B12" s="60" t="inlineStr"/>
+      <c r="C12" s="60" t="inlineStr"/>
+      <c r="D12" s="60" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr"/>
+      <c r="F12" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="61" t="n">
+      <c r="G12" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="60">
+      <c r="H12" s="61">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="62">
+      <c r="I12" s="63">
         <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr"/>
-      <c r="C13" s="63" t="inlineStr"/>
-      <c r="D13" s="63" t="inlineStr"/>
-      <c r="E13" s="63" t="inlineStr"/>
-      <c r="F13" s="61" t="n">
+      <c r="A13" s="64" t="inlineStr"/>
+      <c r="B13" s="64" t="inlineStr"/>
+      <c r="C13" s="64" t="inlineStr"/>
+      <c r="D13" s="64" t="inlineStr"/>
+      <c r="E13" s="64" t="inlineStr"/>
+      <c r="F13" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="61" t="n">
+      <c r="G13" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="64">
+      <c r="H13" s="65">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="65">
+      <c r="I13" s="66">
         <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="67" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="30">
+      <c r="B14" s="67" t="n"/>
+      <c r="C14" s="67" t="n"/>
+      <c r="D14" s="67" t="n"/>
+      <c r="E14" s="67" t="n"/>
+      <c r="F14" s="31">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="32">
         <f>IF(F14=0,"",(G14-F14)/F14)</f>
         <v/>
       </c>
@@ -14450,303 +14481,303 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Tipo de inmueble</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Canton</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Fecha de inscripcion</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Clave catastral</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>3 - Terreno</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="60" t="inlineStr">
         <is>
           <t>22/10/2008</t>
         </is>
       </c>
-      <c r="G6" s="59" t="inlineStr">
+      <c r="G6" s="60" t="inlineStr">
         <is>
           <t>1042203018</t>
         </is>
       </c>
-      <c r="H6" s="59" t="inlineStr"/>
-      <c r="I6" s="59" t="inlineStr"/>
-      <c r="J6" s="60" t="n">
+      <c r="H6" s="60" t="inlineStr"/>
+      <c r="I6" s="60" t="inlineStr"/>
+      <c r="J6" s="61" t="n">
         <v>267340.8</v>
       </c>
-      <c r="K6" s="61" t="n">
+      <c r="K6" s="62" t="n">
         <v>267340.8</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="61">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="63">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>1 - Casa</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C7" s="63" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D7" s="63" t="inlineStr">
+      <c r="D7" s="64" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E7" s="63" t="inlineStr">
+      <c r="E7" s="64" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F7" s="63" t="inlineStr">
+      <c r="F7" s="64" t="inlineStr">
         <is>
           <t>13/03/1997</t>
         </is>
       </c>
-      <c r="G7" s="63" t="inlineStr">
+      <c r="G7" s="64" t="inlineStr">
         <is>
           <t>1012005008000000000</t>
         </is>
       </c>
-      <c r="H7" s="63" t="inlineStr"/>
-      <c r="I7" s="63" t="inlineStr"/>
-      <c r="J7" s="64" t="n">
+      <c r="H7" s="64" t="inlineStr"/>
+      <c r="I7" s="64" t="inlineStr"/>
+      <c r="J7" s="65" t="n">
         <v>198118.55</v>
       </c>
-      <c r="K7" s="61" t="n">
+      <c r="K7" s="62" t="n">
         <v>198118.55</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="65">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="65">
+      <c r="M7" s="66">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>1 - Casa</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F8" s="59" t="inlineStr"/>
-      <c r="G8" s="59" t="inlineStr">
+      <c r="F8" s="60" t="inlineStr"/>
+      <c r="G8" s="60" t="inlineStr">
         <is>
           <t>1042203018</t>
         </is>
       </c>
-      <c r="H8" s="59" t="inlineStr"/>
-      <c r="I8" s="59" t="inlineStr"/>
-      <c r="J8" s="60" t="n">
+      <c r="H8" s="60" t="inlineStr"/>
+      <c r="I8" s="60" t="inlineStr"/>
+      <c r="J8" s="61" t="n">
         <v>33634.04</v>
       </c>
-      <c r="K8" s="61" t="n">
+      <c r="K8" s="62" t="n">
         <v>33634.04</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="61">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="62">
+      <c r="M8" s="63">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>3 - Terreno</t>
         </is>
       </c>
-      <c r="B9" s="63" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C9" s="63" t="inlineStr">
+      <c r="C9" s="64" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D9" s="63" t="inlineStr">
+      <c r="D9" s="64" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E9" s="63" t="inlineStr">
+      <c r="E9" s="64" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F9" s="63" t="inlineStr"/>
-      <c r="G9" s="63" t="inlineStr">
+      <c r="F9" s="64" t="inlineStr"/>
+      <c r="G9" s="64" t="inlineStr">
         <is>
           <t>1012005008000000000</t>
         </is>
       </c>
-      <c r="H9" s="63" t="inlineStr"/>
-      <c r="I9" s="63" t="inlineStr"/>
-      <c r="J9" s="64" t="n">
+      <c r="H9" s="64" t="inlineStr"/>
+      <c r="I9" s="64" t="inlineStr"/>
+      <c r="J9" s="65" t="n">
         <v>82624.22</v>
       </c>
-      <c r="K9" s="61" t="n">
+      <c r="K9" s="62" t="n">
         <v>82624.22</v>
       </c>
-      <c r="L9" s="64">
+      <c r="L9" s="65">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="65">
+      <c r="M9" s="66">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="66" t="n"/>
-      <c r="C10" s="66" t="n"/>
-      <c r="D10" s="66" t="n"/>
-      <c r="E10" s="66" t="n"/>
-      <c r="F10" s="66" t="n"/>
-      <c r="G10" s="66" t="n"/>
-      <c r="H10" s="66" t="n"/>
-      <c r="I10" s="66" t="n"/>
-      <c r="J10" s="30">
+      <c r="B10" s="67" t="n"/>
+      <c r="C10" s="67" t="n"/>
+      <c r="D10" s="67" t="n"/>
+      <c r="E10" s="67" t="n"/>
+      <c r="F10" s="67" t="n"/>
+      <c r="G10" s="67" t="n"/>
+      <c r="H10" s="67" t="n"/>
+      <c r="I10" s="67" t="n"/>
+      <c r="J10" s="31">
         <f>SUM(J6:J9)</f>
         <v/>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="31">
         <f>SUM(K6:K9)</f>
         <v/>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="31">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="31">
+      <c r="M10" s="32">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
@@ -14819,243 +14850,243 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Ubicacion</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Descripcion</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Regularizacion activos</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Anio fiscal adquisicion</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Valor 2025</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Valor 2026</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Variacion</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr"/>
-      <c r="C6" s="59" t="inlineStr"/>
-      <c r="D6" s="59" t="inlineStr"/>
-      <c r="E6" s="59" t="inlineStr"/>
-      <c r="F6" s="61" t="n">
+      <c r="A6" s="60" t="inlineStr"/>
+      <c r="B6" s="60" t="inlineStr"/>
+      <c r="C6" s="60" t="inlineStr"/>
+      <c r="D6" s="60" t="inlineStr"/>
+      <c r="E6" s="60" t="inlineStr"/>
+      <c r="F6" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="61" t="n">
+      <c r="G6" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="61">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="63">
         <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr"/>
-      <c r="C7" s="63" t="inlineStr"/>
-      <c r="D7" s="63" t="inlineStr"/>
-      <c r="E7" s="63" t="inlineStr"/>
-      <c r="F7" s="61" t="n">
+      <c r="A7" s="64" t="inlineStr"/>
+      <c r="B7" s="64" t="inlineStr"/>
+      <c r="C7" s="64" t="inlineStr"/>
+      <c r="D7" s="64" t="inlineStr"/>
+      <c r="E7" s="64" t="inlineStr"/>
+      <c r="F7" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="61" t="n">
+      <c r="G7" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="64">
+      <c r="H7" s="65">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="65">
+      <c r="I7" s="66">
         <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr"/>
-      <c r="B8" s="59" t="inlineStr"/>
-      <c r="C8" s="59" t="inlineStr"/>
-      <c r="D8" s="59" t="inlineStr"/>
-      <c r="E8" s="59" t="inlineStr"/>
-      <c r="F8" s="61" t="n">
+      <c r="A8" s="60" t="inlineStr"/>
+      <c r="B8" s="60" t="inlineStr"/>
+      <c r="C8" s="60" t="inlineStr"/>
+      <c r="D8" s="60" t="inlineStr"/>
+      <c r="E8" s="60" t="inlineStr"/>
+      <c r="F8" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="61" t="n">
+      <c r="G8" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="61">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="63">
         <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr"/>
-      <c r="C9" s="63" t="inlineStr"/>
-      <c r="D9" s="63" t="inlineStr"/>
-      <c r="E9" s="63" t="inlineStr"/>
-      <c r="F9" s="61" t="n">
+      <c r="A9" s="64" t="inlineStr"/>
+      <c r="B9" s="64" t="inlineStr"/>
+      <c r="C9" s="64" t="inlineStr"/>
+      <c r="D9" s="64" t="inlineStr"/>
+      <c r="E9" s="64" t="inlineStr"/>
+      <c r="F9" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="61" t="n">
+      <c r="G9" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="64">
+      <c r="H9" s="65">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="65">
+      <c r="I9" s="66">
         <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr"/>
-      <c r="B10" s="59" t="inlineStr"/>
-      <c r="C10" s="59" t="inlineStr"/>
-      <c r="D10" s="59" t="inlineStr"/>
-      <c r="E10" s="59" t="inlineStr"/>
-      <c r="F10" s="61" t="n">
+      <c r="A10" s="60" t="inlineStr"/>
+      <c r="B10" s="60" t="inlineStr"/>
+      <c r="C10" s="60" t="inlineStr"/>
+      <c r="D10" s="60" t="inlineStr"/>
+      <c r="E10" s="60" t="inlineStr"/>
+      <c r="F10" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="61" t="n">
+      <c r="G10" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="60">
+      <c r="H10" s="61">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="62">
+      <c r="I10" s="63">
         <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="63" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr"/>
-      <c r="C11" s="63" t="inlineStr"/>
-      <c r="D11" s="63" t="inlineStr"/>
-      <c r="E11" s="63" t="inlineStr"/>
-      <c r="F11" s="61" t="n">
+      <c r="A11" s="64" t="inlineStr"/>
+      <c r="B11" s="64" t="inlineStr"/>
+      <c r="C11" s="64" t="inlineStr"/>
+      <c r="D11" s="64" t="inlineStr"/>
+      <c r="E11" s="64" t="inlineStr"/>
+      <c r="F11" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="61" t="n">
+      <c r="G11" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="65">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="65">
+      <c r="I11" s="66">
         <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr"/>
-      <c r="B12" s="59" t="inlineStr"/>
-      <c r="C12" s="59" t="inlineStr"/>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr"/>
-      <c r="F12" s="61" t="n">
+      <c r="A12" s="60" t="inlineStr"/>
+      <c r="B12" s="60" t="inlineStr"/>
+      <c r="C12" s="60" t="inlineStr"/>
+      <c r="D12" s="60" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr"/>
+      <c r="F12" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="61" t="n">
+      <c r="G12" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="60">
+      <c r="H12" s="61">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="62">
+      <c r="I12" s="63">
         <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr"/>
-      <c r="C13" s="63" t="inlineStr"/>
-      <c r="D13" s="63" t="inlineStr"/>
-      <c r="E13" s="63" t="inlineStr"/>
-      <c r="F13" s="61" t="n">
+      <c r="A13" s="64" t="inlineStr"/>
+      <c r="B13" s="64" t="inlineStr"/>
+      <c r="C13" s="64" t="inlineStr"/>
+      <c r="D13" s="64" t="inlineStr"/>
+      <c r="E13" s="64" t="inlineStr"/>
+      <c r="F13" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="61" t="n">
+      <c r="G13" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="64">
+      <c r="H13" s="65">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="65">
+      <c r="I13" s="66">
         <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="67" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="30">
+      <c r="B14" s="67" t="n"/>
+      <c r="C14" s="67" t="n"/>
+      <c r="D14" s="67" t="n"/>
+      <c r="E14" s="67" t="n"/>
+      <c r="F14" s="31">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="32">
         <f>IF(F14=0,"",(G14-F14)/F14)</f>
         <v/>
       </c>

--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -434,7 +434,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2341,7 +2341,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2351,13 +2351,20 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Edite las celdas amarillas para reutilizar la plantilla con otra persona; el XML se genera con estos datos</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="5" customHeight="1">
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="78" t="inlineStr">
         <is>
-          <t>IDENTIFICACION</t>
+          <t>IDENTIFICACION DEL DECLARANTE Y CONYUGE  (editable)</t>
         </is>
       </c>
     </row>
@@ -2458,129 +2465,127 @@
     <row r="14">
       <c r="A14" s="79" t="inlineStr">
         <is>
-          <t>Total creditos / cuentas por cobrar</t>
-        </is>
-      </c>
-      <c r="B14" s="61" t="n">
-        <v>0</v>
-      </c>
+          <t>Regularizacion de activos</t>
+        </is>
+      </c>
+      <c r="B14" s="80" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="78" t="inlineStr">
         <is>
-          <t>PATRIMONIO NETO (enlazado a la hoja Dashboard)</t>
+          <t>PATRIMONIO DECLARADO  (editable)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="79" t="inlineStr">
         <is>
-          <t>Patrimonio neto 2025</t>
-        </is>
-      </c>
-      <c r="B17" s="61">
-        <f>Dashboard!D31</f>
-        <v/>
+          <t>Patrimonio total declarado</t>
+        </is>
+      </c>
+      <c r="B17" s="61" t="n">
+        <v>883285.5600000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="79" t="inlineStr">
         <is>
-          <t>Patrimonio neto 2026 (proyectado)</t>
-        </is>
-      </c>
-      <c r="B18" s="61">
-        <f>Dashboard!E31</f>
-        <v/>
+          <t>Atribuible a hijos no emancipados</t>
+        </is>
+      </c>
+      <c r="B18" s="62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="79" t="inlineStr">
         <is>
-          <t>Variacion proyectada</t>
-        </is>
-      </c>
-      <c r="B19" s="61">
-        <f>Dashboard!F31</f>
-        <v/>
+          <t>Patrimonio en la sociedad conyugal</t>
+        </is>
+      </c>
+      <c r="B19" s="62" t="n">
+        <v>883285.5600000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="79" t="inlineStr">
         <is>
-          <t>Variacion % proyectada</t>
-        </is>
-      </c>
-      <c r="B20" s="63">
-        <f>Dashboard!G31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="78" t="inlineStr">
-        <is>
-          <t>PATRIMONIO DECLARADO EN EL XML</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="79" t="inlineStr">
-        <is>
-          <t>Patrimonio total declarado</t>
-        </is>
-      </c>
-      <c r="B23" s="61" t="n">
-        <v>883285.5600000001</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="79" t="inlineStr">
-        <is>
-          <t>Atribuible a hijos no emancipados</t>
-        </is>
-      </c>
-      <c r="B24" s="61" t="n">
+          <t>Patrimonio individual del declarante</t>
+        </is>
+      </c>
+      <c r="B20" s="62" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="79" t="inlineStr">
+        <is>
+          <t>Patrimonio del anio anterior</t>
+        </is>
+      </c>
+      <c r="B21" s="62" t="n">
+        <v>801569.97</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="79" t="inlineStr">
+        <is>
+          <t>Crecimiento / decremento patrimonial</t>
+        </is>
+      </c>
+      <c r="B22" s="61" t="n">
+        <v>81715.59</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="78" t="inlineStr">
+        <is>
+          <t>PATRIMONIO NETO  (calculado - enlazado al Dashboard)</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="79" t="inlineStr">
         <is>
-          <t>Patrimonio en la sociedad conyugal</t>
-        </is>
-      </c>
-      <c r="B25" s="61" t="n">
-        <v>883285.5600000001</v>
+          <t>Patrimonio neto 2025</t>
+        </is>
+      </c>
+      <c r="B25" s="61">
+        <f>Dashboard!D31</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="79" t="inlineStr">
         <is>
-          <t>Patrimonio individual del declarante</t>
-        </is>
-      </c>
-      <c r="B26" s="61" t="n">
-        <v>0</v>
+          <t>Patrimonio neto 2026 (proyectado)</t>
+        </is>
+      </c>
+      <c r="B26" s="61">
+        <f>Dashboard!E31</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="79" t="inlineStr">
         <is>
-          <t>Patrimonio del anio anterior</t>
-        </is>
-      </c>
-      <c r="B27" s="61" t="n">
-        <v>801569.97</v>
+          <t>Variacion proyectada</t>
+        </is>
+      </c>
+      <c r="B27" s="61">
+        <f>Dashboard!F31</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="79" t="inlineStr">
         <is>
-          <t>Crecimiento / decremento patrimonial</t>
-        </is>
-      </c>
-      <c r="B28" s="61" t="n">
-        <v>81715.59</v>
+          <t>Variacion % proyectada</t>
+        </is>
+      </c>
+      <c r="B28" s="63">
+        <f>Dashboard!G31</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -2607,18 +2612,33 @@
     <row r="34">
       <c r="A34" s="59" t="inlineStr">
         <is>
-          <t>Catalogos del SRI integrados (Tablas 1-19 del archivo CATALOGO.xls). El XML se genera con generar_xml_sri.py.</t>
+          <t>Las celdas amarillas son editables; los totales de creditos y derechos se calculan automaticamente al generar el XML.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
   </mergeCells>
+  <dataValidations count="4">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"IND - Individual,SCD - Sociedad,SOC - Sociedad conyugal o union de hecho"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"C - Cedula,E - Identificacion del exterior,P - Pasaporte,R - RUC"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"C - Cedula,E - Identificacion del exterior,P - Pasaporte,R - RUC"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1 - Si,2 - No"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
+++ b/tools/Declaracion_Patrimonial_2025_MARCO.xlsx
@@ -223,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -385,6 +385,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -395,6 +398,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1874,7 +1880,7 @@
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D6" s="60" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>DINERS CLUB DEL ECUADOR</t>
         </is>
@@ -1884,97 +1890,97 @@
           <t>R - RUC</t>
         </is>
       </c>
-      <c r="F6" s="60" t="inlineStr">
+      <c r="F6" s="61" t="inlineStr">
         <is>
           <t>1792260957001</t>
         </is>
       </c>
-      <c r="G6" s="60" t="inlineStr"/>
+      <c r="G6" s="61" t="inlineStr"/>
       <c r="H6" s="60" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="I6" s="61" t="n">
+      <c r="I6" s="62" t="n">
         <v>4891.88</v>
       </c>
-      <c r="J6" s="62" t="n">
+      <c r="J6" s="63" t="n">
         <v>4891.88</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="62">
         <f>J6-I6</f>
         <v/>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="64">
         <f>IF(I6=0,"",(J6-I6)/I6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C7" s="64" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D7" s="64" t="inlineStr">
+      <c r="D7" s="66" t="inlineStr">
         <is>
           <t>BANCO DEL PICHINCHA</t>
         </is>
       </c>
-      <c r="E7" s="64" t="inlineStr">
+      <c r="E7" s="65" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
-      <c r="F7" s="64" t="inlineStr">
+      <c r="F7" s="66" t="inlineStr">
         <is>
           <t>1790010937001</t>
         </is>
       </c>
-      <c r="G7" s="64" t="inlineStr"/>
-      <c r="H7" s="64" t="inlineStr">
+      <c r="G7" s="66" t="inlineStr"/>
+      <c r="H7" s="65" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="I7" s="65" t="n">
+      <c r="I7" s="67" t="n">
         <v>5547.31</v>
       </c>
-      <c r="J7" s="62" t="n">
+      <c r="J7" s="63" t="n">
         <v>5547.31</v>
       </c>
-      <c r="K7" s="65">
+      <c r="K7" s="67">
         <f>J7-I7</f>
         <v/>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="68">
         <f>IF(I7=0,"",(J7-I7)/I7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="68" t="inlineStr">
+      <c r="A8" s="70" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="68" t="n"/>
-      <c r="C8" s="68" t="n"/>
-      <c r="D8" s="68" t="n"/>
-      <c r="E8" s="68" t="n"/>
-      <c r="F8" s="68" t="n"/>
-      <c r="G8" s="68" t="n"/>
-      <c r="H8" s="68" t="n"/>
+      <c r="B8" s="70" t="n"/>
+      <c r="C8" s="70" t="n"/>
+      <c r="D8" s="70" t="n"/>
+      <c r="E8" s="70" t="n"/>
+      <c r="F8" s="70" t="n"/>
+      <c r="G8" s="70" t="n"/>
+      <c r="H8" s="70" t="n"/>
       <c r="I8" s="38">
         <f>SUM(I6:I7)</f>
         <v/>
@@ -2053,14 +2059,14 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="B5" s="69" t="inlineStr">
+      <c r="B5" s="71" t="inlineStr">
         <is>
           <t>Incremento patrimonial declarado en el XML</t>
         </is>
       </c>
-      <c r="C5" s="70" t="n"/>
-      <c r="D5" s="70" t="n"/>
-      <c r="E5" s="71" t="n">
+      <c r="C5" s="72" t="n"/>
+      <c r="D5" s="72" t="n"/>
+      <c r="E5" s="73" t="n">
         <v>81715.59</v>
       </c>
     </row>
@@ -2077,84 +2083,84 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="72" t="inlineStr">
+      <c r="B8" s="74" t="inlineStr">
         <is>
           <t>1 - Ingresos locales</t>
         </is>
       </c>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="73" t="inlineStr">
+      <c r="E8" s="75" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="72" t="inlineStr">
+      <c r="B9" s="74" t="inlineStr">
         <is>
           <t>2 - Ingresos exterior</t>
         </is>
       </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="73" t="inlineStr">
+      <c r="E9" s="75" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="72" t="inlineStr">
+      <c r="B10" s="74" t="inlineStr">
         <is>
           <t>3 - Herencias, legados o donaciones</t>
         </is>
       </c>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="73" t="inlineStr">
+      <c r="E10" s="75" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="72" t="inlineStr">
+      <c r="B11" s="74" t="inlineStr">
         <is>
           <t>4 - Loterias o rifas</t>
         </is>
       </c>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="73" t="inlineStr">
+      <c r="E11" s="75" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="72" t="inlineStr">
+      <c r="B12" s="74" t="inlineStr">
         <is>
           <t>5 - Ganancias de capital</t>
         </is>
       </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="73" t="inlineStr">
+      <c r="E12" s="75" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="72" t="inlineStr">
+      <c r="B13" s="74" t="inlineStr">
         <is>
           <t>6 - Otros</t>
         </is>
       </c>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="73" t="inlineStr">
+      <c r="E13" s="75" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
@@ -2224,7 +2230,7 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="74" t="inlineStr">
+      <c r="B5" s="76" t="inlineStr">
         <is>
           <t>►   GENERAR XML</t>
         </is>
@@ -2238,83 +2244,83 @@
       <c r="D6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="75" t="inlineStr">
+      <c r="B7" s="77" t="inlineStr">
         <is>
           <t>En el archivo .xlsm el boton verde ya esta vinculado a la macro GenerarXmlSRI.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="78" t="inlineStr">
         <is>
           <t>COMO USAR ESTE ARCHIVO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="77" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>1. Al abrir el archivo .xlsm, pulse 'Habilitar contenido' en la barra de seguridad de Excel.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="77" t="inlineStr">
+      <c r="B11" s="79" t="inlineStr">
         <is>
           <t>2. Llene las columnas amarillas de cada modulo (Dinero, Vehiculos, etc.) y la hoja Justificacion.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="77" t="inlineStr">
+      <c r="B12" s="79" t="inlineStr">
         <is>
           <t>3. Pulse el boton verde GENERAR XML, indique el anio y elija donde guardar el archivo.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="77" t="inlineStr">
+      <c r="B13" s="79" t="inlineStr">
         <is>
           <t>4. El archivo .xml queda listo para subir al portal del SRI.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="77" t="inlineStr"/>
+      <c r="B14" s="79" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="76" t="inlineStr">
+      <c r="B15" s="78" t="inlineStr">
         <is>
           <t>SI EXCEL BLOQUEA LAS MACROS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="77" t="inlineStr">
+      <c r="B16" s="79" t="inlineStr">
         <is>
           <t>- Cierre Excel. En el Explorador, clic derecho sobre el archivo &gt; Propiedades.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="77" t="inlineStr">
+      <c r="B17" s="79" t="inlineStr">
         <is>
           <t>- Al final de la pestana General marque 'Desbloquear' y pulse Aceptar.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="77" t="inlineStr">
+      <c r="B18" s="79" t="inlineStr">
         <is>
           <t>- Vuelva a abrirlo y pulse 'Habilitar contenido'. Conserve siempre la extension .xlsm.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="77" t="inlineStr"/>
+      <c r="B19" s="79" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="B20" s="77" t="inlineStr">
+      <c r="B20" s="79" t="inlineStr">
         <is>
           <t>Alternativa sin macros:  ejecutar  python tools/generar_xml_sri.py  desde la terminal.</t>
         </is>
@@ -2362,248 +2368,248 @@
       <c r="A3" s="3" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="78" t="inlineStr">
+      <c r="A5" s="80" t="inlineStr">
         <is>
           <t>IDENTIFICACION DEL DECLARANTE Y CONYUGE  (editable)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="79" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>Anio de la declaracion</t>
         </is>
       </c>
-      <c r="B6" s="80" t="n">
+      <c r="B6" s="82" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="79" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>Tipo de declaracion</t>
         </is>
       </c>
-      <c r="B7" s="80" t="inlineStr">
+      <c r="B7" s="82" t="inlineStr">
         <is>
           <t>SOC - Sociedad conyugal o union de hecho</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="79" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>Tipo de identificacion</t>
         </is>
       </c>
-      <c r="B8" s="80" t="inlineStr">
+      <c r="B8" s="82" t="inlineStr">
         <is>
           <t>R - RUC</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="79" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Numero de identificacion</t>
         </is>
       </c>
-      <c r="B9" s="80" t="inlineStr">
+      <c r="B9" s="82" t="inlineStr">
         <is>
           <t>1709164899001</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="79" t="inlineStr">
+      <c r="A10" s="81" t="inlineStr">
         <is>
           <t>Nombre del declarante</t>
         </is>
       </c>
-      <c r="B10" s="80" t="inlineStr">
+      <c r="B10" s="82" t="inlineStr">
         <is>
           <t>GONZALEZ NAVAS MARCO VINICIO</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="79" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
         <is>
           <t>Identificacion del conyuge</t>
         </is>
       </c>
-      <c r="B11" s="80" t="inlineStr">
+      <c r="B11" s="82" t="inlineStr">
         <is>
           <t>C - Cedula</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="79" t="inlineStr">
+      <c r="A12" s="81" t="inlineStr">
         <is>
           <t>Numero ident. conyuge</t>
         </is>
       </c>
-      <c r="B12" s="80" t="inlineStr">
+      <c r="B12" s="82" t="inlineStr">
         <is>
           <t>1709784225</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="79" t="inlineStr">
+      <c r="A13" s="81" t="inlineStr">
         <is>
           <t>Nombre del conyuge</t>
         </is>
       </c>
-      <c r="B13" s="80" t="inlineStr">
+      <c r="B13" s="82" t="inlineStr">
         <is>
           <t>HIDALGO LOZA ROSA CONSUELO</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="79" t="inlineStr">
+      <c r="A14" s="81" t="inlineStr">
         <is>
           <t>Regularizacion de activos</t>
         </is>
       </c>
-      <c r="B14" s="80" t="inlineStr"/>
+      <c r="B14" s="82" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="78" t="inlineStr">
+      <c r="A16" s="80" t="inlineStr">
         <is>
           <t>PATRIMONIO DECLARADO  (editable)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="79" t="inlineStr">
+      <c r="A17" s="81" t="inlineStr">
         <is>
           <t>Patrimonio total declarado</t>
         </is>
       </c>
-      <c r="B17" s="61" t="n">
+      <c r="B17" s="62" t="n">
         <v>883285.5600000001</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="79" t="inlineStr">
+      <c r="A18" s="81" t="inlineStr">
         <is>
           <t>Atribuible a hijos no emancipados</t>
         </is>
       </c>
-      <c r="B18" s="62" t="n">
+      <c r="B18" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="79" t="inlineStr">
+      <c r="A19" s="81" t="inlineStr">
         <is>
           <t>Patrimonio en la sociedad conyugal</t>
         </is>
       </c>
-      <c r="B19" s="62" t="n">
+      <c r="B19" s="63" t="n">
         <v>883285.5600000001</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="79" t="inlineStr">
+      <c r="A20" s="81" t="inlineStr">
         <is>
           <t>Patrimonio individual del declarante</t>
         </is>
       </c>
-      <c r="B20" s="62" t="n">
+      <c r="B20" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="79" t="inlineStr">
+      <c r="A21" s="81" t="inlineStr">
         <is>
           <t>Patrimonio del anio anterior</t>
         </is>
       </c>
-      <c r="B21" s="62" t="n">
+      <c r="B21" s="63" t="n">
         <v>801569.97</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="79" t="inlineStr">
+      <c r="A22" s="81" t="inlineStr">
         <is>
           <t>Crecimiento / decremento patrimonial</t>
         </is>
       </c>
-      <c r="B22" s="61" t="n">
+      <c r="B22" s="62" t="n">
         <v>81715.59</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="78" t="inlineStr">
+      <c r="A24" s="80" t="inlineStr">
         <is>
           <t>PATRIMONIO NETO  (calculado - enlazado al Dashboard)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="79" t="inlineStr">
+      <c r="A25" s="81" t="inlineStr">
         <is>
           <t>Patrimonio neto 2025</t>
         </is>
       </c>
-      <c r="B25" s="61">
+      <c r="B25" s="62">
         <f>Dashboard!D31</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="79" t="inlineStr">
+      <c r="A26" s="81" t="inlineStr">
         <is>
           <t>Patrimonio neto 2026 (proyectado)</t>
         </is>
       </c>
-      <c r="B26" s="61">
+      <c r="B26" s="62">
         <f>Dashboard!E31</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="79" t="inlineStr">
+      <c r="A27" s="81" t="inlineStr">
         <is>
           <t>Variacion proyectada</t>
         </is>
       </c>
-      <c r="B27" s="61">
+      <c r="B27" s="62">
         <f>Dashboard!F31</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="79" t="inlineStr">
+      <c r="A28" s="81" t="inlineStr">
         <is>
           <t>Variacion % proyectada</t>
         </is>
       </c>
-      <c r="B28" s="63">
+      <c r="B28" s="64">
         <f>Dashboard!G31</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="76" t="inlineStr">
+      <c r="A30" s="78" t="inlineStr">
         <is>
           <t>Justificacion de la variacion (ver hoja Justificacion)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="77" t="inlineStr">
+      <c r="A31" s="79" t="inlineStr">
         <is>
           <t>- 1 - Ingresos locales</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="77" t="inlineStr">
+      <c r="A32" s="79" t="inlineStr">
         <is>
           <t>- 6 - Otros</t>
         </is>
@@ -5896,97 +5902,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="81" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>DINERO_EN</t>
         </is>
       </c>
-      <c r="B1" s="81" t="inlineStr">
+      <c r="B1" s="83" t="inlineStr">
         <is>
           <t>TIPO_INVERSION</t>
         </is>
       </c>
-      <c r="C1" s="81" t="inlineStr">
+      <c r="C1" s="83" t="inlineStr">
         <is>
           <t>UBICACION</t>
         </is>
       </c>
-      <c r="D1" s="81" t="inlineStr">
+      <c r="D1" s="83" t="inlineStr">
         <is>
           <t>PAIS</t>
         </is>
       </c>
-      <c r="E1" s="81" t="inlineStr">
+      <c r="E1" s="83" t="inlineStr">
         <is>
           <t>INSTITUCION_FINANCIERA</t>
         </is>
       </c>
-      <c r="F1" s="81" t="inlineStr">
+      <c r="F1" s="83" t="inlineStr">
         <is>
           <t>PARTES_RELACIONADAS</t>
         </is>
       </c>
-      <c r="G1" s="81" t="inlineStr">
+      <c r="G1" s="83" t="inlineStr">
         <is>
           <t>TIPO_DRC</t>
         </is>
       </c>
-      <c r="H1" s="81" t="inlineStr">
+      <c r="H1" s="83" t="inlineStr">
         <is>
           <t>TIPO_PERSONA</t>
         </is>
       </c>
-      <c r="I1" s="81" t="inlineStr">
+      <c r="I1" s="83" t="inlineStr">
         <is>
           <t>TIPO_BIEN_MUEBLE</t>
         </is>
       </c>
-      <c r="J1" s="81" t="inlineStr">
+      <c r="J1" s="83" t="inlineStr">
         <is>
           <t>TIPO_VEHICULO</t>
         </is>
       </c>
-      <c r="K1" s="81" t="inlineStr">
+      <c r="K1" s="83" t="inlineStr">
         <is>
           <t>TIPO_DERECHO</t>
         </is>
       </c>
-      <c r="L1" s="81" t="inlineStr">
+      <c r="L1" s="83" t="inlineStr">
         <is>
           <t>TIPO_INMUEBLE</t>
         </is>
       </c>
-      <c r="M1" s="81" t="inlineStr">
+      <c r="M1" s="83" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="N1" s="81" t="inlineStr">
+      <c r="N1" s="83" t="inlineStr">
         <is>
           <t>CANTON</t>
         </is>
       </c>
-      <c r="O1" s="81" t="inlineStr">
+      <c r="O1" s="83" t="inlineStr">
         <is>
           <t>TIPO_ACREEDOR</t>
         </is>
       </c>
-      <c r="P1" s="81" t="inlineStr">
+      <c r="P1" s="83" t="inlineStr">
         <is>
           <t>TIPO_IDENTIFICACION</t>
         </is>
       </c>
-      <c r="Q1" s="81" t="inlineStr">
+      <c r="Q1" s="83" t="inlineStr">
         <is>
           <t>REGULARIZACION</t>
         </is>
       </c>
-      <c r="R1" s="81" t="inlineStr">
+      <c r="R1" s="83" t="inlineStr">
         <is>
           <t>JUSTIF_INCREMENTO</t>
         </is>
       </c>
-      <c r="S1" s="81" t="inlineStr">
+      <c r="S1" s="83" t="inlineStr">
         <is>
           <t>JUSTIF_DECREMENTO</t>
         </is>
@@ -12612,7 +12618,7 @@
           <t>1029 - BANCO PICHINCHA C.A.</t>
         </is>
       </c>
-      <c r="F6" s="60" t="inlineStr">
+      <c r="F6" s="61" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
@@ -12623,71 +12629,71 @@
         </is>
       </c>
       <c r="H6" s="60" t="inlineStr"/>
-      <c r="I6" s="60" t="inlineStr"/>
-      <c r="J6" s="61" t="n">
+      <c r="I6" s="61" t="inlineStr"/>
+      <c r="J6" s="62" t="n">
         <v>130.2</v>
       </c>
-      <c r="K6" s="62" t="n">
+      <c r="K6" s="63" t="n">
         <v>130.2</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="62">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="64">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>4 - Cuenta corriente</t>
         </is>
       </c>
-      <c r="C7" s="64" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D7" s="64" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E7" s="64" t="inlineStr">
+      <c r="E7" s="65" t="inlineStr">
         <is>
           <t>1029 - BANCO PICHINCHA C.A.</t>
         </is>
       </c>
-      <c r="F7" s="64" t="inlineStr">
+      <c r="F7" s="66" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G7" s="64" t="inlineStr">
+      <c r="G7" s="65" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H7" s="64" t="inlineStr"/>
-      <c r="I7" s="64" t="inlineStr"/>
-      <c r="J7" s="65" t="n">
+      <c r="H7" s="65" t="inlineStr"/>
+      <c r="I7" s="66" t="inlineStr"/>
+      <c r="J7" s="67" t="n">
         <v>5590.32</v>
       </c>
-      <c r="K7" s="62" t="n">
+      <c r="K7" s="63" t="n">
         <v>5590.32</v>
       </c>
-      <c r="L7" s="65">
+      <c r="L7" s="67">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="68">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
@@ -12718,7 +12724,7 @@
           <t>1418 - BANCO PROMERICA S.A.</t>
         </is>
       </c>
-      <c r="F8" s="60" t="inlineStr">
+      <c r="F8" s="61" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
@@ -12729,89 +12735,89 @@
         </is>
       </c>
       <c r="H8" s="60" t="inlineStr"/>
-      <c r="I8" s="60" t="inlineStr"/>
-      <c r="J8" s="61" t="n">
+      <c r="I8" s="61" t="inlineStr"/>
+      <c r="J8" s="62" t="n">
         <v>53237.31</v>
       </c>
-      <c r="K8" s="62" t="n">
+      <c r="K8" s="63" t="n">
         <v>53237.31</v>
       </c>
-      <c r="L8" s="61">
+      <c r="L8" s="62">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="63">
+      <c r="M8" s="64">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="64" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>IFI - Instituciones financieras</t>
         </is>
       </c>
-      <c r="B9" s="64" t="inlineStr">
+      <c r="B9" s="65" t="inlineStr">
         <is>
           <t>2 - Inversiones financieras</t>
         </is>
       </c>
-      <c r="C9" s="64" t="inlineStr">
+      <c r="C9" s="65" t="inlineStr">
         <is>
           <t>EXT - En el exterior</t>
         </is>
       </c>
-      <c r="D9" s="64" t="inlineStr">
+      <c r="D9" s="65" t="inlineStr">
         <is>
           <t>118 - PANAMA</t>
         </is>
       </c>
-      <c r="E9" s="64" t="inlineStr">
+      <c r="E9" s="65" t="inlineStr">
         <is>
           <t>BANCO PICHINCHA CA</t>
         </is>
       </c>
-      <c r="F9" s="64" t="inlineStr">
+      <c r="F9" s="66" t="inlineStr">
         <is>
           <t>DOLARES</t>
         </is>
       </c>
-      <c r="G9" s="64" t="inlineStr">
+      <c r="G9" s="65" t="inlineStr">
         <is>
           <t>2 - No</t>
         </is>
       </c>
-      <c r="H9" s="64" t="inlineStr"/>
-      <c r="I9" s="64" t="inlineStr"/>
-      <c r="J9" s="65" t="n">
+      <c r="H9" s="65" t="inlineStr"/>
+      <c r="I9" s="66" t="inlineStr"/>
+      <c r="J9" s="67" t="n">
         <v>189049.31</v>
       </c>
-      <c r="K9" s="62" t="n">
+      <c r="K9" s="63" t="n">
         <v>189049.31</v>
       </c>
-      <c r="L9" s="65">
+      <c r="L9" s="67">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="66">
+      <c r="M9" s="68">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="69" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="67" t="n"/>
-      <c r="C10" s="67" t="n"/>
-      <c r="D10" s="67" t="n"/>
-      <c r="E10" s="67" t="n"/>
-      <c r="F10" s="67" t="n"/>
-      <c r="G10" s="67" t="n"/>
-      <c r="H10" s="67" t="n"/>
-      <c r="I10" s="67" t="n"/>
+      <c r="B10" s="69" t="n"/>
+      <c r="C10" s="69" t="n"/>
+      <c r="D10" s="69" t="n"/>
+      <c r="E10" s="69" t="n"/>
+      <c r="F10" s="69" t="n"/>
+      <c r="G10" s="69" t="n"/>
+      <c r="H10" s="69" t="n"/>
+      <c r="I10" s="69" t="n"/>
       <c r="J10" s="31">
         <f>SUM(J6:J9)</f>
         <v/>
@@ -12974,48 +12980,48 @@
       <c r="A6" s="60" t="inlineStr"/>
       <c r="B6" s="60" t="inlineStr"/>
       <c r="C6" s="60" t="inlineStr"/>
-      <c r="D6" s="60" t="inlineStr"/>
-      <c r="E6" s="60" t="inlineStr"/>
-      <c r="F6" s="60" t="inlineStr"/>
+      <c r="D6" s="61" t="inlineStr"/>
+      <c r="E6" s="61" t="inlineStr"/>
+      <c r="F6" s="61" t="inlineStr"/>
       <c r="G6" s="60" t="inlineStr"/>
       <c r="H6" s="60" t="inlineStr"/>
-      <c r="I6" s="60" t="inlineStr"/>
-      <c r="J6" s="62" t="n">
+      <c r="I6" s="61" t="inlineStr"/>
+      <c r="J6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="62" t="n">
+      <c r="K6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="62">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="64">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr"/>
-      <c r="B7" s="64" t="inlineStr"/>
-      <c r="C7" s="64" t="inlineStr"/>
-      <c r="D7" s="64" t="inlineStr"/>
-      <c r="E7" s="64" t="inlineStr"/>
-      <c r="F7" s="64" t="inlineStr"/>
-      <c r="G7" s="64" t="inlineStr"/>
-      <c r="H7" s="64" t="inlineStr"/>
-      <c r="I7" s="64" t="inlineStr"/>
-      <c r="J7" s="62" t="n">
+      <c r="A7" s="65" t="inlineStr"/>
+      <c r="B7" s="65" t="inlineStr"/>
+      <c r="C7" s="65" t="inlineStr"/>
+      <c r="D7" s="66" t="inlineStr"/>
+      <c r="E7" s="66" t="inlineStr"/>
+      <c r="F7" s="66" t="inlineStr"/>
+      <c r="G7" s="65" t="inlineStr"/>
+      <c r="H7" s="65" t="inlineStr"/>
+      <c r="I7" s="66" t="inlineStr"/>
+      <c r="J7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="62" t="n">
+      <c r="K7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="65">
+      <c r="L7" s="67">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="68">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
@@ -13024,48 +13030,48 @@
       <c r="A8" s="60" t="inlineStr"/>
       <c r="B8" s="60" t="inlineStr"/>
       <c r="C8" s="60" t="inlineStr"/>
-      <c r="D8" s="60" t="inlineStr"/>
-      <c r="E8" s="60" t="inlineStr"/>
-      <c r="F8" s="60" t="inlineStr"/>
+      <c r="D8" s="61" t="inlineStr"/>
+      <c r="E8" s="61" t="inlineStr"/>
+      <c r="F8" s="61" t="inlineStr"/>
       <c r="G8" s="60" t="inlineStr"/>
       <c r="H8" s="60" t="inlineStr"/>
-      <c r="I8" s="60" t="inlineStr"/>
-      <c r="J8" s="62" t="n">
+      <c r="I8" s="61" t="inlineStr"/>
+      <c r="J8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="62" t="n">
+      <c r="K8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="61">
+      <c r="L8" s="62">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="63">
+      <c r="M8" s="64">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="64" t="inlineStr"/>
-      <c r="B9" s="64" t="inlineStr"/>
-      <c r="C9" s="64" t="inlineStr"/>
-      <c r="D9" s="64" t="inlineStr"/>
-      <c r="E9" s="64" t="inlineStr"/>
-      <c r="F9" s="64" t="inlineStr"/>
-      <c r="G9" s="64" t="inlineStr"/>
-      <c r="H9" s="64" t="inlineStr"/>
-      <c r="I9" s="64" t="inlineStr"/>
-      <c r="J9" s="62" t="n">
+      <c r="A9" s="65" t="inlineStr"/>
+      <c r="B9" s="65" t="inlineStr"/>
+      <c r="C9" s="65" t="inlineStr"/>
+      <c r="D9" s="66" t="inlineStr"/>
+      <c r="E9" s="66" t="inlineStr"/>
+      <c r="F9" s="66" t="inlineStr"/>
+      <c r="G9" s="65" t="inlineStr"/>
+      <c r="H9" s="65" t="inlineStr"/>
+      <c r="I9" s="66" t="inlineStr"/>
+      <c r="J9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="62" t="n">
+      <c r="K9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="65">
+      <c r="L9" s="67">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="66">
+      <c r="M9" s="68">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
@@ -13074,48 +13080,48 @@
       <c r="A10" s="60" t="inlineStr"/>
       <c r="B10" s="60" t="inlineStr"/>
       <c r="C10" s="60" t="inlineStr"/>
-      <c r="D10" s="60" t="inlineStr"/>
-      <c r="E10" s="60" t="inlineStr"/>
-      <c r="F10" s="60" t="inlineStr"/>
+      <c r="D10" s="61" t="inlineStr"/>
+      <c r="E10" s="61" t="inlineStr"/>
+      <c r="F10" s="61" t="inlineStr"/>
       <c r="G10" s="60" t="inlineStr"/>
       <c r="H10" s="60" t="inlineStr"/>
-      <c r="I10" s="60" t="inlineStr"/>
-      <c r="J10" s="62" t="n">
+      <c r="I10" s="61" t="inlineStr"/>
+      <c r="J10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="62" t="n">
+      <c r="K10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="61">
+      <c r="L10" s="62">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="63">
+      <c r="M10" s="64">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="64" t="inlineStr"/>
-      <c r="B11" s="64" t="inlineStr"/>
-      <c r="C11" s="64" t="inlineStr"/>
-      <c r="D11" s="64" t="inlineStr"/>
-      <c r="E11" s="64" t="inlineStr"/>
-      <c r="F11" s="64" t="inlineStr"/>
-      <c r="G11" s="64" t="inlineStr"/>
-      <c r="H11" s="64" t="inlineStr"/>
-      <c r="I11" s="64" t="inlineStr"/>
-      <c r="J11" s="62" t="n">
+      <c r="A11" s="65" t="inlineStr"/>
+      <c r="B11" s="65" t="inlineStr"/>
+      <c r="C11" s="65" t="inlineStr"/>
+      <c r="D11" s="66" t="inlineStr"/>
+      <c r="E11" s="66" t="inlineStr"/>
+      <c r="F11" s="66" t="inlineStr"/>
+      <c r="G11" s="65" t="inlineStr"/>
+      <c r="H11" s="65" t="inlineStr"/>
+      <c r="I11" s="66" t="inlineStr"/>
+      <c r="J11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="62" t="n">
+      <c r="K11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="65">
+      <c r="L11" s="67">
         <f>K11-J11</f>
         <v/>
       </c>
-      <c r="M11" s="66">
+      <c r="M11" s="68">
         <f>IF(J11=0,"",(K11-J11)/J11)</f>
         <v/>
       </c>
@@ -13124,66 +13130,66 @@
       <c r="A12" s="60" t="inlineStr"/>
       <c r="B12" s="60" t="inlineStr"/>
       <c r="C12" s="60" t="inlineStr"/>
-      <c r="D12" s="60" t="inlineStr"/>
-      <c r="E12" s="60" t="inlineStr"/>
-      <c r="F12" s="60" t="inlineStr"/>
+      <c r="D12" s="61" t="inlineStr"/>
+      <c r="E12" s="61" t="inlineStr"/>
+      <c r="F12" s="61" t="inlineStr"/>
       <c r="G12" s="60" t="inlineStr"/>
       <c r="H12" s="60" t="inlineStr"/>
-      <c r="I12" s="60" t="inlineStr"/>
-      <c r="J12" s="62" t="n">
+      <c r="I12" s="61" t="inlineStr"/>
+      <c r="J12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="62" t="n">
+      <c r="K12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="61">
+      <c r="L12" s="62">
         <f>K12-J12</f>
         <v/>
       </c>
-      <c r="M12" s="63">
+      <c r="M12" s="64">
         <f>IF(J12=0,"",(K12-J12)/J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="64" t="inlineStr"/>
-      <c r="B13" s="64" t="inlineStr"/>
-      <c r="C13" s="64" t="inlineStr"/>
-      <c r="D13" s="64" t="inlineStr"/>
-      <c r="E13" s="64" t="inlineStr"/>
-      <c r="F13" s="64" t="inlineStr"/>
-      <c r="G13" s="64" t="inlineStr"/>
-      <c r="H13" s="64" t="inlineStr"/>
-      <c r="I13" s="64" t="inlineStr"/>
-      <c r="J13" s="62" t="n">
+      <c r="A13" s="65" t="inlineStr"/>
+      <c r="B13" s="65" t="inlineStr"/>
+      <c r="C13" s="65" t="inlineStr"/>
+      <c r="D13" s="66" t="inlineStr"/>
+      <c r="E13" s="66" t="inlineStr"/>
+      <c r="F13" s="66" t="inlineStr"/>
+      <c r="G13" s="65" t="inlineStr"/>
+      <c r="H13" s="65" t="inlineStr"/>
+      <c r="I13" s="66" t="inlineStr"/>
+      <c r="J13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="62" t="n">
+      <c r="K13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="65">
+      <c r="L13" s="67">
         <f>K13-J13</f>
         <v/>
       </c>
-      <c r="M13" s="66">
+      <c r="M13" s="68">
         <f>IF(J13=0,"",(K13-J13)/J13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="67" t="n"/>
-      <c r="C14" s="67" t="n"/>
-      <c r="D14" s="67" t="n"/>
-      <c r="E14" s="67" t="n"/>
-      <c r="F14" s="67" t="n"/>
-      <c r="G14" s="67" t="n"/>
-      <c r="H14" s="67" t="n"/>
-      <c r="I14" s="67" t="n"/>
+      <c r="B14" s="69" t="n"/>
+      <c r="C14" s="69" t="n"/>
+      <c r="D14" s="69" t="n"/>
+      <c r="E14" s="69" t="n"/>
+      <c r="F14" s="69" t="n"/>
+      <c r="G14" s="69" t="n"/>
+      <c r="H14" s="69" t="n"/>
+      <c r="I14" s="69" t="n"/>
       <c r="J14" s="31">
         <f>SUM(J6:J13)</f>
         <v/>
@@ -13337,219 +13343,219 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="60" t="inlineStr"/>
+      <c r="A6" s="61" t="inlineStr"/>
       <c r="B6" s="60" t="inlineStr"/>
       <c r="C6" s="60" t="inlineStr"/>
-      <c r="D6" s="60" t="inlineStr"/>
+      <c r="D6" s="61" t="inlineStr"/>
       <c r="E6" s="60" t="inlineStr"/>
       <c r="F6" s="60" t="inlineStr"/>
       <c r="G6" s="60" t="inlineStr"/>
       <c r="H6" s="60" t="inlineStr"/>
-      <c r="I6" s="60" t="inlineStr"/>
-      <c r="J6" s="62" t="n">
+      <c r="I6" s="61" t="inlineStr"/>
+      <c r="J6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="62" t="n">
+      <c r="K6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="62">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="64">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr"/>
-      <c r="B7" s="64" t="inlineStr"/>
-      <c r="C7" s="64" t="inlineStr"/>
-      <c r="D7" s="64" t="inlineStr"/>
-      <c r="E7" s="64" t="inlineStr"/>
-      <c r="F7" s="64" t="inlineStr"/>
-      <c r="G7" s="64" t="inlineStr"/>
-      <c r="H7" s="64" t="inlineStr"/>
-      <c r="I7" s="64" t="inlineStr"/>
-      <c r="J7" s="62" t="n">
+      <c r="A7" s="66" t="inlineStr"/>
+      <c r="B7" s="65" t="inlineStr"/>
+      <c r="C7" s="65" t="inlineStr"/>
+      <c r="D7" s="66" t="inlineStr"/>
+      <c r="E7" s="65" t="inlineStr"/>
+      <c r="F7" s="65" t="inlineStr"/>
+      <c r="G7" s="65" t="inlineStr"/>
+      <c r="H7" s="65" t="inlineStr"/>
+      <c r="I7" s="66" t="inlineStr"/>
+      <c r="J7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="62" t="n">
+      <c r="K7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="65">
+      <c r="L7" s="67">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="68">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="60" t="inlineStr"/>
+      <c r="A8" s="61" t="inlineStr"/>
       <c r="B8" s="60" t="inlineStr"/>
       <c r="C8" s="60" t="inlineStr"/>
-      <c r="D8" s="60" t="inlineStr"/>
+      <c r="D8" s="61" t="inlineStr"/>
       <c r="E8" s="60" t="inlineStr"/>
       <c r="F8" s="60" t="inlineStr"/>
       <c r="G8" s="60" t="inlineStr"/>
       <c r="H8" s="60" t="inlineStr"/>
-      <c r="I8" s="60" t="inlineStr"/>
-      <c r="J8" s="62" t="n">
+      <c r="I8" s="61" t="inlineStr"/>
+      <c r="J8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="62" t="n">
+      <c r="K8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="61">
+      <c r="L8" s="62">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="63">
+      <c r="M8" s="64">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="64" t="inlineStr"/>
-      <c r="B9" s="64" t="inlineStr"/>
-      <c r="C9" s="64" t="inlineStr"/>
-      <c r="D9" s="64" t="inlineStr"/>
-      <c r="E9" s="64" t="inlineStr"/>
-      <c r="F9" s="64" t="inlineStr"/>
-      <c r="G9" s="64" t="inlineStr"/>
-      <c r="H9" s="64" t="inlineStr"/>
-      <c r="I9" s="64" t="inlineStr"/>
-      <c r="J9" s="62" t="n">
+      <c r="A9" s="66" t="inlineStr"/>
+      <c r="B9" s="65" t="inlineStr"/>
+      <c r="C9" s="65" t="inlineStr"/>
+      <c r="D9" s="66" t="inlineStr"/>
+      <c r="E9" s="65" t="inlineStr"/>
+      <c r="F9" s="65" t="inlineStr"/>
+      <c r="G9" s="65" t="inlineStr"/>
+      <c r="H9" s="65" t="inlineStr"/>
+      <c r="I9" s="66" t="inlineStr"/>
+      <c r="J9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="62" t="n">
+      <c r="K9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="65">
+      <c r="L9" s="67">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="66">
+      <c r="M9" s="68">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="60" t="inlineStr"/>
+      <c r="A10" s="61" t="inlineStr"/>
       <c r="B10" s="60" t="inlineStr"/>
       <c r="C10" s="60" t="inlineStr"/>
-      <c r="D10" s="60" t="inlineStr"/>
+      <c r="D10" s="61" t="inlineStr"/>
       <c r="E10" s="60" t="inlineStr"/>
       <c r="F10" s="60" t="inlineStr"/>
       <c r="G10" s="60" t="inlineStr"/>
       <c r="H10" s="60" t="inlineStr"/>
-      <c r="I10" s="60" t="inlineStr"/>
-      <c r="J10" s="62" t="n">
+      <c r="I10" s="61" t="inlineStr"/>
+      <c r="J10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="62" t="n">
+      <c r="K10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="61">
+      <c r="L10" s="62">
         <f>K10-J10</f>
         <v/>
       </c>
-      <c r="M10" s="63">
+      <c r="M10" s="64">
         <f>IF(J10=0,"",(K10-J10)/J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="64" t="inlineStr"/>
-      <c r="B11" s="64" t="inlineStr"/>
-      <c r="C11" s="64" t="inlineStr"/>
-      <c r="D11" s="64" t="inlineStr"/>
-      <c r="E11" s="64" t="inlineStr"/>
-      <c r="F11" s="64" t="inlineStr"/>
-      <c r="G11" s="64" t="inlineStr"/>
-      <c r="H11" s="64" t="inlineStr"/>
-      <c r="I11" s="64" t="inlineStr"/>
-      <c r="J11" s="62" t="n">
+      <c r="A11" s="66" t="inlineStr"/>
+      <c r="B11" s="65" t="inlineStr"/>
+      <c r="C11" s="65" t="inlineStr"/>
+      <c r="D11" s="66" t="inlineStr"/>
+      <c r="E11" s="65" t="inlineStr"/>
+      <c r="F11" s="65" t="inlineStr"/>
+      <c r="G11" s="65" t="inlineStr"/>
+      <c r="H11" s="65" t="inlineStr"/>
+      <c r="I11" s="66" t="inlineStr"/>
+      <c r="J11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="62" t="n">
+      <c r="K11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="65">
+      <c r="L11" s="67">
         <f>K11-J11</f>
         <v/>
       </c>
-      <c r="M11" s="66">
+      <c r="M11" s="68">
         <f>IF(J11=0,"",(K11-J11)/J11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="60" t="inlineStr"/>
+      <c r="A12" s="61" t="inlineStr"/>
       <c r="B12" s="60" t="inlineStr"/>
       <c r="C12" s="60" t="inlineStr"/>
-      <c r="D12" s="60" t="inlineStr"/>
+      <c r="D12" s="61" t="inlineStr"/>
       <c r="E12" s="60" t="inlineStr"/>
       <c r="F12" s="60" t="inlineStr"/>
       <c r="G12" s="60" t="inlineStr"/>
       <c r="H12" s="60" t="inlineStr"/>
-      <c r="I12" s="60" t="inlineStr"/>
-      <c r="J12" s="62" t="n">
+      <c r="I12" s="61" t="inlineStr"/>
+      <c r="J12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="62" t="n">
+      <c r="K12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="61">
+      <c r="L12" s="62">
         <f>K12-J12</f>
         <v/>
       </c>
-      <c r="M12" s="63">
+      <c r="M12" s="64">
         <f>IF(J12=0,"",(K12-J12)/J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="64" t="inlineStr"/>
-      <c r="B13" s="64" t="inlineStr"/>
-      <c r="C13" s="64" t="inlineStr"/>
-      <c r="D13" s="64" t="inlineStr"/>
-      <c r="E13" s="64" t="inlineStr"/>
-      <c r="F13" s="64" t="inlineStr"/>
-      <c r="G13" s="64" t="inlineStr"/>
-      <c r="H13" s="64" t="inlineStr"/>
-      <c r="I13" s="64" t="inlineStr"/>
-      <c r="J13" s="62" t="n">
+      <c r="A13" s="66" t="inlineStr"/>
+      <c r="B13" s="65" t="inlineStr"/>
+      <c r="C13" s="65" t="inlineStr"/>
+      <c r="D13" s="66" t="inlineStr"/>
+      <c r="E13" s="65" t="inlineStr"/>
+      <c r="F13" s="65" t="inlineStr"/>
+      <c r="G13" s="65" t="inlineStr"/>
+      <c r="H13" s="65" t="inlineStr"/>
+      <c r="I13" s="66" t="inlineStr"/>
+      <c r="J13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="62" t="n">
+      <c r="K13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="65">
+      <c r="L13" s="67">
         <f>K13-J13</f>
         <v/>
       </c>
-      <c r="M13" s="66">
+      <c r="M13" s="68">
         <f>IF(J13=0,"",(K13-J13)/J13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="67" t="n"/>
-      <c r="C14" s="67" t="n"/>
-      <c r="D14" s="67" t="n"/>
-      <c r="E14" s="67" t="n"/>
-      <c r="F14" s="67" t="n"/>
-      <c r="G14" s="67" t="n"/>
-      <c r="H14" s="67" t="n"/>
-      <c r="I14" s="67" t="n"/>
+      <c r="B14" s="69" t="n"/>
+      <c r="C14" s="69" t="n"/>
+      <c r="D14" s="69" t="n"/>
+      <c r="E14" s="69" t="n"/>
+      <c r="F14" s="69" t="n"/>
+      <c r="G14" s="69" t="n"/>
+      <c r="H14" s="69" t="n"/>
+      <c r="I14" s="69" t="n"/>
       <c r="J14" s="31">
         <f>SUM(J6:J13)</f>
         <v/>
@@ -13686,39 +13692,39 @@
       <c r="B6" s="60" t="inlineStr"/>
       <c r="C6" s="60" t="inlineStr"/>
       <c r="D6" s="60" t="inlineStr"/>
-      <c r="E6" s="60" t="inlineStr"/>
-      <c r="F6" s="62" t="n">
+      <c r="E6" s="61" t="inlineStr"/>
+      <c r="F6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="62" t="n">
+      <c r="G6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="61">
+      <c r="H6" s="62">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="64">
         <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr"/>
-      <c r="B7" s="64" t="inlineStr"/>
-      <c r="C7" s="64" t="inlineStr"/>
-      <c r="D7" s="64" t="inlineStr"/>
-      <c r="E7" s="64" t="inlineStr"/>
-      <c r="F7" s="62" t="n">
+      <c r="A7" s="65" t="inlineStr"/>
+      <c r="B7" s="65" t="inlineStr"/>
+      <c r="C7" s="65" t="inlineStr"/>
+      <c r="D7" s="65" t="inlineStr"/>
+      <c r="E7" s="66" t="inlineStr"/>
+      <c r="F7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="62" t="n">
+      <c r="G7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="65">
+      <c r="H7" s="67">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="68">
         <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
@@ -13728,39 +13734,39 @@
       <c r="B8" s="60" t="inlineStr"/>
       <c r="C8" s="60" t="inlineStr"/>
       <c r="D8" s="60" t="inlineStr"/>
-      <c r="E8" s="60" t="inlineStr"/>
-      <c r="F8" s="62" t="n">
+      <c r="E8" s="61" t="inlineStr"/>
+      <c r="F8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="62" t="n">
+      <c r="G8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="61">
+      <c r="H8" s="62">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="63">
+      <c r="I8" s="64">
         <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="64" t="inlineStr"/>
-      <c r="B9" s="64" t="inlineStr"/>
-      <c r="C9" s="64" t="inlineStr"/>
-      <c r="D9" s="64" t="inlineStr"/>
-      <c r="E9" s="64" t="inlineStr"/>
-      <c r="F9" s="62" t="n">
+      <c r="A9" s="65" t="inlineStr"/>
+      <c r="B9" s="65" t="inlineStr"/>
+      <c r="C9" s="65" t="inlineStr"/>
+      <c r="D9" s="65" t="inlineStr"/>
+      <c r="E9" s="66" t="inlineStr"/>
+      <c r="F9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="62" t="n">
+      <c r="G9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="65">
+      <c r="H9" s="67">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="66">
+      <c r="I9" s="68">
         <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
@@ -13770,39 +13776,39 @@
       <c r="B10" s="60" t="inlineStr"/>
       <c r="C10" s="60" t="inlineStr"/>
       <c r="D10" s="60" t="inlineStr"/>
-      <c r="E10" s="60" t="inlineStr"/>
-      <c r="F10" s="62" t="n">
+      <c r="E10" s="61" t="inlineStr"/>
+      <c r="F10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="62" t="n">
+      <c r="G10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="61">
+      <c r="H10" s="62">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="63">
+      <c r="I10" s="64">
         <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="64" t="inlineStr"/>
-      <c r="B11" s="64" t="inlineStr"/>
-      <c r="C11" s="64" t="inlineStr"/>
-      <c r="D11" s="64" t="inlineStr"/>
-      <c r="E11" s="64" t="inlineStr"/>
-      <c r="F11" s="62" t="n">
+      <c r="A11" s="65" t="inlineStr"/>
+      <c r="B11" s="65" t="inlineStr"/>
+      <c r="C11" s="65" t="inlineStr"/>
+      <c r="D11" s="65" t="inlineStr"/>
+      <c r="E11" s="66" t="inlineStr"/>
+      <c r="F11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="62" t="n">
+      <c r="G11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="65">
+      <c r="H11" s="67">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="66">
+      <c r="I11" s="68">
         <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
@@ -13812,53 +13818,53 @@
       <c r="B12" s="60" t="inlineStr"/>
       <c r="C12" s="60" t="inlineStr"/>
       <c r="D12" s="60" t="inlineStr"/>
-      <c r="E12" s="60" t="inlineStr"/>
-      <c r="F12" s="62" t="n">
+      <c r="E12" s="61" t="inlineStr"/>
+      <c r="F12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="62" t="n">
+      <c r="G12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="61">
+      <c r="H12" s="62">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="63">
+      <c r="I12" s="64">
         <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="64" t="inlineStr"/>
-      <c r="B13" s="64" t="inlineStr"/>
-      <c r="C13" s="64" t="inlineStr"/>
-      <c r="D13" s="64" t="inlineStr"/>
-      <c r="E13" s="64" t="inlineStr"/>
-      <c r="F13" s="62" t="n">
+      <c r="A13" s="65" t="inlineStr"/>
+      <c r="B13" s="65" t="inlineStr"/>
+      <c r="C13" s="65" t="inlineStr"/>
+      <c r="D13" s="65" t="inlineStr"/>
+      <c r="E13" s="66" t="inlineStr"/>
+      <c r="F13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="62" t="n">
+      <c r="G13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="65">
+      <c r="H13" s="67">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="66">
+      <c r="I13" s="68">
         <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="67" t="n"/>
-      <c r="C14" s="67" t="n"/>
-      <c r="D14" s="67" t="n"/>
-      <c r="E14" s="67" t="n"/>
+      <c r="B14" s="69" t="n"/>
+      <c r="C14" s="69" t="n"/>
+      <c r="D14" s="69" t="n"/>
+      <c r="E14" s="69" t="n"/>
       <c r="F14" s="31">
         <f>SUM(F6:F13)</f>
         <v/>
@@ -13996,7 +14002,7 @@
           <t>1 - Vehiculos motorizados terrestres</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>PBO7092</t>
         </is>
@@ -14012,56 +14018,56 @@
         </is>
       </c>
       <c r="E6" s="60" t="inlineStr"/>
-      <c r="F6" s="60" t="inlineStr"/>
-      <c r="G6" s="61" t="n">
+      <c r="F6" s="61" t="inlineStr"/>
+      <c r="G6" s="62" t="n">
         <v>12000</v>
       </c>
-      <c r="H6" s="62" t="n">
+      <c r="H6" s="63" t="n">
         <v>12000</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="62">
         <f>H6-G6</f>
         <v/>
       </c>
-      <c r="J6" s="63">
+      <c r="J6" s="64">
         <f>IF(G6=0,"",(H6-G6)/G6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>1 - Vehiculos motorizados terrestres</t>
         </is>
       </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="B7" s="66" t="inlineStr">
         <is>
           <t>PBF9690</t>
         </is>
       </c>
-      <c r="C7" s="64" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="D7" s="64" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="E7" s="64" t="inlineStr"/>
-      <c r="F7" s="64" t="inlineStr"/>
-      <c r="G7" s="65" t="n">
+      <c r="E7" s="65" t="inlineStr"/>
+      <c r="F7" s="66" t="inlineStr"/>
+      <c r="G7" s="67" t="n">
         <v>20000</v>
       </c>
-      <c r="H7" s="62" t="n">
+      <c r="H7" s="63" t="n">
         <v>20000</v>
       </c>
-      <c r="I7" s="65">
+      <c r="I7" s="67">
         <f>H7-G7</f>
         <v/>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="68">
         <f>IF(G7=0,"",(H7-G7)/G7)</f>
         <v/>
       </c>
@@ -14072,7 +14078,7 @@
           <t>1 - Vehiculos motorizados terrestres</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>PFC8683</t>
         </is>
@@ -14088,33 +14094,33 @@
         </is>
       </c>
       <c r="E8" s="60" t="inlineStr"/>
-      <c r="F8" s="60" t="inlineStr"/>
-      <c r="G8" s="61" t="n">
+      <c r="F8" s="61" t="inlineStr"/>
+      <c r="G8" s="62" t="n">
         <v>32000</v>
       </c>
-      <c r="H8" s="62" t="n">
+      <c r="H8" s="63" t="n">
         <v>32000</v>
       </c>
-      <c r="I8" s="61">
+      <c r="I8" s="62">
         <f>H8-G8</f>
         <v/>
       </c>
-      <c r="J8" s="63">
+      <c r="J8" s="64">
         <f>IF(G8=0,"",(H8-G8)/G8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="67" t="inlineStr">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="67" t="n"/>
-      <c r="C9" s="67" t="n"/>
-      <c r="D9" s="67" t="n"/>
-      <c r="E9" s="67" t="n"/>
-      <c r="F9" s="67" t="n"/>
+      <c r="B9" s="69" t="n"/>
+      <c r="C9" s="69" t="n"/>
+      <c r="D9" s="69" t="n"/>
+      <c r="E9" s="69" t="n"/>
+      <c r="F9" s="69" t="n"/>
       <c r="G9" s="31">
         <f>SUM(G6:G8)</f>
         <v/>
@@ -14245,39 +14251,39 @@
       <c r="B6" s="60" t="inlineStr"/>
       <c r="C6" s="60" t="inlineStr"/>
       <c r="D6" s="60" t="inlineStr"/>
-      <c r="E6" s="60" t="inlineStr"/>
-      <c r="F6" s="62" t="n">
+      <c r="E6" s="61" t="inlineStr"/>
+      <c r="F6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="62" t="n">
+      <c r="G6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="61">
+      <c r="H6" s="62">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="64">
         <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr"/>
-      <c r="B7" s="64" t="inlineStr"/>
-      <c r="C7" s="64" t="inlineStr"/>
-      <c r="D7" s="64" t="inlineStr"/>
-      <c r="E7" s="64" t="inlineStr"/>
-      <c r="F7" s="62" t="n">
+      <c r="A7" s="65" t="inlineStr"/>
+      <c r="B7" s="65" t="inlineStr"/>
+      <c r="C7" s="65" t="inlineStr"/>
+      <c r="D7" s="65" t="inlineStr"/>
+      <c r="E7" s="66" t="inlineStr"/>
+      <c r="F7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="62" t="n">
+      <c r="G7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="65">
+      <c r="H7" s="67">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="68">
         <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
@@ -14287,39 +14293,39 @@
       <c r="B8" s="60" t="inlineStr"/>
       <c r="C8" s="60" t="inlineStr"/>
       <c r="D8" s="60" t="inlineStr"/>
-      <c r="E8" s="60" t="inlineStr"/>
-      <c r="F8" s="62" t="n">
+      <c r="E8" s="61" t="inlineStr"/>
+      <c r="F8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="62" t="n">
+      <c r="G8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="61">
+      <c r="H8" s="62">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="63">
+      <c r="I8" s="64">
         <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="64" t="inlineStr"/>
-      <c r="B9" s="64" t="inlineStr"/>
-      <c r="C9" s="64" t="inlineStr"/>
-      <c r="D9" s="64" t="inlineStr"/>
-      <c r="E9" s="64" t="inlineStr"/>
-      <c r="F9" s="62" t="n">
+      <c r="A9" s="65" t="inlineStr"/>
+      <c r="B9" s="65" t="inlineStr"/>
+      <c r="C9" s="65" t="inlineStr"/>
+      <c r="D9" s="65" t="inlineStr"/>
+      <c r="E9" s="66" t="inlineStr"/>
+      <c r="F9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="62" t="n">
+      <c r="G9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="65">
+      <c r="H9" s="67">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="66">
+      <c r="I9" s="68">
         <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
@@ -14329,39 +14335,39 @@
       <c r="B10" s="60" t="inlineStr"/>
       <c r="C10" s="60" t="inlineStr"/>
       <c r="D10" s="60" t="inlineStr"/>
-      <c r="E10" s="60" t="inlineStr"/>
-      <c r="F10" s="62" t="n">
+      <c r="E10" s="61" t="inlineStr"/>
+      <c r="F10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="62" t="n">
+      <c r="G10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="61">
+      <c r="H10" s="62">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="63">
+      <c r="I10" s="64">
         <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="64" t="inlineStr"/>
-      <c r="B11" s="64" t="inlineStr"/>
-      <c r="C11" s="64" t="inlineStr"/>
-      <c r="D11" s="64" t="inlineStr"/>
-      <c r="E11" s="64" t="inlineStr"/>
-      <c r="F11" s="62" t="n">
+      <c r="A11" s="65" t="inlineStr"/>
+      <c r="B11" s="65" t="inlineStr"/>
+      <c r="C11" s="65" t="inlineStr"/>
+      <c r="D11" s="65" t="inlineStr"/>
+      <c r="E11" s="66" t="inlineStr"/>
+      <c r="F11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="62" t="n">
+      <c r="G11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="65">
+      <c r="H11" s="67">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="66">
+      <c r="I11" s="68">
         <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
@@ -14371,53 +14377,53 @@
       <c r="B12" s="60" t="inlineStr"/>
       <c r="C12" s="60" t="inlineStr"/>
       <c r="D12" s="60" t="inlineStr"/>
-      <c r="E12" s="60" t="inlineStr"/>
-      <c r="F12" s="62" t="n">
+      <c r="E12" s="61" t="inlineStr"/>
+      <c r="F12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="62" t="n">
+      <c r="G12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="61">
+      <c r="H12" s="62">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="63">
+      <c r="I12" s="64">
         <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="64" t="inlineStr"/>
-      <c r="B13" s="64" t="inlineStr"/>
-      <c r="C13" s="64" t="inlineStr"/>
-      <c r="D13" s="64" t="inlineStr"/>
-      <c r="E13" s="64" t="inlineStr"/>
-      <c r="F13" s="62" t="n">
+      <c r="A13" s="65" t="inlineStr"/>
+      <c r="B13" s="65" t="inlineStr"/>
+      <c r="C13" s="65" t="inlineStr"/>
+      <c r="D13" s="65" t="inlineStr"/>
+      <c r="E13" s="66" t="inlineStr"/>
+      <c r="F13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="62" t="n">
+      <c r="G13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="65">
+      <c r="H13" s="67">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="66">
+      <c r="I13" s="68">
         <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="67" t="n"/>
-      <c r="C14" s="67" t="n"/>
-      <c r="D14" s="67" t="n"/>
-      <c r="E14" s="67" t="n"/>
+      <c r="B14" s="69" t="n"/>
+      <c r="C14" s="69" t="n"/>
+      <c r="D14" s="69" t="n"/>
+      <c r="E14" s="69" t="n"/>
       <c r="F14" s="31">
         <f>SUM(F6:F13)</f>
         <v/>
@@ -14593,82 +14599,82 @@
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F6" s="60" t="inlineStr">
+      <c r="F6" s="61" t="inlineStr">
         <is>
           <t>22/10/2008</t>
         </is>
       </c>
-      <c r="G6" s="60" t="inlineStr">
+      <c r="G6" s="61" t="inlineStr">
         <is>
           <t>1042203018</t>
         </is>
       </c>
       <c r="H6" s="60" t="inlineStr"/>
-      <c r="I6" s="60" t="inlineStr"/>
-      <c r="J6" s="61" t="n">
+      <c r="I6" s="61" t="inlineStr"/>
+      <c r="J6" s="62" t="n">
         <v>267340.8</v>
       </c>
-      <c r="K6" s="62" t="n">
+      <c r="K6" s="63" t="n">
         <v>267340.8</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="62">
         <f>K6-J6</f>
         <v/>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="64">
         <f>IF(J6=0,"",(K6-J6)/J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>1 - Casa</t>
         </is>
       </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C7" s="64" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D7" s="64" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E7" s="64" t="inlineStr">
+      <c r="E7" s="65" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F7" s="64" t="inlineStr">
+      <c r="F7" s="66" t="inlineStr">
         <is>
           <t>13/03/1997</t>
         </is>
       </c>
-      <c r="G7" s="64" t="inlineStr">
+      <c r="G7" s="66" t="inlineStr">
         <is>
           <t>1012005008000000000</t>
         </is>
       </c>
-      <c r="H7" s="64" t="inlineStr"/>
-      <c r="I7" s="64" t="inlineStr"/>
-      <c r="J7" s="65" t="n">
+      <c r="H7" s="65" t="inlineStr"/>
+      <c r="I7" s="66" t="inlineStr"/>
+      <c r="J7" s="67" t="n">
         <v>198118.55</v>
       </c>
-      <c r="K7" s="62" t="n">
+      <c r="K7" s="63" t="n">
         <v>198118.55</v>
       </c>
-      <c r="L7" s="65">
+      <c r="L7" s="67">
         <f>K7-J7</f>
         <v/>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="68">
         <f>IF(J7=0,"",(K7-J7)/J7)</f>
         <v/>
       </c>
@@ -14699,92 +14705,92 @@
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F8" s="60" t="inlineStr"/>
-      <c r="G8" s="60" t="inlineStr">
+      <c r="F8" s="61" t="inlineStr"/>
+      <c r="G8" s="61" t="inlineStr">
         <is>
           <t>1042203018</t>
         </is>
       </c>
       <c r="H8" s="60" t="inlineStr"/>
-      <c r="I8" s="60" t="inlineStr"/>
-      <c r="J8" s="61" t="n">
+      <c r="I8" s="61" t="inlineStr"/>
+      <c r="J8" s="62" t="n">
         <v>33634.04</v>
       </c>
-      <c r="K8" s="62" t="n">
+      <c r="K8" s="63" t="n">
         <v>33634.04</v>
       </c>
-      <c r="L8" s="61">
+      <c r="L8" s="62">
         <f>K8-J8</f>
         <v/>
       </c>
-      <c r="M8" s="63">
+      <c r="M8" s="64">
         <f>IF(J8=0,"",(K8-J8)/J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="64" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>3 - Terreno</t>
         </is>
       </c>
-      <c r="B9" s="64" t="inlineStr">
+      <c r="B9" s="65" t="inlineStr">
         <is>
           <t>ECU - En el Ecuador</t>
         </is>
       </c>
-      <c r="C9" s="64" t="inlineStr">
+      <c r="C9" s="65" t="inlineStr">
         <is>
           <t>593 - ECUADOR</t>
         </is>
       </c>
-      <c r="D9" s="64" t="inlineStr">
+      <c r="D9" s="65" t="inlineStr">
         <is>
           <t>217 - PICHINCHA</t>
         </is>
       </c>
-      <c r="E9" s="64" t="inlineStr">
+      <c r="E9" s="65" t="inlineStr">
         <is>
           <t>21701 - QUITO</t>
         </is>
       </c>
-      <c r="F9" s="64" t="inlineStr"/>
-      <c r="G9" s="64" t="inlineStr">
+      <c r="F9" s="66" t="inlineStr"/>
+      <c r="G9" s="66" t="inlineStr">
         <is>
           <t>1012005008000000000</t>
         </is>
       </c>
-      <c r="H9" s="64" t="inlineStr"/>
-      <c r="I9" s="64" t="inlineStr"/>
-      <c r="J9" s="65" t="n">
+      <c r="H9" s="65" t="inlineStr"/>
+      <c r="I9" s="66" t="inlineStr"/>
+      <c r="J9" s="67" t="n">
         <v>82624.22</v>
       </c>
-      <c r="K9" s="62" t="n">
+      <c r="K9" s="63" t="n">
         <v>82624.22</v>
       </c>
-      <c r="L9" s="65">
+      <c r="L9" s="67">
         <f>K9-J9</f>
         <v/>
       </c>
-      <c r="M9" s="66">
+      <c r="M9" s="68">
         <f>IF(J9=0,"",(K9-J9)/J9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="69" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="67" t="n"/>
-      <c r="C10" s="67" t="n"/>
-      <c r="D10" s="67" t="n"/>
-      <c r="E10" s="67" t="n"/>
-      <c r="F10" s="67" t="n"/>
-      <c r="G10" s="67" t="n"/>
-      <c r="H10" s="67" t="n"/>
-      <c r="I10" s="67" t="n"/>
+      <c r="B10" s="69" t="n"/>
+      <c r="C10" s="69" t="n"/>
+      <c r="D10" s="69" t="n"/>
+      <c r="E10" s="69" t="n"/>
+      <c r="F10" s="69" t="n"/>
+      <c r="G10" s="69" t="n"/>
+      <c r="H10" s="69" t="n"/>
+      <c r="I10" s="69" t="n"/>
       <c r="J10" s="31">
         <f>SUM(J6:J9)</f>
         <v/>
@@ -14919,41 +14925,41 @@
     <row r="6">
       <c r="A6" s="60" t="inlineStr"/>
       <c r="B6" s="60" t="inlineStr"/>
-      <c r="C6" s="60" t="inlineStr"/>
+      <c r="C6" s="61" t="inlineStr"/>
       <c r="D6" s="60" t="inlineStr"/>
-      <c r="E6" s="60" t="inlineStr"/>
-      <c r="F6" s="62" t="n">
+      <c r="E6" s="61" t="inlineStr"/>
+      <c r="F6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="62" t="n">
+      <c r="G6" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="61">
+      <c r="H6" s="62">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="64">
         <f>IF(F6=0,"",(G6-F6)/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr"/>
-      <c r="B7" s="64" t="inlineStr"/>
-      <c r="C7" s="64" t="inlineStr"/>
-      <c r="D7" s="64" t="inlineStr"/>
-      <c r="E7" s="64" t="inlineStr"/>
-      <c r="F7" s="62" t="n">
+      <c r="A7" s="65" t="inlineStr"/>
+      <c r="B7" s="65" t="inlineStr"/>
+      <c r="C7" s="66" t="inlineStr"/>
+      <c r="D7" s="65" t="inlineStr"/>
+      <c r="E7" s="66" t="inlineStr"/>
+      <c r="F7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="62" t="n">
+      <c r="G7" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="65">
+      <c r="H7" s="67">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="68">
         <f>IF(F7=0,"",(G7-F7)/F7)</f>
         <v/>
       </c>
@@ -14961,41 +14967,41 @@
     <row r="8">
       <c r="A8" s="60" t="inlineStr"/>
       <c r="B8" s="60" t="inlineStr"/>
-      <c r="C8" s="60" t="inlineStr"/>
+      <c r="C8" s="61" t="inlineStr"/>
       <c r="D8" s="60" t="inlineStr"/>
-      <c r="E8" s="60" t="inlineStr"/>
-      <c r="F8" s="62" t="n">
+      <c r="E8" s="61" t="inlineStr"/>
+      <c r="F8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="62" t="n">
+      <c r="G8" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="61">
+      <c r="H8" s="62">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="63">
+      <c r="I8" s="64">
         <f>IF(F8=0,"",(G8-F8)/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="64" t="inlineStr"/>
-      <c r="B9" s="64" t="inlineStr"/>
-      <c r="C9" s="64" t="inlineStr"/>
-      <c r="D9" s="64" t="inlineStr"/>
-      <c r="E9" s="64" t="inlineStr"/>
-      <c r="F9" s="62" t="n">
+      <c r="A9" s="65" t="inlineStr"/>
+      <c r="B9" s="65" t="inlineStr"/>
+      <c r="C9" s="66" t="inlineStr"/>
+      <c r="D9" s="65" t="inlineStr"/>
+      <c r="E9" s="66" t="inlineStr"/>
+      <c r="F9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="62" t="n">
+      <c r="G9" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="65">
+      <c r="H9" s="67">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="66">
+      <c r="I9" s="68">
         <f>IF(F9=0,"",(G9-F9)/F9)</f>
         <v/>
       </c>
@@ -15003,41 +15009,41 @@
     <row r="10">
       <c r="A10" s="60" t="inlineStr"/>
       <c r="B10" s="60" t="inlineStr"/>
-      <c r="C10" s="60" t="inlineStr"/>
+      <c r="C10" s="61" t="inlineStr"/>
       <c r="D10" s="60" t="inlineStr"/>
-      <c r="E10" s="60" t="inlineStr"/>
-      <c r="F10" s="62" t="n">
+      <c r="E10" s="61" t="inlineStr"/>
+      <c r="F10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="62" t="n">
+      <c r="G10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="61">
+      <c r="H10" s="62">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="63">
+      <c r="I10" s="64">
         <f>IF(F10=0,"",(G10-F10)/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="64" t="inlineStr"/>
-      <c r="B11" s="64" t="inlineStr"/>
-      <c r="C11" s="64" t="inlineStr"/>
-      <c r="D11" s="64" t="inlineStr"/>
-      <c r="E11" s="64" t="inlineStr"/>
-      <c r="F11" s="62" t="n">
+      <c r="A11" s="65" t="inlineStr"/>
+      <c r="B11" s="65" t="inlineStr"/>
+      <c r="C11" s="66" t="inlineStr"/>
+      <c r="D11" s="65" t="inlineStr"/>
+      <c r="E11" s="66" t="inlineStr"/>
+      <c r="F11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="62" t="n">
+      <c r="G11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="65">
+      <c r="H11" s="67">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="66">
+      <c r="I11" s="68">
         <f>IF(F11=0,"",(G11-F11)/F11)</f>
         <v/>
       </c>
@@ -15045,55 +15051,55 @@
     <row r="12">
       <c r="A12" s="60" t="inlineStr"/>
       <c r="B12" s="60" t="inlineStr"/>
-      <c r="C12" s="60" t="inlineStr"/>
+      <c r="C12" s="61" t="inlineStr"/>
       <c r="D12" s="60" t="inlineStr"/>
-      <c r="E12" s="60" t="inlineStr"/>
-      <c r="F12" s="62" t="n">
+      <c r="E12" s="61" t="inlineStr"/>
+      <c r="F12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="62" t="n">
+      <c r="G12" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="61">
+      <c r="H12" s="62">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="63">
+      <c r="I12" s="64">
         <f>IF(F12=0,"",(G12-F12)/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="64" t="inlineStr"/>
-      <c r="B13" s="64" t="inlineStr"/>
-      <c r="C13" s="64" t="inlineStr"/>
-      <c r="D13" s="64" t="inlineStr"/>
-      <c r="E13" s="64" t="inlineStr"/>
-      <c r="F13" s="62" t="n">
+      <c r="A13" s="65" t="inlineStr"/>
+      <c r="B13" s="65" t="inlineStr"/>
+      <c r="C13" s="66" t="inlineStr"/>
+      <c r="D13" s="65" t="inlineStr"/>
+      <c r="E13" s="66" t="inlineStr"/>
+      <c r="F13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="62" t="n">
+      <c r="G13" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="65">
+      <c r="H13" s="67">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="66">
+      <c r="I13" s="68">
         <f>IF(F13=0,"",(G13-F13)/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="67" t="n"/>
-      <c r="C14" s="67" t="n"/>
-      <c r="D14" s="67" t="n"/>
-      <c r="E14" s="67" t="n"/>
+      <c r="B14" s="69" t="n"/>
+      <c r="C14" s="69" t="n"/>
+      <c r="D14" s="69" t="n"/>
+      <c r="E14" s="69" t="n"/>
       <c r="F14" s="31">
         <f>SUM(F6:F13)</f>
         <v/>
